--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="97">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,57 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
+    <t>Ecuadorian Serie A</t>
+  </si>
+  <si>
+    <t>Romanian Liga II</t>
+  </si>
+  <si>
+    <t>2026-09-22</t>
+  </si>
+  <si>
+    <t>00:15:00</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>14:30:00</t>
+  </si>
+  <si>
+    <t>Lanus</t>
+  </si>
+  <si>
+    <t>Cuiaba</t>
+  </si>
+  <si>
+    <t>Barcelona (Ecu)</t>
+  </si>
+  <si>
+    <t>ACS Dumbravita</t>
+  </si>
+  <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
+    <t>Nautico PE</t>
+  </si>
+  <si>
+    <t>Independiente (Ecu)</t>
+  </si>
+  <si>
+    <t>CSM Scolar Resita</t>
+  </si>
+  <si>
+    <t>2026-09-20 00:28:44</t>
   </si>
 </sst>
 </file>
@@ -585,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +879,974 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2">
+        <v>2.2</v>
+      </c>
+      <c r="G2">
+        <v>2.46</v>
+      </c>
+      <c r="H2">
+        <v>3.65</v>
+      </c>
+      <c r="I2">
+        <v>4.4</v>
+      </c>
+      <c r="J2">
+        <v>2.82</v>
+      </c>
+      <c r="K2">
+        <v>3.6</v>
+      </c>
+      <c r="L2">
+        <v>1.6</v>
+      </c>
+      <c r="M2">
+        <v>1.11</v>
+      </c>
+      <c r="N2">
+        <v>2.48</v>
+      </c>
+      <c r="O2">
+        <v>1.52</v>
+      </c>
+      <c r="P2">
+        <v>1.44</v>
+      </c>
+      <c r="Q2">
+        <v>2.66</v>
+      </c>
+      <c r="R2">
+        <v>1.14</v>
+      </c>
+      <c r="S2">
+        <v>5.7</v>
+      </c>
+      <c r="T2">
+        <v>2.2</v>
+      </c>
+      <c r="U2">
+        <v>1.64</v>
+      </c>
+      <c r="V2">
+        <v>1.33</v>
+      </c>
+      <c r="W2">
+        <v>1.73</v>
+      </c>
+      <c r="X2">
+        <v>9.4</v>
+      </c>
+      <c r="Y2">
+        <v>17.5</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>9.6</v>
+      </c>
+      <c r="AC2">
+        <v>10.5</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>27</v>
+      </c>
+      <c r="AG2">
+        <v>28</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>5.9</v>
+      </c>
+      <c r="AQ2">
+        <v>7</v>
+      </c>
+      <c r="AR2">
+        <v>1.77</v>
+      </c>
+      <c r="AS2">
+        <v>1.77</v>
+      </c>
+      <c r="AT2">
+        <v>5.4</v>
+      </c>
+      <c r="AU2">
+        <v>5.6</v>
+      </c>
+      <c r="AV2">
+        <v>11</v>
+      </c>
+      <c r="AW2">
+        <v>1.77</v>
+      </c>
+      <c r="AX2">
+        <v>8</v>
+      </c>
+      <c r="AY2">
+        <v>8.4</v>
+      </c>
+      <c r="AZ2">
+        <v>1.77</v>
+      </c>
+      <c r="BA2">
+        <v>1.77</v>
+      </c>
+      <c r="BB2">
+        <v>1.77</v>
+      </c>
+      <c r="BC2">
+        <v>1.77</v>
+      </c>
+      <c r="BD2">
+        <v>1.77</v>
+      </c>
+      <c r="BE2">
+        <v>1.77</v>
+      </c>
+      <c r="BF2">
+        <v>1.77</v>
+      </c>
+      <c r="BG2">
+        <v>1.77</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>2.26</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>4</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>9.6</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>5.3</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>2.24</v>
+      </c>
+      <c r="H3">
+        <v>3.85</v>
+      </c>
+      <c r="I3">
+        <v>4.8</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>1.5</v>
+      </c>
+      <c r="M3">
+        <v>1.1</v>
+      </c>
+      <c r="N3">
+        <v>2.76</v>
+      </c>
+      <c r="O3">
+        <v>1.45</v>
+      </c>
+      <c r="P3">
+        <v>1.6</v>
+      </c>
+      <c r="Q3">
+        <v>2.24</v>
+      </c>
+      <c r="R3">
+        <v>1.2</v>
+      </c>
+      <c r="S3">
+        <v>4.2</v>
+      </c>
+      <c r="T3">
+        <v>1.92</v>
+      </c>
+      <c r="U3">
+        <v>1.79</v>
+      </c>
+      <c r="V3">
+        <v>1.27</v>
+      </c>
+      <c r="W3">
+        <v>1.8</v>
+      </c>
+      <c r="X3">
+        <v>970</v>
+      </c>
+      <c r="Y3">
+        <v>25</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>970</v>
+      </c>
+      <c r="AC3">
+        <v>970</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>25</v>
+      </c>
+      <c r="AG3">
+        <v>970</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>7.4</v>
+      </c>
+      <c r="AQ3">
+        <v>1.55</v>
+      </c>
+      <c r="AR3">
+        <v>1.58</v>
+      </c>
+      <c r="AS3">
+        <v>1.58</v>
+      </c>
+      <c r="AT3">
+        <v>5.8</v>
+      </c>
+      <c r="AU3">
+        <v>5.7</v>
+      </c>
+      <c r="AV3">
+        <v>1.66</v>
+      </c>
+      <c r="AW3">
+        <v>1.58</v>
+      </c>
+      <c r="AX3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY3">
+        <v>7.8</v>
+      </c>
+      <c r="AZ3">
+        <v>1.58</v>
+      </c>
+      <c r="BA3">
+        <v>1.58</v>
+      </c>
+      <c r="BB3">
+        <v>1.58</v>
+      </c>
+      <c r="BC3">
+        <v>1.58</v>
+      </c>
+      <c r="BD3">
+        <v>1.58</v>
+      </c>
+      <c r="BE3">
+        <v>1.58</v>
+      </c>
+      <c r="BF3">
+        <v>1.58</v>
+      </c>
+      <c r="BG3">
+        <v>1.58</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.23</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.01</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.01</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.47</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.01</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.01</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.01</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.01</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4">
+        <v>1.1</v>
+      </c>
+      <c r="G4">
+        <v>110</v>
+      </c>
+      <c r="H4">
+        <v>1.12</v>
+      </c>
+      <c r="I4">
+        <v>110</v>
+      </c>
+      <c r="J4">
+        <v>1.1</v>
+      </c>
+      <c r="K4">
+        <v>110</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.07</v>
+      </c>
+      <c r="N4">
+        <v>1.01</v>
+      </c>
+      <c r="O4">
+        <v>1.34</v>
+      </c>
+      <c r="P4">
+        <v>1.25</v>
+      </c>
+      <c r="Q4">
+        <v>1.33</v>
+      </c>
+      <c r="R4">
+        <v>1.22</v>
+      </c>
+      <c r="S4">
+        <v>1.34</v>
+      </c>
+      <c r="T4">
+        <v>1.01</v>
+      </c>
+      <c r="U4">
+        <v>1.01</v>
+      </c>
+      <c r="V4">
+        <v>1.02</v>
+      </c>
+      <c r="W4">
+        <v>1.02</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>1000</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>1.01</v>
+      </c>
+      <c r="AQ4">
+        <v>1.01</v>
+      </c>
+      <c r="AR4">
+        <v>1.01</v>
+      </c>
+      <c r="AS4">
+        <v>1.01</v>
+      </c>
+      <c r="AT4">
+        <v>1.01</v>
+      </c>
+      <c r="AU4">
+        <v>1.01</v>
+      </c>
+      <c r="AV4">
+        <v>1.01</v>
+      </c>
+      <c r="AW4">
+        <v>1.01</v>
+      </c>
+      <c r="AX4">
+        <v>1.01</v>
+      </c>
+      <c r="AY4">
+        <v>1.01</v>
+      </c>
+      <c r="AZ4">
+        <v>1.01</v>
+      </c>
+      <c r="BA4">
+        <v>1.01</v>
+      </c>
+      <c r="BB4">
+        <v>1.01</v>
+      </c>
+      <c r="BC4">
+        <v>1.01</v>
+      </c>
+      <c r="BD4">
+        <v>1.01</v>
+      </c>
+      <c r="BE4">
+        <v>1.01</v>
+      </c>
+      <c r="BF4">
+        <v>1.01</v>
+      </c>
+      <c r="BG4">
+        <v>1.01</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.01</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.01</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.01</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.01</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.01</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.01</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5">
+        <v>1.1</v>
+      </c>
+      <c r="G5">
+        <v>1000</v>
+      </c>
+      <c r="H5">
+        <v>1.1</v>
+      </c>
+      <c r="I5">
+        <v>1000</v>
+      </c>
+      <c r="J5">
+        <v>1.1</v>
+      </c>
+      <c r="K5">
+        <v>1000</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1.24</v>
+      </c>
+      <c r="Q5">
+        <v>1.01</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -304,7 +304,7 @@
     <t>CSM Scolar Resita</t>
   </si>
   <si>
-    <t>2026-09-20 00:28:44</t>
+    <t>2026-09-20 02:49:47</t>
   </si>
 </sst>
 </file>
@@ -898,22 +898,22 @@
         <v>92</v>
       </c>
       <c r="F2">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G2">
         <v>2.46</v>
       </c>
       <c r="H2">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I2">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J2">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="K2">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="L2">
         <v>1.6</v>
@@ -922,7 +922,7 @@
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="O2">
         <v>1.52</v>
@@ -934,7 +934,7 @@
         <v>2.66</v>
       </c>
       <c r="R2">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="S2">
         <v>5.7</v>
@@ -943,13 +943,13 @@
         <v>2.2</v>
       </c>
       <c r="U2">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V2">
         <v>1.33</v>
       </c>
       <c r="W2">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="X2">
         <v>9.4</v>
@@ -1140,7 +1140,7 @@
         <v>93</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G3">
         <v>2.24</v>
@@ -1155,7 +1155,7 @@
         <v>3</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="L3">
         <v>1.5</v>
@@ -1188,7 +1188,7 @@
         <v>1.79</v>
       </c>
       <c r="V3">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W3">
         <v>1.8</v>
@@ -1382,7 +1382,7 @@
         <v>94</v>
       </c>
       <c r="F4">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="G4">
         <v>110</v>
@@ -1406,22 +1406,22 @@
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="O4">
         <v>1.34</v>
       </c>
       <c r="P4">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q4">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="R4">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S4">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="T4">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -304,7 +304,7 @@
     <t>CSM Scolar Resita</t>
   </si>
   <si>
-    <t>2026-09-20 02:49:47</t>
+    <t>2026-09-20 05:11:28</t>
   </si>
 </sst>
 </file>
@@ -898,22 +898,22 @@
         <v>92</v>
       </c>
       <c r="F2">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G2">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="H2">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I2">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="J2">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="K2">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="L2">
         <v>1.6</v>
@@ -922,37 +922,37 @@
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="O2">
         <v>1.52</v>
       </c>
       <c r="P2">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q2">
         <v>2.66</v>
       </c>
       <c r="R2">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="S2">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="T2">
         <v>2.2</v>
       </c>
       <c r="U2">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="X2">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="Y2">
         <v>17.5</v>
@@ -964,10 +964,10 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC2">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2">
         <v>1000</v>
@@ -976,7 +976,7 @@
         <v>1000</v>
       </c>
       <c r="AF2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AG2">
         <v>28</v>
@@ -1012,10 +1012,10 @@
         <v>7</v>
       </c>
       <c r="AR2">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AS2">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AT2">
         <v>5.4</v>
@@ -1027,37 +1027,37 @@
         <v>11</v>
       </c>
       <c r="AW2">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AX2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ2">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="BA2">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="BB2">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="BC2">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="BD2">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="BE2">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="BF2">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="BG2">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1143,13 +1143,13 @@
         <v>2.02</v>
       </c>
       <c r="G3">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H3">
         <v>3.85</v>
       </c>
       <c r="I3">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J3">
         <v>3</v>
@@ -1182,13 +1182,13 @@
         <v>4.2</v>
       </c>
       <c r="T3">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U3">
         <v>1.79</v>
       </c>
       <c r="V3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W3">
         <v>1.8</v>
@@ -1218,7 +1218,7 @@
         <v>1000</v>
       </c>
       <c r="AF3">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AG3">
         <v>970</v>
@@ -1248,16 +1248,16 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AQ3">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AR3">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AS3">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AT3">
         <v>5.8</v>
@@ -1266,10 +1266,10 @@
         <v>5.7</v>
       </c>
       <c r="AV3">
+        <v>11</v>
+      </c>
+      <c r="AW3">
         <v>1.66</v>
-      </c>
-      <c r="AW3">
-        <v>1.58</v>
       </c>
       <c r="AX3">
         <v>8.199999999999999</v>
@@ -1278,25 +1278,25 @@
         <v>7.8</v>
       </c>
       <c r="AZ3">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="BA3">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="BB3">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="BC3">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="BD3">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="BE3">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="BF3">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="BG3">
         <v>1.58</v>
@@ -1412,7 +1412,7 @@
         <v>1.34</v>
       </c>
       <c r="P4">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Q4">
         <v>1.34</v>
@@ -1639,7 +1639,7 @@
         <v>1.1</v>
       </c>
       <c r="K5">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="L5">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -304,7 +304,7 @@
     <t>CSM Scolar Resita</t>
   </si>
   <si>
-    <t>2026-09-20 05:11:28</t>
+    <t>2026-09-20 07:32:55</t>
   </si>
 </sst>
 </file>
@@ -901,37 +901,37 @@
         <v>2.2</v>
       </c>
       <c r="G2">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H2">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="I2">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J2">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="K2">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L2">
         <v>1.6</v>
       </c>
       <c r="M2">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="N2">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="O2">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="P2">
         <v>1.45</v>
       </c>
       <c r="Q2">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="R2">
         <v>1.15</v>
@@ -943,13 +943,13 @@
         <v>2.2</v>
       </c>
       <c r="U2">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W2">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X2">
         <v>11.5</v>
@@ -1164,7 +1164,7 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="O3">
         <v>1.45</v>
@@ -1176,7 +1176,7 @@
         <v>2.24</v>
       </c>
       <c r="R3">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S3">
         <v>4.2</v>
@@ -1188,7 +1188,7 @@
         <v>1.79</v>
       </c>
       <c r="V3">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W3">
         <v>1.8</v>
@@ -1248,7 +1248,7 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3">
         <v>1.63</v>
@@ -1266,7 +1266,7 @@
         <v>5.7</v>
       </c>
       <c r="AV3">
-        <v>11</v>
+        <v>1.74</v>
       </c>
       <c r="AW3">
         <v>1.66</v>
@@ -1394,7 +1394,7 @@
         <v>110</v>
       </c>
       <c r="J4">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="K4">
         <v>110</v>
@@ -1430,7 +1430,7 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="W4">
         <v>1.02</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="96">
   <si>
     <t>League</t>
   </si>
@@ -262,12 +262,12 @@
     <t>Brazilian Serie B</t>
   </si>
   <si>
+    <t>Colombian Primera B</t>
+  </si>
+  <si>
     <t>Ecuadorian Serie A</t>
   </si>
   <si>
-    <t>Romanian Liga II</t>
-  </si>
-  <si>
     <t>2026-09-22</t>
   </si>
   <si>
@@ -277,34 +277,31 @@
     <t>00:30:00</t>
   </si>
   <si>
-    <t>14:30:00</t>
-  </si>
-  <si>
     <t>Lanus</t>
   </si>
   <si>
     <t>Cuiaba</t>
   </si>
   <si>
+    <t>Real Cartagena</t>
+  </si>
+  <si>
     <t>Barcelona (Ecu)</t>
   </si>
   <si>
-    <t>ACS Dumbravita</t>
-  </si>
-  <si>
     <t>Estudiantes</t>
   </si>
   <si>
     <t>Nautico PE</t>
   </si>
   <si>
+    <t>Envigado</t>
+  </si>
+  <si>
     <t>Independiente (Ecu)</t>
   </si>
   <si>
-    <t>CSM Scolar Resita</t>
-  </si>
-  <si>
-    <t>2026-09-20 07:32:55</t>
+    <t>2026-09-20 09:53:02</t>
   </si>
 </sst>
 </file>
@@ -892,28 +889,28 @@
         <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F2">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G2">
         <v>2.36</v>
       </c>
       <c r="H2">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J2">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="K2">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="L2">
         <v>1.6</v>
@@ -925,40 +922,40 @@
         <v>2.46</v>
       </c>
       <c r="O2">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="P2">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="Q2">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="R2">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="S2">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="T2">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U2">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="V2">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X2">
         <v>11.5</v>
       </c>
       <c r="Y2">
-        <v>17.5</v>
+        <v>11</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA2">
         <v>1000</v>
@@ -967,13 +964,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC2">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD2">
         <v>1000</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF2">
         <v>22</v>
@@ -982,25 +979,25 @@
         <v>28</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI2">
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM2">
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO2">
         <v>1000</v>
@@ -1012,10 +1009,10 @@
         <v>7</v>
       </c>
       <c r="AR2">
-        <v>1.75</v>
+        <v>2.62</v>
       </c>
       <c r="AS2">
-        <v>1.75</v>
+        <v>2.86</v>
       </c>
       <c r="AT2">
         <v>5.4</v>
@@ -1027,37 +1024,37 @@
         <v>11</v>
       </c>
       <c r="AW2">
-        <v>1.75</v>
+        <v>2.78</v>
       </c>
       <c r="AX2">
         <v>8.199999999999999</v>
       </c>
       <c r="AY2">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AZ2">
-        <v>1.75</v>
+        <v>2.62</v>
       </c>
       <c r="BA2">
-        <v>1.75</v>
+        <v>2.86</v>
       </c>
       <c r="BB2">
-        <v>1.75</v>
+        <v>2.66</v>
       </c>
       <c r="BC2">
-        <v>1.75</v>
+        <v>2.66</v>
       </c>
       <c r="BD2">
-        <v>1.75</v>
+        <v>2.76</v>
       </c>
       <c r="BE2">
-        <v>1.75</v>
+        <v>2.86</v>
       </c>
       <c r="BF2">
-        <v>1.75</v>
+        <v>2.68</v>
       </c>
       <c r="BG2">
-        <v>1.75</v>
+        <v>2.86</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1120,7 +1117,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1134,28 +1131,28 @@
         <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F3">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G3">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="H3">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="K3">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L3">
         <v>1.5</v>
@@ -1182,16 +1179,16 @@
         <v>4.2</v>
       </c>
       <c r="T3">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="U3">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="V3">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W3">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="X3">
         <v>970</v>
@@ -1341,7 +1338,7 @@
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1362,7 +1359,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1376,52 +1373,52 @@
         <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F4">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="G4">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H4">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="I4">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J4">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="K4">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N4">
-        <v>3.25</v>
+        <v>1.08</v>
       </c>
       <c r="O4">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="P4">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
       <c r="Q4">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="R4">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>1.37</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1430,10 +1427,10 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1604,7 +1601,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1615,238 +1612,238 @@
         <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5">
+        <v>1.12</v>
+      </c>
+      <c r="G5">
+        <v>110</v>
+      </c>
+      <c r="H5">
+        <v>1.12</v>
+      </c>
+      <c r="I5">
+        <v>110</v>
+      </c>
+      <c r="J5">
+        <v>3.2</v>
+      </c>
+      <c r="K5">
+        <v>110</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.07</v>
+      </c>
+      <c r="N5">
+        <v>3.25</v>
+      </c>
+      <c r="O5">
+        <v>1.34</v>
+      </c>
+      <c r="P5">
+        <v>1.34</v>
+      </c>
+      <c r="Q5">
+        <v>1.34</v>
+      </c>
+      <c r="R5">
+        <v>1.23</v>
+      </c>
+      <c r="S5">
+        <v>2</v>
+      </c>
+      <c r="T5">
+        <v>1.01</v>
+      </c>
+      <c r="U5">
+        <v>1.01</v>
+      </c>
+      <c r="V5">
+        <v>1.27</v>
+      </c>
+      <c r="W5">
+        <v>1.35</v>
+      </c>
+      <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>1000</v>
+      </c>
+      <c r="Z5">
+        <v>1000</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>1000</v>
+      </c>
+      <c r="AC5">
+        <v>1000</v>
+      </c>
+      <c r="AD5">
+        <v>1000</v>
+      </c>
+      <c r="AE5">
+        <v>1000</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
+        <v>1000</v>
+      </c>
+      <c r="AH5">
+        <v>1000</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>1000</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>1000</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>1.01</v>
+      </c>
+      <c r="AQ5">
+        <v>1.01</v>
+      </c>
+      <c r="AR5">
+        <v>1.01</v>
+      </c>
+      <c r="AS5">
+        <v>1.01</v>
+      </c>
+      <c r="AT5">
+        <v>1.01</v>
+      </c>
+      <c r="AU5">
+        <v>1.01</v>
+      </c>
+      <c r="AV5">
+        <v>1.01</v>
+      </c>
+      <c r="AW5">
+        <v>1.01</v>
+      </c>
+      <c r="AX5">
+        <v>1.01</v>
+      </c>
+      <c r="AY5">
+        <v>1.01</v>
+      </c>
+      <c r="AZ5">
+        <v>1.01</v>
+      </c>
+      <c r="BA5">
+        <v>1.01</v>
+      </c>
+      <c r="BB5">
+        <v>1.01</v>
+      </c>
+      <c r="BC5">
+        <v>1.01</v>
+      </c>
+      <c r="BD5">
+        <v>1.01</v>
+      </c>
+      <c r="BE5">
+        <v>1.01</v>
+      </c>
+      <c r="BF5">
+        <v>1.01</v>
+      </c>
+      <c r="BG5">
+        <v>1.01</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5">
+        <v>1000</v>
+      </c>
+      <c r="BK5">
+        <v>1.01</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.01</v>
+      </c>
+      <c r="BN5">
+        <v>1000</v>
+      </c>
+      <c r="BO5">
+        <v>1.01</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>1.01</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>1.01</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>1.01</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.01</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="s">
         <v>95</v>
-      </c>
-      <c r="F5">
-        <v>1.1</v>
-      </c>
-      <c r="G5">
-        <v>1000</v>
-      </c>
-      <c r="H5">
-        <v>1.1</v>
-      </c>
-      <c r="I5">
-        <v>1000</v>
-      </c>
-      <c r="J5">
-        <v>1.1</v>
-      </c>
-      <c r="K5">
-        <v>870</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>1.24</v>
-      </c>
-      <c r="Q5">
-        <v>1.01</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
-      <c r="AK5">
-        <v>0</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>0</v>
-      </c>
-      <c r="AO5">
-        <v>0</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>0</v>
-      </c>
-      <c r="BC5">
-        <v>0</v>
-      </c>
-      <c r="BD5">
-        <v>0</v>
-      </c>
-      <c r="BE5">
-        <v>0</v>
-      </c>
-      <c r="BF5">
-        <v>0</v>
-      </c>
-      <c r="BG5">
-        <v>0</v>
-      </c>
-      <c r="BH5">
-        <v>0</v>
-      </c>
-      <c r="BI5">
-        <v>0</v>
-      </c>
-      <c r="BJ5">
-        <v>0</v>
-      </c>
-      <c r="BK5">
-        <v>0</v>
-      </c>
-      <c r="BL5">
-        <v>0</v>
-      </c>
-      <c r="BM5">
-        <v>0</v>
-      </c>
-      <c r="BN5">
-        <v>0</v>
-      </c>
-      <c r="BO5">
-        <v>0</v>
-      </c>
-      <c r="BP5">
-        <v>0</v>
-      </c>
-      <c r="BQ5">
-        <v>0</v>
-      </c>
-      <c r="BR5">
-        <v>0</v>
-      </c>
-      <c r="BS5">
-        <v>0</v>
-      </c>
-      <c r="BT5">
-        <v>0</v>
-      </c>
-      <c r="BU5">
-        <v>0</v>
-      </c>
-      <c r="BV5">
-        <v>0</v>
-      </c>
-      <c r="BW5">
-        <v>0</v>
-      </c>
-      <c r="BX5">
-        <v>0</v>
-      </c>
-      <c r="BY5">
-        <v>0</v>
-      </c>
-      <c r="BZ5">
-        <v>0</v>
-      </c>
-      <c r="CA5">
-        <v>0</v>
-      </c>
-      <c r="CB5" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="100">
   <si>
     <t>League</t>
   </si>
@@ -268,6 +268,9 @@
     <t>Ecuadorian Serie A</t>
   </si>
   <si>
+    <t>Romanian Liga II</t>
+  </si>
+  <si>
     <t>2026-09-22</t>
   </si>
   <si>
@@ -277,6 +280,9 @@
     <t>00:30:00</t>
   </si>
   <si>
+    <t>14:30:00</t>
+  </si>
+  <si>
     <t>Lanus</t>
   </si>
   <si>
@@ -289,6 +295,9 @@
     <t>Barcelona (Ecu)</t>
   </si>
   <si>
+    <t>ACS Dumbravita</t>
+  </si>
+  <si>
     <t>Estudiantes</t>
   </si>
   <si>
@@ -301,7 +310,10 @@
     <t>Independiente (Ecu)</t>
   </si>
   <si>
-    <t>2026-09-20 09:53:02</t>
+    <t>CSM Scolar Resita</t>
+  </si>
+  <si>
+    <t>2026-09-20 12:11:10</t>
   </si>
 </sst>
 </file>
@@ -633,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -883,22 +895,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F2">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G2">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H2">
         <v>4</v>
@@ -907,25 +919,25 @@
         <v>4.3</v>
       </c>
       <c r="J2">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="K2">
         <v>3.25</v>
       </c>
       <c r="L2">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="M2">
         <v>1.14</v>
       </c>
       <c r="N2">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="O2">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="P2">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q2">
         <v>2.82</v>
@@ -937,58 +949,58 @@
         <v>6</v>
       </c>
       <c r="T2">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="U2">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W2">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X2">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="Y2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z2">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AC2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF2">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AG2">
-        <v>28</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI2">
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL2">
         <v>90</v>
@@ -997,127 +1009,127 @@
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO2">
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AQ2">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2">
+        <v>17</v>
+      </c>
+      <c r="AS2">
+        <v>36</v>
+      </c>
+      <c r="AT2">
+        <v>6.4</v>
+      </c>
+      <c r="AU2">
+        <v>6.6</v>
+      </c>
+      <c r="AV2">
+        <v>16.5</v>
+      </c>
+      <c r="AW2">
+        <v>32</v>
+      </c>
+      <c r="AX2">
+        <v>11</v>
+      </c>
+      <c r="AY2">
+        <v>11.5</v>
+      </c>
+      <c r="AZ2">
+        <v>19</v>
+      </c>
+      <c r="BA2">
+        <v>40</v>
+      </c>
+      <c r="BB2">
+        <v>19.5</v>
+      </c>
+      <c r="BC2">
+        <v>21</v>
+      </c>
+      <c r="BD2">
+        <v>34</v>
+      </c>
+      <c r="BE2">
+        <v>50</v>
+      </c>
+      <c r="BF2">
+        <v>21</v>
+      </c>
+      <c r="BG2">
+        <v>38</v>
+      </c>
+      <c r="BH2">
         <v>2.62</v>
       </c>
-      <c r="AS2">
-        <v>2.86</v>
-      </c>
-      <c r="AT2">
-        <v>5.4</v>
-      </c>
-      <c r="AU2">
+      <c r="BI2">
+        <v>2.42</v>
+      </c>
+      <c r="BJ2">
+        <v>14.5</v>
+      </c>
+      <c r="BK2">
+        <v>4.8</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>6.6</v>
+      </c>
+      <c r="BN2">
         <v>5.6</v>
       </c>
-      <c r="AV2">
-        <v>11</v>
-      </c>
-      <c r="AW2">
-        <v>2.78</v>
-      </c>
-      <c r="AX2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY2">
-        <v>11</v>
-      </c>
-      <c r="AZ2">
-        <v>2.62</v>
-      </c>
-      <c r="BA2">
-        <v>2.86</v>
-      </c>
-      <c r="BB2">
-        <v>2.66</v>
-      </c>
-      <c r="BC2">
-        <v>2.66</v>
-      </c>
-      <c r="BD2">
-        <v>2.76</v>
-      </c>
-      <c r="BE2">
-        <v>2.86</v>
-      </c>
-      <c r="BF2">
-        <v>2.68</v>
-      </c>
-      <c r="BG2">
-        <v>2.86</v>
-      </c>
-      <c r="BH2">
-        <v>1000</v>
-      </c>
-      <c r="BI2">
-        <v>2.26</v>
-      </c>
-      <c r="BJ2">
-        <v>1000</v>
-      </c>
-      <c r="BK2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>1.01</v>
-      </c>
-      <c r="BN2">
-        <v>1000</v>
-      </c>
       <c r="BO2">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ2">
-        <v>9.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU2">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="CB2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1125,34 +1137,34 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F3">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G3">
         <v>2.18</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I3">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K3">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L3">
         <v>1.5</v>
@@ -1170,133 +1182,133 @@
         <v>1.6</v>
       </c>
       <c r="Q3">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R3">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S3">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T3">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="U3">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="V3">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W3">
         <v>1.84</v>
       </c>
       <c r="X3">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Y3">
+        <v>14.5</v>
+      </c>
+      <c r="Z3">
+        <v>36</v>
+      </c>
+      <c r="AA3">
+        <v>120</v>
+      </c>
+      <c r="AB3">
+        <v>7.6</v>
+      </c>
+      <c r="AC3">
+        <v>7.6</v>
+      </c>
+      <c r="AD3">
+        <v>21</v>
+      </c>
+      <c r="AE3">
+        <v>75</v>
+      </c>
+      <c r="AF3">
+        <v>14.5</v>
+      </c>
+      <c r="AG3">
+        <v>11.5</v>
+      </c>
+      <c r="AH3">
         <v>25</v>
       </c>
-      <c r="Z3">
-        <v>1000</v>
-      </c>
-      <c r="AA3">
-        <v>1000</v>
-      </c>
-      <c r="AB3">
-        <v>970</v>
-      </c>
-      <c r="AC3">
-        <v>970</v>
-      </c>
-      <c r="AD3">
-        <v>1000</v>
-      </c>
-      <c r="AE3">
-        <v>1000</v>
-      </c>
-      <c r="AF3">
-        <v>970</v>
-      </c>
-      <c r="AG3">
-        <v>970</v>
-      </c>
-      <c r="AH3">
-        <v>1000</v>
-      </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ3">
+        <v>11</v>
+      </c>
+      <c r="AR3">
+        <v>6.4</v>
+      </c>
+      <c r="AS3">
         <v>7.4</v>
       </c>
-      <c r="AQ3">
-        <v>1.63</v>
-      </c>
-      <c r="AR3">
-        <v>1.66</v>
-      </c>
-      <c r="AS3">
-        <v>1.66</v>
-      </c>
       <c r="AT3">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AU3">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>1.74</v>
+        <v>15.5</v>
       </c>
       <c r="AW3">
-        <v>1.66</v>
+        <v>7.2</v>
       </c>
       <c r="AX3">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AY3">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>1.66</v>
+        <v>19</v>
       </c>
       <c r="BA3">
-        <v>1.66</v>
+        <v>7.2</v>
       </c>
       <c r="BB3">
-        <v>1.66</v>
+        <v>6.6</v>
       </c>
       <c r="BC3">
-        <v>1.66</v>
+        <v>6.6</v>
       </c>
       <c r="BD3">
-        <v>1.66</v>
+        <v>7</v>
       </c>
       <c r="BE3">
-        <v>1.66</v>
+        <v>7.6</v>
       </c>
       <c r="BF3">
-        <v>1.74</v>
+        <v>20</v>
       </c>
       <c r="BG3">
-        <v>1.58</v>
+        <v>7.4</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1359,7 +1371,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1367,175 +1379,175 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F4">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="G4">
-        <v>1000</v>
+        <v>1.91</v>
       </c>
       <c r="H4">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="I4">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="K4">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N4">
-        <v>1.08</v>
+        <v>2.82</v>
       </c>
       <c r="O4">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P4">
-        <v>1.08</v>
+        <v>1.69</v>
       </c>
       <c r="Q4">
-        <v>1.37</v>
+        <v>2.16</v>
       </c>
       <c r="R4">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
-        <v>1.37</v>
+        <v>3.75</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V4">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AW4">
         <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BD4">
         <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG4">
         <v>1.01</v>
@@ -1601,7 +1613,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1609,34 +1621,34 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F5">
-        <v>1.12</v>
+        <v>2.68</v>
       </c>
       <c r="G5">
-        <v>110</v>
+        <v>3.5</v>
       </c>
       <c r="H5">
-        <v>1.12</v>
+        <v>2.52</v>
       </c>
       <c r="I5">
-        <v>110</v>
+        <v>3.3</v>
       </c>
       <c r="J5">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="K5">
-        <v>110</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1645,88 +1657,88 @@
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O5">
         <v>1.34</v>
       </c>
       <c r="P5">
-        <v>1.34</v>
+        <v>1.69</v>
       </c>
       <c r="Q5">
-        <v>1.34</v>
+        <v>1.97</v>
       </c>
       <c r="R5">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S5">
-        <v>2</v>
+        <v>3.35</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V5">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="W5">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP5">
         <v>1.01</v>
@@ -1843,7 +1855,249 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>95</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6">
+        <v>1.1</v>
+      </c>
+      <c r="G6">
+        <v>1000</v>
+      </c>
+      <c r="H6">
+        <v>1.1</v>
+      </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="J6">
+        <v>1.1</v>
+      </c>
+      <c r="K6">
+        <v>870</v>
+      </c>
+      <c r="L6">
+        <v>1.01</v>
+      </c>
+      <c r="M6">
+        <v>1.01</v>
+      </c>
+      <c r="N6">
+        <v>1.24</v>
+      </c>
+      <c r="O6">
+        <v>1.28</v>
+      </c>
+      <c r="P6">
+        <v>1.24</v>
+      </c>
+      <c r="Q6">
+        <v>1.28</v>
+      </c>
+      <c r="R6">
+        <v>1.07</v>
+      </c>
+      <c r="S6">
+        <v>1.28</v>
+      </c>
+      <c r="T6">
+        <v>1.01</v>
+      </c>
+      <c r="U6">
+        <v>1.01</v>
+      </c>
+      <c r="V6">
+        <v>1.01</v>
+      </c>
+      <c r="W6">
+        <v>1.01</v>
+      </c>
+      <c r="X6">
+        <v>1000</v>
+      </c>
+      <c r="Y6">
+        <v>1000</v>
+      </c>
+      <c r="Z6">
+        <v>1000</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>1000</v>
+      </c>
+      <c r="AC6">
+        <v>1000</v>
+      </c>
+      <c r="AD6">
+        <v>1000</v>
+      </c>
+      <c r="AE6">
+        <v>1000</v>
+      </c>
+      <c r="AF6">
+        <v>1000</v>
+      </c>
+      <c r="AG6">
+        <v>1000</v>
+      </c>
+      <c r="AH6">
+        <v>1000</v>
+      </c>
+      <c r="AI6">
+        <v>1000</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>1000</v>
+      </c>
+      <c r="AL6">
+        <v>1000</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>1000</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6">
+        <v>1.01</v>
+      </c>
+      <c r="AR6">
+        <v>1.01</v>
+      </c>
+      <c r="AS6">
+        <v>1.01</v>
+      </c>
+      <c r="AT6">
+        <v>1.01</v>
+      </c>
+      <c r="AU6">
+        <v>1.01</v>
+      </c>
+      <c r="AV6">
+        <v>1.01</v>
+      </c>
+      <c r="AW6">
+        <v>1.01</v>
+      </c>
+      <c r="AX6">
+        <v>1.01</v>
+      </c>
+      <c r="AY6">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6">
+        <v>1.01</v>
+      </c>
+      <c r="BA6">
+        <v>1.01</v>
+      </c>
+      <c r="BB6">
+        <v>1.01</v>
+      </c>
+      <c r="BC6">
+        <v>1.01</v>
+      </c>
+      <c r="BD6">
+        <v>1.01</v>
+      </c>
+      <c r="BE6">
+        <v>1.01</v>
+      </c>
+      <c r="BF6">
+        <v>1.01</v>
+      </c>
+      <c r="BG6">
+        <v>1.01</v>
+      </c>
+      <c r="BH6">
+        <v>1000</v>
+      </c>
+      <c r="BI6">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
+        <v>1.01</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.01</v>
+      </c>
+      <c r="BN6">
+        <v>1000</v>
+      </c>
+      <c r="BO6">
+        <v>1.01</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>1.01</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>1.01</v>
+      </c>
+      <c r="BT6">
+        <v>1000</v>
+      </c>
+      <c r="BU6">
+        <v>1.01</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>1.01</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6">
+        <v>1000</v>
+      </c>
+      <c r="CA6">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="107">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,9 @@
     <t>Romanian Liga II</t>
   </si>
   <si>
+    <t>Algerian Ligue 1</t>
+  </si>
+  <si>
     <t>2026-09-22</t>
   </si>
   <si>
@@ -283,6 +286,12 @@
     <t>14:30:00</t>
   </si>
   <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
     <t>Lanus</t>
   </si>
   <si>
@@ -298,6 +307,12 @@
     <t>ACS Dumbravita</t>
   </si>
   <si>
+    <t>US Biskra</t>
+  </si>
+  <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
     <t>Estudiantes</t>
   </si>
   <si>
@@ -313,7 +328,13 @@
     <t>CSM Scolar Resita</t>
   </si>
   <si>
-    <t>2026-09-20 12:11:10</t>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>2026-09-20 14:26:14</t>
   </si>
 </sst>
 </file>
@@ -645,7 +666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -895,22 +916,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F2">
         <v>2.24</v>
       </c>
       <c r="G2">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H2">
         <v>4</v>
@@ -922,7 +943,7 @@
         <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L2">
         <v>1.62</v>
@@ -940,7 +961,7 @@
         <v>1.5</v>
       </c>
       <c r="Q2">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="R2">
         <v>1.17</v>
@@ -976,7 +997,7 @@
         <v>6.8</v>
       </c>
       <c r="AC2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD2">
         <v>23</v>
@@ -991,13 +1012,13 @@
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI2">
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK2">
         <v>38</v>
@@ -1021,7 +1042,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS2">
         <v>36</v>
@@ -1045,7 +1066,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA2">
         <v>40</v>
@@ -1075,37 +1096,37 @@
         <v>2.42</v>
       </c>
       <c r="BJ2">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BK2">
+        <v>6.4</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>12.5</v>
+      </c>
+      <c r="BN2">
         <v>4.8</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>6.6</v>
-      </c>
-      <c r="BN2">
-        <v>5.6</v>
       </c>
       <c r="BO2">
         <v>4.2</v>
       </c>
       <c r="BP2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ2">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BR2">
         <v>55</v>
       </c>
       <c r="BS2">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BT2">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU2">
         <v>6.4</v>
@@ -1114,22 +1135,22 @@
         <v>55</v>
       </c>
       <c r="BW2">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BY2">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BZ2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="CA2">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="CB2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1137,22 +1158,22 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F3">
         <v>2.08</v>
       </c>
       <c r="G3">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H3">
         <v>4.1</v>
@@ -1161,7 +1182,7 @@
         <v>4.4</v>
       </c>
       <c r="J3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K3">
         <v>3.45</v>
@@ -1173,22 +1194,22 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O3">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P3">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="Q3">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="R3">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S3">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="T3">
         <v>2.02</v>
@@ -1200,7 +1221,7 @@
         <v>1.29</v>
       </c>
       <c r="W3">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X3">
         <v>10.5</v>
@@ -1290,7 +1311,7 @@
         <v>19</v>
       </c>
       <c r="BA3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB3">
         <v>6.6</v>
@@ -1371,7 +1392,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1379,34 +1400,34 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F4">
         <v>1.75</v>
       </c>
       <c r="G4">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="H4">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>6</v>
       </c>
       <c r="J4">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K4">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1415,10 +1436,10 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="O4">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P4">
         <v>1.69</v>
@@ -1430,10 +1451,10 @@
         <v>1.26</v>
       </c>
       <c r="S4">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T4">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U4">
         <v>1.72</v>
@@ -1442,13 +1463,13 @@
         <v>1.2</v>
       </c>
       <c r="W4">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X4">
         <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z4">
         <v>50</v>
@@ -1457,13 +1478,13 @@
         <v>190</v>
       </c>
       <c r="AB4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC4">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD4">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE4">
         <v>110</v>
@@ -1472,10 +1493,10 @@
         <v>12</v>
       </c>
       <c r="AG4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI4">
         <v>120</v>
@@ -1484,7 +1505,7 @@
         <v>21</v>
       </c>
       <c r="AK4">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL4">
         <v>55</v>
@@ -1493,64 +1514,64 @@
         <v>190</v>
       </c>
       <c r="AN4">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AO4">
         <v>160</v>
       </c>
       <c r="AP4">
-        <v>8.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="AQ4">
-        <v>12</v>
+        <v>4.9</v>
       </c>
       <c r="AR4">
-        <v>27</v>
+        <v>6.2</v>
       </c>
       <c r="AS4">
-        <v>85</v>
+        <v>6.8</v>
       </c>
       <c r="AT4">
-        <v>5.7</v>
+        <v>3.75</v>
       </c>
       <c r="AU4">
-        <v>6.4</v>
+        <v>3.85</v>
       </c>
       <c r="AV4">
-        <v>16.5</v>
+        <v>5.4</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AX4">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="AY4">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="AZ4">
-        <v>17.5</v>
+        <v>5.4</v>
       </c>
       <c r="BA4">
-        <v>60</v>
+        <v>6.6</v>
       </c>
       <c r="BB4">
-        <v>15</v>
+        <v>5.3</v>
       </c>
       <c r="BC4">
-        <v>16.5</v>
+        <v>5.4</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE4">
-        <v>85</v>
+        <v>6.8</v>
       </c>
       <c r="BF4">
-        <v>12</v>
+        <v>4.9</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1613,7 +1634,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1621,34 +1642,34 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F5">
-        <v>2.68</v>
+        <v>1.1</v>
       </c>
       <c r="G5">
-        <v>3.5</v>
+        <v>110</v>
       </c>
       <c r="H5">
-        <v>2.52</v>
+        <v>1.1</v>
       </c>
       <c r="I5">
-        <v>3.3</v>
+        <v>110</v>
       </c>
       <c r="J5">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1657,34 +1678,34 @@
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="O5">
         <v>1.34</v>
       </c>
       <c r="P5">
-        <v>1.69</v>
+        <v>1.27</v>
       </c>
       <c r="Q5">
-        <v>1.97</v>
+        <v>1.33</v>
       </c>
       <c r="R5">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S5">
-        <v>3.35</v>
+        <v>1.34</v>
       </c>
       <c r="T5">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="W5">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
         <v>970</v>
@@ -1741,121 +1762,121 @@
         <v>34</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BH5">
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="CB5" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1863,34 +1884,34 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F6">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="G6">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="H6">
         <v>1.1</v>
       </c>
       <c r="I6">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K6">
-        <v>870</v>
+        <v>950</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1899,205 +1920,689 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O6">
         <v>1.28</v>
       </c>
       <c r="P6">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q6">
         <v>1.28</v>
       </c>
       <c r="R6">
+        <v>1.15</v>
+      </c>
+      <c r="S6">
+        <v>1.29</v>
+      </c>
+      <c r="T6">
+        <v>1.01</v>
+      </c>
+      <c r="U6">
+        <v>1.01</v>
+      </c>
+      <c r="V6">
+        <v>1.27</v>
+      </c>
+      <c r="W6">
+        <v>1.02</v>
+      </c>
+      <c r="X6">
+        <v>1000</v>
+      </c>
+      <c r="Y6">
+        <v>1000</v>
+      </c>
+      <c r="Z6">
+        <v>1000</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>1000</v>
+      </c>
+      <c r="AC6">
+        <v>1000</v>
+      </c>
+      <c r="AD6">
+        <v>1000</v>
+      </c>
+      <c r="AE6">
+        <v>1000</v>
+      </c>
+      <c r="AF6">
+        <v>1000</v>
+      </c>
+      <c r="AG6">
+        <v>1000</v>
+      </c>
+      <c r="AH6">
+        <v>1000</v>
+      </c>
+      <c r="AI6">
+        <v>1000</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>1000</v>
+      </c>
+      <c r="AL6">
+        <v>1000</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>1000</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>1.03</v>
+      </c>
+      <c r="AQ6">
+        <v>1.03</v>
+      </c>
+      <c r="AR6">
+        <v>1.03</v>
+      </c>
+      <c r="AS6">
+        <v>1.03</v>
+      </c>
+      <c r="AT6">
+        <v>1.03</v>
+      </c>
+      <c r="AU6">
+        <v>1.03</v>
+      </c>
+      <c r="AV6">
+        <v>1.03</v>
+      </c>
+      <c r="AW6">
+        <v>1.03</v>
+      </c>
+      <c r="AX6">
+        <v>1.03</v>
+      </c>
+      <c r="AY6">
+        <v>1.03</v>
+      </c>
+      <c r="AZ6">
+        <v>1.03</v>
+      </c>
+      <c r="BA6">
+        <v>1.03</v>
+      </c>
+      <c r="BB6">
+        <v>1.03</v>
+      </c>
+      <c r="BC6">
+        <v>1.03</v>
+      </c>
+      <c r="BD6">
+        <v>1.03</v>
+      </c>
+      <c r="BE6">
+        <v>1.03</v>
+      </c>
+      <c r="BF6">
+        <v>1.01</v>
+      </c>
+      <c r="BG6">
+        <v>1.01</v>
+      </c>
+      <c r="BH6">
+        <v>1000</v>
+      </c>
+      <c r="BI6">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
+        <v>1.01</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.01</v>
+      </c>
+      <c r="BN6">
+        <v>1000</v>
+      </c>
+      <c r="BO6">
+        <v>1.01</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>1.01</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>1.01</v>
+      </c>
+      <c r="BT6">
+        <v>1000</v>
+      </c>
+      <c r="BU6">
+        <v>1.01</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>1.01</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6">
+        <v>1000</v>
+      </c>
+      <c r="CA6">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F7">
+        <v>1.1</v>
+      </c>
+      <c r="G7">
+        <v>1000</v>
+      </c>
+      <c r="H7">
+        <v>1.1</v>
+      </c>
+      <c r="I7">
+        <v>1000</v>
+      </c>
+      <c r="J7">
+        <v>1.1</v>
+      </c>
+      <c r="K7">
+        <v>950</v>
+      </c>
+      <c r="L7">
+        <v>1.01</v>
+      </c>
+      <c r="M7">
+        <v>1.01</v>
+      </c>
+      <c r="N7">
+        <v>1.24</v>
+      </c>
+      <c r="O7">
+        <v>1.01</v>
+      </c>
+      <c r="P7">
+        <v>1.24</v>
+      </c>
+      <c r="Q7">
+        <v>1.02</v>
+      </c>
+      <c r="R7">
+        <v>1.08</v>
+      </c>
+      <c r="S7">
+        <v>1.02</v>
+      </c>
+      <c r="T7">
+        <v>1.01</v>
+      </c>
+      <c r="U7">
+        <v>1.01</v>
+      </c>
+      <c r="V7">
+        <v>1.01</v>
+      </c>
+      <c r="W7">
+        <v>1.01</v>
+      </c>
+      <c r="X7">
+        <v>1000</v>
+      </c>
+      <c r="Y7">
+        <v>1000</v>
+      </c>
+      <c r="Z7">
+        <v>1000</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>1000</v>
+      </c>
+      <c r="AC7">
+        <v>1000</v>
+      </c>
+      <c r="AD7">
+        <v>1000</v>
+      </c>
+      <c r="AE7">
+        <v>1000</v>
+      </c>
+      <c r="AF7">
+        <v>1000</v>
+      </c>
+      <c r="AG7">
+        <v>1000</v>
+      </c>
+      <c r="AH7">
+        <v>1000</v>
+      </c>
+      <c r="AI7">
+        <v>1000</v>
+      </c>
+      <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>1000</v>
+      </c>
+      <c r="AL7">
+        <v>1000</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>1000</v>
+      </c>
+      <c r="AO7">
+        <v>1000</v>
+      </c>
+      <c r="AP7">
+        <v>1.01</v>
+      </c>
+      <c r="AQ7">
+        <v>1.01</v>
+      </c>
+      <c r="AR7">
+        <v>1.01</v>
+      </c>
+      <c r="AS7">
+        <v>1.01</v>
+      </c>
+      <c r="AT7">
+        <v>1.01</v>
+      </c>
+      <c r="AU7">
+        <v>1.01</v>
+      </c>
+      <c r="AV7">
+        <v>1.01</v>
+      </c>
+      <c r="AW7">
+        <v>1.01</v>
+      </c>
+      <c r="AX7">
+        <v>1.01</v>
+      </c>
+      <c r="AY7">
+        <v>1.01</v>
+      </c>
+      <c r="AZ7">
+        <v>1.01</v>
+      </c>
+      <c r="BA7">
+        <v>1.01</v>
+      </c>
+      <c r="BB7">
+        <v>1.01</v>
+      </c>
+      <c r="BC7">
+        <v>1.01</v>
+      </c>
+      <c r="BD7">
+        <v>1.01</v>
+      </c>
+      <c r="BE7">
+        <v>1.01</v>
+      </c>
+      <c r="BF7">
+        <v>1.01</v>
+      </c>
+      <c r="BG7">
+        <v>1.01</v>
+      </c>
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7">
+        <v>1000</v>
+      </c>
+      <c r="BK7">
+        <v>1.01</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.01</v>
+      </c>
+      <c r="BN7">
+        <v>1000</v>
+      </c>
+      <c r="BO7">
+        <v>1.01</v>
+      </c>
+      <c r="BP7">
+        <v>1000</v>
+      </c>
+      <c r="BQ7">
+        <v>1.01</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>1.01</v>
+      </c>
+      <c r="BT7">
+        <v>1000</v>
+      </c>
+      <c r="BU7">
+        <v>1.01</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
+        <v>1.01</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7">
+        <v>1000</v>
+      </c>
+      <c r="CA7">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8">
+        <v>1.1</v>
+      </c>
+      <c r="G8">
+        <v>1000</v>
+      </c>
+      <c r="H8">
+        <v>1.1</v>
+      </c>
+      <c r="I8">
+        <v>1000</v>
+      </c>
+      <c r="J8">
+        <v>1.1</v>
+      </c>
+      <c r="K8">
+        <v>950</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
         <v>1.07</v>
       </c>
-      <c r="S6">
-        <v>1.28</v>
-      </c>
-      <c r="T6">
-        <v>1.01</v>
-      </c>
-      <c r="U6">
-        <v>1.01</v>
-      </c>
-      <c r="V6">
-        <v>1.01</v>
-      </c>
-      <c r="W6">
-        <v>1.01</v>
-      </c>
-      <c r="X6">
-        <v>1000</v>
-      </c>
-      <c r="Y6">
-        <v>1000</v>
-      </c>
-      <c r="Z6">
-        <v>1000</v>
-      </c>
-      <c r="AA6">
-        <v>1000</v>
-      </c>
-      <c r="AB6">
-        <v>1000</v>
-      </c>
-      <c r="AC6">
-        <v>1000</v>
-      </c>
-      <c r="AD6">
-        <v>1000</v>
-      </c>
-      <c r="AE6">
-        <v>1000</v>
-      </c>
-      <c r="AF6">
-        <v>1000</v>
-      </c>
-      <c r="AG6">
-        <v>1000</v>
-      </c>
-      <c r="AH6">
-        <v>1000</v>
-      </c>
-      <c r="AI6">
-        <v>1000</v>
-      </c>
-      <c r="AJ6">
-        <v>1000</v>
-      </c>
-      <c r="AK6">
-        <v>1000</v>
-      </c>
-      <c r="AL6">
-        <v>1000</v>
-      </c>
-      <c r="AM6">
-        <v>1000</v>
-      </c>
-      <c r="AN6">
-        <v>1000</v>
-      </c>
-      <c r="AO6">
-        <v>1000</v>
-      </c>
-      <c r="AP6">
-        <v>1.01</v>
-      </c>
-      <c r="AQ6">
-        <v>1.01</v>
-      </c>
-      <c r="AR6">
-        <v>1.01</v>
-      </c>
-      <c r="AS6">
-        <v>1.01</v>
-      </c>
-      <c r="AT6">
-        <v>1.01</v>
-      </c>
-      <c r="AU6">
-        <v>1.01</v>
-      </c>
-      <c r="AV6">
-        <v>1.01</v>
-      </c>
-      <c r="AW6">
-        <v>1.01</v>
-      </c>
-      <c r="AX6">
-        <v>1.01</v>
-      </c>
-      <c r="AY6">
-        <v>1.01</v>
-      </c>
-      <c r="AZ6">
-        <v>1.01</v>
-      </c>
-      <c r="BA6">
-        <v>1.01</v>
-      </c>
-      <c r="BB6">
-        <v>1.01</v>
-      </c>
-      <c r="BC6">
-        <v>1.01</v>
-      </c>
-      <c r="BD6">
-        <v>1.01</v>
-      </c>
-      <c r="BE6">
-        <v>1.01</v>
-      </c>
-      <c r="BF6">
-        <v>1.01</v>
-      </c>
-      <c r="BG6">
-        <v>1.01</v>
-      </c>
-      <c r="BH6">
-        <v>1000</v>
-      </c>
-      <c r="BI6">
-        <v>1.01</v>
-      </c>
-      <c r="BJ6">
-        <v>1000</v>
-      </c>
-      <c r="BK6">
-        <v>1.01</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>1.01</v>
-      </c>
-      <c r="BN6">
-        <v>1000</v>
-      </c>
-      <c r="BO6">
-        <v>1.01</v>
-      </c>
-      <c r="BP6">
-        <v>1000</v>
-      </c>
-      <c r="BQ6">
-        <v>1.01</v>
-      </c>
-      <c r="BR6">
-        <v>1000</v>
-      </c>
-      <c r="BS6">
-        <v>1.01</v>
-      </c>
-      <c r="BT6">
-        <v>1000</v>
-      </c>
-      <c r="BU6">
-        <v>1.01</v>
-      </c>
-      <c r="BV6">
-        <v>1000</v>
-      </c>
-      <c r="BW6">
-        <v>1.01</v>
-      </c>
-      <c r="BX6">
-        <v>1000</v>
-      </c>
-      <c r="BY6">
-        <v>1.01</v>
-      </c>
-      <c r="BZ6">
-        <v>1000</v>
-      </c>
-      <c r="CA6">
-        <v>1.01</v>
-      </c>
-      <c r="CB6" t="s">
-        <v>99</v>
+      <c r="Q8">
+        <v>1.01</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -334,7 +334,7 @@
     <t>MC Oran</t>
   </si>
   <si>
-    <t>2026-09-20 14:26:14</t>
+    <t>2026-09-20 16:39:31</t>
   </si>
 </sst>
 </file>
@@ -928,7 +928,7 @@
         <v>99</v>
       </c>
       <c r="F2">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G2">
         <v>2.32</v>
@@ -937,13 +937,13 @@
         <v>4</v>
       </c>
       <c r="I2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J2">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L2">
         <v>1.62</v>
@@ -958,13 +958,13 @@
         <v>1.6</v>
       </c>
       <c r="P2">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q2">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="R2">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S2">
         <v>6</v>
@@ -988,7 +988,7 @@
         <v>10.5</v>
       </c>
       <c r="Z2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AA2">
         <v>1000</v>
@@ -1006,7 +1006,7 @@
         <v>95</v>
       </c>
       <c r="AF2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
@@ -1018,10 +1018,10 @@
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK2">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AL2">
         <v>90</v>
@@ -1030,19 +1030,19 @@
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AO2">
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS2">
         <v>36</v>
@@ -1063,7 +1063,7 @@
         <v>11</v>
       </c>
       <c r="AY2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ2">
         <v>18.5</v>
@@ -1072,10 +1072,10 @@
         <v>40</v>
       </c>
       <c r="BB2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD2">
         <v>34</v>
@@ -1105,7 +1105,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN2">
         <v>4.8</v>
@@ -1117,16 +1117,16 @@
         <v>23</v>
       </c>
       <c r="BQ2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR2">
         <v>55</v>
       </c>
       <c r="BS2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU2">
         <v>6.4</v>
@@ -1135,19 +1135,19 @@
         <v>55</v>
       </c>
       <c r="BW2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX2">
         <v>85</v>
       </c>
       <c r="BY2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BZ2">
         <v>60</v>
       </c>
       <c r="CA2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB2" t="s">
         <v>106</v>
@@ -1206,7 +1206,7 @@
         <v>2.36</v>
       </c>
       <c r="R3">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S3">
         <v>4.7</v>
@@ -1242,13 +1242,13 @@
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AE3">
         <v>75</v>
       </c>
       <c r="AF3">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG3">
         <v>11.5</v>
@@ -1263,7 +1263,7 @@
         <v>32</v>
       </c>
       <c r="AK3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL3">
         <v>60</v>
@@ -1284,10 +1284,10 @@
         <v>11</v>
       </c>
       <c r="AR3">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS3">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
@@ -1299,7 +1299,7 @@
         <v>15.5</v>
       </c>
       <c r="AW3">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX3">
         <v>10.5</v>
@@ -1311,25 +1311,25 @@
         <v>19</v>
       </c>
       <c r="BA3">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB3">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD3">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BE3">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3">
         <v>20</v>
       </c>
       <c r="BG3">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1415,16 +1415,16 @@
         <v>1.75</v>
       </c>
       <c r="G4">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I4">
         <v>6</v>
       </c>
       <c r="J4">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K4">
         <v>3.95</v>
@@ -1454,16 +1454,16 @@
         <v>4</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U4">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="V4">
         <v>1.2</v>
       </c>
       <c r="W4">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X4">
         <v>13.5</v>
@@ -1520,10 +1520,10 @@
         <v>160</v>
       </c>
       <c r="AP4">
-        <v>4.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ4">
-        <v>4.9</v>
+        <v>12</v>
       </c>
       <c r="AR4">
         <v>6.2</v>
@@ -1532,34 +1532,34 @@
         <v>6.8</v>
       </c>
       <c r="AT4">
-        <v>3.75</v>
+        <v>5.7</v>
       </c>
       <c r="AU4">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="AV4">
-        <v>5.4</v>
+        <v>16.5</v>
       </c>
       <c r="AW4">
         <v>6.6</v>
       </c>
       <c r="AX4">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY4">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="AZ4">
-        <v>5.4</v>
+        <v>17.5</v>
       </c>
       <c r="BA4">
         <v>6.6</v>
       </c>
       <c r="BB4">
-        <v>5.3</v>
+        <v>15</v>
       </c>
       <c r="BC4">
-        <v>5.4</v>
+        <v>16.5</v>
       </c>
       <c r="BD4">
         <v>6.2</v>
@@ -1568,7 +1568,7 @@
         <v>6.8</v>
       </c>
       <c r="BF4">
-        <v>4.9</v>
+        <v>12</v>
       </c>
       <c r="BG4">
         <v>6.8</v>
@@ -1654,22 +1654,22 @@
         <v>102</v>
       </c>
       <c r="F5">
-        <v>1.1</v>
+        <v>2.68</v>
       </c>
       <c r="G5">
         <v>110</v>
       </c>
       <c r="H5">
-        <v>1.1</v>
+        <v>2.52</v>
       </c>
       <c r="I5">
-        <v>110</v>
+        <v>3.45</v>
       </c>
       <c r="J5">
-        <v>2.44</v>
+        <v>1.12</v>
       </c>
       <c r="K5">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1678,34 +1678,34 @@
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="O5">
         <v>1.34</v>
       </c>
       <c r="P5">
-        <v>1.27</v>
+        <v>1.63</v>
       </c>
       <c r="Q5">
-        <v>1.33</v>
+        <v>1.92</v>
       </c>
       <c r="R5">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S5">
-        <v>1.34</v>
+        <v>3.25</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U5">
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="X5">
         <v>970</v>
@@ -1762,16 +1762,16 @@
         <v>34</v>
       </c>
       <c r="AP5">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AQ5">
         <v>1.3</v>
       </c>
       <c r="AR5">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AS5">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AT5">
         <v>1.3</v>
@@ -1780,100 +1780,100 @@
         <v>1.3</v>
       </c>
       <c r="AV5">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AW5">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AX5">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AY5">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AZ5">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="BA5">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="BB5">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="BC5">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="BD5">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="BE5">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="BF5">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="BG5">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI5">
-        <v>1.15</v>
+        <v>2.5</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>1.15</v>
+        <v>2.54</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.15</v>
+        <v>2.88</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO5">
-        <v>1.15</v>
+        <v>2.3</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ5">
-        <v>1.11</v>
+        <v>2.9</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.12</v>
+        <v>3</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU5">
-        <v>1.15</v>
+        <v>2.28</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.11</v>
+        <v>2.88</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY5">
-        <v>1.12</v>
+        <v>3</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA5">
-        <v>1.12</v>
+        <v>3</v>
       </c>
       <c r="CB5" t="s">
         <v>106</v>
@@ -1896,19 +1896,19 @@
         <v>103</v>
       </c>
       <c r="F6">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="G6">
-        <v>240</v>
+        <v>110</v>
       </c>
       <c r="H6">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I6">
         <v>5</v>
       </c>
       <c r="J6">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -1920,13 +1920,13 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O6">
         <v>1.28</v>
       </c>
       <c r="P6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q6">
         <v>1.28</v>
@@ -2141,16 +2141,16 @@
         <v>1.1</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H7">
         <v>1.1</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J7">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2162,35 +2162,35 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P7">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q7">
+        <v>1.52</v>
+      </c>
+      <c r="R7">
+        <v>1.12</v>
+      </c>
+      <c r="S7">
+        <v>1.53</v>
+      </c>
+      <c r="T7">
+        <v>1.01</v>
+      </c>
+      <c r="U7">
+        <v>1.01</v>
+      </c>
+      <c r="V7">
         <v>1.02</v>
       </c>
-      <c r="R7">
-        <v>1.08</v>
-      </c>
-      <c r="S7">
+      <c r="W7">
         <v>1.02</v>
       </c>
-      <c r="T7">
-        <v>1.01</v>
-      </c>
-      <c r="U7">
-        <v>1.01</v>
-      </c>
-      <c r="V7">
-        <v>1.01</v>
-      </c>
-      <c r="W7">
-        <v>1.01</v>
-      </c>
       <c r="X7">
         <v>1000</v>
       </c>
@@ -2246,52 +2246,52 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7">
         <v>1.01</v>
@@ -2392,214 +2392,214 @@
         <v>1000</v>
       </c>
       <c r="J8">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K8">
         <v>950</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P8">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
         <v>106</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -334,7 +334,7 @@
     <t>MC Oran</t>
   </si>
   <si>
-    <t>2026-09-20 16:39:31</t>
+    <t>2026-09-20 18:53:20</t>
   </si>
 </sst>
 </file>
@@ -928,7 +928,7 @@
         <v>99</v>
       </c>
       <c r="F2">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="G2">
         <v>2.32</v>
@@ -937,10 +937,10 @@
         <v>4</v>
       </c>
       <c r="I2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K2">
         <v>3.15</v>
@@ -958,13 +958,13 @@
         <v>1.6</v>
       </c>
       <c r="P2">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q2">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="R2">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S2">
         <v>6</v>
@@ -973,22 +973,22 @@
         <v>2.3</v>
       </c>
       <c r="U2">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
         <v>1.75</v>
       </c>
       <c r="X2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA2">
         <v>1000</v>
@@ -1006,7 +1006,7 @@
         <v>95</v>
       </c>
       <c r="AF2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
@@ -1021,7 +1021,7 @@
         <v>34</v>
       </c>
       <c r="AK2">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AL2">
         <v>90</v>
@@ -1042,7 +1042,7 @@
         <v>9.4</v>
       </c>
       <c r="AR2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS2">
         <v>36</v>
@@ -1060,7 +1060,7 @@
         <v>32</v>
       </c>
       <c r="AX2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY2">
         <v>11</v>
@@ -1072,10 +1072,10 @@
         <v>40</v>
       </c>
       <c r="BB2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD2">
         <v>34</v>
@@ -1170,7 +1170,7 @@
         <v>100</v>
       </c>
       <c r="F3">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G3">
         <v>2.16</v>
@@ -1182,25 +1182,25 @@
         <v>4.4</v>
       </c>
       <c r="J3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K3">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L3">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="M3">
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O3">
         <v>1.46</v>
       </c>
       <c r="P3">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q3">
         <v>2.36</v>
@@ -1212,7 +1212,7 @@
         <v>4.7</v>
       </c>
       <c r="T3">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U3">
         <v>1.88</v>
@@ -1221,13 +1221,13 @@
         <v>1.29</v>
       </c>
       <c r="W3">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X3">
         <v>10.5</v>
       </c>
       <c r="Y3">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z3">
         <v>36</v>
@@ -1242,22 +1242,22 @@
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AE3">
         <v>75</v>
       </c>
       <c r="AF3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG3">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AH3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI3">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ3">
         <v>32</v>
@@ -1272,22 +1272,22 @@
         <v>180</v>
       </c>
       <c r="AN3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO3">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ3">
         <v>11</v>
       </c>
       <c r="AR3">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS3">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
@@ -1296,10 +1296,10 @@
         <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW3">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AX3">
         <v>10.5</v>
@@ -1308,64 +1308,64 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA3">
+        <v>10.5</v>
+      </c>
+      <c r="BB3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC3">
+        <v>8.6</v>
+      </c>
+      <c r="BD3">
+        <v>10.5</v>
+      </c>
+      <c r="BE3">
+        <v>11</v>
+      </c>
+      <c r="BF3">
         <v>8.4</v>
       </c>
-      <c r="BB3">
-        <v>7.2</v>
-      </c>
-      <c r="BC3">
-        <v>7</v>
-      </c>
-      <c r="BD3">
-        <v>7.8</v>
-      </c>
-      <c r="BE3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF3">
-        <v>20</v>
-      </c>
       <c r="BG3">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.47</v>
+        <v>1.1</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BT3">
         <v>1000</v>
@@ -1377,19 +1377,19 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="CB3" t="s">
         <v>106</v>
@@ -1424,7 +1424,7 @@
         <v>6</v>
       </c>
       <c r="J4">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K4">
         <v>3.95</v>
@@ -1436,7 +1436,7 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O4">
         <v>1.39</v>
@@ -1457,7 +1457,7 @@
         <v>1.89</v>
       </c>
       <c r="U4">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V4">
         <v>1.2</v>
@@ -1538,7 +1538,7 @@
         <v>6.4</v>
       </c>
       <c r="AV4">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW4">
         <v>6.6</v>
@@ -1550,7 +1550,7 @@
         <v>8</v>
       </c>
       <c r="AZ4">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA4">
         <v>6.6</v>
@@ -1559,7 +1559,7 @@
         <v>15</v>
       </c>
       <c r="BC4">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD4">
         <v>6.2</v>
@@ -1657,19 +1657,19 @@
         <v>2.68</v>
       </c>
       <c r="G5">
-        <v>110</v>
+        <v>3.5</v>
       </c>
       <c r="H5">
         <v>2.52</v>
       </c>
       <c r="I5">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="J5">
-        <v>1.12</v>
+        <v>2.86</v>
       </c>
       <c r="K5">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1684,22 +1684,22 @@
         <v>1.34</v>
       </c>
       <c r="P5">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="Q5">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="R5">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S5">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T5">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V5">
         <v>1.44</v>
@@ -1708,10 +1708,10 @@
         <v>1.4</v>
       </c>
       <c r="X5">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Y5">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z5">
         <v>22</v>
@@ -1720,13 +1720,13 @@
         <v>55</v>
       </c>
       <c r="AB5">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AC5">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AE5">
         <v>38</v>
@@ -1735,10 +1735,10 @@
         <v>24</v>
       </c>
       <c r="AG5">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH5">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI5">
         <v>55</v>
@@ -1747,13 +1747,13 @@
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL5">
         <v>60</v>
       </c>
       <c r="AM5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN5">
         <v>40</v>
@@ -1762,64 +1762,64 @@
         <v>34</v>
       </c>
       <c r="AP5">
-        <v>1.48</v>
+        <v>3.65</v>
       </c>
       <c r="AQ5">
-        <v>1.3</v>
+        <v>3.45</v>
       </c>
       <c r="AR5">
-        <v>1.38</v>
+        <v>3.9</v>
       </c>
       <c r="AS5">
-        <v>1.44</v>
+        <v>4.3</v>
       </c>
       <c r="AT5">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="AU5">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="AV5">
-        <v>1.48</v>
+        <v>3.6</v>
       </c>
       <c r="AW5">
-        <v>1.42</v>
+        <v>4.2</v>
       </c>
       <c r="AX5">
-        <v>1.39</v>
+        <v>3.95</v>
       </c>
       <c r="AY5">
-        <v>1.48</v>
+        <v>3.65</v>
       </c>
       <c r="AZ5">
-        <v>1.38</v>
+        <v>3.8</v>
       </c>
       <c r="BA5">
-        <v>1.44</v>
+        <v>4.3</v>
       </c>
       <c r="BB5">
-        <v>1.44</v>
+        <v>4.4</v>
       </c>
       <c r="BC5">
-        <v>1.42</v>
+        <v>4.2</v>
       </c>
       <c r="BD5">
-        <v>1.44</v>
+        <v>4.4</v>
       </c>
       <c r="BE5">
-        <v>1.46</v>
+        <v>4.5</v>
       </c>
       <c r="BF5">
-        <v>1.42</v>
+        <v>4.2</v>
       </c>
       <c r="BG5">
-        <v>1.42</v>
+        <v>4.1</v>
       </c>
       <c r="BH5">
         <v>4.4</v>
       </c>
       <c r="BI5">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="BJ5">
         <v>12.5</v>
@@ -1831,7 +1831,7 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="BN5">
         <v>8.199999999999999</v>
@@ -1846,7 +1846,7 @@
         <v>2.9</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS5">
         <v>3</v>
@@ -1858,7 +1858,7 @@
         <v>2.28</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW5">
         <v>2.88</v>
@@ -1896,7 +1896,7 @@
         <v>103</v>
       </c>
       <c r="F6">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="G6">
         <v>110</v>
@@ -1908,7 +1908,7 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -1920,13 +1920,13 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O6">
         <v>1.28</v>
       </c>
       <c r="P6">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q6">
         <v>1.28</v>
@@ -1944,7 +1944,7 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W6">
         <v>1.02</v>
@@ -2186,10 +2186,10 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2404,34 +2404,34 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P8">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q8">
-        <v>1.02</v>
+        <v>1.54</v>
       </c>
       <c r="R8">
         <v>1.08</v>
       </c>
       <c r="S8">
+        <v>1.55</v>
+      </c>
+      <c r="T8">
+        <v>1.01</v>
+      </c>
+      <c r="U8">
+        <v>1.01</v>
+      </c>
+      <c r="V8">
         <v>1.02</v>
       </c>
-      <c r="T8">
-        <v>1.01</v>
-      </c>
-      <c r="U8">
-        <v>1.01</v>
-      </c>
-      <c r="V8">
-        <v>1.01</v>
-      </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2488,52 +2488,52 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -334,7 +334,7 @@
     <t>MC Oran</t>
   </si>
   <si>
-    <t>2026-09-20 18:53:20</t>
+    <t>2026-09-20 21:06:52</t>
   </si>
 </sst>
 </file>
@@ -958,7 +958,7 @@
         <v>1.6</v>
       </c>
       <c r="P2">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q2">
         <v>2.82</v>
@@ -985,10 +985,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Y2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AA2">
         <v>1000</v>
@@ -1003,7 +1003,7 @@
         <v>23</v>
       </c>
       <c r="AE2">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
         <v>12</v>
@@ -1012,16 +1012,16 @@
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI2">
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AK2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL2">
         <v>90</v>
@@ -1048,7 +1048,7 @@
         <v>36</v>
       </c>
       <c r="AT2">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AU2">
         <v>6.6</v>
@@ -1173,19 +1173,19 @@
         <v>2.06</v>
       </c>
       <c r="G3">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K3">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L3">
         <v>1.47</v>
@@ -1194,28 +1194,28 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O3">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P3">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q3">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="R3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S3">
         <v>4.7</v>
       </c>
       <c r="T3">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U3">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V3">
         <v>1.29</v>
@@ -1224,7 +1224,7 @@
         <v>1.87</v>
       </c>
       <c r="X3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y3">
         <v>12.5</v>
@@ -1239,7 +1239,7 @@
         <v>7.6</v>
       </c>
       <c r="AC3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD3">
         <v>970</v>
@@ -1251,7 +1251,7 @@
         <v>12</v>
       </c>
       <c r="AG3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH3">
         <v>26</v>
@@ -1263,7 +1263,7 @@
         <v>32</v>
       </c>
       <c r="AK3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL3">
         <v>60</v>
@@ -1284,10 +1284,10 @@
         <v>11</v>
       </c>
       <c r="AR3">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
@@ -1299,37 +1299,37 @@
         <v>16</v>
       </c>
       <c r="AW3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX3">
         <v>10.5</v>
       </c>
       <c r="AY3">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA3">
         <v>10.5</v>
       </c>
       <c r="BB3">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BC3">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE3">
         <v>10.5</v>
       </c>
-      <c r="BE3">
-        <v>11</v>
-      </c>
       <c r="BF3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BG3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1424,10 +1424,10 @@
         <v>6</v>
       </c>
       <c r="J4">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K4">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1439,7 +1439,7 @@
         <v>2.96</v>
       </c>
       <c r="O4">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P4">
         <v>1.69</v>
@@ -1520,7 +1520,7 @@
         <v>160</v>
       </c>
       <c r="AP4">
-        <v>8.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="AQ4">
         <v>12</v>
@@ -1538,7 +1538,7 @@
         <v>6.4</v>
       </c>
       <c r="AV4">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW4">
         <v>6.6</v>
@@ -1550,16 +1550,16 @@
         <v>8</v>
       </c>
       <c r="AZ4">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA4">
         <v>6.6</v>
       </c>
       <c r="BB4">
-        <v>15</v>
+        <v>5.3</v>
       </c>
       <c r="BC4">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD4">
         <v>6.2</v>
@@ -1568,7 +1568,7 @@
         <v>6.8</v>
       </c>
       <c r="BF4">
-        <v>12</v>
+        <v>4.9</v>
       </c>
       <c r="BG4">
         <v>6.8</v>
@@ -1654,22 +1654,22 @@
         <v>102</v>
       </c>
       <c r="F5">
-        <v>2.68</v>
+        <v>1.12</v>
       </c>
       <c r="G5">
-        <v>3.5</v>
+        <v>110</v>
       </c>
       <c r="H5">
-        <v>2.52</v>
+        <v>1.12</v>
       </c>
       <c r="I5">
-        <v>3.25</v>
+        <v>110</v>
       </c>
       <c r="J5">
-        <v>2.86</v>
+        <v>1.12</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1678,40 +1678,40 @@
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="O5">
         <v>1.34</v>
       </c>
       <c r="P5">
-        <v>1.69</v>
+        <v>1.29</v>
       </c>
       <c r="Q5">
-        <v>1.97</v>
+        <v>1.34</v>
       </c>
       <c r="R5">
         <v>1.27</v>
       </c>
       <c r="S5">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
       <c r="T5">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="U5">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="W5">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X5">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Y5">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z5">
         <v>22</v>
@@ -1720,13 +1720,13 @@
         <v>55</v>
       </c>
       <c r="AB5">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AC5">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD5">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AE5">
         <v>38</v>
@@ -1735,10 +1735,10 @@
         <v>24</v>
       </c>
       <c r="AG5">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AH5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AI5">
         <v>55</v>
@@ -1747,13 +1747,13 @@
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL5">
         <v>60</v>
       </c>
       <c r="AM5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN5">
         <v>40</v>
@@ -1762,118 +1762,118 @@
         <v>34</v>
       </c>
       <c r="AP5">
-        <v>3.65</v>
+        <v>1.48</v>
       </c>
       <c r="AQ5">
-        <v>3.45</v>
+        <v>1.3</v>
       </c>
       <c r="AR5">
-        <v>3.9</v>
+        <v>1.38</v>
       </c>
       <c r="AS5">
-        <v>4.3</v>
+        <v>1.44</v>
       </c>
       <c r="AT5">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="AU5">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="AV5">
-        <v>3.6</v>
+        <v>1.48</v>
       </c>
       <c r="AW5">
-        <v>4.2</v>
+        <v>1.42</v>
       </c>
       <c r="AX5">
-        <v>3.95</v>
+        <v>1.39</v>
       </c>
       <c r="AY5">
-        <v>3.65</v>
+        <v>1.48</v>
       </c>
       <c r="AZ5">
-        <v>3.8</v>
+        <v>1.38</v>
       </c>
       <c r="BA5">
-        <v>4.3</v>
+        <v>1.44</v>
       </c>
       <c r="BB5">
-        <v>4.4</v>
+        <v>1.44</v>
       </c>
       <c r="BC5">
-        <v>4.2</v>
+        <v>1.42</v>
       </c>
       <c r="BD5">
-        <v>4.4</v>
+        <v>1.44</v>
       </c>
       <c r="BE5">
-        <v>4.5</v>
+        <v>1.46</v>
       </c>
       <c r="BF5">
-        <v>4.2</v>
+        <v>1.42</v>
       </c>
       <c r="BG5">
-        <v>4.1</v>
+        <v>1.42</v>
       </c>
       <c r="BH5">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>2.32</v>
+        <v>1.27</v>
       </c>
       <c r="BJ5">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>2.54</v>
+        <v>1.15</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>3.2</v>
+        <v>1.15</v>
       </c>
       <c r="BN5">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>2.3</v>
+        <v>1.27</v>
       </c>
       <c r="BP5">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>2.9</v>
+        <v>1.11</v>
       </c>
       <c r="BR5">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>3</v>
+        <v>1.13</v>
       </c>
       <c r="BT5">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>2.28</v>
+        <v>1.27</v>
       </c>
       <c r="BV5">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>2.88</v>
+        <v>1.11</v>
       </c>
       <c r="BX5">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>3</v>
+        <v>1.13</v>
       </c>
       <c r="BZ5">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>3</v>
+        <v>1.13</v>
       </c>
       <c r="CB5" t="s">
         <v>106</v>
@@ -1908,7 +1908,7 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -1920,13 +1920,13 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O6">
         <v>1.28</v>
       </c>
       <c r="P6">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q6">
         <v>1.28</v>
@@ -1944,7 +1944,7 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W6">
         <v>1.02</v>
@@ -2150,7 +2150,7 @@
         <v>110</v>
       </c>
       <c r="J7">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2186,10 +2186,10 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="W7">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2383,13 +2383,13 @@
         <v>1.1</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H8">
         <v>1.1</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J8">
         <v>1.12</v>
@@ -2428,10 +2428,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -334,7 +334,7 @@
     <t>MC Oran</t>
   </si>
   <si>
-    <t>2026-09-20 21:06:52</t>
+    <t>2026-09-20 23:19:02</t>
   </si>
 </sst>
 </file>
@@ -928,7 +928,7 @@
         <v>99</v>
       </c>
       <c r="F2">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G2">
         <v>2.32</v>
@@ -952,22 +952,22 @@
         <v>1.14</v>
       </c>
       <c r="N2">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="O2">
         <v>1.6</v>
       </c>
       <c r="P2">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q2">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="R2">
         <v>1.17</v>
       </c>
       <c r="S2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T2">
         <v>2.3</v>
@@ -982,13 +982,13 @@
         <v>1.75</v>
       </c>
       <c r="X2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y2">
         <v>10.5</v>
       </c>
       <c r="Z2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AA2">
         <v>1000</v>
@@ -1006,7 +1006,7 @@
         <v>1000</v>
       </c>
       <c r="AF2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
@@ -1018,10 +1018,10 @@
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL2">
         <v>90</v>
@@ -1060,7 +1060,7 @@
         <v>32</v>
       </c>
       <c r="AX2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY2">
         <v>11</v>
@@ -1072,10 +1072,10 @@
         <v>40</v>
       </c>
       <c r="BB2">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="BC2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD2">
         <v>34</v>
@@ -1084,7 +1084,7 @@
         <v>50</v>
       </c>
       <c r="BF2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG2">
         <v>38</v>
@@ -1111,7 +1111,7 @@
         <v>4.8</v>
       </c>
       <c r="BO2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP2">
         <v>23</v>
@@ -1173,7 +1173,7 @@
         <v>2.06</v>
       </c>
       <c r="G3">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H3">
         <v>4.2</v>
@@ -1185,7 +1185,7 @@
         <v>3.35</v>
       </c>
       <c r="K3">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L3">
         <v>1.47</v>
@@ -1197,13 +1197,13 @@
         <v>3</v>
       </c>
       <c r="O3">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P3">
         <v>1.69</v>
       </c>
       <c r="Q3">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R3">
         <v>1.25</v>
@@ -1218,10 +1218,10 @@
         <v>1.89</v>
       </c>
       <c r="V3">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W3">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X3">
         <v>11</v>
@@ -1248,10 +1248,10 @@
         <v>75</v>
       </c>
       <c r="AF3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH3">
         <v>26</v>
@@ -1263,7 +1263,7 @@
         <v>32</v>
       </c>
       <c r="AK3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL3">
         <v>60</v>
@@ -1293,7 +1293,7 @@
         <v>6.8</v>
       </c>
       <c r="AU3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV3">
         <v>16</v>
@@ -1305,7 +1305,7 @@
         <v>10.5</v>
       </c>
       <c r="AY3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3">
         <v>20</v>
@@ -1320,16 +1320,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BD3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE3">
+        <v>11</v>
+      </c>
+      <c r="BF3">
+        <v>17</v>
+      </c>
+      <c r="BG3">
         <v>10.5</v>
-      </c>
-      <c r="BF3">
-        <v>8</v>
-      </c>
-      <c r="BG3">
-        <v>10</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1412,7 +1412,7 @@
         <v>101</v>
       </c>
       <c r="F4">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="G4">
         <v>1.91</v>
@@ -1421,13 +1421,13 @@
         <v>5.1</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J4">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K4">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1436,61 +1436,61 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="O4">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="P4">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="Q4">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R4">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T4">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="U4">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V4">
         <v>1.2</v>
       </c>
       <c r="W4">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X4">
         <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="Z4">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AA4">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC4">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF4">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AG4">
         <v>11</v>
@@ -1499,7 +1499,7 @@
         <v>24</v>
       </c>
       <c r="AI4">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ4">
         <v>21</v>
@@ -1511,67 +1511,67 @@
         <v>55</v>
       </c>
       <c r="AM4">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN4">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO4">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AP4">
-        <v>4.6</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AR4">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AS4">
+        <v>7</v>
+      </c>
+      <c r="AT4">
+        <v>6.6</v>
+      </c>
+      <c r="AU4">
+        <v>7</v>
+      </c>
+      <c r="AV4">
+        <v>18.5</v>
+      </c>
+      <c r="AW4">
+        <v>7.4</v>
+      </c>
+      <c r="AX4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY4">
+        <v>9</v>
+      </c>
+      <c r="AZ4">
+        <v>19.5</v>
+      </c>
+      <c r="BA4">
         <v>6.8</v>
       </c>
-      <c r="AT4">
-        <v>5.7</v>
-      </c>
-      <c r="AU4">
-        <v>6.4</v>
-      </c>
-      <c r="AV4">
-        <v>16.5</v>
-      </c>
-      <c r="AW4">
-        <v>6.6</v>
-      </c>
-      <c r="AX4">
-        <v>7.8</v>
-      </c>
-      <c r="AY4">
-        <v>8</v>
-      </c>
-      <c r="AZ4">
-        <v>17.5</v>
-      </c>
-      <c r="BA4">
-        <v>6.6</v>
-      </c>
       <c r="BB4">
-        <v>5.3</v>
+        <v>17</v>
       </c>
       <c r="BC4">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD4">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF4">
-        <v>4.9</v>
+        <v>13.5</v>
       </c>
       <c r="BG4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1654,7 +1654,7 @@
         <v>102</v>
       </c>
       <c r="F5">
-        <v>1.12</v>
+        <v>2.68</v>
       </c>
       <c r="G5">
         <v>110</v>
@@ -1663,10 +1663,10 @@
         <v>1.12</v>
       </c>
       <c r="I5">
-        <v>110</v>
+        <v>3.2</v>
       </c>
       <c r="J5">
-        <v>1.12</v>
+        <v>3.2</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1678,37 +1678,37 @@
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="O5">
         <v>1.34</v>
       </c>
       <c r="P5">
+        <v>1.84</v>
+      </c>
+      <c r="Q5">
+        <v>1.91</v>
+      </c>
+      <c r="R5">
         <v>1.29</v>
       </c>
-      <c r="Q5">
-        <v>1.34</v>
-      </c>
-      <c r="R5">
-        <v>1.27</v>
-      </c>
       <c r="S5">
-        <v>1.02</v>
+        <v>3.15</v>
       </c>
       <c r="T5">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="V5">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="W5">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X5">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Y5">
         <v>970</v>
@@ -1732,7 +1732,7 @@
         <v>38</v>
       </c>
       <c r="AF5">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AG5">
         <v>970</v>
@@ -1762,118 +1762,118 @@
         <v>34</v>
       </c>
       <c r="AP5">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
       <c r="AQ5">
-        <v>1.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR5">
-        <v>1.38</v>
+        <v>12</v>
       </c>
       <c r="AS5">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AT5">
-        <v>1.3</v>
+        <v>2.06</v>
       </c>
       <c r="AU5">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="AV5">
-        <v>1.48</v>
+        <v>2.06</v>
       </c>
       <c r="AW5">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AX5">
-        <v>1.39</v>
+        <v>12</v>
       </c>
       <c r="AY5">
-        <v>1.48</v>
+        <v>2.06</v>
       </c>
       <c r="AZ5">
-        <v>1.38</v>
+        <v>1.89</v>
       </c>
       <c r="BA5">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="BB5">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="BC5">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="BD5">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="BE5">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="BF5">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="BG5">
-        <v>1.42</v>
+        <v>1.78</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI5">
-        <v>1.27</v>
+        <v>1.85</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>1.15</v>
+        <v>2.54</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.15</v>
+        <v>3.2</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO5">
-        <v>1.27</v>
+        <v>2.3</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ5">
-        <v>1.11</v>
+        <v>2.9</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS5">
-        <v>1.13</v>
+        <v>3</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU5">
-        <v>1.27</v>
+        <v>2.28</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW5">
-        <v>1.11</v>
+        <v>2.88</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY5">
-        <v>1.13</v>
+        <v>3</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA5">
-        <v>1.13</v>
+        <v>3</v>
       </c>
       <c r="CB5" t="s">
         <v>106</v>
@@ -1908,7 +1908,7 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -1944,7 +1944,7 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W6">
         <v>1.02</v>
@@ -2138,19 +2138,19 @@
         <v>104</v>
       </c>
       <c r="F7">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G7">
         <v>110</v>
       </c>
       <c r="H7">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I7">
         <v>110</v>
       </c>
       <c r="J7">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2186,10 +2186,10 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2392,7 +2392,7 @@
         <v>110</v>
       </c>
       <c r="J8">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2428,10 +2428,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="111">
   <si>
     <t>League</t>
   </si>
@@ -274,6 +274,9 @@
     <t>Algerian Ligue 1</t>
   </si>
   <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
     <t>2026-09-22</t>
   </si>
   <si>
@@ -292,6 +295,9 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
     <t>Lanus</t>
   </si>
   <si>
@@ -313,6 +319,9 @@
     <t>MC Alger</t>
   </si>
   <si>
+    <t>Ind Medellin</t>
+  </si>
+  <si>
     <t>Estudiantes</t>
   </si>
   <si>
@@ -334,7 +343,10 @@
     <t>MC Oran</t>
   </si>
   <si>
-    <t>2026-09-20 23:19:02</t>
+    <t>Jaguares de Cordoba</t>
+  </si>
+  <si>
+    <t>2026-09-21 01:29:42</t>
   </si>
 </sst>
 </file>
@@ -666,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -916,43 +928,43 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F2">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G2">
         <v>2.32</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K2">
         <v>3.15</v>
       </c>
       <c r="L2">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M2">
         <v>1.14</v>
       </c>
       <c r="N2">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O2">
         <v>1.6</v>
@@ -961,10 +973,10 @@
         <v>1.5</v>
       </c>
       <c r="Q2">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="R2">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S2">
         <v>6.2</v>
@@ -976,7 +988,7 @@
         <v>1.72</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W2">
         <v>1.75</v>
@@ -1000,10 +1012,10 @@
         <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF2">
         <v>12.5</v>
@@ -1033,22 +1045,22 @@
         <v>38</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP2">
         <v>7.2</v>
       </c>
       <c r="AQ2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AS2">
         <v>36</v>
       </c>
       <c r="AT2">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU2">
         <v>6.6</v>
@@ -1057,7 +1069,7 @@
         <v>16.5</v>
       </c>
       <c r="AW2">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AX2">
         <v>11</v>
@@ -1066,7 +1078,7 @@
         <v>11</v>
       </c>
       <c r="AZ2">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BA2">
         <v>40</v>
@@ -1075,7 +1087,7 @@
         <v>27</v>
       </c>
       <c r="BC2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="BD2">
         <v>34</v>
@@ -1090,7 +1102,7 @@
         <v>38</v>
       </c>
       <c r="BH2">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BI2">
         <v>2.42</v>
@@ -1099,7 +1111,7 @@
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1111,13 +1123,13 @@
         <v>4.8</v>
       </c>
       <c r="BO2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR2">
         <v>55</v>
@@ -1126,7 +1138,7 @@
         <v>11</v>
       </c>
       <c r="BT2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU2">
         <v>6.4</v>
@@ -1150,7 +1162,7 @@
         <v>11</v>
       </c>
       <c r="CB2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1158,25 +1170,25 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F3">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G3">
         <v>2.12</v>
       </c>
       <c r="H3">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I3">
         <v>4.5</v>
@@ -1188,13 +1200,13 @@
         <v>3.45</v>
       </c>
       <c r="L3">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="M3">
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O3">
         <v>1.46</v>
@@ -1203,52 +1215,52 @@
         <v>1.69</v>
       </c>
       <c r="Q3">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R3">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S3">
         <v>4.7</v>
       </c>
       <c r="T3">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U3">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V3">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W3">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X3">
         <v>11</v>
       </c>
       <c r="Y3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z3">
         <v>36</v>
       </c>
       <c r="AA3">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AB3">
         <v>7.6</v>
       </c>
       <c r="AC3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AE3">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AF3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG3">
         <v>9.6</v>
@@ -1275,13 +1287,13 @@
         <v>26</v>
       </c>
       <c r="AO3">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AP3">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR3">
         <v>8.800000000000001</v>
@@ -1293,10 +1305,10 @@
         <v>6.8</v>
       </c>
       <c r="AU3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW3">
         <v>10</v>
@@ -1305,31 +1317,31 @@
         <v>10.5</v>
       </c>
       <c r="AY3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB3">
         <v>8.4</v>
       </c>
       <c r="BC3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BD3">
+        <v>9.6</v>
+      </c>
+      <c r="BE3">
+        <v>10.5</v>
+      </c>
+      <c r="BF3">
+        <v>19.5</v>
+      </c>
+      <c r="BG3">
         <v>10</v>
-      </c>
-      <c r="BE3">
-        <v>11</v>
-      </c>
-      <c r="BF3">
-        <v>17</v>
-      </c>
-      <c r="BG3">
-        <v>10.5</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1392,7 +1404,7 @@
         <v>1.1</v>
       </c>
       <c r="CB3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1400,58 +1412,58 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F4">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="G4">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="H4">
         <v>5.1</v>
       </c>
       <c r="I4">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K4">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M4">
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O4">
         <v>1.41</v>
       </c>
       <c r="P4">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q4">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="R4">
         <v>1.27</v>
       </c>
       <c r="S4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T4">
         <v>2</v>
@@ -1460,22 +1472,22 @@
         <v>1.83</v>
       </c>
       <c r="V4">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W4">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X4">
         <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z4">
         <v>44</v>
       </c>
       <c r="AA4">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB4">
         <v>7.6</v>
@@ -1514,7 +1526,7 @@
         <v>180</v>
       </c>
       <c r="AN4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO4">
         <v>140</v>
@@ -1523,25 +1535,25 @@
         <v>10</v>
       </c>
       <c r="AQ4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR4">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="AS4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU4">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV4">
         <v>18.5</v>
       </c>
       <c r="AW4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX4">
         <v>8.800000000000001</v>
@@ -1553,7 +1565,7 @@
         <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB4">
         <v>17</v>
@@ -1562,16 +1574,16 @@
         <v>18.5</v>
       </c>
       <c r="BD4">
+        <v>6.8</v>
+      </c>
+      <c r="BE4">
         <v>7.2</v>
-      </c>
-      <c r="BE4">
-        <v>7</v>
       </c>
       <c r="BF4">
         <v>13.5</v>
       </c>
       <c r="BG4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1634,7 +1646,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1642,76 +1654,76 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F5">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
       <c r="G5">
-        <v>110</v>
+        <v>3.05</v>
       </c>
       <c r="H5">
-        <v>1.12</v>
+        <v>2.66</v>
       </c>
       <c r="I5">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="J5">
         <v>3.2</v>
       </c>
       <c r="K5">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M5">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N5">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="O5">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P5">
         <v>1.84</v>
       </c>
       <c r="Q5">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="R5">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S5">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U5">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="V5">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="W5">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="X5">
         <v>16</v>
       </c>
       <c r="Y5">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z5">
         <v>22</v>
@@ -1720,22 +1732,22 @@
         <v>55</v>
       </c>
       <c r="AB5">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AC5">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AE5">
         <v>38</v>
       </c>
       <c r="AF5">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AG5">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH5">
         <v>22</v>
@@ -1747,136 +1759,136 @@
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL5">
         <v>60</v>
       </c>
       <c r="AM5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO5">
         <v>34</v>
       </c>
       <c r="AP5">
-        <v>1.83</v>
+        <v>3.6</v>
       </c>
       <c r="AQ5">
-        <v>2.36</v>
+        <v>3.4</v>
       </c>
       <c r="AR5">
-        <v>12</v>
+        <v>3.65</v>
       </c>
       <c r="AS5">
-        <v>1.55</v>
+        <v>4</v>
       </c>
       <c r="AT5">
-        <v>2.06</v>
+        <v>3.45</v>
       </c>
       <c r="AU5">
-        <v>1.64</v>
+        <v>3</v>
       </c>
       <c r="AV5">
-        <v>2.06</v>
+        <v>3.6</v>
       </c>
       <c r="AW5">
-        <v>1.53</v>
+        <v>3.9</v>
       </c>
       <c r="AX5">
         <v>12</v>
       </c>
       <c r="AY5">
-        <v>2.06</v>
+        <v>3.6</v>
       </c>
       <c r="AZ5">
-        <v>1.89</v>
+        <v>3.75</v>
       </c>
       <c r="BA5">
-        <v>1.55</v>
+        <v>4</v>
       </c>
       <c r="BB5">
-        <v>1.55</v>
+        <v>12.5</v>
       </c>
       <c r="BC5">
-        <v>1.53</v>
+        <v>3.9</v>
       </c>
       <c r="BD5">
-        <v>1.55</v>
+        <v>17.5</v>
       </c>
       <c r="BE5">
-        <v>1.57</v>
+        <v>4.2</v>
       </c>
       <c r="BF5">
-        <v>1.53</v>
+        <v>3.9</v>
       </c>
       <c r="BG5">
-        <v>1.78</v>
+        <v>3.85</v>
       </c>
       <c r="BH5">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BJ5">
         <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>2.54</v>
+        <v>1.62</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>3.2</v>
+        <v>1.86</v>
       </c>
       <c r="BN5">
         <v>8.199999999999999</v>
       </c>
       <c r="BO5">
-        <v>2.3</v>
+        <v>1.52</v>
       </c>
       <c r="BP5">
         <v>30</v>
       </c>
       <c r="BQ5">
-        <v>2.9</v>
+        <v>1.75</v>
       </c>
       <c r="BR5">
         <v>48</v>
       </c>
       <c r="BS5">
-        <v>3</v>
+        <v>1.79</v>
       </c>
       <c r="BT5">
         <v>8</v>
       </c>
       <c r="BU5">
-        <v>2.28</v>
+        <v>1.51</v>
       </c>
       <c r="BV5">
         <v>28</v>
       </c>
       <c r="BW5">
-        <v>2.88</v>
+        <v>1.75</v>
       </c>
       <c r="BX5">
         <v>46</v>
       </c>
       <c r="BY5">
-        <v>3</v>
+        <v>1.79</v>
       </c>
       <c r="BZ5">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="CA5">
-        <v>3</v>
+        <v>1.78</v>
       </c>
       <c r="CB5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1884,16 +1896,16 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F6">
         <v>1.1</v>
@@ -1908,7 +1920,7 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -1944,7 +1956,7 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
         <v>1.02</v>
@@ -2118,7 +2130,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2126,19 +2138,19 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F7">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="G7">
         <v>110</v>
@@ -2150,7 +2162,7 @@
         <v>110</v>
       </c>
       <c r="J7">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2186,10 +2198,10 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W7">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2360,7 +2372,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2368,31 +2380,31 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F8">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G8">
         <v>110</v>
       </c>
       <c r="H8">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I8">
         <v>110</v>
       </c>
       <c r="J8">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2428,10 +2440,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2602,7 +2614,249 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>106</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F9">
+        <v>1.35</v>
+      </c>
+      <c r="G9">
+        <v>1.39</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
+      <c r="I9">
+        <v>12.5</v>
+      </c>
+      <c r="J9">
+        <v>5.2</v>
+      </c>
+      <c r="K9">
+        <v>5.9</v>
+      </c>
+      <c r="L9">
+        <v>1.22</v>
+      </c>
+      <c r="M9">
+        <v>1.05</v>
+      </c>
+      <c r="N9">
+        <v>4.8</v>
+      </c>
+      <c r="O9">
+        <v>1.24</v>
+      </c>
+      <c r="P9">
+        <v>2.28</v>
+      </c>
+      <c r="Q9">
+        <v>1.69</v>
+      </c>
+      <c r="R9">
+        <v>1.52</v>
+      </c>
+      <c r="S9">
+        <v>2.74</v>
+      </c>
+      <c r="T9">
+        <v>2.1</v>
+      </c>
+      <c r="U9">
+        <v>1.82</v>
+      </c>
+      <c r="V9">
+        <v>1.09</v>
+      </c>
+      <c r="W9">
+        <v>3.55</v>
+      </c>
+      <c r="X9">
+        <v>25</v>
+      </c>
+      <c r="Y9">
+        <v>40</v>
+      </c>
+      <c r="Z9">
+        <v>120</v>
+      </c>
+      <c r="AA9">
+        <v>460</v>
+      </c>
+      <c r="AB9">
+        <v>9</v>
+      </c>
+      <c r="AC9">
+        <v>12.5</v>
+      </c>
+      <c r="AD9">
+        <v>44</v>
+      </c>
+      <c r="AE9">
+        <v>200</v>
+      </c>
+      <c r="AF9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG9">
+        <v>11</v>
+      </c>
+      <c r="AH9">
+        <v>32</v>
+      </c>
+      <c r="AI9">
+        <v>160</v>
+      </c>
+      <c r="AJ9">
+        <v>11</v>
+      </c>
+      <c r="AK9">
+        <v>17.5</v>
+      </c>
+      <c r="AL9">
+        <v>46</v>
+      </c>
+      <c r="AM9">
+        <v>180</v>
+      </c>
+      <c r="AN9">
+        <v>5.5</v>
+      </c>
+      <c r="AO9">
+        <v>270</v>
+      </c>
+      <c r="AP9">
+        <v>7.6</v>
+      </c>
+      <c r="AQ9">
+        <v>9</v>
+      </c>
+      <c r="AR9">
+        <v>9.6</v>
+      </c>
+      <c r="AS9">
+        <v>10</v>
+      </c>
+      <c r="AT9">
+        <v>8</v>
+      </c>
+      <c r="AU9">
+        <v>11</v>
+      </c>
+      <c r="AV9">
+        <v>8.6</v>
+      </c>
+      <c r="AW9">
+        <v>10</v>
+      </c>
+      <c r="AX9">
+        <v>7.4</v>
+      </c>
+      <c r="AY9">
+        <v>9.6</v>
+      </c>
+      <c r="AZ9">
+        <v>21</v>
+      </c>
+      <c r="BA9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB9">
+        <v>9.6</v>
+      </c>
+      <c r="BC9">
+        <v>13</v>
+      </c>
+      <c r="BD9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE9">
+        <v>10</v>
+      </c>
+      <c r="BF9">
+        <v>5</v>
+      </c>
+      <c r="BG9">
+        <v>10</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>1.99</v>
+      </c>
+      <c r="BJ9">
+        <v>17</v>
+      </c>
+      <c r="BK9">
+        <v>1.79</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.99</v>
+      </c>
+      <c r="BN9">
+        <v>5</v>
+      </c>
+      <c r="BO9">
+        <v>2.72</v>
+      </c>
+      <c r="BP9">
+        <v>10.5</v>
+      </c>
+      <c r="BQ9">
+        <v>5.1</v>
+      </c>
+      <c r="BR9">
+        <v>32</v>
+      </c>
+      <c r="BS9">
+        <v>1.88</v>
+      </c>
+      <c r="BT9">
+        <v>18.5</v>
+      </c>
+      <c r="BU9">
+        <v>1.8</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.99</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.99</v>
+      </c>
+      <c r="BZ9">
+        <v>17.5</v>
+      </c>
+      <c r="CA9">
+        <v>1.79</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -346,7 +346,7 @@
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-09-21 01:29:42</t>
+    <t>2026-09-21 03:39:58</t>
   </si>
 </sst>
 </file>
@@ -940,58 +940,58 @@
         <v>102</v>
       </c>
       <c r="F2">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G2">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K2">
         <v>3.15</v>
       </c>
       <c r="L2">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="M2">
         <v>1.14</v>
       </c>
       <c r="N2">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="O2">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="P2">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q2">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="R2">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="T2">
         <v>2.3</v>
       </c>
       <c r="U2">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X2">
         <v>8</v>
@@ -1006,19 +1006,19 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC2">
         <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
@@ -1045,7 +1045,7 @@
         <v>38</v>
       </c>
       <c r="AO2">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
         <v>7.2</v>
@@ -1060,7 +1060,7 @@
         <v>36</v>
       </c>
       <c r="AT2">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AU2">
         <v>6.6</v>
@@ -1069,7 +1069,7 @@
         <v>16.5</v>
       </c>
       <c r="AW2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX2">
         <v>11</v>
@@ -1078,10 +1078,10 @@
         <v>11</v>
       </c>
       <c r="AZ2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA2">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="BB2">
         <v>27</v>
@@ -1099,13 +1099,13 @@
         <v>22</v>
       </c>
       <c r="BG2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH2">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BI2">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ2">
         <v>12</v>
@@ -1117,25 +1117,25 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN2">
         <v>4.8</v>
       </c>
       <c r="BO2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BQ2">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BR2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BS2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT2">
         <v>7.4</v>
@@ -1147,19 +1147,19 @@
         <v>55</v>
       </c>
       <c r="BW2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX2">
         <v>85</v>
       </c>
       <c r="BY2">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BZ2">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="CB2" t="s">
         <v>110</v>
@@ -1188,10 +1188,10 @@
         <v>2.12</v>
       </c>
       <c r="H3">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J3">
         <v>3.35</v>
@@ -1209,13 +1209,13 @@
         <v>3.05</v>
       </c>
       <c r="O3">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P3">
         <v>1.69</v>
       </c>
       <c r="Q3">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R3">
         <v>1.24</v>
@@ -1227,16 +1227,16 @@
         <v>2</v>
       </c>
       <c r="U3">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V3">
         <v>1.29</v>
       </c>
       <c r="W3">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X3">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="Y3">
         <v>12</v>
@@ -1275,7 +1275,7 @@
         <v>32</v>
       </c>
       <c r="AK3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL3">
         <v>60</v>
@@ -1296,10 +1296,10 @@
         <v>10.5</v>
       </c>
       <c r="AR3">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AS3">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
@@ -1311,7 +1311,7 @@
         <v>15.5</v>
       </c>
       <c r="AW3">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX3">
         <v>10.5</v>
@@ -1320,88 +1320,88 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA3">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB3">
+        <v>7.8</v>
+      </c>
+      <c r="BC3">
+        <v>20</v>
+      </c>
+      <c r="BD3">
         <v>8.4</v>
       </c>
-      <c r="BC3">
+      <c r="BE3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF3">
+        <v>17</v>
+      </c>
+      <c r="BG3">
+        <v>9</v>
+      </c>
+      <c r="BH3">
+        <v>2.92</v>
+      </c>
+      <c r="BI3">
+        <v>2.72</v>
+      </c>
+      <c r="BJ3">
+        <v>11</v>
+      </c>
+      <c r="BK3">
+        <v>8.4</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>14.5</v>
+      </c>
+      <c r="BN3">
+        <v>4.7</v>
+      </c>
+      <c r="BO3">
+        <v>4.2</v>
+      </c>
+      <c r="BP3">
+        <v>16.5</v>
+      </c>
+      <c r="BQ3">
         <v>8</v>
       </c>
-      <c r="BD3">
-        <v>9.6</v>
-      </c>
-      <c r="BE3">
-        <v>10.5</v>
-      </c>
-      <c r="BF3">
-        <v>19.5</v>
-      </c>
-      <c r="BG3">
-        <v>10</v>
-      </c>
-      <c r="BH3">
-        <v>1000</v>
-      </c>
-      <c r="BI3">
-        <v>1.38</v>
-      </c>
-      <c r="BJ3">
-        <v>1000</v>
-      </c>
-      <c r="BK3">
-        <v>1.1</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>1.1</v>
-      </c>
-      <c r="BN3">
-        <v>1000</v>
-      </c>
-      <c r="BO3">
-        <v>1.1</v>
-      </c>
-      <c r="BP3">
-        <v>1000</v>
-      </c>
-      <c r="BQ3">
-        <v>1.1</v>
-      </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS3">
-        <v>1.1</v>
+        <v>11.5</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU3">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW3">
-        <v>1.1</v>
+        <v>11.5</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY3">
-        <v>1.1</v>
+        <v>12.5</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA3">
-        <v>1.1</v>
+        <v>11</v>
       </c>
       <c r="CB3" t="s">
         <v>110</v>
@@ -1424,79 +1424,79 @@
         <v>104</v>
       </c>
       <c r="F4">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G4">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="H4">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J4">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K4">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L4">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="M4">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O4">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="P4">
+        <v>1.69</v>
+      </c>
+      <c r="Q4">
+        <v>2.38</v>
+      </c>
+      <c r="R4">
+        <v>1.23</v>
+      </c>
+      <c r="S4">
+        <v>4.7</v>
+      </c>
+      <c r="T4">
+        <v>2.08</v>
+      </c>
+      <c r="U4">
         <v>1.76</v>
-      </c>
-      <c r="Q4">
-        <v>2.24</v>
-      </c>
-      <c r="R4">
-        <v>1.27</v>
-      </c>
-      <c r="S4">
-        <v>4.2</v>
-      </c>
-      <c r="T4">
-        <v>2</v>
-      </c>
-      <c r="U4">
-        <v>1.83</v>
       </c>
       <c r="V4">
         <v>1.22</v>
       </c>
       <c r="W4">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X4">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y4">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA4">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB4">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC4">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE4">
         <v>100</v>
@@ -1508,52 +1508,52 @@
         <v>11</v>
       </c>
       <c r="AH4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI4">
         <v>110</v>
       </c>
       <c r="AJ4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL4">
         <v>55</v>
       </c>
       <c r="AM4">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AN4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AO4">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AP4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR4">
         <v>32</v>
       </c>
       <c r="AS4">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AT4">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AU4">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV4">
         <v>18.5</v>
       </c>
       <c r="AW4">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX4">
         <v>8.800000000000001</v>
@@ -1565,34 +1565,34 @@
         <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC4">
         <v>18.5</v>
       </c>
       <c r="BD4">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE4">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BF4">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BG4">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK4">
         <v>1.01</v>
@@ -1604,31 +1604,31 @@
         <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ4">
         <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS4">
         <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU4">
         <v>1.01</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW4">
         <v>1.01</v>
@@ -1640,7 +1640,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA4">
         <v>1.01</v>
@@ -1666,46 +1666,46 @@
         <v>105</v>
       </c>
       <c r="F5">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="G5">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="H5">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="I5">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="J5">
         <v>3.2</v>
       </c>
       <c r="K5">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="L5">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M5">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O5">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P5">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q5">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R5">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S5">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="T5">
         <v>1.64</v>
@@ -1714,10 +1714,10 @@
         <v>2.06</v>
       </c>
       <c r="V5">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W5">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="X5">
         <v>16</v>
@@ -1774,10 +1774,10 @@
         <v>34</v>
       </c>
       <c r="AP5">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AQ5">
-        <v>3.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR5">
         <v>3.65</v>
@@ -1786,13 +1786,13 @@
         <v>4</v>
       </c>
       <c r="AT5">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AU5">
         <v>3</v>
       </c>
       <c r="AV5">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="AW5">
         <v>3.9</v>
@@ -1801,16 +1801,16 @@
         <v>12</v>
       </c>
       <c r="AY5">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AZ5">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BA5">
         <v>4</v>
       </c>
       <c r="BB5">
-        <v>12.5</v>
+        <v>4</v>
       </c>
       <c r="BC5">
         <v>3.9</v>
@@ -1828,64 +1828,64 @@
         <v>3.85</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI5">
-        <v>1.86</v>
+        <v>2.64</v>
       </c>
       <c r="BJ5">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK5">
-        <v>1.62</v>
+        <v>3.45</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.86</v>
+        <v>4.8</v>
       </c>
       <c r="BN5">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BO5">
-        <v>1.52</v>
+        <v>2.9</v>
       </c>
       <c r="BP5">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BQ5">
-        <v>1.75</v>
+        <v>4.2</v>
       </c>
       <c r="BR5">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BS5">
-        <v>1.79</v>
+        <v>4.4</v>
       </c>
       <c r="BT5">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BU5">
-        <v>1.51</v>
+        <v>2.86</v>
       </c>
       <c r="BV5">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BW5">
-        <v>1.75</v>
+        <v>4.1</v>
       </c>
       <c r="BX5">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="BY5">
-        <v>1.79</v>
+        <v>4.3</v>
       </c>
       <c r="BZ5">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="CA5">
-        <v>1.78</v>
+        <v>4.3</v>
       </c>
       <c r="CB5" t="s">
         <v>110</v>
@@ -1920,10 +1920,10 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="K6">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1956,7 +1956,7 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
         <v>1.02</v>
@@ -2150,22 +2150,22 @@
         <v>107</v>
       </c>
       <c r="F7">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="G7">
         <v>110</v>
       </c>
       <c r="H7">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="I7">
         <v>110</v>
       </c>
       <c r="J7">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>65</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2198,10 +2198,10 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2404,7 +2404,7 @@
         <v>110</v>
       </c>
       <c r="J8">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2440,10 +2440,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W8">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2712,7 +2712,7 @@
         <v>200</v>
       </c>
       <c r="AF9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AG9">
         <v>11</v>
@@ -2736,16 +2736,16 @@
         <v>180</v>
       </c>
       <c r="AN9">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AO9">
         <v>270</v>
       </c>
       <c r="AP9">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ9">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR9">
         <v>9.6</v>
@@ -2760,7 +2760,7 @@
         <v>11</v>
       </c>
       <c r="AV9">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AW9">
         <v>10</v>
@@ -2784,7 +2784,7 @@
         <v>13</v>
       </c>
       <c r="BD9">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE9">
         <v>10</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="114">
   <si>
     <t>League</t>
   </si>
@@ -295,6 +295,9 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>21:00:00</t>
+  </si>
+  <si>
     <t>23:00:00</t>
   </si>
   <si>
@@ -319,6 +322,9 @@
     <t>MC Alger</t>
   </si>
   <si>
+    <t>Real Santander</t>
+  </si>
+  <si>
     <t>Ind Medellin</t>
   </si>
   <si>
@@ -343,10 +349,13 @@
     <t>MC Oran</t>
   </si>
   <si>
+    <t>Orsomarso</t>
+  </si>
+  <si>
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-09-21 03:39:58</t>
+    <t>2026-09-21 05:50:28</t>
   </si>
 </sst>
 </file>
@@ -678,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -934,16 +943,16 @@
         <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F2">
         <v>2.24</v>
       </c>
       <c r="G2">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H2">
         <v>4</v>
@@ -961,40 +970,40 @@
         <v>1.65</v>
       </c>
       <c r="M2">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N2">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="O2">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P2">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q2">
         <v>2.98</v>
       </c>
       <c r="R2">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S2">
         <v>6.6</v>
       </c>
       <c r="T2">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="U2">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V2">
         <v>1.3</v>
       </c>
       <c r="W2">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y2">
         <v>10.5</v>
@@ -1015,7 +1024,7 @@
         <v>21</v>
       </c>
       <c r="AE2">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
         <v>12</v>
@@ -1024,7 +1033,7 @@
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AI2">
         <v>1000</v>
@@ -1054,7 +1063,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR2">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AS2">
         <v>36</v>
@@ -1069,10 +1078,10 @@
         <v>16.5</v>
       </c>
       <c r="AW2">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AX2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY2">
         <v>11</v>
@@ -1081,13 +1090,13 @@
         <v>24</v>
       </c>
       <c r="BA2">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="BB2">
         <v>27</v>
       </c>
       <c r="BC2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="BD2">
         <v>34</v>
@@ -1102,7 +1111,7 @@
         <v>40</v>
       </c>
       <c r="BH2">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BI2">
         <v>2.4</v>
@@ -1111,31 +1120,31 @@
         <v>12</v>
       </c>
       <c r="BK2">
+        <v>7</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>14.5</v>
+      </c>
+      <c r="BN2">
+        <v>4.7</v>
+      </c>
+      <c r="BO2">
+        <v>4.2</v>
+      </c>
+      <c r="BP2">
+        <v>23</v>
+      </c>
+      <c r="BQ2">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>15.5</v>
-      </c>
-      <c r="BN2">
-        <v>4.8</v>
-      </c>
-      <c r="BO2">
-        <v>4.3</v>
-      </c>
-      <c r="BP2">
-        <v>20</v>
-      </c>
-      <c r="BQ2">
-        <v>9.6</v>
       </c>
       <c r="BR2">
         <v>60</v>
       </c>
       <c r="BS2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT2">
         <v>7.4</v>
@@ -1144,25 +1153,25 @@
         <v>6.4</v>
       </c>
       <c r="BV2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BW2">
+        <v>11.5</v>
+      </c>
+      <c r="BX2">
+        <v>90</v>
+      </c>
+      <c r="BY2">
+        <v>12.5</v>
+      </c>
+      <c r="BZ2">
+        <v>70</v>
+      </c>
+      <c r="CA2">
         <v>12</v>
       </c>
-      <c r="BX2">
-        <v>85</v>
-      </c>
-      <c r="BY2">
-        <v>13.5</v>
-      </c>
-      <c r="BZ2">
-        <v>1000</v>
-      </c>
-      <c r="CA2">
-        <v>12.5</v>
-      </c>
       <c r="CB2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1176,22 +1185,22 @@
         <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F3">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G3">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
         <v>4.2</v>
-      </c>
-      <c r="I3">
-        <v>4.4</v>
       </c>
       <c r="J3">
         <v>3.35</v>
@@ -1206,7 +1215,7 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O3">
         <v>1.45</v>
@@ -1215,28 +1224,28 @@
         <v>1.69</v>
       </c>
       <c r="Q3">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S3">
         <v>4.7</v>
       </c>
       <c r="T3">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U3">
         <v>1.92</v>
       </c>
       <c r="V3">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W3">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X3">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y3">
         <v>12</v>
@@ -1245,7 +1254,7 @@
         <v>36</v>
       </c>
       <c r="AA3">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AB3">
         <v>7.6</v>
@@ -1254,28 +1263,28 @@
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AE3">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AF3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG3">
         <v>9.6</v>
       </c>
       <c r="AH3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI3">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ3">
         <v>32</v>
       </c>
       <c r="AK3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL3">
         <v>60</v>
@@ -1284,64 +1293,64 @@
         <v>180</v>
       </c>
       <c r="AN3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO3">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AP3">
         <v>10</v>
       </c>
       <c r="AQ3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR3">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS3">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU3">
         <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AW3">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX3">
         <v>10.5</v>
       </c>
       <c r="AY3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3">
         <v>19</v>
       </c>
       <c r="BA3">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB3">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BC3">
         <v>20</v>
       </c>
       <c r="BD3">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE3">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF3">
         <v>17</v>
       </c>
       <c r="BG3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH3">
         <v>2.92</v>
@@ -1353,16 +1362,16 @@
         <v>11</v>
       </c>
       <c r="BK3">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>14.5</v>
+        <v>9.6</v>
       </c>
       <c r="BN3">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BO3">
         <v>4.2</v>
@@ -1371,40 +1380,40 @@
         <v>16.5</v>
       </c>
       <c r="BQ3">
+        <v>6.2</v>
+      </c>
+      <c r="BR3">
+        <v>40</v>
+      </c>
+      <c r="BS3">
         <v>8</v>
       </c>
-      <c r="BR3">
-        <v>42</v>
-      </c>
-      <c r="BS3">
-        <v>11.5</v>
-      </c>
       <c r="BT3">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BU3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW3">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="BX3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="BZ3">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="CB3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1418,16 +1427,16 @@
         <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F4">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="G4">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -1436,73 +1445,73 @@
         <v>5.6</v>
       </c>
       <c r="J4">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K4">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L4">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="M4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O4">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="Q4">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="S4">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="T4">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="U4">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="V4">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W4">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X4">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="Y4">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="Z4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA4">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB4">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AC4">
         <v>8.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE4">
         <v>100</v>
       </c>
       <c r="AF4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG4">
         <v>11</v>
@@ -1514,94 +1523,94 @@
         <v>110</v>
       </c>
       <c r="AJ4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL4">
         <v>55</v>
       </c>
       <c r="AM4">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN4">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AO4">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AP4">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR4">
         <v>32</v>
       </c>
       <c r="AS4">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="AT4">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW4">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AX4">
         <v>8.800000000000001</v>
       </c>
       <c r="AY4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ4">
         <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BB4">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BC4">
         <v>18.5</v>
       </c>
       <c r="BD4">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="BE4">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BF4">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BG4">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH4">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="BI4">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="BJ4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN4">
         <v>4.4</v>
@@ -1610,43 +1619,43 @@
         <v>3.45</v>
       </c>
       <c r="BP4">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BR4">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BT4">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BZ4">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="CB4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1660,22 +1669,22 @@
         <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F5">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G5">
         <v>3.2</v>
       </c>
       <c r="H5">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="I5">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J5">
         <v>3.2</v>
@@ -1696,7 +1705,7 @@
         <v>1.34</v>
       </c>
       <c r="P5">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q5">
         <v>2.06</v>
@@ -1705,10 +1714,10 @@
         <v>1.31</v>
       </c>
       <c r="S5">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="T5">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U5">
         <v>2.06</v>
@@ -1729,13 +1738,13 @@
         <v>22</v>
       </c>
       <c r="AA5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD5">
         <v>15</v>
@@ -1780,10 +1789,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AS5">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AT5">
         <v>3.3</v>
@@ -1792,10 +1801,10 @@
         <v>3</v>
       </c>
       <c r="AV5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AW5">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AX5">
         <v>12</v>
@@ -1804,7 +1813,7 @@
         <v>3.4</v>
       </c>
       <c r="AZ5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BA5">
         <v>4</v>
@@ -1813,19 +1822,19 @@
         <v>4</v>
       </c>
       <c r="BC5">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BD5">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BE5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF5">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BG5">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BH5">
         <v>3.8</v>
@@ -1837,19 +1846,19 @@
         <v>11.5</v>
       </c>
       <c r="BK5">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN5">
         <v>7</v>
       </c>
       <c r="BO5">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="BP5">
         <v>28</v>
@@ -1861,34 +1870,34 @@
         <v>44</v>
       </c>
       <c r="BS5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT5">
         <v>6.8</v>
       </c>
       <c r="BU5">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="BV5">
         <v>26</v>
       </c>
       <c r="BW5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BX5">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BY5">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BZ5">
         <v>36</v>
       </c>
       <c r="CA5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1902,10 +1911,10 @@
         <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F6">
         <v>1.1</v>
@@ -1914,16 +1923,16 @@
         <v>110</v>
       </c>
       <c r="H6">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="I6">
         <v>5</v>
       </c>
       <c r="J6">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="K6">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1956,10 +1965,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2130,7 +2139,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2144,49 +2153,49 @@
         <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F7">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="G7">
         <v>110</v>
       </c>
       <c r="H7">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="I7">
         <v>110</v>
       </c>
       <c r="J7">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="K7">
-        <v>65</v>
+        <v>950</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N7">
         <v>1.26</v>
       </c>
       <c r="O7">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="P7">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q7">
         <v>1.52</v>
       </c>
       <c r="R7">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S7">
         <v>1.53</v>
@@ -2198,10 +2207,10 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="W7">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2372,7 +2381,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2386,25 +2395,25 @@
         <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F8">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="G8">
         <v>110</v>
       </c>
       <c r="H8">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="I8">
         <v>110</v>
       </c>
       <c r="J8">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2416,19 +2425,19 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="O8">
         <v>1.02</v>
       </c>
       <c r="P8">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="Q8">
         <v>1.54</v>
       </c>
       <c r="R8">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="S8">
         <v>1.55</v>
@@ -2440,10 +2449,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2614,12 +2623,12 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
         <v>87</v>
@@ -2628,235 +2637,477 @@
         <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F9">
+        <v>1.1</v>
+      </c>
+      <c r="G9">
+        <v>110</v>
+      </c>
+      <c r="H9">
+        <v>1.1</v>
+      </c>
+      <c r="I9">
+        <v>950</v>
+      </c>
+      <c r="J9">
+        <v>1.1</v>
+      </c>
+      <c r="K9">
+        <v>950</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.01</v>
+      </c>
+      <c r="N9">
+        <v>1.26</v>
+      </c>
+      <c r="O9">
+        <v>1.42</v>
+      </c>
+      <c r="P9">
+        <v>1.25</v>
+      </c>
+      <c r="Q9">
+        <v>1.41</v>
+      </c>
+      <c r="R9">
+        <v>1.13</v>
+      </c>
+      <c r="S9">
+        <v>1.43</v>
+      </c>
+      <c r="T9">
+        <v>1.01</v>
+      </c>
+      <c r="U9">
+        <v>1.01</v>
+      </c>
+      <c r="V9">
+        <v>1.02</v>
+      </c>
+      <c r="W9">
+        <v>1.02</v>
+      </c>
+      <c r="X9">
+        <v>1000</v>
+      </c>
+      <c r="Y9">
+        <v>1000</v>
+      </c>
+      <c r="Z9">
+        <v>1000</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>1000</v>
+      </c>
+      <c r="AC9">
+        <v>1000</v>
+      </c>
+      <c r="AD9">
+        <v>1000</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>1000</v>
+      </c>
+      <c r="AG9">
+        <v>1000</v>
+      </c>
+      <c r="AH9">
+        <v>1000</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9">
+        <v>1.03</v>
+      </c>
+      <c r="AR9">
+        <v>1.03</v>
+      </c>
+      <c r="AS9">
+        <v>1.03</v>
+      </c>
+      <c r="AT9">
+        <v>1.03</v>
+      </c>
+      <c r="AU9">
+        <v>1.03</v>
+      </c>
+      <c r="AV9">
+        <v>1.03</v>
+      </c>
+      <c r="AW9">
+        <v>1.03</v>
+      </c>
+      <c r="AX9">
+        <v>1.03</v>
+      </c>
+      <c r="AY9">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9">
+        <v>1.03</v>
+      </c>
+      <c r="BA9">
+        <v>1.03</v>
+      </c>
+      <c r="BB9">
+        <v>1.03</v>
+      </c>
+      <c r="BC9">
+        <v>1.03</v>
+      </c>
+      <c r="BD9">
+        <v>1.03</v>
+      </c>
+      <c r="BE9">
+        <v>1.03</v>
+      </c>
+      <c r="BF9">
+        <v>1.01</v>
+      </c>
+      <c r="BG9">
+        <v>1.01</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>1.01</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.01</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>1.01</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>1.01</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.01</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>1.01</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.01</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F10">
         <v>1.35</v>
       </c>
-      <c r="G9">
+      <c r="G10">
         <v>1.39</v>
       </c>
-      <c r="H9">
+      <c r="H10">
         <v>10</v>
       </c>
-      <c r="I9">
+      <c r="I10">
         <v>12.5</v>
       </c>
-      <c r="J9">
+      <c r="J10">
         <v>5.2</v>
       </c>
-      <c r="K9">
+      <c r="K10">
         <v>5.9</v>
       </c>
-      <c r="L9">
+      <c r="L10">
         <v>1.22</v>
       </c>
-      <c r="M9">
-        <v>1.05</v>
-      </c>
-      <c r="N9">
+      <c r="M10">
+        <v>1.04</v>
+      </c>
+      <c r="N10">
         <v>4.8</v>
       </c>
-      <c r="O9">
+      <c r="O10">
         <v>1.24</v>
       </c>
-      <c r="P9">
+      <c r="P10">
         <v>2.28</v>
       </c>
-      <c r="Q9">
+      <c r="Q10">
         <v>1.69</v>
       </c>
-      <c r="R9">
+      <c r="R10">
         <v>1.52</v>
       </c>
-      <c r="S9">
-        <v>2.74</v>
-      </c>
-      <c r="T9">
+      <c r="S10">
+        <v>2.72</v>
+      </c>
+      <c r="T10">
         <v>2.1</v>
       </c>
-      <c r="U9">
+      <c r="U10">
         <v>1.82</v>
       </c>
-      <c r="V9">
+      <c r="V10">
         <v>1.09</v>
       </c>
-      <c r="W9">
+      <c r="W10">
         <v>3.55</v>
       </c>
-      <c r="X9">
+      <c r="X10">
         <v>25</v>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <v>40</v>
       </c>
-      <c r="Z9">
+      <c r="Z10">
         <v>120</v>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <v>460</v>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <v>9</v>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <v>12.5</v>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <v>44</v>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <v>200</v>
       </c>
-      <c r="AF9">
+      <c r="AF10">
         <v>8.4</v>
       </c>
-      <c r="AG9">
+      <c r="AG10">
         <v>11</v>
       </c>
-      <c r="AH9">
+      <c r="AH10">
         <v>32</v>
       </c>
-      <c r="AI9">
+      <c r="AI10">
         <v>160</v>
       </c>
-      <c r="AJ9">
+      <c r="AJ10">
         <v>11</v>
       </c>
-      <c r="AK9">
+      <c r="AK10">
         <v>17.5</v>
       </c>
-      <c r="AL9">
+      <c r="AL10">
         <v>46</v>
       </c>
-      <c r="AM9">
+      <c r="AM10">
         <v>180</v>
       </c>
-      <c r="AN9">
+      <c r="AN10">
         <v>5.4</v>
       </c>
-      <c r="AO9">
+      <c r="AO10">
         <v>270</v>
       </c>
-      <c r="AP9">
+      <c r="AP10">
         <v>7.4</v>
       </c>
-      <c r="AQ9">
+      <c r="AQ10">
         <v>8.800000000000001</v>
       </c>
-      <c r="AR9">
+      <c r="AR10">
         <v>9.6</v>
       </c>
-      <c r="AS9">
+      <c r="AS10">
         <v>10</v>
       </c>
-      <c r="AT9">
+      <c r="AT10">
         <v>8</v>
       </c>
-      <c r="AU9">
+      <c r="AU10">
         <v>11</v>
       </c>
-      <c r="AV9">
+      <c r="AV10">
         <v>8.4</v>
       </c>
-      <c r="AW9">
+      <c r="AW10">
         <v>10</v>
       </c>
-      <c r="AX9">
+      <c r="AX10">
         <v>7.4</v>
       </c>
-      <c r="AY9">
+      <c r="AY10">
         <v>9.6</v>
       </c>
-      <c r="AZ9">
+      <c r="AZ10">
         <v>21</v>
       </c>
-      <c r="BA9">
+      <c r="BA10">
         <v>9.800000000000001</v>
       </c>
-      <c r="BB9">
+      <c r="BB10">
         <v>9.6</v>
       </c>
-      <c r="BC9">
+      <c r="BC10">
         <v>13</v>
       </c>
-      <c r="BD9">
+      <c r="BD10">
         <v>9</v>
       </c>
-      <c r="BE9">
+      <c r="BE10">
         <v>10</v>
       </c>
-      <c r="BF9">
+      <c r="BF10">
         <v>5</v>
       </c>
-      <c r="BG9">
+      <c r="BG10">
         <v>10</v>
       </c>
-      <c r="BH9">
-        <v>1000</v>
-      </c>
-      <c r="BI9">
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
         <v>1.99</v>
       </c>
-      <c r="BJ9">
+      <c r="BJ10">
         <v>17</v>
       </c>
-      <c r="BK9">
+      <c r="BK10">
         <v>1.79</v>
       </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
         <v>1.99</v>
       </c>
-      <c r="BN9">
+      <c r="BN10">
         <v>5</v>
       </c>
-      <c r="BO9">
+      <c r="BO10">
         <v>2.72</v>
       </c>
-      <c r="BP9">
+      <c r="BP10">
         <v>10.5</v>
       </c>
-      <c r="BQ9">
+      <c r="BQ10">
         <v>5.1</v>
       </c>
-      <c r="BR9">
+      <c r="BR10">
         <v>32</v>
       </c>
-      <c r="BS9">
+      <c r="BS10">
         <v>1.88</v>
       </c>
-      <c r="BT9">
+      <c r="BT10">
         <v>18.5</v>
       </c>
-      <c r="BU9">
+      <c r="BU10">
         <v>1.8</v>
       </c>
-      <c r="BV9">
-        <v>1000</v>
-      </c>
-      <c r="BW9">
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
         <v>1.99</v>
       </c>
-      <c r="BX9">
-        <v>1000</v>
-      </c>
-      <c r="BY9">
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
         <v>1.99</v>
       </c>
-      <c r="BZ9">
+      <c r="BZ10">
         <v>17.5</v>
       </c>
-      <c r="CA9">
+      <c r="CA10">
         <v>1.79</v>
       </c>
-      <c r="CB9" t="s">
-        <v>110</v>
+      <c r="CB10" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -355,7 +355,7 @@
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-09-21 05:50:28</t>
+    <t>2026-09-21 08:00:59</t>
   </si>
 </sst>
 </file>
@@ -949,13 +949,13 @@
         <v>104</v>
       </c>
       <c r="F2">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I2">
         <v>4.3</v>
@@ -967,22 +967,22 @@
         <v>3.15</v>
       </c>
       <c r="L2">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M2">
         <v>1.15</v>
       </c>
       <c r="N2">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="O2">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P2">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q2">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R2">
         <v>1.16</v>
@@ -994,13 +994,13 @@
         <v>2.36</v>
       </c>
       <c r="U2">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V2">
         <v>1.3</v>
       </c>
       <c r="W2">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X2">
         <v>7.8</v>
@@ -1024,28 +1024,28 @@
         <v>21</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF2">
         <v>12</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH2">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="AI2">
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AK2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL2">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
         <v>1000</v>
@@ -1057,16 +1057,16 @@
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ2">
         <v>9.199999999999999</v>
       </c>
       <c r="AR2">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AS2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AT2">
         <v>6</v>
@@ -1075,7 +1075,7 @@
         <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW2">
         <v>34</v>
@@ -1090,31 +1090,31 @@
         <v>24</v>
       </c>
       <c r="BA2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BB2">
         <v>27</v>
       </c>
       <c r="BC2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="BD2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE2">
         <v>50</v>
       </c>
       <c r="BF2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BG2">
         <v>40</v>
       </c>
       <c r="BH2">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BI2">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BJ2">
         <v>12</v>
@@ -1126,25 +1126,25 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN2">
         <v>4.7</v>
       </c>
       <c r="BO2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP2">
         <v>23</v>
       </c>
       <c r="BQ2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BR2">
         <v>60</v>
       </c>
       <c r="BS2">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT2">
         <v>7.4</v>
@@ -1156,19 +1156,19 @@
         <v>60</v>
       </c>
       <c r="BW2">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BX2">
         <v>90</v>
       </c>
       <c r="BY2">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ2">
         <v>70</v>
       </c>
       <c r="CA2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CB2" t="s">
         <v>113</v>
@@ -1191,25 +1191,25 @@
         <v>105</v>
       </c>
       <c r="F3">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="G3">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="I3">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K3">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L3">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M3">
         <v>1.1</v>
@@ -1221,10 +1221,10 @@
         <v>1.45</v>
       </c>
       <c r="P3">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q3">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R3">
         <v>1.25</v>
@@ -1236,49 +1236,49 @@
         <v>1.99</v>
       </c>
       <c r="U3">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V3">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W3">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="X3">
+        <v>11</v>
+      </c>
+      <c r="Y3">
         <v>11.5</v>
       </c>
-      <c r="Y3">
-        <v>12</v>
-      </c>
       <c r="Z3">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AA3">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AB3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC3">
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE3">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AF3">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG3">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AH3">
         <v>25</v>
       </c>
       <c r="AI3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ3">
         <v>32</v>
@@ -1287,31 +1287,31 @@
         <v>30</v>
       </c>
       <c r="AL3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM3">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AN3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AP3">
         <v>10</v>
       </c>
       <c r="AQ3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR3">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AS3">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AT3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU3">
         <v>6.8</v>
@@ -1320,97 +1320,97 @@
         <v>14</v>
       </c>
       <c r="AW3">
-        <v>9.800000000000001</v>
+        <v>46</v>
       </c>
       <c r="AX3">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY3">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ3">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA3">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="BB3">
-        <v>8.6</v>
+        <v>27</v>
       </c>
       <c r="BC3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BD3">
-        <v>9.6</v>
+        <v>44</v>
       </c>
       <c r="BE3">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF3">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BG3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BH3">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BI3">
         <v>2.72</v>
       </c>
       <c r="BJ3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
+        <v>12</v>
+      </c>
+      <c r="BN3">
+        <v>5.6</v>
+      </c>
+      <c r="BO3">
+        <v>4.5</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>7.6</v>
+      </c>
+      <c r="BR3">
+        <v>38</v>
+      </c>
+      <c r="BS3">
         <v>9.6</v>
       </c>
-      <c r="BN3">
-        <v>5.3</v>
-      </c>
-      <c r="BO3">
-        <v>4.2</v>
-      </c>
-      <c r="BP3">
-        <v>16.5</v>
-      </c>
-      <c r="BQ3">
-        <v>6.2</v>
-      </c>
-      <c r="BR3">
-        <v>40</v>
-      </c>
-      <c r="BS3">
-        <v>8</v>
-      </c>
       <c r="BT3">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BU3">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BV3">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BW3">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY3">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA3">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="CB3" t="s">
         <v>113</v>
@@ -1442,13 +1442,13 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J4">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K4">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L4">
         <v>1.47</v>
@@ -1457,25 +1457,25 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O4">
         <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
       </c>
       <c r="R4">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T4">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U4">
         <v>1.85</v>
@@ -1490,7 +1490,7 @@
         <v>14.5</v>
       </c>
       <c r="Y4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z4">
         <v>44</v>
@@ -1499,16 +1499,16 @@
         <v>170</v>
       </c>
       <c r="AB4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC4">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4">
         <v>22</v>
       </c>
       <c r="AE4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF4">
         <v>11</v>
@@ -1520,22 +1520,22 @@
         <v>25</v>
       </c>
       <c r="AI4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ4">
         <v>21</v>
       </c>
       <c r="AK4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM4">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO4">
         <v>140</v>
@@ -1550,19 +1550,19 @@
         <v>32</v>
       </c>
       <c r="AS4">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT4">
         <v>6.4</v>
       </c>
       <c r="AU4">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV4">
         <v>18</v>
       </c>
       <c r="AW4">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX4">
         <v>8.800000000000001</v>
@@ -1571,46 +1571,46 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA4">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB4">
         <v>16.5</v>
       </c>
       <c r="BC4">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD4">
         <v>36</v>
       </c>
       <c r="BE4">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF4">
         <v>12.5</v>
       </c>
       <c r="BG4">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH4">
         <v>3.5</v>
       </c>
       <c r="BI4">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ4">
         <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BN4">
         <v>4.4</v>
@@ -1619,40 +1619,40 @@
         <v>3.45</v>
       </c>
       <c r="BP4">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BQ4">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BT4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BU4">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BV4">
         <v>55</v>
       </c>
       <c r="BW4">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BX4">
         <v>75</v>
       </c>
       <c r="BY4">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BZ4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="CA4">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="CB4" t="s">
         <v>113</v>
@@ -1684,10 +1684,10 @@
         <v>2.54</v>
       </c>
       <c r="I5">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J5">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K5">
         <v>3.7</v>
@@ -1696,16 +1696,16 @@
         <v>1.43</v>
       </c>
       <c r="M5">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N5">
         <v>3.5</v>
       </c>
       <c r="O5">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="Q5">
         <v>2.06</v>
@@ -1714,16 +1714,16 @@
         <v>1.31</v>
       </c>
       <c r="S5">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="T5">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U5">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V5">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W5">
         <v>1.46</v>
@@ -1777,7 +1777,7 @@
         <v>120</v>
       </c>
       <c r="AN5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO5">
         <v>34</v>
@@ -1801,13 +1801,13 @@
         <v>3</v>
       </c>
       <c r="AV5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AW5">
-        <v>3.85</v>
+        <v>19</v>
       </c>
       <c r="AX5">
-        <v>12</v>
+        <v>3.65</v>
       </c>
       <c r="AY5">
         <v>3.4</v>
@@ -1819,7 +1819,7 @@
         <v>4</v>
       </c>
       <c r="BB5">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="BC5">
         <v>3.85</v>
@@ -1858,7 +1858,7 @@
         <v>7</v>
       </c>
       <c r="BO5">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BP5">
         <v>28</v>
@@ -1923,13 +1923,13 @@
         <v>110</v>
       </c>
       <c r="H6">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="I6">
         <v>5</v>
       </c>
       <c r="J6">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="K6">
         <v>48</v>
@@ -1965,10 +1965,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W6">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2159,19 +2159,19 @@
         <v>109</v>
       </c>
       <c r="F7">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="G7">
         <v>110</v>
       </c>
       <c r="H7">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="I7">
         <v>110</v>
       </c>
       <c r="J7">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2183,13 +2183,13 @@
         <v>1.05</v>
       </c>
       <c r="N7">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O7">
         <v>1.06</v>
       </c>
       <c r="P7">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q7">
         <v>1.52</v>
@@ -2207,10 +2207,10 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W7">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2401,19 +2401,19 @@
         <v>110</v>
       </c>
       <c r="F8">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="G8">
         <v>110</v>
       </c>
       <c r="H8">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="I8">
         <v>110</v>
       </c>
       <c r="J8">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2431,13 +2431,13 @@
         <v>1.02</v>
       </c>
       <c r="P8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q8">
         <v>1.54</v>
       </c>
       <c r="R8">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S8">
         <v>1.55</v>
@@ -2449,10 +2449,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="W8">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2643,166 +2643,166 @@
         <v>111</v>
       </c>
       <c r="F9">
-        <v>1.1</v>
+        <v>2.48</v>
       </c>
       <c r="G9">
-        <v>110</v>
+        <v>2.8</v>
       </c>
       <c r="H9">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="I9">
-        <v>950</v>
+        <v>3.4</v>
       </c>
       <c r="J9">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N9">
+        <v>2.88</v>
+      </c>
+      <c r="O9">
+        <v>1.41</v>
+      </c>
+      <c r="P9">
+        <v>1.7</v>
+      </c>
+      <c r="Q9">
+        <v>2</v>
+      </c>
+      <c r="R9">
         <v>1.26</v>
       </c>
-      <c r="O9">
-        <v>1.42</v>
-      </c>
-      <c r="P9">
-        <v>1.25</v>
-      </c>
-      <c r="Q9">
+      <c r="S9">
+        <v>1.02</v>
+      </c>
+      <c r="T9">
+        <v>1.89</v>
+      </c>
+      <c r="U9">
+        <v>1.97</v>
+      </c>
+      <c r="V9">
         <v>1.41</v>
       </c>
-      <c r="R9">
-        <v>1.13</v>
-      </c>
-      <c r="S9">
-        <v>1.43</v>
-      </c>
-      <c r="T9">
-        <v>1.01</v>
-      </c>
-      <c r="U9">
-        <v>1.01</v>
-      </c>
-      <c r="V9">
-        <v>1.02</v>
-      </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -2885,7 +2885,7 @@
         <v>112</v>
       </c>
       <c r="F10">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G10">
         <v>1.39</v>
@@ -2894,13 +2894,13 @@
         <v>10</v>
       </c>
       <c r="I10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J10">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K10">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L10">
         <v>1.22</v>
@@ -2912,10 +2912,10 @@
         <v>4.8</v>
       </c>
       <c r="O10">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P10">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q10">
         <v>1.69</v>
@@ -2924,13 +2924,13 @@
         <v>1.52</v>
       </c>
       <c r="S10">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="T10">
         <v>2.1</v>
       </c>
       <c r="U10">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="V10">
         <v>1.09</v>
@@ -2987,19 +2987,19 @@
         <v>180</v>
       </c>
       <c r="AN10">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AO10">
         <v>270</v>
       </c>
       <c r="AP10">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ10">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AR10">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS10">
         <v>10</v>
@@ -3011,10 +3011,10 @@
         <v>11</v>
       </c>
       <c r="AV10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW10">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AX10">
         <v>7.4</v>
@@ -3026,7 +3026,7 @@
         <v>21</v>
       </c>
       <c r="BA10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB10">
         <v>9.6</v>
@@ -3035,34 +3035,34 @@
         <v>13</v>
       </c>
       <c r="BD10">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE10">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF10">
         <v>5</v>
       </c>
       <c r="BG10">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH10">
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="BJ10">
         <v>17</v>
       </c>
       <c r="BK10">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="BN10">
         <v>5</v>
@@ -3077,13 +3077,13 @@
         <v>5.1</v>
       </c>
       <c r="BR10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS10">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="BT10">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BU10">
         <v>1.8</v>
@@ -3092,19 +3092,19 @@
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="BZ10">
         <v>17.5</v>
       </c>
       <c r="CA10">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CB10" t="s">
         <v>113</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="118">
   <si>
     <t>League</t>
   </si>
@@ -322,9 +322,15 @@
     <t>MC Alger</t>
   </si>
   <si>
+    <t>Independiente Yumbo</t>
+  </si>
+  <si>
     <t>Real Santander</t>
   </si>
   <si>
+    <t>Atletico FC Cali</t>
+  </si>
+  <si>
     <t>Ind Medellin</t>
   </si>
   <si>
@@ -349,13 +355,19 @@
     <t>MC Oran</t>
   </si>
   <si>
+    <t>Internacional de Palmira</t>
+  </si>
+  <si>
     <t>Orsomarso</t>
   </si>
   <si>
+    <t>Tigres FC Zipaquira</t>
+  </si>
+  <si>
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-09-21 08:00:59</t>
+    <t>2026-09-21 10:12:17</t>
   </si>
 </sst>
 </file>
@@ -687,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -946,19 +958,19 @@
         <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F2">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G2">
         <v>2.3</v>
       </c>
       <c r="H2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J2">
         <v>3.05</v>
@@ -967,52 +979,52 @@
         <v>3.15</v>
       </c>
       <c r="L2">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="M2">
         <v>1.15</v>
       </c>
       <c r="N2">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="O2">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="P2">
         <v>1.47</v>
       </c>
       <c r="Q2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R2">
         <v>1.16</v>
       </c>
       <c r="S2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="T2">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U2">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W2">
         <v>1.76</v>
       </c>
       <c r="X2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y2">
         <v>10.5</v>
       </c>
       <c r="Z2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB2">
         <v>6.6</v>
@@ -1021,31 +1033,31 @@
         <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AF2">
         <v>12</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI2">
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM2">
         <v>1000</v>
@@ -1054,79 +1066,79 @@
         <v>38</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP2">
         <v>7</v>
       </c>
       <c r="AQ2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS2">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AT2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU2">
         <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW2">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AX2">
         <v>10.5</v>
       </c>
       <c r="AY2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA2">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="BB2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD2">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BE2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BF2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BG2">
         <v>40</v>
       </c>
       <c r="BH2">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BI2">
         <v>2.38</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BN2">
         <v>4.7</v>
@@ -1135,7 +1147,7 @@
         <v>4.3</v>
       </c>
       <c r="BP2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BQ2">
         <v>9.4</v>
@@ -1144,34 +1156,34 @@
         <v>60</v>
       </c>
       <c r="BS2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BT2">
         <v>7.4</v>
       </c>
       <c r="BU2">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="BV2">
+        <v>50</v>
+      </c>
+      <c r="BW2">
+        <v>12.5</v>
+      </c>
+      <c r="BX2">
+        <v>80</v>
+      </c>
+      <c r="BY2">
+        <v>14</v>
+      </c>
+      <c r="BZ2">
         <v>60</v>
       </c>
-      <c r="BW2">
+      <c r="CA2">
         <v>13</v>
       </c>
-      <c r="BX2">
-        <v>90</v>
-      </c>
-      <c r="BY2">
-        <v>14.5</v>
-      </c>
-      <c r="BZ2">
-        <v>70</v>
-      </c>
-      <c r="CA2">
-        <v>14</v>
-      </c>
       <c r="CB2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1188,64 +1200,64 @@
         <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="G3">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="H3">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="I3">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K3">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L3">
         <v>1.53</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N3">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O3">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P3">
         <v>1.7</v>
       </c>
       <c r="Q3">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="R3">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T3">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="U3">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="V3">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="X3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y3">
         <v>11.5</v>
@@ -1254,34 +1266,34 @@
         <v>26</v>
       </c>
       <c r="AA3">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AB3">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD3">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE3">
         <v>60</v>
       </c>
       <c r="AF3">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG3">
         <v>11</v>
       </c>
       <c r="AH3">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK3">
         <v>30</v>
@@ -1293,34 +1305,34 @@
         <v>150</v>
       </c>
       <c r="AN3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AP3">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AQ3">
         <v>10.5</v>
       </c>
       <c r="AR3">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AS3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW3">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AX3">
         <v>11.5</v>
@@ -1332,52 +1344,52 @@
         <v>19.5</v>
       </c>
       <c r="BA3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BC3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD3">
         <v>44</v>
       </c>
       <c r="BE3">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF3">
         <v>22</v>
       </c>
       <c r="BG3">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BH3">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BI3">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN3">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BO3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ3">
         <v>7.6</v>
@@ -1386,34 +1398,34 @@
         <v>38</v>
       </c>
       <c r="BS3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT3">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BU3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV3">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BW3">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY3">
         <v>10.5</v>
       </c>
       <c r="BZ3">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1430,31 +1442,31 @@
         <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F4">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="G4">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I4">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J4">
         <v>3.6</v>
       </c>
       <c r="K4">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L4">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M4">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N4">
         <v>3.3</v>
@@ -1463,7 +1475,7 @@
         <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1475,31 +1487,31 @@
         <v>4.1</v>
       </c>
       <c r="T4">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="U4">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V4">
         <v>1.21</v>
       </c>
       <c r="W4">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X4">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA4">
         <v>170</v>
       </c>
       <c r="AB4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC4">
         <v>9.199999999999999</v>
@@ -1514,13 +1526,13 @@
         <v>11</v>
       </c>
       <c r="AG4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI4">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ4">
         <v>21</v>
@@ -1529,16 +1541,16 @@
         <v>22</v>
       </c>
       <c r="AL4">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM4">
         <v>170</v>
       </c>
       <c r="AN4">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AO4">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP4">
         <v>10.5</v>
@@ -1550,7 +1562,7 @@
         <v>32</v>
       </c>
       <c r="AS4">
-        <v>7.4</v>
+        <v>90</v>
       </c>
       <c r="AT4">
         <v>6.4</v>
@@ -1562,7 +1574,7 @@
         <v>18</v>
       </c>
       <c r="AW4">
-        <v>7.2</v>
+        <v>50</v>
       </c>
       <c r="AX4">
         <v>8.800000000000001</v>
@@ -1574,25 +1586,25 @@
         <v>18.5</v>
       </c>
       <c r="BA4">
-        <v>7.2</v>
+        <v>55</v>
       </c>
       <c r="BB4">
         <v>16.5</v>
       </c>
       <c r="BC4">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD4">
         <v>36</v>
       </c>
       <c r="BE4">
-        <v>7.4</v>
+        <v>100</v>
       </c>
       <c r="BF4">
         <v>12.5</v>
       </c>
       <c r="BG4">
-        <v>7.4</v>
+        <v>65</v>
       </c>
       <c r="BH4">
         <v>3.5</v>
@@ -1604,58 +1616,58 @@
         <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BN4">
         <v>4.4</v>
       </c>
       <c r="BO4">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="BP4">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BQ4">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BR4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS4">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BT4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BU4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BW4">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX4">
         <v>75</v>
       </c>
       <c r="BY4">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ4">
         <v>32</v>
       </c>
       <c r="CA4">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="CB4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1672,40 +1684,40 @@
         <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F5">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="G5">
         <v>3.2</v>
       </c>
       <c r="H5">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="I5">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J5">
         <v>3.25</v>
       </c>
       <c r="K5">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L5">
         <v>1.43</v>
       </c>
       <c r="M5">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N5">
         <v>3.5</v>
       </c>
       <c r="O5">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P5">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="Q5">
         <v>2.06</v>
@@ -1717,13 +1729,13 @@
         <v>3.65</v>
       </c>
       <c r="T5">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U5">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V5">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W5">
         <v>1.46</v>
@@ -1732,10 +1744,10 @@
         <v>16</v>
       </c>
       <c r="Y5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA5">
         <v>50</v>
@@ -1753,7 +1765,7 @@
         <v>38</v>
       </c>
       <c r="AF5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG5">
         <v>16</v>
@@ -1768,7 +1780,7 @@
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL5">
         <v>60</v>
@@ -1786,7 +1798,7 @@
         <v>3.4</v>
       </c>
       <c r="AQ5">
-        <v>8.800000000000001</v>
+        <v>3.25</v>
       </c>
       <c r="AR5">
         <v>3.6</v>
@@ -1798,7 +1810,7 @@
         <v>3.3</v>
       </c>
       <c r="AU5">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AV5">
         <v>3.35</v>
@@ -1807,13 +1819,13 @@
         <v>19</v>
       </c>
       <c r="AX5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AY5">
         <v>3.4</v>
       </c>
       <c r="AZ5">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BA5">
         <v>4</v>
@@ -1822,19 +1834,19 @@
         <v>24</v>
       </c>
       <c r="BC5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BD5">
         <v>23</v>
       </c>
       <c r="BE5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF5">
+        <v>3.9</v>
+      </c>
+      <c r="BG5">
         <v>3.85</v>
-      </c>
-      <c r="BG5">
-        <v>3.8</v>
       </c>
       <c r="BH5">
         <v>3.8</v>
@@ -1846,7 +1858,7 @@
         <v>11.5</v>
       </c>
       <c r="BK5">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -1855,10 +1867,10 @@
         <v>4.9</v>
       </c>
       <c r="BN5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO5">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="BP5">
         <v>28</v>
@@ -1870,34 +1882,34 @@
         <v>44</v>
       </c>
       <c r="BS5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BT5">
         <v>6.8</v>
       </c>
       <c r="BU5">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="BV5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BX5">
         <v>42</v>
       </c>
       <c r="BY5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BZ5">
         <v>36</v>
       </c>
       <c r="CA5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="CB5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1914,25 +1926,25 @@
         <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F6">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>110</v>
       </c>
       <c r="H6">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="I6">
         <v>5</v>
       </c>
       <c r="J6">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1947,7 +1959,7 @@
         <v>1.28</v>
       </c>
       <c r="P6">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q6">
         <v>1.28</v>
@@ -1956,7 +1968,7 @@
         <v>1.15</v>
       </c>
       <c r="S6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -1965,10 +1977,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2139,7 +2151,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2156,148 +2168,148 @@
         <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F7">
-        <v>1.21</v>
+        <v>2.8</v>
       </c>
       <c r="G7">
+        <v>3.1</v>
+      </c>
+      <c r="H7">
+        <v>3.1</v>
+      </c>
+      <c r="I7">
+        <v>3.35</v>
+      </c>
+      <c r="J7">
+        <v>2.78</v>
+      </c>
+      <c r="K7">
+        <v>3.1</v>
+      </c>
+      <c r="L7">
+        <v>1.56</v>
+      </c>
+      <c r="M7">
+        <v>1.13</v>
+      </c>
+      <c r="N7">
+        <v>2.34</v>
+      </c>
+      <c r="O7">
+        <v>1.64</v>
+      </c>
+      <c r="P7">
+        <v>1.44</v>
+      </c>
+      <c r="Q7">
+        <v>2.94</v>
+      </c>
+      <c r="R7">
+        <v>1.15</v>
+      </c>
+      <c r="S7">
+        <v>6.4</v>
+      </c>
+      <c r="T7">
+        <v>2.24</v>
+      </c>
+      <c r="U7">
+        <v>1.7</v>
+      </c>
+      <c r="V7">
+        <v>1.42</v>
+      </c>
+      <c r="W7">
+        <v>1.47</v>
+      </c>
+      <c r="X7">
+        <v>7.4</v>
+      </c>
+      <c r="Y7">
+        <v>8.4</v>
+      </c>
+      <c r="Z7">
+        <v>19.5</v>
+      </c>
+      <c r="AA7">
+        <v>75</v>
+      </c>
+      <c r="AB7">
+        <v>8</v>
+      </c>
+      <c r="AC7">
+        <v>7</v>
+      </c>
+      <c r="AD7">
+        <v>15.5</v>
+      </c>
+      <c r="AE7">
+        <v>65</v>
+      </c>
+      <c r="AF7">
+        <v>18</v>
+      </c>
+      <c r="AG7">
+        <v>15</v>
+      </c>
+      <c r="AH7">
+        <v>26</v>
+      </c>
+      <c r="AI7">
         <v>110</v>
       </c>
-      <c r="H7">
-        <v>1.21</v>
-      </c>
-      <c r="I7">
-        <v>110</v>
-      </c>
-      <c r="J7">
-        <v>1.45</v>
-      </c>
-      <c r="K7">
-        <v>950</v>
-      </c>
-      <c r="L7">
-        <v>1.01</v>
-      </c>
-      <c r="M7">
-        <v>1.05</v>
-      </c>
-      <c r="N7">
-        <v>1.28</v>
-      </c>
-      <c r="O7">
-        <v>1.06</v>
-      </c>
-      <c r="P7">
-        <v>1.28</v>
-      </c>
-      <c r="Q7">
-        <v>1.52</v>
-      </c>
-      <c r="R7">
-        <v>1.13</v>
-      </c>
-      <c r="S7">
-        <v>1.53</v>
-      </c>
-      <c r="T7">
-        <v>1.01</v>
-      </c>
-      <c r="U7">
-        <v>1.01</v>
-      </c>
-      <c r="V7">
-        <v>1.18</v>
-      </c>
-      <c r="W7">
-        <v>1.18</v>
-      </c>
-      <c r="X7">
-        <v>1000</v>
-      </c>
-      <c r="Y7">
-        <v>1000</v>
-      </c>
-      <c r="Z7">
-        <v>1000</v>
-      </c>
-      <c r="AA7">
-        <v>1000</v>
-      </c>
-      <c r="AB7">
-        <v>1000</v>
-      </c>
-      <c r="AC7">
-        <v>1000</v>
-      </c>
-      <c r="AD7">
-        <v>1000</v>
-      </c>
-      <c r="AE7">
-        <v>1000</v>
-      </c>
-      <c r="AF7">
-        <v>1000</v>
-      </c>
-      <c r="AG7">
-        <v>1000</v>
-      </c>
-      <c r="AH7">
-        <v>1000</v>
-      </c>
-      <c r="AI7">
-        <v>1000</v>
-      </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP7">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AQ7">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AR7">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT7">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AU7">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV7">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AY7">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AZ7">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BA7">
         <v>1.03</v>
@@ -2315,16 +2327,16 @@
         <v>1.03</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH7">
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
@@ -2381,7 +2393,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2398,70 +2410,70 @@
         <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F8">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="G8">
-        <v>110</v>
+        <v>1.73</v>
       </c>
       <c r="H8">
-        <v>1.18</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>110</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J8">
-        <v>1.38</v>
+        <v>3.45</v>
       </c>
       <c r="K8">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N8">
-        <v>1.26</v>
+        <v>2.48</v>
       </c>
       <c r="O8">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="P8">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="Q8">
-        <v>1.54</v>
+        <v>2.56</v>
       </c>
       <c r="R8">
+        <v>1.15</v>
+      </c>
+      <c r="S8">
+        <v>2.96</v>
+      </c>
+      <c r="T8">
+        <v>1.01</v>
+      </c>
+      <c r="U8">
+        <v>1.01</v>
+      </c>
+      <c r="V8">
         <v>1.13</v>
       </c>
-      <c r="S8">
-        <v>1.55</v>
-      </c>
-      <c r="T8">
-        <v>1.01</v>
-      </c>
-      <c r="U8">
-        <v>1.01</v>
-      </c>
-      <c r="V8">
-        <v>1.16</v>
-      </c>
       <c r="W8">
-        <v>1.16</v>
+        <v>2.36</v>
       </c>
       <c r="X8">
         <v>1000</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA8">
         <v>1000</v>
@@ -2470,40 +2482,40 @@
         <v>1000</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE8">
         <v>1000</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG8">
         <v>1000</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI8">
         <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK8">
         <v>1000</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM8">
         <v>1000</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO8">
         <v>1000</v>
@@ -2557,10 +2569,10 @@
         <v>1.03</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2569,61 +2581,61 @@
         <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB8" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2640,82 +2652,82 @@
         <v>102</v>
       </c>
       <c r="E9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F9">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="G9">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="H9">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="I9">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="J9">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="K9">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N9">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="O9">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="P9">
+        <v>1.56</v>
+      </c>
+      <c r="Q9">
+        <v>2.42</v>
+      </c>
+      <c r="R9">
+        <v>1.23</v>
+      </c>
+      <c r="S9">
+        <v>4.4</v>
+      </c>
+      <c r="T9">
+        <v>1.98</v>
+      </c>
+      <c r="U9">
         <v>1.7</v>
       </c>
-      <c r="Q9">
-        <v>2</v>
-      </c>
-      <c r="R9">
-        <v>1.26</v>
-      </c>
-      <c r="S9">
-        <v>1.02</v>
-      </c>
-      <c r="T9">
-        <v>1.89</v>
-      </c>
-      <c r="U9">
-        <v>1.97</v>
-      </c>
       <c r="V9">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="X9">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y9">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="Z9">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AA9">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB9">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC9">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AD9">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AE9">
         <v>55</v>
@@ -2727,82 +2739,82 @@
         <v>14</v>
       </c>
       <c r="AH9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI9">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AJ9">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AK9">
+        <v>50</v>
+      </c>
+      <c r="AL9">
+        <v>85</v>
+      </c>
+      <c r="AM9">
+        <v>190</v>
+      </c>
+      <c r="AN9">
+        <v>60</v>
+      </c>
+      <c r="AO9">
+        <v>65</v>
+      </c>
+      <c r="AP9">
+        <v>6.8</v>
+      </c>
+      <c r="AQ9">
+        <v>6.8</v>
+      </c>
+      <c r="AR9">
+        <v>13.5</v>
+      </c>
+      <c r="AS9">
+        <v>38</v>
+      </c>
+      <c r="AT9">
+        <v>6.6</v>
+      </c>
+      <c r="AU9">
+        <v>5.4</v>
+      </c>
+      <c r="AV9">
+        <v>10</v>
+      </c>
+      <c r="AW9">
+        <v>30</v>
+      </c>
+      <c r="AX9">
+        <v>13</v>
+      </c>
+      <c r="AY9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ9">
+        <v>15</v>
+      </c>
+      <c r="BA9">
+        <v>46</v>
+      </c>
+      <c r="BB9">
         <v>34</v>
       </c>
-      <c r="AL9">
-        <v>55</v>
-      </c>
-      <c r="AM9">
-        <v>140</v>
-      </c>
-      <c r="AN9">
-        <v>30</v>
-      </c>
-      <c r="AO9">
-        <v>60</v>
-      </c>
-      <c r="AP9">
-        <v>3.55</v>
-      </c>
-      <c r="AQ9">
-        <v>3.55</v>
-      </c>
-      <c r="AR9">
-        <v>4.1</v>
-      </c>
-      <c r="AS9">
-        <v>4.6</v>
-      </c>
-      <c r="AT9">
-        <v>3.35</v>
-      </c>
-      <c r="AU9">
-        <v>3.1</v>
-      </c>
-      <c r="AV9">
-        <v>3.8</v>
-      </c>
-      <c r="AW9">
-        <v>4.5</v>
-      </c>
-      <c r="AX9">
-        <v>3.85</v>
-      </c>
-      <c r="AY9">
-        <v>3.6</v>
-      </c>
-      <c r="AZ9">
-        <v>4</v>
-      </c>
-      <c r="BA9">
-        <v>4.5</v>
-      </c>
-      <c r="BB9">
-        <v>4.3</v>
-      </c>
       <c r="BC9">
-        <v>4.2</v>
+        <v>29</v>
       </c>
       <c r="BD9">
-        <v>4.5</v>
+        <v>44</v>
       </c>
       <c r="BE9">
-        <v>4.7</v>
+        <v>110</v>
       </c>
       <c r="BF9">
-        <v>4.2</v>
+        <v>32</v>
       </c>
       <c r="BG9">
-        <v>4.5</v>
+        <v>36</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -2865,249 +2877,733 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B10" t="s">
         <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
         <v>103</v>
       </c>
       <c r="E10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F10">
-        <v>1.36</v>
+        <v>2.48</v>
       </c>
       <c r="G10">
-        <v>1.39</v>
+        <v>2.78</v>
       </c>
       <c r="H10">
-        <v>10</v>
+        <v>3.05</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>3.4</v>
       </c>
       <c r="J10">
+        <v>3.15</v>
+      </c>
+      <c r="K10">
+        <v>3.5</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.09</v>
+      </c>
+      <c r="N10">
+        <v>3.05</v>
+      </c>
+      <c r="O10">
+        <v>1.41</v>
+      </c>
+      <c r="P10">
+        <v>1.71</v>
+      </c>
+      <c r="Q10">
+        <v>2</v>
+      </c>
+      <c r="R10">
+        <v>1.26</v>
+      </c>
+      <c r="S10">
+        <v>4.2</v>
+      </c>
+      <c r="T10">
+        <v>1.87</v>
+      </c>
+      <c r="U10">
+        <v>1.97</v>
+      </c>
+      <c r="V10">
+        <v>1.41</v>
+      </c>
+      <c r="W10">
+        <v>1.57</v>
+      </c>
+      <c r="X10">
+        <v>13.5</v>
+      </c>
+      <c r="Y10">
+        <v>13</v>
+      </c>
+      <c r="Z10">
+        <v>26</v>
+      </c>
+      <c r="AA10">
+        <v>75</v>
+      </c>
+      <c r="AB10">
+        <v>9.4</v>
+      </c>
+      <c r="AC10">
+        <v>7.6</v>
+      </c>
+      <c r="AD10">
+        <v>17</v>
+      </c>
+      <c r="AE10">
+        <v>50</v>
+      </c>
+      <c r="AF10">
+        <v>18.5</v>
+      </c>
+      <c r="AG10">
+        <v>14</v>
+      </c>
+      <c r="AH10">
+        <v>23</v>
+      </c>
+      <c r="AI10">
+        <v>70</v>
+      </c>
+      <c r="AJ10">
+        <v>42</v>
+      </c>
+      <c r="AK10">
+        <v>34</v>
+      </c>
+      <c r="AL10">
+        <v>55</v>
+      </c>
+      <c r="AM10">
+        <v>140</v>
+      </c>
+      <c r="AN10">
+        <v>30</v>
+      </c>
+      <c r="AO10">
+        <v>55</v>
+      </c>
+      <c r="AP10">
+        <v>4.1</v>
+      </c>
+      <c r="AQ10">
+        <v>4.1</v>
+      </c>
+      <c r="AR10">
+        <v>4.8</v>
+      </c>
+      <c r="AS10">
+        <v>5.5</v>
+      </c>
+      <c r="AT10">
+        <v>3.65</v>
+      </c>
+      <c r="AU10">
+        <v>3.35</v>
+      </c>
+      <c r="AV10">
+        <v>4.4</v>
+      </c>
+      <c r="AW10">
         <v>5.3</v>
       </c>
-      <c r="K10">
-        <v>5.8</v>
-      </c>
-      <c r="L10">
-        <v>1.22</v>
-      </c>
-      <c r="M10">
-        <v>1.04</v>
-      </c>
-      <c r="N10">
-        <v>4.8</v>
-      </c>
-      <c r="O10">
-        <v>1.23</v>
-      </c>
-      <c r="P10">
-        <v>2.3</v>
-      </c>
-      <c r="Q10">
-        <v>1.69</v>
-      </c>
-      <c r="R10">
-        <v>1.52</v>
-      </c>
-      <c r="S10">
-        <v>2.78</v>
-      </c>
-      <c r="T10">
-        <v>2.1</v>
-      </c>
-      <c r="U10">
-        <v>1.85</v>
-      </c>
-      <c r="V10">
-        <v>1.09</v>
-      </c>
-      <c r="W10">
-        <v>3.55</v>
-      </c>
-      <c r="X10">
-        <v>25</v>
-      </c>
-      <c r="Y10">
-        <v>40</v>
-      </c>
-      <c r="Z10">
-        <v>120</v>
-      </c>
-      <c r="AA10">
-        <v>460</v>
-      </c>
-      <c r="AB10">
-        <v>9</v>
-      </c>
-      <c r="AC10">
-        <v>12.5</v>
-      </c>
-      <c r="AD10">
-        <v>44</v>
-      </c>
-      <c r="AE10">
-        <v>200</v>
-      </c>
-      <c r="AF10">
-        <v>8.4</v>
-      </c>
-      <c r="AG10">
-        <v>11</v>
-      </c>
-      <c r="AH10">
-        <v>32</v>
-      </c>
-      <c r="AI10">
-        <v>160</v>
-      </c>
-      <c r="AJ10">
-        <v>11</v>
-      </c>
-      <c r="AK10">
-        <v>17.5</v>
-      </c>
-      <c r="AL10">
-        <v>46</v>
-      </c>
-      <c r="AM10">
-        <v>180</v>
-      </c>
-      <c r="AN10">
+      <c r="AX10">
+        <v>4.5</v>
+      </c>
+      <c r="AY10">
+        <v>4.2</v>
+      </c>
+      <c r="AZ10">
+        <v>4.7</v>
+      </c>
+      <c r="BA10">
         <v>5.5</v>
       </c>
-      <c r="AO10">
-        <v>270</v>
-      </c>
-      <c r="AP10">
-        <v>7.2</v>
-      </c>
-      <c r="AQ10">
-        <v>8.4</v>
-      </c>
-      <c r="AR10">
-        <v>9.4</v>
-      </c>
-      <c r="AS10">
-        <v>10</v>
-      </c>
-      <c r="AT10">
-        <v>8</v>
-      </c>
-      <c r="AU10">
-        <v>11</v>
-      </c>
-      <c r="AV10">
-        <v>8.6</v>
-      </c>
-      <c r="AW10">
-        <v>9.6</v>
-      </c>
-      <c r="AX10">
-        <v>7.4</v>
-      </c>
-      <c r="AY10">
-        <v>9.6</v>
-      </c>
-      <c r="AZ10">
-        <v>21</v>
-      </c>
-      <c r="BA10">
-        <v>9.6</v>
-      </c>
       <c r="BB10">
-        <v>9.6</v>
+        <v>5.2</v>
       </c>
       <c r="BC10">
-        <v>13</v>
+        <v>5.1</v>
       </c>
       <c r="BD10">
-        <v>8.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="BE10">
-        <v>9.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF10">
         <v>5</v>
       </c>
       <c r="BG10">
-        <v>9.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="BH10">
         <v>1000</v>
       </c>
       <c r="BI10">
+        <v>1.01</v>
+      </c>
+      <c r="BJ10">
+        <v>1000</v>
+      </c>
+      <c r="BK10">
+        <v>1.01</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.01</v>
+      </c>
+      <c r="BN10">
+        <v>1000</v>
+      </c>
+      <c r="BO10">
+        <v>1.01</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>1.01</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>1.01</v>
+      </c>
+      <c r="BT10">
+        <v>1000</v>
+      </c>
+      <c r="BU10">
+        <v>1.01</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>1.01</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>1.01</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11" t="s">
+        <v>115</v>
+      </c>
+      <c r="F11">
+        <v>2.76</v>
+      </c>
+      <c r="G11">
+        <v>3.25</v>
+      </c>
+      <c r="H11">
+        <v>2.74</v>
+      </c>
+      <c r="I11">
+        <v>3.2</v>
+      </c>
+      <c r="J11">
+        <v>2.88</v>
+      </c>
+      <c r="K11">
+        <v>3.6</v>
+      </c>
+      <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.1</v>
+      </c>
+      <c r="N11">
+        <v>2.7</v>
+      </c>
+      <c r="O11">
+        <v>1.44</v>
+      </c>
+      <c r="P11">
+        <v>1.56</v>
+      </c>
+      <c r="Q11">
+        <v>2.46</v>
+      </c>
+      <c r="R11">
+        <v>1.18</v>
+      </c>
+      <c r="S11">
+        <v>4.9</v>
+      </c>
+      <c r="T11">
+        <v>1.01</v>
+      </c>
+      <c r="U11">
+        <v>1.01</v>
+      </c>
+      <c r="V11">
+        <v>1.45</v>
+      </c>
+      <c r="W11">
+        <v>1.44</v>
+      </c>
+      <c r="X11">
+        <v>10.5</v>
+      </c>
+      <c r="Y11">
+        <v>10.5</v>
+      </c>
+      <c r="Z11">
+        <v>21</v>
+      </c>
+      <c r="AA11">
+        <v>60</v>
+      </c>
+      <c r="AB11">
+        <v>10.5</v>
+      </c>
+      <c r="AC11">
+        <v>7.4</v>
+      </c>
+      <c r="AD11">
+        <v>16</v>
+      </c>
+      <c r="AE11">
+        <v>50</v>
+      </c>
+      <c r="AF11">
+        <v>22</v>
+      </c>
+      <c r="AG11">
+        <v>16</v>
+      </c>
+      <c r="AH11">
+        <v>25</v>
+      </c>
+      <c r="AI11">
+        <v>75</v>
+      </c>
+      <c r="AJ11">
+        <v>60</v>
+      </c>
+      <c r="AK11">
+        <v>50</v>
+      </c>
+      <c r="AL11">
+        <v>75</v>
+      </c>
+      <c r="AM11">
+        <v>190</v>
+      </c>
+      <c r="AN11">
+        <v>60</v>
+      </c>
+      <c r="AO11">
+        <v>60</v>
+      </c>
+      <c r="AP11">
+        <v>7</v>
+      </c>
+      <c r="AQ11">
+        <v>6.8</v>
+      </c>
+      <c r="AR11">
+        <v>14</v>
+      </c>
+      <c r="AS11">
+        <v>38</v>
+      </c>
+      <c r="AT11">
+        <v>7</v>
+      </c>
+      <c r="AU11">
+        <v>5.6</v>
+      </c>
+      <c r="AV11">
+        <v>10.5</v>
+      </c>
+      <c r="AW11">
+        <v>30</v>
+      </c>
+      <c r="AX11">
+        <v>14</v>
+      </c>
+      <c r="AY11">
+        <v>10.5</v>
+      </c>
+      <c r="AZ11">
+        <v>16</v>
+      </c>
+      <c r="BA11">
+        <v>48</v>
+      </c>
+      <c r="BB11">
+        <v>40</v>
+      </c>
+      <c r="BC11">
+        <v>32</v>
+      </c>
+      <c r="BD11">
+        <v>48</v>
+      </c>
+      <c r="BE11">
+        <v>120</v>
+      </c>
+      <c r="BF11">
+        <v>38</v>
+      </c>
+      <c r="BG11">
+        <v>36</v>
+      </c>
+      <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
+        <v>1.01</v>
+      </c>
+      <c r="BJ11">
+        <v>1000</v>
+      </c>
+      <c r="BK11">
+        <v>1.01</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.01</v>
+      </c>
+      <c r="BN11">
+        <v>1000</v>
+      </c>
+      <c r="BO11">
+        <v>1.01</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
+        <v>1.01</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>1.01</v>
+      </c>
+      <c r="BT11">
+        <v>1000</v>
+      </c>
+      <c r="BU11">
+        <v>1.01</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>1.01</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11">
+        <v>1000</v>
+      </c>
+      <c r="CA11">
+        <v>1.01</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" t="s">
+        <v>116</v>
+      </c>
+      <c r="F12">
+        <v>1.36</v>
+      </c>
+      <c r="G12">
+        <v>1.39</v>
+      </c>
+      <c r="H12">
+        <v>10</v>
+      </c>
+      <c r="I12">
+        <v>11.5</v>
+      </c>
+      <c r="J12">
+        <v>5.4</v>
+      </c>
+      <c r="K12">
+        <v>5.8</v>
+      </c>
+      <c r="L12">
+        <v>1.22</v>
+      </c>
+      <c r="M12">
+        <v>1.05</v>
+      </c>
+      <c r="N12">
+        <v>4.8</v>
+      </c>
+      <c r="O12">
+        <v>1.23</v>
+      </c>
+      <c r="P12">
+        <v>2.32</v>
+      </c>
+      <c r="Q12">
+        <v>1.7</v>
+      </c>
+      <c r="R12">
+        <v>1.52</v>
+      </c>
+      <c r="S12">
+        <v>2.74</v>
+      </c>
+      <c r="T12">
+        <v>2.1</v>
+      </c>
+      <c r="U12">
+        <v>1.85</v>
+      </c>
+      <c r="V12">
+        <v>1.09</v>
+      </c>
+      <c r="W12">
+        <v>3.55</v>
+      </c>
+      <c r="X12">
+        <v>25</v>
+      </c>
+      <c r="Y12">
+        <v>40</v>
+      </c>
+      <c r="Z12">
+        <v>120</v>
+      </c>
+      <c r="AA12">
+        <v>460</v>
+      </c>
+      <c r="AB12">
+        <v>9</v>
+      </c>
+      <c r="AC12">
+        <v>12.5</v>
+      </c>
+      <c r="AD12">
+        <v>42</v>
+      </c>
+      <c r="AE12">
+        <v>200</v>
+      </c>
+      <c r="AF12">
+        <v>8.4</v>
+      </c>
+      <c r="AG12">
+        <v>11</v>
+      </c>
+      <c r="AH12">
+        <v>32</v>
+      </c>
+      <c r="AI12">
+        <v>160</v>
+      </c>
+      <c r="AJ12">
+        <v>11</v>
+      </c>
+      <c r="AK12">
+        <v>17.5</v>
+      </c>
+      <c r="AL12">
+        <v>46</v>
+      </c>
+      <c r="AM12">
+        <v>180</v>
+      </c>
+      <c r="AN12">
+        <v>5.5</v>
+      </c>
+      <c r="AO12">
+        <v>270</v>
+      </c>
+      <c r="AP12">
+        <v>7.6</v>
+      </c>
+      <c r="AQ12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR12">
+        <v>10</v>
+      </c>
+      <c r="AS12">
+        <v>10.5</v>
+      </c>
+      <c r="AT12">
+        <v>8</v>
+      </c>
+      <c r="AU12">
+        <v>11</v>
+      </c>
+      <c r="AV12">
+        <v>8.6</v>
+      </c>
+      <c r="AW12">
+        <v>10.5</v>
+      </c>
+      <c r="AX12">
+        <v>7.4</v>
+      </c>
+      <c r="AY12">
+        <v>9.6</v>
+      </c>
+      <c r="AZ12">
+        <v>21</v>
+      </c>
+      <c r="BA12">
+        <v>10</v>
+      </c>
+      <c r="BB12">
+        <v>9.6</v>
+      </c>
+      <c r="BC12">
+        <v>13</v>
+      </c>
+      <c r="BD12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE12">
+        <v>10</v>
+      </c>
+      <c r="BF12">
+        <v>5</v>
+      </c>
+      <c r="BG12">
+        <v>10.5</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
         <v>1.98</v>
       </c>
-      <c r="BJ10">
+      <c r="BJ12">
         <v>17</v>
       </c>
-      <c r="BK10">
+      <c r="BK12">
         <v>1.78</v>
       </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
         <v>1.98</v>
       </c>
-      <c r="BN10">
+      <c r="BN12">
         <v>5</v>
       </c>
-      <c r="BO10">
+      <c r="BO12">
         <v>2.72</v>
       </c>
-      <c r="BP10">
+      <c r="BP12">
         <v>10.5</v>
       </c>
-      <c r="BQ10">
+      <c r="BQ12">
         <v>5.1</v>
       </c>
-      <c r="BR10">
+      <c r="BR12">
         <v>34</v>
       </c>
-      <c r="BS10">
+      <c r="BS12">
         <v>1.87</v>
       </c>
-      <c r="BT10">
+      <c r="BT12">
         <v>19</v>
       </c>
-      <c r="BU10">
+      <c r="BU12">
         <v>1.8</v>
       </c>
-      <c r="BV10">
-        <v>1000</v>
-      </c>
-      <c r="BW10">
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
         <v>1.98</v>
       </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
         <v>1.98</v>
       </c>
-      <c r="BZ10">
+      <c r="BZ12">
         <v>17.5</v>
       </c>
-      <c r="CA10">
+      <c r="CA12">
         <v>1.78</v>
       </c>
-      <c r="CB10" t="s">
-        <v>113</v>
+      <c r="CB12" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -367,7 +367,7 @@
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-09-21 10:12:17</t>
+    <t>2026-09-21 12:23:53</t>
   </si>
 </sst>
 </file>
@@ -961,10 +961,10 @@
         <v>106</v>
       </c>
       <c r="F2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G2">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H2">
         <v>4</v>
@@ -976,49 +976,49 @@
         <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="M2">
         <v>1.15</v>
       </c>
       <c r="N2">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O2">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="P2">
         <v>1.47</v>
       </c>
       <c r="Q2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R2">
         <v>1.16</v>
       </c>
       <c r="S2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="T2">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U2">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V2">
         <v>1.31</v>
       </c>
       <c r="W2">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="X2">
         <v>7.6</v>
       </c>
       <c r="Y2">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z2">
         <v>27</v>
@@ -1033,13 +1033,13 @@
         <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE2">
         <v>80</v>
       </c>
       <c r="AF2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
@@ -1054,16 +1054,16 @@
         <v>34</v>
       </c>
       <c r="AK2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL2">
         <v>75</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO2">
         <v>140</v>
@@ -1078,7 +1078,7 @@
         <v>24</v>
       </c>
       <c r="AS2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT2">
         <v>6.2</v>
@@ -1093,7 +1093,7 @@
         <v>65</v>
       </c>
       <c r="AX2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY2">
         <v>11.5</v>
@@ -1105,16 +1105,16 @@
         <v>90</v>
       </c>
       <c r="BB2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD2">
         <v>65</v>
       </c>
       <c r="BE2">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="BF2">
         <v>30</v>
@@ -1126,61 +1126,61 @@
         <v>2.52</v>
       </c>
       <c r="BI2">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BJ2">
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BN2">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP2">
         <v>21</v>
       </c>
       <c r="BQ2">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BS2">
+        <v>13.5</v>
+      </c>
+      <c r="BT2">
+        <v>7.2</v>
+      </c>
+      <c r="BU2">
+        <v>6.4</v>
+      </c>
+      <c r="BV2">
+        <v>46</v>
+      </c>
+      <c r="BW2">
         <v>13</v>
       </c>
-      <c r="BT2">
-        <v>7.4</v>
-      </c>
-      <c r="BU2">
-        <v>5.1</v>
-      </c>
-      <c r="BV2">
-        <v>50</v>
-      </c>
-      <c r="BW2">
-        <v>12.5</v>
-      </c>
       <c r="BX2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BY2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BZ2">
         <v>60</v>
       </c>
       <c r="CA2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CB2" t="s">
         <v>117</v>
@@ -1206,13 +1206,13 @@
         <v>2.2</v>
       </c>
       <c r="G3">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H3">
         <v>3.95</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J3">
         <v>3.35</v>
@@ -1227,31 +1227,31 @@
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O3">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P3">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q3">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R3">
         <v>1.24</v>
       </c>
       <c r="S3">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T3">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U3">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V3">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
         <v>1.81</v>
@@ -1263,7 +1263,7 @@
         <v>11.5</v>
       </c>
       <c r="Z3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AA3">
         <v>95</v>
@@ -1284,52 +1284,52 @@
         <v>12.5</v>
       </c>
       <c r="AG3">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI3">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AJ3">
         <v>30</v>
       </c>
       <c r="AK3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL3">
         <v>55</v>
       </c>
       <c r="AM3">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AN3">
         <v>25</v>
       </c>
       <c r="AO3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ3">
         <v>10.5</v>
       </c>
       <c r="AR3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS3">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AT3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU3">
         <v>7.2</v>
       </c>
       <c r="AV3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW3">
         <v>50</v>
@@ -1338,13 +1338,13 @@
         <v>11.5</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ3">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA3">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BB3">
         <v>25</v>
@@ -1353,52 +1353,52 @@
         <v>26</v>
       </c>
       <c r="BD3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BE3">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="BF3">
         <v>22</v>
       </c>
       <c r="BG3">
-        <v>14.5</v>
+        <v>50</v>
       </c>
       <c r="BH3">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="BI3">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="BJ3">
         <v>11</v>
       </c>
       <c r="BK3">
+        <v>9.4</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BN3">
+        <v>5.4</v>
+      </c>
+      <c r="BO3">
+        <v>4.3</v>
+      </c>
+      <c r="BP3">
+        <v>21</v>
+      </c>
+      <c r="BQ3">
         <v>6</v>
       </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>12.5</v>
-      </c>
-      <c r="BN3">
-        <v>4.8</v>
-      </c>
-      <c r="BO3">
-        <v>4.4</v>
-      </c>
-      <c r="BP3">
-        <v>17.5</v>
-      </c>
-      <c r="BQ3">
-        <v>7.6</v>
-      </c>
       <c r="BR3">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BS3">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BT3">
         <v>8</v>
@@ -1407,22 +1407,22 @@
         <v>6.2</v>
       </c>
       <c r="BV3">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BW3">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BX3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BY3">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA3">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="CB3" t="s">
         <v>117</v>
@@ -1454,10 +1454,10 @@
         <v>5.1</v>
       </c>
       <c r="I4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J4">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K4">
         <v>3.85</v>
@@ -1469,37 +1469,37 @@
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O4">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P4">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q4">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T4">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="U4">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V4">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W4">
         <v>2.14</v>
       </c>
       <c r="X4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y4">
         <v>18</v>
@@ -1535,13 +1535,13 @@
         <v>110</v>
       </c>
       <c r="AJ4">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AK4">
         <v>22</v>
       </c>
       <c r="AL4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM4">
         <v>170</v>
@@ -1550,22 +1550,22 @@
         <v>15.5</v>
       </c>
       <c r="AO4">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP4">
         <v>10.5</v>
       </c>
       <c r="AQ4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS4">
         <v>90</v>
       </c>
       <c r="AT4">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU4">
         <v>7.6</v>
@@ -1574,7 +1574,7 @@
         <v>18</v>
       </c>
       <c r="AW4">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AX4">
         <v>8.800000000000001</v>
@@ -1586,7 +1586,7 @@
         <v>18.5</v>
       </c>
       <c r="BA4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB4">
         <v>16.5</v>
@@ -1595,34 +1595,34 @@
         <v>18</v>
       </c>
       <c r="BD4">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BE4">
         <v>100</v>
       </c>
       <c r="BF4">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BH4">
         <v>3.5</v>
       </c>
       <c r="BI4">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BJ4">
         <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN4">
         <v>4.4</v>
@@ -1631,40 +1631,40 @@
         <v>3.75</v>
       </c>
       <c r="BP4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ4">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="BR4">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BS4">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT4">
         <v>9</v>
       </c>
       <c r="BU4">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BV4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BW4">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BX4">
         <v>75</v>
       </c>
       <c r="BY4">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ4">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="CA4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB4" t="s">
         <v>117</v>
@@ -1687,22 +1687,22 @@
         <v>109</v>
       </c>
       <c r="F5">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="G5">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H5">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I5">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="J5">
         <v>3.25</v>
       </c>
       <c r="K5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L5">
         <v>1.43</v>
@@ -1732,43 +1732,43 @@
         <v>1.65</v>
       </c>
       <c r="U5">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V5">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W5">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X5">
         <v>16</v>
       </c>
       <c r="Y5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z5">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA5">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC5">
         <v>9.4</v>
       </c>
       <c r="AD5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE5">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AG5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH5">
         <v>22</v>
@@ -1777,76 +1777,76 @@
         <v>55</v>
       </c>
       <c r="AJ5">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AK5">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AL5">
         <v>60</v>
       </c>
       <c r="AM5">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN5">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AO5">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AP5">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AQ5">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AR5">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AS5">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AT5">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AU5">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AV5">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AW5">
-        <v>19</v>
+        <v>3.9</v>
       </c>
       <c r="AX5">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AY5">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="AZ5">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="BA5">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BB5">
-        <v>24</v>
+        <v>4.3</v>
       </c>
       <c r="BC5">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BD5">
-        <v>23</v>
+        <v>4.3</v>
       </c>
       <c r="BE5">
         <v>4.2</v>
       </c>
       <c r="BF5">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BG5">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BH5">
         <v>3.8</v>
@@ -1858,7 +1858,7 @@
         <v>11.5</v>
       </c>
       <c r="BK5">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -1867,46 +1867,46 @@
         <v>4.9</v>
       </c>
       <c r="BN5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BO5">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BP5">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BQ5">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BR5">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS5">
+        <v>4.5</v>
+      </c>
+      <c r="BT5">
+        <v>6.4</v>
+      </c>
+      <c r="BU5">
+        <v>2.96</v>
+      </c>
+      <c r="BV5">
+        <v>23</v>
+      </c>
+      <c r="BW5">
         <v>4.4</v>
       </c>
-      <c r="BT5">
-        <v>6.8</v>
-      </c>
-      <c r="BU5">
-        <v>4.4</v>
-      </c>
-      <c r="BV5">
-        <v>25</v>
-      </c>
-      <c r="BW5">
-        <v>4.1</v>
-      </c>
       <c r="BX5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BZ5">
         <v>36</v>
       </c>
       <c r="CA5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="CB5" t="s">
         <v>117</v>
@@ -1929,166 +1929,166 @@
         <v>110</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="G6">
-        <v>110</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H6">
+        <v>1.54</v>
+      </c>
+      <c r="I6">
+        <v>1.67</v>
+      </c>
+      <c r="J6">
+        <v>3.95</v>
+      </c>
+      <c r="K6">
+        <v>4.7</v>
+      </c>
+      <c r="L6">
+        <v>1.01</v>
+      </c>
+      <c r="M6">
+        <v>1.06</v>
+      </c>
+      <c r="N6">
+        <v>3.65</v>
+      </c>
+      <c r="O6">
         <v>1.3</v>
       </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>950</v>
-      </c>
-      <c r="L6">
-        <v>1.01</v>
-      </c>
-      <c r="M6">
-        <v>1.01</v>
-      </c>
-      <c r="N6">
-        <v>1.3</v>
-      </c>
-      <c r="O6">
-        <v>1.28</v>
-      </c>
       <c r="P6">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="Q6">
-        <v>1.28</v>
+        <v>1.86</v>
       </c>
       <c r="R6">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="S6">
-        <v>1.3</v>
+        <v>2.96</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>2.48</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP6">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AQ6">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AR6">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AT6">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AU6">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AV6">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AX6">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AY6">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AZ6">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BA6">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BE6">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2171,28 +2171,28 @@
         <v>111</v>
       </c>
       <c r="F7">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="G7">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="H7">
         <v>3.1</v>
       </c>
       <c r="I7">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="J7">
         <v>2.78</v>
       </c>
       <c r="K7">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L7">
         <v>1.56</v>
       </c>
       <c r="M7">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="N7">
         <v>2.34</v>
@@ -2201,7 +2201,7 @@
         <v>1.64</v>
       </c>
       <c r="P7">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q7">
         <v>2.94</v>
@@ -2219,40 +2219,40 @@
         <v>1.7</v>
       </c>
       <c r="V7">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W7">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="X7">
         <v>7.4</v>
       </c>
       <c r="Y7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AA7">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AB7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC7">
         <v>7</v>
       </c>
       <c r="AD7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF7">
         <v>18</v>
       </c>
       <c r="AG7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH7">
         <v>26</v>
@@ -2261,10 +2261,10 @@
         <v>110</v>
       </c>
       <c r="AJ7">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK7">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AL7">
         <v>100</v>
@@ -2273,25 +2273,25 @@
         <v>270</v>
       </c>
       <c r="AN7">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO7">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP7">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AQ7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR7">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS7">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AT7">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU7">
         <v>6</v>
@@ -2300,13 +2300,13 @@
         <v>11.5</v>
       </c>
       <c r="AW7">
-        <v>9.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AX7">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AY7">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7">
         <v>20</v>
@@ -2330,7 +2330,7 @@
         <v>9</v>
       </c>
       <c r="BG7">
-        <v>9.199999999999999</v>
+        <v>60</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2416,7 +2416,7 @@
         <v>1.62</v>
       </c>
       <c r="G8">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H8">
         <v>6</v>
@@ -2434,91 +2434,91 @@
         <v>1.46</v>
       </c>
       <c r="M8">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N8">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="O8">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P8">
         <v>1.54</v>
       </c>
       <c r="Q8">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="R8">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="S8">
-        <v>2.96</v>
+        <v>1.02</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="V8">
         <v>1.13</v>
       </c>
       <c r="W8">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y8">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="Z8">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AF8">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL8">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AN8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AP8">
         <v>1.03</v>
@@ -2569,10 +2569,10 @@
         <v>1.03</v>
       </c>
       <c r="BF8">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BG8">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2658,13 +2658,13 @@
         <v>2.7</v>
       </c>
       <c r="G9">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H9">
         <v>2.82</v>
       </c>
       <c r="I9">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J9">
         <v>2.9</v>
@@ -2679,7 +2679,7 @@
         <v>1.11</v>
       </c>
       <c r="N9">
-        <v>2.42</v>
+        <v>2.68</v>
       </c>
       <c r="O9">
         <v>1.48</v>
@@ -2688,25 +2688,25 @@
         <v>1.56</v>
       </c>
       <c r="Q9">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R9">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="S9">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="T9">
         <v>1.98</v>
       </c>
       <c r="U9">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="V9">
         <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X9">
         <v>11.5</v>
@@ -2721,7 +2721,7 @@
         <v>70</v>
       </c>
       <c r="AB9">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AC9">
         <v>7.4</v>
@@ -2742,7 +2742,7 @@
         <v>22</v>
       </c>
       <c r="AI9">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ9">
         <v>60</v>
@@ -2751,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="AL9">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AM9">
         <v>190</v>
@@ -2766,52 +2766,52 @@
         <v>6.8</v>
       </c>
       <c r="AQ9">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AR9">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AS9">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AU9">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AV9">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW9">
+        <v>32</v>
+      </c>
+      <c r="AX9">
+        <v>15</v>
+      </c>
+      <c r="AY9">
+        <v>11</v>
+      </c>
+      <c r="AZ9">
+        <v>18</v>
+      </c>
+      <c r="BA9">
+        <v>1.01</v>
+      </c>
+      <c r="BB9">
+        <v>36</v>
+      </c>
+      <c r="BC9">
         <v>30</v>
       </c>
-      <c r="AX9">
-        <v>13</v>
-      </c>
-      <c r="AY9">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ9">
-        <v>15</v>
-      </c>
-      <c r="BA9">
-        <v>46</v>
-      </c>
-      <c r="BB9">
+      <c r="BD9">
+        <v>1.03</v>
+      </c>
+      <c r="BE9">
+        <v>1.02</v>
+      </c>
+      <c r="BF9">
         <v>34</v>
-      </c>
-      <c r="BC9">
-        <v>29</v>
-      </c>
-      <c r="BD9">
-        <v>44</v>
-      </c>
-      <c r="BE9">
-        <v>110</v>
-      </c>
-      <c r="BF9">
-        <v>32</v>
       </c>
       <c r="BG9">
         <v>36</v>
@@ -2897,13 +2897,13 @@
         <v>114</v>
       </c>
       <c r="F10">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="G10">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="H10">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I10">
         <v>3.4</v>
@@ -2930,43 +2930,43 @@
         <v>1.71</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="R10">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S10">
         <v>4.2</v>
       </c>
       <c r="T10">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U10">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V10">
         <v>1.41</v>
       </c>
       <c r="W10">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="X10">
         <v>13.5</v>
       </c>
       <c r="Y10">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z10">
         <v>26</v>
       </c>
       <c r="AA10">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB10">
         <v>9.4</v>
       </c>
       <c r="AC10">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD10">
         <v>17</v>
@@ -2975,7 +2975,7 @@
         <v>50</v>
       </c>
       <c r="AF10">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AG10">
         <v>14</v>
@@ -3008,7 +3008,7 @@
         <v>4.1</v>
       </c>
       <c r="AQ10">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AR10">
         <v>4.8</v>
@@ -3020,7 +3020,7 @@
         <v>3.65</v>
       </c>
       <c r="AU10">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AV10">
         <v>4.4</v>
@@ -3029,7 +3029,7 @@
         <v>5.3</v>
       </c>
       <c r="AX10">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AY10">
         <v>4.2</v>
@@ -3139,67 +3139,67 @@
         <v>115</v>
       </c>
       <c r="F11">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="G11">
         <v>3.25</v>
       </c>
       <c r="H11">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I11">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J11">
         <v>2.88</v>
       </c>
       <c r="K11">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N11">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O11">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="P11">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q11">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R11">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V11">
+        <v>1.46</v>
+      </c>
+      <c r="W11">
         <v>1.45</v>
-      </c>
-      <c r="W11">
-        <v>1.44</v>
       </c>
       <c r="X11">
         <v>10.5</v>
       </c>
       <c r="Y11">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z11">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA11">
         <v>60</v>
@@ -3208,13 +3208,13 @@
         <v>10.5</v>
       </c>
       <c r="AC11">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE11">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF11">
         <v>22</v>
@@ -3229,7 +3229,7 @@
         <v>75</v>
       </c>
       <c r="AJ11">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK11">
         <v>50</v>
@@ -3256,19 +3256,19 @@
         <v>14</v>
       </c>
       <c r="AS11">
-        <v>38</v>
+        <v>5.2</v>
       </c>
       <c r="AT11">
         <v>7</v>
       </c>
       <c r="AU11">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AV11">
         <v>10.5</v>
       </c>
       <c r="AW11">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="AX11">
         <v>14</v>
@@ -3280,25 +3280,25 @@
         <v>16</v>
       </c>
       <c r="BA11">
-        <v>48</v>
+        <v>5.2</v>
       </c>
       <c r="BB11">
-        <v>40</v>
+        <v>5.2</v>
       </c>
       <c r="BC11">
-        <v>32</v>
+        <v>5.1</v>
       </c>
       <c r="BD11">
-        <v>48</v>
+        <v>5.2</v>
       </c>
       <c r="BE11">
-        <v>120</v>
+        <v>5.5</v>
       </c>
       <c r="BF11">
-        <v>38</v>
+        <v>5.2</v>
       </c>
       <c r="BG11">
-        <v>36</v>
+        <v>5.2</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3393,7 +3393,7 @@
         <v>11.5</v>
       </c>
       <c r="J12">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K12">
         <v>5.8</v>
@@ -3420,7 +3420,7 @@
         <v>1.52</v>
       </c>
       <c r="S12">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T12">
         <v>2.1</v>
@@ -3435,16 +3435,16 @@
         <v>3.55</v>
       </c>
       <c r="X12">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y12">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Z12">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA12">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AB12">
         <v>9</v>
@@ -3474,7 +3474,7 @@
         <v>11</v>
       </c>
       <c r="AK12">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL12">
         <v>46</v>
@@ -3489,16 +3489,16 @@
         <v>270</v>
       </c>
       <c r="AP12">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="AQ12">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR12">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AS12">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AT12">
         <v>8</v>
@@ -3507,10 +3507,10 @@
         <v>11</v>
       </c>
       <c r="AV12">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AW12">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AX12">
         <v>7.4</v>
@@ -3522,7 +3522,7 @@
         <v>21</v>
       </c>
       <c r="BA12">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BB12">
         <v>9.6</v>
@@ -3531,34 +3531,34 @@
         <v>13</v>
       </c>
       <c r="BD12">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BE12">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BF12">
         <v>5</v>
       </c>
       <c r="BG12">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH12">
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="BJ12">
         <v>17</v>
       </c>
       <c r="BK12">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="BN12">
         <v>5</v>
@@ -3573,13 +3573,13 @@
         <v>5.1</v>
       </c>
       <c r="BR12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS12">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BT12">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BU12">
         <v>1.8</v>
@@ -3588,19 +3588,19 @@
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="BZ12">
         <v>17.5</v>
       </c>
       <c r="CA12">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CB12" t="s">
         <v>117</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -367,7 +367,7 @@
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-09-21 12:23:53</t>
+    <t>2026-09-21 14:35:42</t>
   </si>
 </sst>
 </file>
@@ -961,16 +961,16 @@
         <v>106</v>
       </c>
       <c r="F2">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G2">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H2">
         <v>4</v>
       </c>
       <c r="I2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J2">
         <v>3.05</v>
@@ -988,16 +988,16 @@
         <v>2.44</v>
       </c>
       <c r="O2">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="P2">
         <v>1.47</v>
       </c>
       <c r="Q2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R2">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S2">
         <v>7</v>
@@ -1009,10 +1009,10 @@
         <v>1.68</v>
       </c>
       <c r="V2">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W2">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X2">
         <v>7.6</v>
@@ -1042,13 +1042,13 @@
         <v>12.5</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ2">
         <v>34</v>
@@ -1060,10 +1060,10 @@
         <v>75</v>
       </c>
       <c r="AM2">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AO2">
         <v>140</v>
@@ -1072,13 +1072,13 @@
         <v>7</v>
       </c>
       <c r="AQ2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AR2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS2">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AT2">
         <v>6.2</v>
@@ -1087,10 +1087,10 @@
         <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AX2">
         <v>11</v>
@@ -1105,7 +1105,7 @@
         <v>90</v>
       </c>
       <c r="BB2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BC2">
         <v>32</v>
@@ -1114,19 +1114,19 @@
         <v>65</v>
       </c>
       <c r="BE2">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="BF2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BG2">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="BH2">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BI2">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BJ2">
         <v>12.5</v>
@@ -1138,7 +1138,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BN2">
         <v>4.8</v>
@@ -1153,10 +1153,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BR2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BS2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BT2">
         <v>7.2</v>
@@ -1165,7 +1165,7 @@
         <v>6.4</v>
       </c>
       <c r="BV2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BW2">
         <v>13</v>
@@ -1174,13 +1174,13 @@
         <v>75</v>
       </c>
       <c r="BY2">
+        <v>15</v>
+      </c>
+      <c r="BZ2">
+        <v>75</v>
+      </c>
+      <c r="CA2">
         <v>14.5</v>
-      </c>
-      <c r="BZ2">
-        <v>60</v>
-      </c>
-      <c r="CA2">
-        <v>14</v>
       </c>
       <c r="CB2" t="s">
         <v>117</v>
@@ -1203,10 +1203,10 @@
         <v>107</v>
       </c>
       <c r="F3">
+        <v>2.18</v>
+      </c>
+      <c r="G3">
         <v>2.2</v>
-      </c>
-      <c r="G3">
-        <v>2.22</v>
       </c>
       <c r="H3">
         <v>3.95</v>
@@ -1218,7 +1218,7 @@
         <v>3.35</v>
       </c>
       <c r="K3">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L3">
         <v>1.53</v>
@@ -1227,19 +1227,19 @@
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O3">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="P3">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q3">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R3">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S3">
         <v>5</v>
@@ -1248,22 +1248,22 @@
         <v>2.1</v>
       </c>
       <c r="U3">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V3">
         <v>1.32</v>
       </c>
       <c r="W3">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X3">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA3">
         <v>95</v>
@@ -1275,25 +1275,25 @@
         <v>7.8</v>
       </c>
       <c r="AD3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF3">
         <v>12.5</v>
       </c>
       <c r="AG3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH3">
         <v>23</v>
       </c>
       <c r="AI3">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK3">
         <v>28</v>
@@ -1302,7 +1302,7 @@
         <v>55</v>
       </c>
       <c r="AM3">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN3">
         <v>25</v>
@@ -1317,10 +1317,10 @@
         <v>10.5</v>
       </c>
       <c r="AR3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS3">
-        <v>18.5</v>
+        <v>75</v>
       </c>
       <c r="AT3">
         <v>7</v>
@@ -1332,16 +1332,16 @@
         <v>15.5</v>
       </c>
       <c r="AW3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX3">
         <v>11.5</v>
       </c>
       <c r="AY3">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA3">
         <v>65</v>
@@ -1350,22 +1350,22 @@
         <v>25</v>
       </c>
       <c r="BC3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD3">
         <v>48</v>
       </c>
       <c r="BE3">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BF3">
         <v>22</v>
       </c>
       <c r="BG3">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="BH3">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BI3">
         <v>2.7</v>
@@ -1374,34 +1374,34 @@
         <v>11</v>
       </c>
       <c r="BK3">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BN3">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BO3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP3">
         <v>21</v>
       </c>
       <c r="BQ3">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BR3">
         <v>44</v>
       </c>
       <c r="BS3">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BT3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BU3">
         <v>6.2</v>
@@ -1410,19 +1410,19 @@
         <v>44</v>
       </c>
       <c r="BW3">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
         <v>65</v>
       </c>
       <c r="BY3">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3">
         <v>46</v>
       </c>
       <c r="CA3">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="CB3" t="s">
         <v>117</v>
@@ -1445,40 +1445,40 @@
         <v>108</v>
       </c>
       <c r="F4">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="G4">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H4">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I4">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J4">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K4">
         <v>3.85</v>
       </c>
       <c r="L4">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M4">
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O4">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P4">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q4">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R4">
         <v>1.3</v>
@@ -1487,25 +1487,25 @@
         <v>4</v>
       </c>
       <c r="T4">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U4">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V4">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W4">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X4">
         <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA4">
         <v>170</v>
@@ -1514,22 +1514,22 @@
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD4">
         <v>22</v>
       </c>
       <c r="AE4">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI4">
         <v>110</v>
@@ -1538,19 +1538,19 @@
         <v>19.5</v>
       </c>
       <c r="AK4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL4">
         <v>44</v>
       </c>
       <c r="AM4">
+        <v>160</v>
+      </c>
+      <c r="AN4">
+        <v>14.5</v>
+      </c>
+      <c r="AO4">
         <v>170</v>
-      </c>
-      <c r="AN4">
-        <v>15.5</v>
-      </c>
-      <c r="AO4">
-        <v>140</v>
       </c>
       <c r="AP4">
         <v>10.5</v>
@@ -1574,7 +1574,7 @@
         <v>18</v>
       </c>
       <c r="AW4">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AX4">
         <v>8.800000000000001</v>
@@ -1586,13 +1586,13 @@
         <v>18.5</v>
       </c>
       <c r="BA4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD4">
         <v>29</v>
@@ -1607,22 +1607,22 @@
         <v>60</v>
       </c>
       <c r="BH4">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BI4">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ4">
         <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN4">
         <v>4.4</v>
@@ -1634,37 +1634,37 @@
         <v>13</v>
       </c>
       <c r="BQ4">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="BR4">
         <v>32</v>
       </c>
       <c r="BS4">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BT4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU4">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="BV4">
         <v>55</v>
       </c>
       <c r="BW4">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BX4">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BZ4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA4">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="CB4" t="s">
         <v>117</v>
@@ -1687,46 +1687,46 @@
         <v>109</v>
       </c>
       <c r="F5">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H5">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="I5">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J5">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K5">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L5">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M5">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O5">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q5">
         <v>2.06</v>
       </c>
       <c r="R5">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S5">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="T5">
         <v>1.65</v>
@@ -1735,43 +1735,43 @@
         <v>2.08</v>
       </c>
       <c r="V5">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X5">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z5">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AA5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB5">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC5">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE5">
         <v>34</v>
       </c>
       <c r="AF5">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AG5">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AH5">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AI5">
         <v>55</v>
@@ -1786,67 +1786,67 @@
         <v>60</v>
       </c>
       <c r="AM5">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AO5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP5">
-        <v>3.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5">
-        <v>3.35</v>
+        <v>8.4</v>
       </c>
       <c r="AR5">
-        <v>3.75</v>
+        <v>13</v>
       </c>
       <c r="AS5">
-        <v>4.2</v>
+        <v>17</v>
       </c>
       <c r="AT5">
-        <v>3.55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU5">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="AV5">
-        <v>3.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW5">
-        <v>3.9</v>
+        <v>13</v>
       </c>
       <c r="AX5">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="AY5">
-        <v>3.65</v>
+        <v>10</v>
       </c>
       <c r="AZ5">
-        <v>3.85</v>
+        <v>14</v>
       </c>
       <c r="BA5">
-        <v>4.3</v>
+        <v>30</v>
       </c>
       <c r="BB5">
-        <v>4.3</v>
+        <v>34</v>
       </c>
       <c r="BC5">
-        <v>4.1</v>
+        <v>15.5</v>
       </c>
       <c r="BD5">
-        <v>4.3</v>
+        <v>34</v>
       </c>
       <c r="BE5">
-        <v>4.2</v>
+        <v>48</v>
       </c>
       <c r="BF5">
-        <v>4.1</v>
+        <v>17.5</v>
       </c>
       <c r="BG5">
-        <v>4</v>
+        <v>16.5</v>
       </c>
       <c r="BH5">
         <v>3.8</v>
@@ -1858,19 +1858,19 @@
         <v>11.5</v>
       </c>
       <c r="BK5">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BN5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BO5">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BP5">
         <v>32</v>
@@ -1879,7 +1879,7 @@
         <v>4.4</v>
       </c>
       <c r="BR5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BS5">
         <v>4.5</v>
@@ -1888,19 +1888,19 @@
         <v>6.4</v>
       </c>
       <c r="BU5">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BV5">
         <v>23</v>
       </c>
       <c r="BW5">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BX5">
         <v>40</v>
       </c>
       <c r="BY5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BZ5">
         <v>36</v>
@@ -1929,10 +1929,10 @@
         <v>110</v>
       </c>
       <c r="F6">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="G6">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="H6">
         <v>1.54</v>
@@ -1980,7 +1980,7 @@
         <v>2.48</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X6">
         <v>19</v>
@@ -2171,16 +2171,16 @@
         <v>111</v>
       </c>
       <c r="F7">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G7">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="H7">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I7">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J7">
         <v>2.78</v>
@@ -2189,10 +2189,10 @@
         <v>3.05</v>
       </c>
       <c r="L7">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="M7">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="N7">
         <v>2.34</v>
@@ -2204,7 +2204,7 @@
         <v>1.45</v>
       </c>
       <c r="Q7">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="R7">
         <v>1.15</v>
@@ -2216,28 +2216,28 @@
         <v>2.24</v>
       </c>
       <c r="U7">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V7">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X7">
         <v>7.4</v>
       </c>
       <c r="Y7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA7">
         <v>85</v>
       </c>
       <c r="AB7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC7">
         <v>7</v>
@@ -2249,19 +2249,19 @@
         <v>60</v>
       </c>
       <c r="AF7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH7">
         <v>26</v>
       </c>
       <c r="AI7">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ7">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK7">
         <v>48</v>
@@ -2270,16 +2270,16 @@
         <v>100</v>
       </c>
       <c r="AM7">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AN7">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO7">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AP7">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ7">
         <v>7.4</v>
@@ -2294,22 +2294,22 @@
         <v>6.6</v>
       </c>
       <c r="AU7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV7">
         <v>11.5</v>
       </c>
       <c r="AW7">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="AX7">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY7">
         <v>10.5</v>
       </c>
       <c r="AZ7">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA7">
         <v>1.03</v>
@@ -2330,13 +2330,13 @@
         <v>9</v>
       </c>
       <c r="BG7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BH7">
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
@@ -2413,16 +2413,16 @@
         <v>112</v>
       </c>
       <c r="F8">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G8">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I8">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
         <v>3.45</v>
@@ -2437,7 +2437,7 @@
         <v>1.12</v>
       </c>
       <c r="N8">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="O8">
         <v>1.52</v>
@@ -2446,13 +2446,13 @@
         <v>1.54</v>
       </c>
       <c r="Q8">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="R8">
         <v>1.19</v>
       </c>
       <c r="S8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T8">
         <v>2.4</v>
@@ -2461,10 +2461,10 @@
         <v>1.6</v>
       </c>
       <c r="V8">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W8">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X8">
         <v>11</v>
@@ -2575,16 +2575,16 @@
         <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BJ8">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="BK8">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2593,16 +2593,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN8">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="BO8">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="BP8">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="BQ8">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BR8">
         <v>1000</v>
@@ -2611,10 +2611,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BT8">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="BU8">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BV8">
         <v>1000</v>
@@ -2629,7 +2629,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BZ8">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="CA8">
         <v>8.800000000000001</v>
@@ -2658,16 +2658,16 @@
         <v>2.7</v>
       </c>
       <c r="G9">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H9">
         <v>2.82</v>
       </c>
       <c r="I9">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J9">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K9">
         <v>3.65</v>
@@ -2688,7 +2688,7 @@
         <v>1.56</v>
       </c>
       <c r="Q9">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R9">
         <v>1.2</v>
@@ -2706,7 +2706,7 @@
         <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X9">
         <v>11.5</v>
@@ -2721,7 +2721,7 @@
         <v>70</v>
       </c>
       <c r="AB9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC9">
         <v>7.4</v>
@@ -2772,22 +2772,22 @@
         <v>16</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AT9">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AU9">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AV9">
         <v>11.5</v>
       </c>
       <c r="AW9">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AX9">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY9">
         <v>11</v>
@@ -2796,25 +2796,25 @@
         <v>18</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BB9">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BC9">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="BE9">
-        <v>1.02</v>
+        <v>6</v>
       </c>
       <c r="BF9">
         <v>34</v>
       </c>
       <c r="BG9">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -2912,16 +2912,16 @@
         <v>3.15</v>
       </c>
       <c r="K10">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M10">
         <v>1.09</v>
       </c>
       <c r="N10">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O10">
         <v>1.41</v>
@@ -2954,7 +2954,7 @@
         <v>13.5</v>
       </c>
       <c r="Y10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z10">
         <v>26</v>
@@ -3005,118 +3005,118 @@
         <v>55</v>
       </c>
       <c r="AP10">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ10">
         <v>3.95</v>
       </c>
       <c r="AR10">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS10">
+        <v>5.6</v>
+      </c>
+      <c r="AT10">
+        <v>3.7</v>
+      </c>
+      <c r="AU10">
+        <v>5.7</v>
+      </c>
+      <c r="AV10">
+        <v>4.5</v>
+      </c>
+      <c r="AW10">
         <v>5.5</v>
       </c>
-      <c r="AT10">
-        <v>3.65</v>
-      </c>
-      <c r="AU10">
-        <v>3.55</v>
-      </c>
-      <c r="AV10">
+      <c r="AX10">
         <v>4.4</v>
-      </c>
-      <c r="AW10">
-        <v>5.3</v>
-      </c>
-      <c r="AX10">
-        <v>4.3</v>
       </c>
       <c r="AY10">
         <v>4.2</v>
       </c>
       <c r="AZ10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA10">
+        <v>5.6</v>
+      </c>
+      <c r="BB10">
+        <v>5.3</v>
+      </c>
+      <c r="BC10">
+        <v>5.2</v>
+      </c>
+      <c r="BD10">
         <v>5.5</v>
       </c>
-      <c r="BB10">
-        <v>5.2</v>
-      </c>
-      <c r="BC10">
+      <c r="BE10">
+        <v>5.9</v>
+      </c>
+      <c r="BF10">
         <v>5.1</v>
       </c>
-      <c r="BD10">
+      <c r="BG10">
+        <v>5.5</v>
+      </c>
+      <c r="BH10">
+        <v>3.1</v>
+      </c>
+      <c r="BI10">
+        <v>2.54</v>
+      </c>
+      <c r="BJ10">
+        <v>10.5</v>
+      </c>
+      <c r="BK10">
+        <v>6</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>13</v>
+      </c>
+      <c r="BN10">
         <v>5.4</v>
       </c>
-      <c r="BE10">
-        <v>5.7</v>
-      </c>
-      <c r="BF10">
-        <v>5</v>
-      </c>
-      <c r="BG10">
-        <v>5.4</v>
-      </c>
-      <c r="BH10">
-        <v>1000</v>
-      </c>
-      <c r="BI10">
-        <v>1.01</v>
-      </c>
-      <c r="BJ10">
-        <v>1000</v>
-      </c>
-      <c r="BK10">
-        <v>1.01</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>1.01</v>
-      </c>
-      <c r="BN10">
-        <v>1000</v>
-      </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB10" t="s">
         <v>117</v>
@@ -3139,13 +3139,13 @@
         <v>115</v>
       </c>
       <c r="F11">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="G11">
         <v>3.25</v>
       </c>
       <c r="H11">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I11">
         <v>3.15</v>
@@ -3166,10 +3166,10 @@
         <v>2.68</v>
       </c>
       <c r="O11">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P11">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q11">
         <v>2.48</v>
@@ -3181,10 +3181,10 @@
         <v>5</v>
       </c>
       <c r="T11">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U11">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="V11">
         <v>1.46</v>
@@ -3250,10 +3250,10 @@
         <v>7</v>
       </c>
       <c r="AQ11">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="AR11">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS11">
         <v>5.2</v>
@@ -3262,10 +3262,10 @@
         <v>7</v>
       </c>
       <c r="AU11">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AV11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW11">
         <v>5</v>
@@ -3393,13 +3393,13 @@
         <v>11.5</v>
       </c>
       <c r="J12">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K12">
         <v>5.8</v>
       </c>
       <c r="L12">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="M12">
         <v>1.05</v>
@@ -3408,7 +3408,7 @@
         <v>4.8</v>
       </c>
       <c r="O12">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P12">
         <v>2.32</v>
@@ -3435,7 +3435,7 @@
         <v>3.55</v>
       </c>
       <c r="X12">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y12">
         <v>36</v>
@@ -3489,16 +3489,16 @@
         <v>270</v>
       </c>
       <c r="AP12">
-        <v>18</v>
+        <v>8.4</v>
       </c>
       <c r="AQ12">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT12">
         <v>8</v>
@@ -3522,7 +3522,7 @@
         <v>21</v>
       </c>
       <c r="BA12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BB12">
         <v>9.6</v>
@@ -3531,76 +3531,76 @@
         <v>13</v>
       </c>
       <c r="BD12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF12">
         <v>5</v>
       </c>
       <c r="BG12">
+        <v>13.5</v>
+      </c>
+      <c r="BH12">
+        <v>4.1</v>
+      </c>
+      <c r="BI12">
+        <v>3.3</v>
+      </c>
+      <c r="BJ12">
         <v>12.5</v>
       </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>1.99</v>
-      </c>
-      <c r="BJ12">
-        <v>17</v>
-      </c>
       <c r="BK12">
-        <v>1.79</v>
+        <v>9.4</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.99</v>
+        <v>14</v>
       </c>
       <c r="BN12">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="BO12">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="BP12">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="BQ12">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BR12">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.88</v>
+        <v>9.4</v>
       </c>
       <c r="BT12">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="BU12">
-        <v>1.8</v>
+        <v>7.4</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.99</v>
+        <v>13.5</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.99</v>
+        <v>13</v>
       </c>
       <c r="BZ12">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA12">
-        <v>1.79</v>
+        <v>9.6</v>
       </c>
       <c r="CB12" t="s">
         <v>117</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="121">
   <si>
     <t>League</t>
   </si>
@@ -292,6 +292,9 @@
     <t>16:00:00</t>
   </si>
   <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
     <t>19:00:00</t>
   </si>
   <si>
@@ -319,6 +322,9 @@
     <t>US Biskra</t>
   </si>
   <si>
+    <t>ASA Targu Mures</t>
+  </si>
+  <si>
     <t>MC Alger</t>
   </si>
   <si>
@@ -352,6 +358,9 @@
     <t>JS Saoura</t>
   </si>
   <si>
+    <t>CS FC Dinamo Bucuresti</t>
+  </si>
+  <si>
     <t>MC Oran</t>
   </si>
   <si>
@@ -367,7 +376,7 @@
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-09-21 14:35:42</t>
+    <t>2026-09-21 16:47:36</t>
   </si>
 </sst>
 </file>
@@ -699,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -955,10 +964,10 @@
         <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F2">
         <v>2.34</v>
@@ -970,13 +979,13 @@
         <v>4</v>
       </c>
       <c r="I2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
         <v>3.05</v>
-      </c>
-      <c r="K2">
-        <v>3.1</v>
       </c>
       <c r="L2">
         <v>1.69</v>
@@ -988,7 +997,7 @@
         <v>2.44</v>
       </c>
       <c r="O2">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="P2">
         <v>1.47</v>
@@ -1000,16 +1009,16 @@
         <v>1.15</v>
       </c>
       <c r="S2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="T2">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U2">
         <v>1.68</v>
       </c>
       <c r="V2">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W2">
         <v>1.73</v>
@@ -1030,7 +1039,7 @@
         <v>6.6</v>
       </c>
       <c r="AC2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD2">
         <v>20</v>
@@ -1042,10 +1051,10 @@
         <v>12.5</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI2">
         <v>130</v>
@@ -1063,7 +1072,7 @@
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO2">
         <v>140</v>
@@ -1078,7 +1087,7 @@
         <v>23</v>
       </c>
       <c r="AS2">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AT2">
         <v>6.2</v>
@@ -1090,7 +1099,7 @@
         <v>17</v>
       </c>
       <c r="AW2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AX2">
         <v>11</v>
@@ -1105,7 +1114,7 @@
         <v>90</v>
       </c>
       <c r="BB2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC2">
         <v>32</v>
@@ -1114,7 +1123,7 @@
         <v>65</v>
       </c>
       <c r="BE2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BF2">
         <v>36</v>
@@ -1126,13 +1135,13 @@
         <v>2.5</v>
       </c>
       <c r="BI2">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BJ2">
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1150,7 +1159,7 @@
         <v>21</v>
       </c>
       <c r="BQ2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR2">
         <v>60</v>
@@ -1165,10 +1174,10 @@
         <v>6.4</v>
       </c>
       <c r="BV2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX2">
         <v>75</v>
@@ -1177,13 +1186,13 @@
         <v>15</v>
       </c>
       <c r="BZ2">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="CA2">
         <v>14.5</v>
       </c>
       <c r="CB2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1197,22 +1206,22 @@
         <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G3">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H3">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J3">
         <v>3.35</v>
@@ -1221,7 +1230,7 @@
         <v>3.4</v>
       </c>
       <c r="L3">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M3">
         <v>1.11</v>
@@ -1236,28 +1245,28 @@
         <v>1.67</v>
       </c>
       <c r="Q3">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="R3">
         <v>1.23</v>
       </c>
       <c r="S3">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T3">
         <v>2.1</v>
       </c>
       <c r="U3">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="X3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Y3">
         <v>11</v>
@@ -1272,13 +1281,13 @@
         <v>7.6</v>
       </c>
       <c r="AC3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF3">
         <v>12.5</v>
@@ -1296,7 +1305,7 @@
         <v>29</v>
       </c>
       <c r="AK3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AL3">
         <v>55</v>
@@ -1305,13 +1314,13 @@
         <v>150</v>
       </c>
       <c r="AN3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO3">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AP3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ3">
         <v>10.5</v>
@@ -1320,7 +1329,7 @@
         <v>24</v>
       </c>
       <c r="AS3">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AT3">
         <v>7</v>
@@ -1332,13 +1341,13 @@
         <v>15.5</v>
       </c>
       <c r="AW3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX3">
         <v>11.5</v>
       </c>
       <c r="AY3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3">
         <v>21</v>
@@ -1347,7 +1356,7 @@
         <v>65</v>
       </c>
       <c r="BB3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC3">
         <v>27</v>
@@ -1356,52 +1365,52 @@
         <v>48</v>
       </c>
       <c r="BE3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BF3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BG3">
         <v>20</v>
       </c>
       <c r="BH3">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="BI3">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="BJ3">
         <v>11</v>
       </c>
       <c r="BK3">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BN3">
         <v>4.7</v>
       </c>
       <c r="BO3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP3">
         <v>21</v>
       </c>
       <c r="BQ3">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BR3">
         <v>44</v>
       </c>
       <c r="BS3">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BU3">
         <v>6.2</v>
@@ -1410,22 +1419,22 @@
         <v>44</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX3">
         <v>65</v>
       </c>
       <c r="BY3">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BZ3">
         <v>46</v>
       </c>
       <c r="CA3">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="CB3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1439,28 +1448,28 @@
         <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F4">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="G4">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I4">
         <v>5.7</v>
       </c>
       <c r="J4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L4">
         <v>1.45</v>
@@ -1469,37 +1478,37 @@
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O4">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P4">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Q4">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R4">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S4">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T4">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U4">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V4">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y4">
         <v>18.5</v>
@@ -1514,13 +1523,13 @@
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4">
         <v>22</v>
       </c>
       <c r="AE4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF4">
         <v>10.5</v>
@@ -1532,22 +1541,22 @@
         <v>22</v>
       </c>
       <c r="AI4">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK4">
         <v>21</v>
       </c>
       <c r="AL4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM4">
         <v>160</v>
       </c>
       <c r="AN4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO4">
         <v>170</v>
@@ -1556,7 +1565,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR4">
         <v>30</v>
@@ -1586,7 +1595,7 @@
         <v>18.5</v>
       </c>
       <c r="BA4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB4">
         <v>16</v>
@@ -1595,34 +1604,34 @@
         <v>17</v>
       </c>
       <c r="BD4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="BF4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG4">
         <v>60</v>
       </c>
       <c r="BH4">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI4">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ4">
         <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN4">
         <v>4.4</v>
@@ -1634,40 +1643,40 @@
         <v>13</v>
       </c>
       <c r="BQ4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR4">
         <v>32</v>
       </c>
       <c r="BS4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT4">
         <v>9.199999999999999</v>
       </c>
       <c r="BU4">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="BV4">
         <v>55</v>
       </c>
       <c r="BW4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ4">
         <v>27</v>
       </c>
       <c r="CA4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1681,235 +1690,235 @@
         <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="G5">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="H5">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="I5">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="J5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K5">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>1.44</v>
       </c>
       <c r="M5">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N5">
+        <v>3.5</v>
+      </c>
+      <c r="O5">
+        <v>1.34</v>
+      </c>
+      <c r="P5">
+        <v>1.84</v>
+      </c>
+      <c r="Q5">
+        <v>2</v>
+      </c>
+      <c r="R5">
+        <v>1.31</v>
+      </c>
+      <c r="S5">
         <v>3.6</v>
       </c>
-      <c r="O5">
-        <v>1.35</v>
-      </c>
-      <c r="P5">
-        <v>1.89</v>
-      </c>
-      <c r="Q5">
-        <v>2.06</v>
-      </c>
-      <c r="R5">
-        <v>1.33</v>
-      </c>
-      <c r="S5">
-        <v>3.85</v>
-      </c>
       <c r="T5">
-        <v>1.65</v>
+        <v>1.05</v>
       </c>
       <c r="U5">
         <v>2.08</v>
       </c>
       <c r="V5">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W5">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="X5">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Y5">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Z5">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AA5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AB5">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AC5">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD5">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AE5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG5">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH5">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ5">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK5">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AL5">
         <v>60</v>
       </c>
       <c r="AM5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AN5">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AO5">
         <v>28</v>
       </c>
       <c r="AP5">
-        <v>10.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ5">
-        <v>8.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR5">
-        <v>13</v>
+        <v>1.52</v>
       </c>
       <c r="AS5">
-        <v>17</v>
+        <v>1.58</v>
       </c>
       <c r="AT5">
-        <v>9.199999999999999</v>
+        <v>1.67</v>
       </c>
       <c r="AU5">
-        <v>5.8</v>
+        <v>1.67</v>
       </c>
       <c r="AV5">
-        <v>9.199999999999999</v>
+        <v>1.67</v>
       </c>
       <c r="AW5">
-        <v>13</v>
+        <v>1.57</v>
       </c>
       <c r="AX5">
-        <v>17</v>
+        <v>1.55</v>
       </c>
       <c r="AY5">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="AZ5">
-        <v>14</v>
+        <v>1.67</v>
       </c>
       <c r="BA5">
-        <v>30</v>
+        <v>1.59</v>
       </c>
       <c r="BB5">
-        <v>34</v>
+        <v>1.6</v>
       </c>
       <c r="BC5">
-        <v>15.5</v>
+        <v>1.58</v>
       </c>
       <c r="BD5">
-        <v>34</v>
+        <v>1.6</v>
       </c>
       <c r="BE5">
-        <v>48</v>
+        <v>1.61</v>
       </c>
       <c r="BF5">
-        <v>17.5</v>
+        <v>1.57</v>
       </c>
       <c r="BG5">
-        <v>16.5</v>
+        <v>1.55</v>
       </c>
       <c r="BH5">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>2.64</v>
+        <v>1.22</v>
       </c>
       <c r="BJ5">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>3.5</v>
+        <v>1.22</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.8</v>
+        <v>1.22</v>
       </c>
       <c r="BN5">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="BP5">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>4.4</v>
+        <v>1.16</v>
       </c>
       <c r="BR5">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>4.5</v>
+        <v>1.18</v>
       </c>
       <c r="BT5">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>2.98</v>
+        <v>1.22</v>
       </c>
       <c r="BV5">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>4.1</v>
+        <v>1.15</v>
       </c>
       <c r="BX5">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>4.4</v>
+        <v>1.18</v>
       </c>
       <c r="BZ5">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>4.4</v>
+        <v>1.17</v>
       </c>
       <c r="CB5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1923,25 +1932,25 @@
         <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F6">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="G6">
         <v>7.6</v>
       </c>
       <c r="H6">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I6">
         <v>1.67</v>
       </c>
       <c r="J6">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <v>4.7</v>
@@ -2040,7 +2049,7 @@
         <v>5.8</v>
       </c>
       <c r="AQ6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AR6">
         <v>4.5</v>
@@ -2082,7 +2091,7 @@
         <v>7.8</v>
       </c>
       <c r="BE6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF6">
         <v>7.8</v>
@@ -2151,7 +2160,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2165,25 +2174,25 @@
         <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F7">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G7">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="H7">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I7">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J7">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="K7">
         <v>3.05</v>
@@ -2192,37 +2201,37 @@
         <v>1.61</v>
       </c>
       <c r="M7">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N7">
         <v>2.34</v>
       </c>
       <c r="O7">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="P7">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q7">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="R7">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S7">
         <v>6.4</v>
       </c>
       <c r="T7">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U7">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W7">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X7">
         <v>7.4</v>
@@ -2282,10 +2291,10 @@
         <v>6.4</v>
       </c>
       <c r="AQ7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR7">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AS7">
         <v>1.03</v>
@@ -2297,7 +2306,7 @@
         <v>6.2</v>
       </c>
       <c r="AV7">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AW7">
         <v>1.03</v>
@@ -2306,7 +2315,7 @@
         <v>14.5</v>
       </c>
       <c r="AY7">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AZ7">
         <v>17</v>
@@ -2393,12 +2402,12 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
         <v>87</v>
@@ -2407,240 +2416,240 @@
         <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F8">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="G8">
-        <v>1.71</v>
+        <v>1.16</v>
       </c>
       <c r="H8">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="I8">
-        <v>7.8</v>
+        <v>38</v>
       </c>
       <c r="J8">
+        <v>7</v>
+      </c>
+      <c r="K8">
+        <v>13.5</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.01</v>
+      </c>
+      <c r="N8">
         <v>3.45</v>
       </c>
-      <c r="K8">
-        <v>3.9</v>
-      </c>
-      <c r="L8">
-        <v>1.46</v>
-      </c>
-      <c r="M8">
-        <v>1.12</v>
-      </c>
-      <c r="N8">
-        <v>2.56</v>
-      </c>
       <c r="O8">
-        <v>1.52</v>
+        <v>1.1</v>
       </c>
       <c r="P8">
-        <v>1.54</v>
+        <v>3.1</v>
       </c>
       <c r="Q8">
-        <v>2.56</v>
+        <v>1.28</v>
       </c>
       <c r="R8">
-        <v>1.19</v>
+        <v>2</v>
       </c>
       <c r="S8">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="T8">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="U8">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V8">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="W8">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="X8">
+        <v>60</v>
+      </c>
+      <c r="Y8">
+        <v>120</v>
+      </c>
+      <c r="Z8">
+        <v>360</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>17</v>
+      </c>
+      <c r="AC8">
+        <v>32</v>
+      </c>
+      <c r="AD8">
+        <v>120</v>
+      </c>
+      <c r="AE8">
+        <v>570</v>
+      </c>
+      <c r="AF8">
         <v>11</v>
       </c>
-      <c r="Y8">
+      <c r="AG8">
+        <v>18</v>
+      </c>
+      <c r="AH8">
+        <v>60</v>
+      </c>
+      <c r="AI8">
+        <v>350</v>
+      </c>
+      <c r="AJ8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK8">
         <v>17.5</v>
       </c>
-      <c r="Z8">
-        <v>80</v>
-      </c>
-      <c r="AA8">
-        <v>400</v>
-      </c>
-      <c r="AB8">
-        <v>6.8</v>
-      </c>
-      <c r="AC8">
-        <v>10.5</v>
-      </c>
-      <c r="AD8">
-        <v>40</v>
-      </c>
-      <c r="AE8">
-        <v>220</v>
-      </c>
-      <c r="AF8">
-        <v>8.4</v>
-      </c>
-      <c r="AG8">
-        <v>13.5</v>
-      </c>
-      <c r="AH8">
-        <v>40</v>
-      </c>
-      <c r="AI8">
-        <v>230</v>
-      </c>
-      <c r="AJ8">
-        <v>21</v>
-      </c>
-      <c r="AK8">
-        <v>29</v>
-      </c>
       <c r="AL8">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AM8">
-        <v>370</v>
+        <v>290</v>
       </c>
       <c r="AN8">
-        <v>21</v>
+        <v>2.64</v>
       </c>
       <c r="AO8">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>12.5</v>
+        <v>2.24</v>
       </c>
       <c r="BG8">
         <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
         <v>87</v>
@@ -2649,235 +2658,235 @@
         <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F9">
-        <v>2.7</v>
+        <v>1.64</v>
       </c>
       <c r="G9">
-        <v>3.05</v>
+        <v>1.71</v>
       </c>
       <c r="H9">
-        <v>2.82</v>
+        <v>7</v>
       </c>
       <c r="I9">
-        <v>3.25</v>
+        <v>7.8</v>
       </c>
       <c r="J9">
-        <v>2.92</v>
+        <v>3.45</v>
       </c>
       <c r="K9">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M9">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N9">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="O9">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="P9">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q9">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="R9">
         <v>1.2</v>
       </c>
       <c r="S9">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="T9">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="U9">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="W9">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="X9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y9">
+        <v>17.5</v>
+      </c>
+      <c r="Z9">
+        <v>75</v>
+      </c>
+      <c r="AA9">
+        <v>390</v>
+      </c>
+      <c r="AB9">
+        <v>5.9</v>
+      </c>
+      <c r="AC9">
+        <v>10.5</v>
+      </c>
+      <c r="AD9">
+        <v>38</v>
+      </c>
+      <c r="AE9">
+        <v>210</v>
+      </c>
+      <c r="AF9">
+        <v>8.4</v>
+      </c>
+      <c r="AG9">
+        <v>13.5</v>
+      </c>
+      <c r="AH9">
+        <v>40</v>
+      </c>
+      <c r="AI9">
+        <v>220</v>
+      </c>
+      <c r="AJ9">
+        <v>21</v>
+      </c>
+      <c r="AK9">
+        <v>29</v>
+      </c>
+      <c r="AL9">
+        <v>80</v>
+      </c>
+      <c r="AM9">
+        <v>360</v>
+      </c>
+      <c r="AN9">
+        <v>21</v>
+      </c>
+      <c r="AO9">
+        <v>430</v>
+      </c>
+      <c r="AP9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ9">
+        <v>12.5</v>
+      </c>
+      <c r="AR9">
+        <v>5.4</v>
+      </c>
+      <c r="AS9">
+        <v>5.7</v>
+      </c>
+      <c r="AT9">
+        <v>5.1</v>
+      </c>
+      <c r="AU9">
+        <v>7.6</v>
+      </c>
+      <c r="AV9">
+        <v>5</v>
+      </c>
+      <c r="AW9">
+        <v>5.7</v>
+      </c>
+      <c r="AX9">
+        <v>7.4</v>
+      </c>
+      <c r="AY9">
+        <v>4</v>
+      </c>
+      <c r="AZ9">
+        <v>5.1</v>
+      </c>
+      <c r="BA9">
+        <v>5.7</v>
+      </c>
+      <c r="BB9">
+        <v>4.5</v>
+      </c>
+      <c r="BC9">
+        <v>17</v>
+      </c>
+      <c r="BD9">
+        <v>5.4</v>
+      </c>
+      <c r="BE9">
+        <v>5.7</v>
+      </c>
+      <c r="BF9">
+        <v>12.5</v>
+      </c>
+      <c r="BG9">
+        <v>5.7</v>
+      </c>
+      <c r="BH9">
+        <v>2.82</v>
+      </c>
+      <c r="BI9">
+        <v>2.28</v>
+      </c>
+      <c r="BJ9">
+        <v>13.5</v>
+      </c>
+      <c r="BK9">
         <v>9.6</v>
       </c>
-      <c r="Z9">
-        <v>20</v>
-      </c>
-      <c r="AA9">
-        <v>70</v>
-      </c>
-      <c r="AB9">
-        <v>10.5</v>
-      </c>
-      <c r="AC9">
-        <v>7.4</v>
-      </c>
-      <c r="AD9">
-        <v>14.5</v>
-      </c>
-      <c r="AE9">
-        <v>55</v>
-      </c>
-      <c r="AF9">
-        <v>18.5</v>
-      </c>
-      <c r="AG9">
-        <v>14</v>
-      </c>
-      <c r="AH9">
-        <v>22</v>
-      </c>
-      <c r="AI9">
-        <v>95</v>
-      </c>
-      <c r="AJ9">
-        <v>60</v>
-      </c>
-      <c r="AK9">
-        <v>50</v>
-      </c>
-      <c r="AL9">
-        <v>95</v>
-      </c>
-      <c r="AM9">
-        <v>190</v>
-      </c>
-      <c r="AN9">
-        <v>60</v>
-      </c>
-      <c r="AO9">
-        <v>65</v>
-      </c>
-      <c r="AP9">
-        <v>6.8</v>
-      </c>
-      <c r="AQ9">
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN9">
+        <v>3.9</v>
+      </c>
+      <c r="BO9">
+        <v>3.05</v>
+      </c>
+      <c r="BP9">
+        <v>12.5</v>
+      </c>
+      <c r="BQ9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>28</v>
+      </c>
+      <c r="BT9">
+        <v>11</v>
+      </c>
+      <c r="BU9">
         <v>7.8</v>
       </c>
-      <c r="AR9">
-        <v>16</v>
-      </c>
-      <c r="AS9">
-        <v>32</v>
-      </c>
-      <c r="AT9">
-        <v>6.6</v>
-      </c>
-      <c r="AU9">
-        <v>5.4</v>
-      </c>
-      <c r="AV9">
-        <v>11.5</v>
-      </c>
-      <c r="AW9">
-        <v>26</v>
-      </c>
-      <c r="AX9">
-        <v>13</v>
-      </c>
-      <c r="AY9">
-        <v>11</v>
-      </c>
-      <c r="AZ9">
-        <v>18</v>
-      </c>
-      <c r="BA9">
-        <v>5.8</v>
-      </c>
-      <c r="BB9">
-        <v>29</v>
-      </c>
-      <c r="BC9">
-        <v>24</v>
-      </c>
-      <c r="BD9">
-        <v>38</v>
-      </c>
-      <c r="BE9">
-        <v>6</v>
-      </c>
-      <c r="BF9">
-        <v>34</v>
-      </c>
-      <c r="BG9">
-        <v>32</v>
-      </c>
-      <c r="BH9">
-        <v>1000</v>
-      </c>
-      <c r="BI9">
-        <v>1.01</v>
-      </c>
-      <c r="BJ9">
-        <v>1000</v>
-      </c>
-      <c r="BK9">
-        <v>1.01</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>1.01</v>
-      </c>
-      <c r="BN9">
-        <v>1000</v>
-      </c>
-      <c r="BO9">
-        <v>1.01</v>
-      </c>
-      <c r="BP9">
-        <v>1000</v>
-      </c>
-      <c r="BQ9">
-        <v>1.01</v>
-      </c>
-      <c r="BR9">
-        <v>1000</v>
-      </c>
-      <c r="BS9">
-        <v>1.01</v>
-      </c>
-      <c r="BT9">
-        <v>1000</v>
-      </c>
-      <c r="BU9">
-        <v>1.01</v>
-      </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2888,238 +2897,238 @@
         <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F10">
+        <v>2.7</v>
+      </c>
+      <c r="G10">
+        <v>3.05</v>
+      </c>
+      <c r="H10">
+        <v>2.82</v>
+      </c>
+      <c r="I10">
+        <v>3.25</v>
+      </c>
+      <c r="J10">
+        <v>2.9</v>
+      </c>
+      <c r="K10">
+        <v>3.55</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.11</v>
+      </c>
+      <c r="N10">
+        <v>2.68</v>
+      </c>
+      <c r="O10">
+        <v>1.48</v>
+      </c>
+      <c r="P10">
+        <v>1.56</v>
+      </c>
+      <c r="Q10">
         <v>2.44</v>
       </c>
-      <c r="G10">
-        <v>2.7</v>
-      </c>
-      <c r="H10">
-        <v>3.1</v>
-      </c>
-      <c r="I10">
-        <v>3.4</v>
-      </c>
-      <c r="J10">
-        <v>3.15</v>
-      </c>
-      <c r="K10">
-        <v>3.75</v>
-      </c>
-      <c r="L10">
-        <v>1.4</v>
-      </c>
-      <c r="M10">
-        <v>1.09</v>
-      </c>
-      <c r="N10">
-        <v>3.1</v>
-      </c>
-      <c r="O10">
-        <v>1.41</v>
-      </c>
-      <c r="P10">
-        <v>1.71</v>
-      </c>
-      <c r="Q10">
-        <v>2.18</v>
-      </c>
       <c r="R10">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="S10">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="T10">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="U10">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="V10">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W10">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="X10">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y10">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Z10">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AA10">
         <v>70</v>
       </c>
       <c r="AB10">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AC10">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AD10">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AE10">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF10">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AG10">
         <v>14</v>
       </c>
       <c r="AH10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI10">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="AJ10">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AK10">
+        <v>50</v>
+      </c>
+      <c r="AL10">
+        <v>95</v>
+      </c>
+      <c r="AM10">
+        <v>190</v>
+      </c>
+      <c r="AN10">
+        <v>60</v>
+      </c>
+      <c r="AO10">
+        <v>65</v>
+      </c>
+      <c r="AP10">
+        <v>6.8</v>
+      </c>
+      <c r="AQ10">
+        <v>7.8</v>
+      </c>
+      <c r="AR10">
+        <v>16</v>
+      </c>
+      <c r="AS10">
+        <v>32</v>
+      </c>
+      <c r="AT10">
+        <v>6.6</v>
+      </c>
+      <c r="AU10">
+        <v>6</v>
+      </c>
+      <c r="AV10">
+        <v>11.5</v>
+      </c>
+      <c r="AW10">
+        <v>26</v>
+      </c>
+      <c r="AX10">
+        <v>13</v>
+      </c>
+      <c r="AY10">
+        <v>11</v>
+      </c>
+      <c r="AZ10">
+        <v>18</v>
+      </c>
+      <c r="BA10">
+        <v>5.8</v>
+      </c>
+      <c r="BB10">
+        <v>29</v>
+      </c>
+      <c r="BC10">
+        <v>24</v>
+      </c>
+      <c r="BD10">
+        <v>38</v>
+      </c>
+      <c r="BE10">
+        <v>6</v>
+      </c>
+      <c r="BF10">
         <v>34</v>
       </c>
-      <c r="AL10">
-        <v>55</v>
-      </c>
-      <c r="AM10">
-        <v>140</v>
-      </c>
-      <c r="AN10">
-        <v>30</v>
-      </c>
-      <c r="AO10">
-        <v>55</v>
-      </c>
-      <c r="AP10">
-        <v>4.2</v>
-      </c>
-      <c r="AQ10">
-        <v>3.95</v>
-      </c>
-      <c r="AR10">
-        <v>4.9</v>
-      </c>
-      <c r="AS10">
-        <v>5.6</v>
-      </c>
-      <c r="AT10">
-        <v>3.7</v>
-      </c>
-      <c r="AU10">
-        <v>5.7</v>
-      </c>
-      <c r="AV10">
-        <v>4.5</v>
-      </c>
-      <c r="AW10">
-        <v>5.5</v>
-      </c>
-      <c r="AX10">
-        <v>4.4</v>
-      </c>
-      <c r="AY10">
-        <v>4.2</v>
-      </c>
-      <c r="AZ10">
-        <v>4.8</v>
-      </c>
-      <c r="BA10">
-        <v>5.6</v>
-      </c>
-      <c r="BB10">
-        <v>5.3</v>
-      </c>
-      <c r="BC10">
-        <v>5.2</v>
-      </c>
-      <c r="BD10">
-        <v>5.5</v>
-      </c>
-      <c r="BE10">
-        <v>5.9</v>
-      </c>
-      <c r="BF10">
-        <v>5.1</v>
-      </c>
       <c r="BG10">
-        <v>5.5</v>
+        <v>32</v>
       </c>
       <c r="BH10">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3130,243 +3139,243 @@
         <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F11">
-        <v>2.82</v>
+        <v>2.44</v>
       </c>
       <c r="G11">
-        <v>3.25</v>
+        <v>2.66</v>
       </c>
       <c r="H11">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="I11">
+        <v>3.4</v>
+      </c>
+      <c r="J11">
         <v>3.15</v>
       </c>
-      <c r="J11">
-        <v>2.88</v>
-      </c>
       <c r="K11">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M11">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="N11">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="O11">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="P11">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="Q11">
-        <v>2.48</v>
+        <v>2.18</v>
       </c>
       <c r="R11">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S11">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="T11">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="U11">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="V11">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W11">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="X11">
+        <v>13.5</v>
+      </c>
+      <c r="Y11">
+        <v>11</v>
+      </c>
+      <c r="Z11">
+        <v>26</v>
+      </c>
+      <c r="AA11">
+        <v>70</v>
+      </c>
+      <c r="AB11">
+        <v>9.4</v>
+      </c>
+      <c r="AC11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD11">
+        <v>17</v>
+      </c>
+      <c r="AE11">
+        <v>50</v>
+      </c>
+      <c r="AF11">
+        <v>16</v>
+      </c>
+      <c r="AG11">
+        <v>14</v>
+      </c>
+      <c r="AH11">
+        <v>23</v>
+      </c>
+      <c r="AI11">
+        <v>70</v>
+      </c>
+      <c r="AJ11">
+        <v>42</v>
+      </c>
+      <c r="AK11">
+        <v>34</v>
+      </c>
+      <c r="AL11">
+        <v>55</v>
+      </c>
+      <c r="AM11">
+        <v>140</v>
+      </c>
+      <c r="AN11">
+        <v>30</v>
+      </c>
+      <c r="AO11">
+        <v>55</v>
+      </c>
+      <c r="AP11">
+        <v>4.2</v>
+      </c>
+      <c r="AQ11">
+        <v>3.95</v>
+      </c>
+      <c r="AR11">
+        <v>15.5</v>
+      </c>
+      <c r="AS11">
+        <v>5.6</v>
+      </c>
+      <c r="AT11">
+        <v>3.7</v>
+      </c>
+      <c r="AU11">
+        <v>5.7</v>
+      </c>
+      <c r="AV11">
+        <v>4.5</v>
+      </c>
+      <c r="AW11">
+        <v>5.5</v>
+      </c>
+      <c r="AX11">
+        <v>4.4</v>
+      </c>
+      <c r="AY11">
+        <v>4.2</v>
+      </c>
+      <c r="AZ11">
+        <v>4.8</v>
+      </c>
+      <c r="BA11">
+        <v>5.6</v>
+      </c>
+      <c r="BB11">
+        <v>5.3</v>
+      </c>
+      <c r="BC11">
+        <v>5.2</v>
+      </c>
+      <c r="BD11">
+        <v>5.5</v>
+      </c>
+      <c r="BE11">
+        <v>5.9</v>
+      </c>
+      <c r="BF11">
+        <v>5.1</v>
+      </c>
+      <c r="BG11">
+        <v>5.5</v>
+      </c>
+      <c r="BH11">
+        <v>3.1</v>
+      </c>
+      <c r="BI11">
+        <v>2.54</v>
+      </c>
+      <c r="BJ11">
         <v>10.5</v>
       </c>
-      <c r="Y11">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z11">
-        <v>19</v>
-      </c>
-      <c r="AA11">
-        <v>60</v>
-      </c>
-      <c r="AB11">
+      <c r="BK11">
+        <v>6</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>13</v>
+      </c>
+      <c r="BN11">
+        <v>5.4</v>
+      </c>
+      <c r="BO11">
+        <v>4.1</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
+        <v>8.4</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
         <v>10.5</v>
       </c>
-      <c r="AC11">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD11">
-        <v>15.5</v>
-      </c>
-      <c r="AE11">
-        <v>48</v>
-      </c>
-      <c r="AF11">
-        <v>22</v>
-      </c>
-      <c r="AG11">
-        <v>16</v>
-      </c>
-      <c r="AH11">
-        <v>25</v>
-      </c>
-      <c r="AI11">
-        <v>75</v>
-      </c>
-      <c r="AJ11">
-        <v>65</v>
-      </c>
-      <c r="AK11">
-        <v>50</v>
-      </c>
-      <c r="AL11">
-        <v>75</v>
-      </c>
-      <c r="AM11">
-        <v>190</v>
-      </c>
-      <c r="AN11">
-        <v>60</v>
-      </c>
-      <c r="AO11">
-        <v>60</v>
-      </c>
-      <c r="AP11">
-        <v>7</v>
-      </c>
-      <c r="AQ11">
-        <v>3.5</v>
-      </c>
-      <c r="AR11">
-        <v>13.5</v>
-      </c>
-      <c r="AS11">
-        <v>5.2</v>
-      </c>
-      <c r="AT11">
-        <v>7</v>
-      </c>
-      <c r="AU11">
-        <v>5.6</v>
-      </c>
-      <c r="AV11">
+      <c r="BT11">
+        <v>6.2</v>
+      </c>
+      <c r="BU11">
+        <v>5.5</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>9.4</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>10.5</v>
+      </c>
+      <c r="BZ11">
+        <v>1000</v>
+      </c>
+      <c r="CA11">
         <v>10</v>
       </c>
-      <c r="AW11">
-        <v>5</v>
-      </c>
-      <c r="AX11">
-        <v>14</v>
-      </c>
-      <c r="AY11">
-        <v>10.5</v>
-      </c>
-      <c r="AZ11">
-        <v>16</v>
-      </c>
-      <c r="BA11">
-        <v>5.2</v>
-      </c>
-      <c r="BB11">
-        <v>5.2</v>
-      </c>
-      <c r="BC11">
-        <v>5.1</v>
-      </c>
-      <c r="BD11">
-        <v>5.2</v>
-      </c>
-      <c r="BE11">
-        <v>5.5</v>
-      </c>
-      <c r="BF11">
-        <v>5.2</v>
-      </c>
-      <c r="BG11">
-        <v>5.2</v>
-      </c>
-      <c r="BH11">
-        <v>1000</v>
-      </c>
-      <c r="BI11">
-        <v>1.01</v>
-      </c>
-      <c r="BJ11">
-        <v>1000</v>
-      </c>
-      <c r="BK11">
-        <v>1.01</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>1.01</v>
-      </c>
-      <c r="BN11">
-        <v>1000</v>
-      </c>
-      <c r="BO11">
-        <v>1.01</v>
-      </c>
-      <c r="BP11">
-        <v>1000</v>
-      </c>
-      <c r="BQ11">
-        <v>1.01</v>
-      </c>
-      <c r="BR11">
-        <v>1000</v>
-      </c>
-      <c r="BS11">
-        <v>1.01</v>
-      </c>
-      <c r="BT11">
-        <v>1000</v>
-      </c>
-      <c r="BU11">
-        <v>1.01</v>
-      </c>
-      <c r="BV11">
-        <v>1000</v>
-      </c>
-      <c r="BW11">
-        <v>1.01</v>
-      </c>
-      <c r="BX11">
-        <v>1000</v>
-      </c>
-      <c r="BY11">
-        <v>1.01</v>
-      </c>
-      <c r="BZ11">
-        <v>1000</v>
-      </c>
-      <c r="CA11">
-        <v>1.01</v>
-      </c>
       <c r="CB11" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
         <v>87</v>
@@ -3375,235 +3384,477 @@
         <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F12">
-        <v>1.36</v>
+        <v>2.82</v>
       </c>
       <c r="G12">
-        <v>1.39</v>
+        <v>3.25</v>
       </c>
       <c r="H12">
-        <v>10</v>
+        <v>2.76</v>
       </c>
       <c r="I12">
-        <v>11.5</v>
+        <v>3.15</v>
       </c>
       <c r="J12">
-        <v>5.4</v>
+        <v>2.88</v>
       </c>
       <c r="K12">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="L12">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="N12">
-        <v>4.8</v>
+        <v>2.68</v>
       </c>
       <c r="O12">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="P12">
-        <v>2.32</v>
+        <v>1.55</v>
       </c>
       <c r="Q12">
-        <v>1.7</v>
+        <v>2.48</v>
       </c>
       <c r="R12">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="S12">
-        <v>2.78</v>
+        <v>5.1</v>
       </c>
       <c r="T12">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="U12">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="V12">
-        <v>1.09</v>
+        <v>1.46</v>
       </c>
       <c r="W12">
-        <v>3.55</v>
+        <v>1.45</v>
       </c>
       <c r="X12">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="Y12">
-        <v>36</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z12">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="AA12">
-        <v>450</v>
+        <v>60</v>
       </c>
       <c r="AB12">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AC12">
-        <v>12.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD12">
-        <v>42</v>
+        <v>15.5</v>
       </c>
       <c r="AE12">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="AF12">
-        <v>8.4</v>
+        <v>22</v>
       </c>
       <c r="AG12">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AH12">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AI12">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AJ12">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="AK12">
-        <v>15.5</v>
+        <v>50</v>
       </c>
       <c r="AL12">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="AM12">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN12">
-        <v>5.5</v>
+        <v>60</v>
       </c>
       <c r="AO12">
-        <v>270</v>
+        <v>60</v>
       </c>
       <c r="AP12">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AQ12">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="AR12">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS12">
-        <v>13.5</v>
+        <v>5.2</v>
       </c>
       <c r="AT12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU12">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AV12">
         <v>10</v>
       </c>
       <c r="AW12">
+        <v>5</v>
+      </c>
+      <c r="AX12">
+        <v>14</v>
+      </c>
+      <c r="AY12">
+        <v>10.5</v>
+      </c>
+      <c r="AZ12">
+        <v>16.5</v>
+      </c>
+      <c r="BA12">
+        <v>5.2</v>
+      </c>
+      <c r="BB12">
+        <v>5.2</v>
+      </c>
+      <c r="BC12">
+        <v>5.1</v>
+      </c>
+      <c r="BD12">
+        <v>5.2</v>
+      </c>
+      <c r="BE12">
+        <v>5.5</v>
+      </c>
+      <c r="BF12">
+        <v>5.2</v>
+      </c>
+      <c r="BG12">
+        <v>5.2</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>1.01</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
+        <v>1.01</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>1.01</v>
+      </c>
+      <c r="BN12">
+        <v>1000</v>
+      </c>
+      <c r="BO12">
+        <v>1.01</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>1.01</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>1.01</v>
+      </c>
+      <c r="BT12">
+        <v>1000</v>
+      </c>
+      <c r="BU12">
+        <v>1.01</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>1.01</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>1.01</v>
+      </c>
+      <c r="BZ12">
+        <v>1000</v>
+      </c>
+      <c r="CA12">
+        <v>1.01</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" t="s">
+        <v>119</v>
+      </c>
+      <c r="F13">
+        <v>1.35</v>
+      </c>
+      <c r="G13">
+        <v>1.38</v>
+      </c>
+      <c r="H13">
+        <v>11</v>
+      </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
+      <c r="J13">
+        <v>5.3</v>
+      </c>
+      <c r="K13">
+        <v>5.8</v>
+      </c>
+      <c r="L13">
+        <v>1.32</v>
+      </c>
+      <c r="M13">
+        <v>1.05</v>
+      </c>
+      <c r="N13">
+        <v>4.8</v>
+      </c>
+      <c r="O13">
+        <v>1.23</v>
+      </c>
+      <c r="P13">
+        <v>2.32</v>
+      </c>
+      <c r="Q13">
+        <v>1.7</v>
+      </c>
+      <c r="R13">
+        <v>1.52</v>
+      </c>
+      <c r="S13">
+        <v>2.78</v>
+      </c>
+      <c r="T13">
+        <v>2.12</v>
+      </c>
+      <c r="U13">
+        <v>1.85</v>
+      </c>
+      <c r="V13">
+        <v>1.09</v>
+      </c>
+      <c r="W13">
+        <v>3.6</v>
+      </c>
+      <c r="X13">
+        <v>21</v>
+      </c>
+      <c r="Y13">
+        <v>42</v>
+      </c>
+      <c r="Z13">
+        <v>110</v>
+      </c>
+      <c r="AA13">
+        <v>450</v>
+      </c>
+      <c r="AB13">
+        <v>9</v>
+      </c>
+      <c r="AC13">
+        <v>12.5</v>
+      </c>
+      <c r="AD13">
+        <v>42</v>
+      </c>
+      <c r="AE13">
+        <v>200</v>
+      </c>
+      <c r="AF13">
+        <v>8.4</v>
+      </c>
+      <c r="AG13">
+        <v>11</v>
+      </c>
+      <c r="AH13">
+        <v>32</v>
+      </c>
+      <c r="AI13">
+        <v>160</v>
+      </c>
+      <c r="AJ13">
+        <v>11</v>
+      </c>
+      <c r="AK13">
+        <v>15.5</v>
+      </c>
+      <c r="AL13">
+        <v>46</v>
+      </c>
+      <c r="AM13">
+        <v>180</v>
+      </c>
+      <c r="AN13">
+        <v>5.5</v>
+      </c>
+      <c r="AO13">
+        <v>270</v>
+      </c>
+      <c r="AP13">
+        <v>8</v>
+      </c>
+      <c r="AQ13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR13">
+        <v>11.5</v>
+      </c>
+      <c r="AS13">
+        <v>12.5</v>
+      </c>
+      <c r="AT13">
+        <v>8</v>
+      </c>
+      <c r="AU13">
+        <v>11</v>
+      </c>
+      <c r="AV13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW13">
+        <v>12</v>
+      </c>
+      <c r="AX13">
+        <v>7.4</v>
+      </c>
+      <c r="AY13">
+        <v>9.6</v>
+      </c>
+      <c r="AZ13">
+        <v>21</v>
+      </c>
+      <c r="BA13">
+        <v>12</v>
+      </c>
+      <c r="BB13">
+        <v>9.6</v>
+      </c>
+      <c r="BC13">
         <v>13</v>
       </c>
-      <c r="AX12">
+      <c r="BD13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE13">
+        <v>12</v>
+      </c>
+      <c r="BF13">
+        <v>5</v>
+      </c>
+      <c r="BG13">
+        <v>12</v>
+      </c>
+      <c r="BH13">
+        <v>4.1</v>
+      </c>
+      <c r="BI13">
+        <v>3.3</v>
+      </c>
+      <c r="BJ13">
+        <v>12.5</v>
+      </c>
+      <c r="BK13">
+        <v>9.4</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>14</v>
+      </c>
+      <c r="BN13">
+        <v>3.8</v>
+      </c>
+      <c r="BO13">
+        <v>3.4</v>
+      </c>
+      <c r="BP13">
+        <v>7.8</v>
+      </c>
+      <c r="BQ13">
+        <v>6.2</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>9.4</v>
+      </c>
+      <c r="BT13">
+        <v>14</v>
+      </c>
+      <c r="BU13">
         <v>7.4</v>
       </c>
-      <c r="AY12">
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>13.5</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>13</v>
+      </c>
+      <c r="BZ13">
+        <v>12.5</v>
+      </c>
+      <c r="CA13">
         <v>9.6</v>
       </c>
-      <c r="AZ12">
-        <v>21</v>
-      </c>
-      <c r="BA12">
-        <v>13</v>
-      </c>
-      <c r="BB12">
-        <v>9.6</v>
-      </c>
-      <c r="BC12">
-        <v>13</v>
-      </c>
-      <c r="BD12">
-        <v>10.5</v>
-      </c>
-      <c r="BE12">
-        <v>13</v>
-      </c>
-      <c r="BF12">
-        <v>5</v>
-      </c>
-      <c r="BG12">
-        <v>13.5</v>
-      </c>
-      <c r="BH12">
-        <v>4.1</v>
-      </c>
-      <c r="BI12">
-        <v>3.3</v>
-      </c>
-      <c r="BJ12">
-        <v>12.5</v>
-      </c>
-      <c r="BK12">
-        <v>9.4</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>14</v>
-      </c>
-      <c r="BN12">
-        <v>3.8</v>
-      </c>
-      <c r="BO12">
-        <v>3.1</v>
-      </c>
-      <c r="BP12">
-        <v>7.8</v>
-      </c>
-      <c r="BQ12">
-        <v>6</v>
-      </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>9.4</v>
-      </c>
-      <c r="BT12">
-        <v>14</v>
-      </c>
-      <c r="BU12">
-        <v>7.4</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>13.5</v>
-      </c>
-      <c r="BX12">
-        <v>1000</v>
-      </c>
-      <c r="BY12">
-        <v>13</v>
-      </c>
-      <c r="BZ12">
-        <v>12.5</v>
-      </c>
-      <c r="CA12">
-        <v>9.6</v>
-      </c>
-      <c r="CB12" t="s">
-        <v>117</v>
+      <c r="CB13" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="124">
   <si>
     <t>League</t>
   </si>
@@ -301,6 +301,9 @@
     <t>21:00:00</t>
   </si>
   <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
     <t>23:00:00</t>
   </si>
   <si>
@@ -337,6 +340,9 @@
     <t>Atletico FC Cali</t>
   </si>
   <si>
+    <t>Criciuma</t>
+  </si>
+  <si>
     <t>Ind Medellin</t>
   </si>
   <si>
@@ -373,10 +379,13 @@
     <t>Tigres FC Zipaquira</t>
   </si>
   <si>
+    <t>Operario PR</t>
+  </si>
+  <si>
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-09-21 16:47:36</t>
+    <t>2026-09-21 19:13:49</t>
   </si>
 </sst>
 </file>
@@ -708,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -964,70 +973,70 @@
         <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F2">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="G2">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="M2">
         <v>1.15</v>
       </c>
       <c r="N2">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="O2">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="P2">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q2">
         <v>3.05</v>
       </c>
       <c r="R2">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="T2">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U2">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="V2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="X2">
         <v>7.6</v>
       </c>
       <c r="Y2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z2">
         <v>27</v>
@@ -1036,73 +1045,73 @@
         <v>110</v>
       </c>
       <c r="AB2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD2">
         <v>20</v>
       </c>
       <c r="AE2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI2">
         <v>130</v>
       </c>
       <c r="AJ2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL2">
         <v>75</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AN2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO2">
         <v>140</v>
       </c>
       <c r="AP2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2">
         <v>23</v>
       </c>
       <c r="AS2">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AT2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV2">
         <v>17</v>
       </c>
       <c r="AW2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AX2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY2">
         <v>11.5</v>
@@ -1114,7 +1123,7 @@
         <v>90</v>
       </c>
       <c r="BB2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BC2">
         <v>32</v>
@@ -1123,49 +1132,49 @@
         <v>65</v>
       </c>
       <c r="BE2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="BF2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BG2">
         <v>80</v>
       </c>
       <c r="BH2">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="BI2">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BJ2">
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>18</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN2">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ2">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="BR2">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BS2">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="BT2">
         <v>7.2</v>
@@ -1174,25 +1183,25 @@
         <v>6.4</v>
       </c>
       <c r="BV2">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="BW2">
-        <v>13.5</v>
+        <v>7.6</v>
       </c>
       <c r="BX2">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="BY2">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BZ2">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="CA2">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="CB2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1206,22 +1215,22 @@
         <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F3">
+        <v>2.18</v>
+      </c>
+      <c r="G3">
         <v>2.2</v>
       </c>
-      <c r="G3">
-        <v>2.22</v>
-      </c>
       <c r="H3">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J3">
         <v>3.35</v>
@@ -1236,49 +1245,49 @@
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O3">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P3">
         <v>1.67</v>
       </c>
       <c r="Q3">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R3">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S3">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T3">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U3">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V3">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X3">
         <v>10</v>
       </c>
       <c r="Y3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA3">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC3">
         <v>7.6</v>
@@ -1287,25 +1296,25 @@
         <v>16.5</v>
       </c>
       <c r="AE3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF3">
         <v>12.5</v>
       </c>
       <c r="AG3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH3">
         <v>23</v>
       </c>
       <c r="AI3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ3">
+        <v>28</v>
+      </c>
+      <c r="AK3">
         <v>29</v>
-      </c>
-      <c r="AK3">
-        <v>30</v>
       </c>
       <c r="AL3">
         <v>55</v>
@@ -1320,13 +1329,13 @@
         <v>110</v>
       </c>
       <c r="AP3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ3">
         <v>10.5</v>
       </c>
       <c r="AR3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS3">
         <v>50</v>
@@ -1341,16 +1350,16 @@
         <v>15.5</v>
       </c>
       <c r="AW3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX3">
         <v>11.5</v>
       </c>
       <c r="AY3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA3">
         <v>65</v>
@@ -1359,37 +1368,37 @@
         <v>26</v>
       </c>
       <c r="BC3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD3">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="BE3">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="BF3">
         <v>24</v>
       </c>
       <c r="BG3">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="BH3">
         <v>2.84</v>
       </c>
       <c r="BI3">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="BM3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BN3">
         <v>4.7</v>
@@ -1401,40 +1410,40 @@
         <v>21</v>
       </c>
       <c r="BQ3">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BR3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS3">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BT3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BU3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV3">
         <v>44</v>
       </c>
       <c r="BW3">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ3">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="CA3">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1448,28 +1457,28 @@
         <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F4">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="G4">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="H4">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="I4">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="K4">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L4">
         <v>1.45</v>
@@ -1478,76 +1487,76 @@
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O4">
         <v>1.37</v>
       </c>
       <c r="P4">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q4">
         <v>2.12</v>
       </c>
       <c r="R4">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S4">
         <v>3.9</v>
       </c>
       <c r="T4">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="U4">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="V4">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W4">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="X4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z4">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AA4">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AB4">
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD4">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AE4">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AF4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI4">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AK4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL4">
         <v>42</v>
@@ -1556,64 +1565,64 @@
         <v>160</v>
       </c>
       <c r="AN4">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AO4">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="AP4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AR4">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AS4">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AT4">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV4">
+        <v>16</v>
+      </c>
+      <c r="AW4">
+        <v>42</v>
+      </c>
+      <c r="AX4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ4">
         <v>18</v>
       </c>
-      <c r="AW4">
-        <v>50</v>
-      </c>
-      <c r="AX4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ4">
-        <v>18.5</v>
-      </c>
       <c r="BA4">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BB4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BC4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE4">
         <v>90</v>
       </c>
       <c r="BF4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BG4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BH4">
         <v>3.55</v>
@@ -1622,28 +1631,28 @@
         <v>2.7</v>
       </c>
       <c r="BJ4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK4">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN4">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BO4">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BP4">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BQ4">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BR4">
         <v>32</v>
@@ -1652,31 +1661,31 @@
         <v>7</v>
       </c>
       <c r="BT4">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU4">
+        <v>4.3</v>
+      </c>
+      <c r="BV4">
+        <v>44</v>
+      </c>
+      <c r="BW4">
+        <v>7.4</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>7.6</v>
+      </c>
+      <c r="BZ4">
+        <v>32</v>
+      </c>
+      <c r="CA4">
         <v>7</v>
       </c>
-      <c r="BV4">
-        <v>55</v>
-      </c>
-      <c r="BW4">
-        <v>7.6</v>
-      </c>
-      <c r="BX4">
-        <v>1000</v>
-      </c>
-      <c r="BY4">
-        <v>7.8</v>
-      </c>
-      <c r="BZ4">
-        <v>27</v>
-      </c>
-      <c r="CA4">
-        <v>6.6</v>
-      </c>
       <c r="CB4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1690,28 +1699,28 @@
         <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F5">
-        <v>2.94</v>
+        <v>1.12</v>
       </c>
       <c r="G5">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="H5">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="I5">
-        <v>2.72</v>
+        <v>970</v>
       </c>
       <c r="J5">
-        <v>3.3</v>
+        <v>1.12</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>990</v>
       </c>
       <c r="L5">
         <v>1.44</v>
@@ -1720,25 +1729,25 @@
         <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="O5">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1.35</v>
       </c>
       <c r="R5">
         <v>1.31</v>
       </c>
       <c r="S5">
-        <v>3.6</v>
+        <v>1.35</v>
       </c>
       <c r="T5">
-        <v>1.05</v>
+        <v>1.79</v>
       </c>
       <c r="U5">
         <v>2.08</v>
@@ -1747,7 +1756,7 @@
         <v>1.6</v>
       </c>
       <c r="W5">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
         <v>970</v>
@@ -1795,7 +1804,7 @@
         <v>60</v>
       </c>
       <c r="AM5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN5">
         <v>38</v>
@@ -1804,37 +1813,37 @@
         <v>28</v>
       </c>
       <c r="AP5">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AQ5">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AR5">
-        <v>1.52</v>
+        <v>1.97</v>
       </c>
       <c r="AS5">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AT5">
-        <v>1.67</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU5">
-        <v>1.67</v>
+        <v>6.4</v>
       </c>
       <c r="AV5">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AW5">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AX5">
-        <v>1.55</v>
+        <v>14</v>
       </c>
       <c r="AY5">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="AZ5">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="BA5">
         <v>1.59</v>
@@ -1843,82 +1852,82 @@
         <v>1.6</v>
       </c>
       <c r="BC5">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="BD5">
         <v>1.6</v>
       </c>
       <c r="BE5">
-        <v>1.61</v>
+        <v>2.18</v>
       </c>
       <c r="BF5">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="BG5">
-        <v>1.55</v>
+        <v>11.5</v>
       </c>
       <c r="BH5">
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.85</v>
+        <v>1.23</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
+        <v>1.17</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>1.19</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>1.23</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
         <v>1.16</v>
       </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
-      <c r="BS5">
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.19</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
         <v>1.18</v>
       </c>
-      <c r="BT5">
-        <v>1000</v>
-      </c>
-      <c r="BU5">
-        <v>1.22</v>
-      </c>
-      <c r="BV5">
-        <v>1000</v>
-      </c>
-      <c r="BW5">
-        <v>1.15</v>
-      </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
-        <v>1.18</v>
-      </c>
-      <c r="BZ5">
-        <v>1000</v>
-      </c>
-      <c r="CA5">
-        <v>1.17</v>
-      </c>
       <c r="CB5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1932,13 +1941,13 @@
         <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F6">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="G6">
         <v>7.6</v>
@@ -1947,7 +1956,7 @@
         <v>1.55</v>
       </c>
       <c r="I6">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -1962,7 +1971,7 @@
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O6">
         <v>1.3</v>
@@ -1971,13 +1980,13 @@
         <v>1.94</v>
       </c>
       <c r="Q6">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R6">
         <v>1.35</v>
       </c>
       <c r="S6">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="T6">
         <v>1.93</v>
@@ -1986,13 +1995,13 @@
         <v>1.88</v>
       </c>
       <c r="V6">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="W6">
         <v>1.15</v>
       </c>
       <c r="X6">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Y6">
         <v>8.4</v>
@@ -2004,10 +2013,10 @@
         <v>15.5</v>
       </c>
       <c r="AB6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD6">
         <v>10.5</v>
@@ -2016,10 +2025,10 @@
         <v>18</v>
       </c>
       <c r="AF6">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AG6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH6">
         <v>24</v>
@@ -2031,73 +2040,73 @@
         <v>250</v>
       </c>
       <c r="AK6">
-        <v>130</v>
+        <v>400</v>
       </c>
       <c r="AL6">
         <v>120</v>
       </c>
       <c r="AM6">
-        <v>170</v>
+        <v>390</v>
       </c>
       <c r="AN6">
-        <v>170</v>
+        <v>440</v>
       </c>
       <c r="AO6">
         <v>9.800000000000001</v>
       </c>
       <c r="AP6">
+        <v>6.2</v>
+      </c>
+      <c r="AQ6">
+        <v>4.9</v>
+      </c>
+      <c r="AR6">
+        <v>5.1</v>
+      </c>
+      <c r="AS6">
+        <v>6</v>
+      </c>
+      <c r="AT6">
+        <v>6.8</v>
+      </c>
+      <c r="AU6">
+        <v>5.1</v>
+      </c>
+      <c r="AV6">
         <v>5.8</v>
       </c>
-      <c r="AQ6">
-        <v>4.2</v>
-      </c>
-      <c r="AR6">
-        <v>4.5</v>
-      </c>
-      <c r="AS6">
-        <v>5.4</v>
-      </c>
-      <c r="AT6">
-        <v>6</v>
-      </c>
-      <c r="AU6">
-        <v>4.6</v>
-      </c>
-      <c r="AV6">
-        <v>4.6</v>
-      </c>
       <c r="AW6">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AX6">
+        <v>8.4</v>
+      </c>
+      <c r="AY6">
         <v>7.2</v>
       </c>
-      <c r="AY6">
-        <v>6.4</v>
-      </c>
       <c r="AZ6">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BA6">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB6">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BC6">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BD6">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BE6">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF6">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG6">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2160,7 +2169,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2174,22 +2183,22 @@
         <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F7">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="G7">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="H7">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I7">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="J7">
         <v>2.84</v>
@@ -2201,16 +2210,16 @@
         <v>1.61</v>
       </c>
       <c r="M7">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N7">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O7">
         <v>1.65</v>
       </c>
       <c r="P7">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Q7">
         <v>2.94</v>
@@ -2228,37 +2237,37 @@
         <v>1.7</v>
       </c>
       <c r="V7">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W7">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X7">
         <v>7.4</v>
       </c>
       <c r="Y7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z7">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AA7">
         <v>85</v>
       </c>
       <c r="AB7">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC7">
         <v>7</v>
       </c>
       <c r="AD7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE7">
         <v>60</v>
       </c>
       <c r="AF7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG7">
         <v>14</v>
@@ -2267,40 +2276,40 @@
         <v>26</v>
       </c>
       <c r="AI7">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="AJ7">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AK7">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AL7">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="AM7">
         <v>250</v>
       </c>
       <c r="AN7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO7">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="AP7">
         <v>6.4</v>
       </c>
       <c r="AQ7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR7">
         <v>18</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AT7">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU7">
         <v>6.2</v>
@@ -2309,10 +2318,10 @@
         <v>14</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AX7">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY7">
         <v>12</v>
@@ -2321,25 +2330,25 @@
         <v>17</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BF7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BG7">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2402,7 +2411,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2416,13 +2425,13 @@
         <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F8">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="G8">
         <v>1.16</v>
@@ -2431,13 +2440,13 @@
         <v>12</v>
       </c>
       <c r="I8">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2446,43 +2455,43 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>3.45</v>
+        <v>1.02</v>
       </c>
       <c r="O8">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P8">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="Q8">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S8">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="T8">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="U8">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="V8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="X8">
         <v>60</v>
       </c>
       <c r="Y8">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="Z8">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="AA8">
         <v>1000</v>
@@ -2491,97 +2500,97 @@
         <v>17</v>
       </c>
       <c r="AC8">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AD8">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AE8">
-        <v>570</v>
+        <v>500</v>
       </c>
       <c r="AF8">
         <v>11</v>
       </c>
       <c r="AG8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI8">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="AJ8">
         <v>9.800000000000001</v>
       </c>
       <c r="AK8">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL8">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM8">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="AN8">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BF8">
         <v>2.24</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2644,7 +2653,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2658,10 +2667,10 @@
         <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F9">
         <v>1.64</v>
@@ -2673,13 +2682,13 @@
         <v>7</v>
       </c>
       <c r="I9">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
         <v>3.45</v>
       </c>
       <c r="K9">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L9">
         <v>1.45</v>
@@ -2691,10 +2700,10 @@
         <v>2.66</v>
       </c>
       <c r="O9">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P9">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q9">
         <v>2.56</v>
@@ -2709,16 +2718,16 @@
         <v>2.4</v>
       </c>
       <c r="U9">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V9">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W9">
         <v>2.4</v>
       </c>
       <c r="X9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y9">
         <v>17.5</v>
@@ -2727,10 +2736,10 @@
         <v>75</v>
       </c>
       <c r="AA9">
-        <v>390</v>
+        <v>700</v>
       </c>
       <c r="AB9">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AC9">
         <v>10.5</v>
@@ -2739,49 +2748,49 @@
         <v>38</v>
       </c>
       <c r="AE9">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AF9">
         <v>8.4</v>
       </c>
       <c r="AG9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH9">
         <v>40</v>
       </c>
       <c r="AI9">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AJ9">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AK9">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AL9">
         <v>80</v>
       </c>
       <c r="AM9">
-        <v>360</v>
+        <v>700</v>
       </c>
       <c r="AN9">
         <v>21</v>
       </c>
       <c r="AO9">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AP9">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ9">
-        <v>12.5</v>
+        <v>4.7</v>
       </c>
       <c r="AR9">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AS9">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AT9">
         <v>5.1</v>
@@ -2790,40 +2799,40 @@
         <v>7.6</v>
       </c>
       <c r="AV9">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AW9">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AX9">
         <v>7.4</v>
       </c>
       <c r="AY9">
-        <v>4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BA9">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB9">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BC9">
         <v>17</v>
       </c>
       <c r="BD9">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BE9">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF9">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="BG9">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH9">
         <v>2.82</v>
@@ -2853,13 +2862,13 @@
         <v>12.5</v>
       </c>
       <c r="BQ9">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BT9">
         <v>11</v>
@@ -2871,22 +2880,22 @@
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>8.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>8.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="BZ9">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA9">
-        <v>8.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="CB9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2900,73 +2909,73 @@
         <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F10">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="G10">
+        <v>2.88</v>
+      </c>
+      <c r="H10">
+        <v>2.96</v>
+      </c>
+      <c r="I10">
+        <v>3.35</v>
+      </c>
+      <c r="J10">
         <v>3.05</v>
       </c>
-      <c r="H10">
-        <v>2.82</v>
-      </c>
-      <c r="I10">
-        <v>3.25</v>
-      </c>
-      <c r="J10">
-        <v>2.9</v>
-      </c>
       <c r="K10">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="L10">
         <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N10">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O10">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P10">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q10">
         <v>2.44</v>
       </c>
       <c r="R10">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S10">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T10">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U10">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V10">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W10">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="X10">
         <v>11.5</v>
       </c>
       <c r="Y10">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA10">
         <v>70</v>
@@ -2975,97 +2984,97 @@
         <v>10.5</v>
       </c>
       <c r="AC10">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD10">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE10">
         <v>55</v>
       </c>
       <c r="AF10">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AG10">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH10">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AI10">
         <v>95</v>
       </c>
       <c r="AJ10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK10">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AL10">
         <v>95</v>
       </c>
       <c r="AM10">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO10">
         <v>65</v>
       </c>
       <c r="AP10">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AQ10">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS10">
-        <v>32</v>
+        <v>4.9</v>
       </c>
       <c r="AT10">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU10">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW10">
+        <v>5.1</v>
+      </c>
+      <c r="AX10">
+        <v>14</v>
+      </c>
+      <c r="AY10">
+        <v>10.5</v>
+      </c>
+      <c r="AZ10">
+        <v>4.4</v>
+      </c>
+      <c r="BA10">
+        <v>5</v>
+      </c>
+      <c r="BB10">
+        <v>5.1</v>
+      </c>
+      <c r="BC10">
+        <v>5</v>
+      </c>
+      <c r="BD10">
+        <v>5.2</v>
+      </c>
+      <c r="BE10">
+        <v>5.1</v>
+      </c>
+      <c r="BF10">
         <v>26</v>
       </c>
-      <c r="AX10">
-        <v>13</v>
-      </c>
-      <c r="AY10">
-        <v>11</v>
-      </c>
-      <c r="AZ10">
-        <v>18</v>
-      </c>
-      <c r="BA10">
-        <v>5.8</v>
-      </c>
-      <c r="BB10">
-        <v>29</v>
-      </c>
-      <c r="BC10">
-        <v>24</v>
-      </c>
-      <c r="BD10">
-        <v>38</v>
-      </c>
-      <c r="BE10">
-        <v>6</v>
-      </c>
-      <c r="BF10">
-        <v>34</v>
-      </c>
       <c r="BG10">
-        <v>32</v>
+        <v>4.9</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3128,7 +3137,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3142,13 +3151,13 @@
         <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F11">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G11">
         <v>2.66</v>
@@ -3163,10 +3172,10 @@
         <v>3.15</v>
       </c>
       <c r="K11">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L11">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
         <v>1.09</v>
@@ -3178,49 +3187,49 @@
         <v>1.41</v>
       </c>
       <c r="P11">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q11">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R11">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S11">
         <v>4.2</v>
       </c>
       <c r="T11">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="U11">
         <v>1.98</v>
       </c>
       <c r="V11">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W11">
         <v>1.6</v>
       </c>
       <c r="X11">
+        <v>11.5</v>
+      </c>
+      <c r="Y11">
         <v>13.5</v>
-      </c>
-      <c r="Y11">
-        <v>11</v>
       </c>
       <c r="Z11">
         <v>26</v>
       </c>
       <c r="AA11">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AB11">
         <v>9.4</v>
       </c>
       <c r="AC11">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD11">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AE11">
         <v>50</v>
@@ -3229,13 +3238,13 @@
         <v>16</v>
       </c>
       <c r="AG11">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH11">
         <v>23</v>
       </c>
       <c r="AI11">
-        <v>70</v>
+        <v>370</v>
       </c>
       <c r="AJ11">
         <v>42</v>
@@ -3247,7 +3256,7 @@
         <v>55</v>
       </c>
       <c r="AM11">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN11">
         <v>30</v>
@@ -3256,121 +3265,121 @@
         <v>55</v>
       </c>
       <c r="AP11">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ11">
-        <v>3.95</v>
+        <v>9.6</v>
       </c>
       <c r="AR11">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS11">
+        <v>6.2</v>
+      </c>
+      <c r="AT11">
+        <v>8</v>
+      </c>
+      <c r="AU11">
+        <v>6.6</v>
+      </c>
+      <c r="AV11">
+        <v>12.5</v>
+      </c>
+      <c r="AW11">
+        <v>6</v>
+      </c>
+      <c r="AX11">
+        <v>4.8</v>
+      </c>
+      <c r="AY11">
+        <v>10.5</v>
+      </c>
+      <c r="AZ11">
+        <v>5.3</v>
+      </c>
+      <c r="BA11">
+        <v>6</v>
+      </c>
+      <c r="BB11">
+        <v>5.8</v>
+      </c>
+      <c r="BC11">
         <v>5.6</v>
       </c>
-      <c r="AT11">
-        <v>3.7</v>
-      </c>
-      <c r="AU11">
-        <v>5.7</v>
-      </c>
-      <c r="AV11">
-        <v>4.5</v>
-      </c>
-      <c r="AW11">
-        <v>5.5</v>
-      </c>
-      <c r="AX11">
-        <v>4.4</v>
-      </c>
-      <c r="AY11">
-        <v>4.2</v>
-      </c>
-      <c r="AZ11">
-        <v>4.8</v>
-      </c>
-      <c r="BA11">
+      <c r="BD11">
+        <v>6</v>
+      </c>
+      <c r="BE11">
+        <v>6.4</v>
+      </c>
+      <c r="BF11">
         <v>5.6</v>
       </c>
-      <c r="BB11">
-        <v>5.3</v>
-      </c>
-      <c r="BC11">
-        <v>5.2</v>
-      </c>
-      <c r="BD11">
-        <v>5.5</v>
-      </c>
-      <c r="BE11">
-        <v>5.9</v>
-      </c>
-      <c r="BF11">
-        <v>5.1</v>
-      </c>
       <c r="BG11">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="BH11">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3384,28 +3393,28 @@
         <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F12">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G12">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H12">
         <v>2.76</v>
       </c>
       <c r="I12">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="J12">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="K12">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3417,31 +3426,31 @@
         <v>2.68</v>
       </c>
       <c r="O12">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P12">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q12">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="R12">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S12">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T12">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="U12">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="V12">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W12">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X12">
         <v>10.5</v>
@@ -3450,13 +3459,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z12">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA12">
         <v>60</v>
       </c>
       <c r="AB12">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC12">
         <v>8.199999999999999</v>
@@ -3489,68 +3498,68 @@
         <v>75</v>
       </c>
       <c r="AM12">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN12">
         <v>60</v>
       </c>
       <c r="AO12">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ12">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="AR12">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AS12">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT12">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AU12">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW12">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AX12">
-        <v>14</v>
+        <v>4.8</v>
       </c>
       <c r="AY12">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ12">
         <v>16.5</v>
       </c>
       <c r="BA12">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB12">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BC12">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BD12">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BE12">
+        <v>5.9</v>
+      </c>
+      <c r="BF12">
+        <v>5.6</v>
+      </c>
+      <c r="BG12">
         <v>5.5</v>
       </c>
-      <c r="BF12">
-        <v>5.2</v>
-      </c>
-      <c r="BG12">
-        <v>5.2</v>
-      </c>
       <c r="BH12">
         <v>1000</v>
       </c>
@@ -3612,12 +3621,12 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B13" t="s">
         <v>87</v>
@@ -3626,235 +3635,477 @@
         <v>95</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F13">
-        <v>1.35</v>
+        <v>2.02</v>
       </c>
       <c r="G13">
-        <v>1.38</v>
+        <v>2.04</v>
       </c>
       <c r="H13">
-        <v>11</v>
+        <v>4.7</v>
       </c>
       <c r="I13">
-        <v>12</v>
+        <v>4.8</v>
       </c>
       <c r="J13">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="K13">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="L13">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="M13">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="N13">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="O13">
+        <v>1.48</v>
+      </c>
+      <c r="P13">
+        <v>1.66</v>
+      </c>
+      <c r="Q13">
+        <v>2.48</v>
+      </c>
+      <c r="R13">
         <v>1.23</v>
       </c>
-      <c r="P13">
-        <v>2.32</v>
-      </c>
-      <c r="Q13">
-        <v>1.7</v>
-      </c>
-      <c r="R13">
-        <v>1.52</v>
-      </c>
       <c r="S13">
-        <v>2.78</v>
+        <v>5</v>
       </c>
       <c r="T13">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U13">
         <v>1.85</v>
       </c>
       <c r="V13">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="W13">
-        <v>3.6</v>
+        <v>1.96</v>
       </c>
       <c r="X13">
-        <v>21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y13">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="Z13">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="AA13">
-        <v>450</v>
+        <v>130</v>
       </c>
       <c r="AB13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC13">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="AD13">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="AE13">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AF13">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AG13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH13">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AI13">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AJ13">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="AK13">
-        <v>15.5</v>
+        <v>26</v>
       </c>
       <c r="AL13">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM13">
         <v>180</v>
       </c>
       <c r="AN13">
-        <v>5.5</v>
+        <v>23</v>
       </c>
       <c r="AO13">
+        <v>110</v>
+      </c>
+      <c r="AP13">
+        <v>9.6</v>
+      </c>
+      <c r="AQ13">
+        <v>12</v>
+      </c>
+      <c r="AR13">
+        <v>28</v>
+      </c>
+      <c r="AS13">
+        <v>24</v>
+      </c>
+      <c r="AT13">
+        <v>6.8</v>
+      </c>
+      <c r="AU13">
+        <v>6.8</v>
+      </c>
+      <c r="AV13">
+        <v>18</v>
+      </c>
+      <c r="AW13">
+        <v>65</v>
+      </c>
+      <c r="AX13">
+        <v>10</v>
+      </c>
+      <c r="AY13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ13">
+        <v>22</v>
+      </c>
+      <c r="BA13">
+        <v>21</v>
+      </c>
+      <c r="BB13">
+        <v>22</v>
+      </c>
+      <c r="BC13">
+        <v>23</v>
+      </c>
+      <c r="BD13">
+        <v>48</v>
+      </c>
+      <c r="BE13">
+        <v>120</v>
+      </c>
+      <c r="BF13">
+        <v>20</v>
+      </c>
+      <c r="BG13">
+        <v>90</v>
+      </c>
+      <c r="BH13">
+        <v>2.88</v>
+      </c>
+      <c r="BI13">
+        <v>2.66</v>
+      </c>
+      <c r="BJ13">
+        <v>16</v>
+      </c>
+      <c r="BK13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>140</v>
+      </c>
+      <c r="BN13">
+        <v>4.5</v>
+      </c>
+      <c r="BO13">
+        <v>4.1</v>
+      </c>
+      <c r="BP13">
+        <v>23</v>
+      </c>
+      <c r="BQ13">
+        <v>5.9</v>
+      </c>
+      <c r="BR13">
+        <v>44</v>
+      </c>
+      <c r="BS13">
+        <v>6.8</v>
+      </c>
+      <c r="BT13">
+        <v>8</v>
+      </c>
+      <c r="BU13">
+        <v>7</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>6.8</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>7</v>
+      </c>
+      <c r="BZ13">
+        <v>46</v>
+      </c>
+      <c r="CA13">
+        <v>6.8</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" t="s">
+        <v>122</v>
+      </c>
+      <c r="F14">
+        <v>1.35</v>
+      </c>
+      <c r="G14">
+        <v>1.37</v>
+      </c>
+      <c r="H14">
+        <v>11</v>
+      </c>
+      <c r="I14">
+        <v>12.5</v>
+      </c>
+      <c r="J14">
+        <v>5.4</v>
+      </c>
+      <c r="K14">
+        <v>5.8</v>
+      </c>
+      <c r="L14">
+        <v>1.27</v>
+      </c>
+      <c r="M14">
+        <v>1.05</v>
+      </c>
+      <c r="N14">
+        <v>4.8</v>
+      </c>
+      <c r="O14">
+        <v>1.23</v>
+      </c>
+      <c r="P14">
+        <v>2.36</v>
+      </c>
+      <c r="Q14">
+        <v>1.69</v>
+      </c>
+      <c r="R14">
+        <v>1.53</v>
+      </c>
+      <c r="S14">
+        <v>2.74</v>
+      </c>
+      <c r="T14">
+        <v>2.1</v>
+      </c>
+      <c r="U14">
+        <v>1.85</v>
+      </c>
+      <c r="V14">
+        <v>1.09</v>
+      </c>
+      <c r="W14">
+        <v>3.7</v>
+      </c>
+      <c r="X14">
+        <v>21</v>
+      </c>
+      <c r="Y14">
+        <v>42</v>
+      </c>
+      <c r="Z14">
+        <v>110</v>
+      </c>
+      <c r="AA14">
+        <v>450</v>
+      </c>
+      <c r="AB14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC14">
+        <v>15</v>
+      </c>
+      <c r="AD14">
+        <v>48</v>
+      </c>
+      <c r="AE14">
+        <v>200</v>
+      </c>
+      <c r="AF14">
+        <v>8.4</v>
+      </c>
+      <c r="AG14">
+        <v>11</v>
+      </c>
+      <c r="AH14">
+        <v>32</v>
+      </c>
+      <c r="AI14">
+        <v>160</v>
+      </c>
+      <c r="AJ14">
+        <v>11</v>
+      </c>
+      <c r="AK14">
+        <v>15</v>
+      </c>
+      <c r="AL14">
+        <v>42</v>
+      </c>
+      <c r="AM14">
+        <v>180</v>
+      </c>
+      <c r="AN14">
+        <v>5.4</v>
+      </c>
+      <c r="AO14">
         <v>270</v>
       </c>
-      <c r="AP13">
-        <v>8</v>
-      </c>
-      <c r="AQ13">
+      <c r="AP14">
+        <v>7.2</v>
+      </c>
+      <c r="AQ14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR14">
         <v>9.800000000000001</v>
       </c>
-      <c r="AR13">
-        <v>11.5</v>
-      </c>
-      <c r="AS13">
+      <c r="AS14">
+        <v>10.5</v>
+      </c>
+      <c r="AT14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU14">
+        <v>11</v>
+      </c>
+      <c r="AV14">
+        <v>9</v>
+      </c>
+      <c r="AW14">
+        <v>10</v>
+      </c>
+      <c r="AX14">
+        <v>7.4</v>
+      </c>
+      <c r="AY14">
+        <v>9.4</v>
+      </c>
+      <c r="AZ14">
+        <v>21</v>
+      </c>
+      <c r="BA14">
+        <v>10</v>
+      </c>
+      <c r="BB14">
+        <v>9.4</v>
+      </c>
+      <c r="BC14">
+        <v>13</v>
+      </c>
+      <c r="BD14">
+        <v>8.6</v>
+      </c>
+      <c r="BE14">
+        <v>10</v>
+      </c>
+      <c r="BF14">
+        <v>4.9</v>
+      </c>
+      <c r="BG14">
+        <v>10</v>
+      </c>
+      <c r="BH14">
+        <v>4.1</v>
+      </c>
+      <c r="BI14">
+        <v>3.3</v>
+      </c>
+      <c r="BJ14">
         <v>12.5</v>
       </c>
-      <c r="AT13">
-        <v>8</v>
-      </c>
-      <c r="AU13">
-        <v>11</v>
-      </c>
-      <c r="AV13">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW13">
-        <v>12</v>
-      </c>
-      <c r="AX13">
+      <c r="BK14">
+        <v>9.4</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>14</v>
+      </c>
+      <c r="BN14">
+        <v>3.8</v>
+      </c>
+      <c r="BO14">
+        <v>3.1</v>
+      </c>
+      <c r="BP14">
+        <v>7.8</v>
+      </c>
+      <c r="BQ14">
+        <v>6.2</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>9.4</v>
+      </c>
+      <c r="BT14">
+        <v>14</v>
+      </c>
+      <c r="BU14">
         <v>7.4</v>
       </c>
-      <c r="AY13">
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>13.5</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>13</v>
+      </c>
+      <c r="BZ14">
+        <v>12.5</v>
+      </c>
+      <c r="CA14">
         <v>9.6</v>
       </c>
-      <c r="AZ13">
-        <v>21</v>
-      </c>
-      <c r="BA13">
-        <v>12</v>
-      </c>
-      <c r="BB13">
-        <v>9.6</v>
-      </c>
-      <c r="BC13">
-        <v>13</v>
-      </c>
-      <c r="BD13">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE13">
-        <v>12</v>
-      </c>
-      <c r="BF13">
-        <v>5</v>
-      </c>
-      <c r="BG13">
-        <v>12</v>
-      </c>
-      <c r="BH13">
-        <v>4.1</v>
-      </c>
-      <c r="BI13">
-        <v>3.3</v>
-      </c>
-      <c r="BJ13">
-        <v>12.5</v>
-      </c>
-      <c r="BK13">
-        <v>9.4</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>14</v>
-      </c>
-      <c r="BN13">
-        <v>3.8</v>
-      </c>
-      <c r="BO13">
-        <v>3.4</v>
-      </c>
-      <c r="BP13">
-        <v>7.8</v>
-      </c>
-      <c r="BQ13">
-        <v>6.2</v>
-      </c>
-      <c r="BR13">
-        <v>1000</v>
-      </c>
-      <c r="BS13">
-        <v>9.4</v>
-      </c>
-      <c r="BT13">
-        <v>14</v>
-      </c>
-      <c r="BU13">
-        <v>7.4</v>
-      </c>
-      <c r="BV13">
-        <v>1000</v>
-      </c>
-      <c r="BW13">
-        <v>13.5</v>
-      </c>
-      <c r="BX13">
-        <v>1000</v>
-      </c>
-      <c r="BY13">
-        <v>13</v>
-      </c>
-      <c r="BZ13">
-        <v>12.5</v>
-      </c>
-      <c r="CA13">
-        <v>9.6</v>
-      </c>
-      <c r="CB13" t="s">
-        <v>120</v>
+      <c r="CB14" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -385,7 +385,7 @@
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-09-21 19:13:49</t>
+    <t>2026-09-21 21:23:30</t>
   </si>
 </sst>
 </file>
@@ -979,226 +979,226 @@
         <v>110</v>
       </c>
       <c r="F2">
-        <v>2.28</v>
+        <v>2.58</v>
       </c>
       <c r="G2">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="H2">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="I2">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="J2">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="K2">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="L2">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="M2">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="N2">
-        <v>2.52</v>
+        <v>2.26</v>
       </c>
       <c r="O2">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="P2">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="Q2">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="R2">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="S2">
+        <v>9</v>
+      </c>
+      <c r="T2">
+        <v>2.48</v>
+      </c>
+      <c r="U2">
+        <v>1.62</v>
+      </c>
+      <c r="V2">
+        <v>1.37</v>
+      </c>
+      <c r="W2">
+        <v>1.58</v>
+      </c>
+      <c r="X2">
         <v>6.6</v>
       </c>
-      <c r="T2">
-        <v>2.36</v>
-      </c>
-      <c r="U2">
-        <v>1.71</v>
-      </c>
-      <c r="V2">
-        <v>1.3</v>
-      </c>
-      <c r="W2">
-        <v>1.76</v>
-      </c>
-      <c r="X2">
-        <v>7.6</v>
-      </c>
       <c r="Y2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AA2">
+        <v>120</v>
+      </c>
+      <c r="AB2">
+        <v>6.6</v>
+      </c>
+      <c r="AC2">
+        <v>7</v>
+      </c>
+      <c r="AD2">
+        <v>18.5</v>
+      </c>
+      <c r="AE2">
+        <v>90</v>
+      </c>
+      <c r="AF2">
+        <v>14</v>
+      </c>
+      <c r="AG2">
+        <v>14.5</v>
+      </c>
+      <c r="AH2">
+        <v>32</v>
+      </c>
+      <c r="AI2">
+        <v>140</v>
+      </c>
+      <c r="AJ2">
+        <v>46</v>
+      </c>
+      <c r="AK2">
+        <v>48</v>
+      </c>
+      <c r="AL2">
         <v>110</v>
       </c>
-      <c r="AB2">
-        <v>6.4</v>
-      </c>
-      <c r="AC2">
-        <v>7.2</v>
-      </c>
-      <c r="AD2">
+      <c r="AM2">
+        <v>380</v>
+      </c>
+      <c r="AN2">
+        <v>70</v>
+      </c>
+      <c r="AO2">
+        <v>150</v>
+      </c>
+      <c r="AP2">
+        <v>6.2</v>
+      </c>
+      <c r="AQ2">
+        <v>7.8</v>
+      </c>
+      <c r="AR2">
         <v>20</v>
-      </c>
-      <c r="AE2">
-        <v>85</v>
-      </c>
-      <c r="AF2">
-        <v>12</v>
-      </c>
-      <c r="AG2">
-        <v>12.5</v>
-      </c>
-      <c r="AH2">
-        <v>27</v>
-      </c>
-      <c r="AI2">
-        <v>130</v>
-      </c>
-      <c r="AJ2">
-        <v>32</v>
-      </c>
-      <c r="AK2">
-        <v>36</v>
-      </c>
-      <c r="AL2">
-        <v>75</v>
-      </c>
-      <c r="AM2">
-        <v>310</v>
-      </c>
-      <c r="AN2">
-        <v>38</v>
-      </c>
-      <c r="AO2">
-        <v>140</v>
-      </c>
-      <c r="AP2">
-        <v>7.2</v>
-      </c>
-      <c r="AQ2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR2">
-        <v>23</v>
       </c>
       <c r="AS2">
         <v>60</v>
       </c>
       <c r="AT2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU2">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AX2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY2">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BA2">
+        <v>100</v>
+      </c>
+      <c r="BB2">
+        <v>34</v>
+      </c>
+      <c r="BC2">
+        <v>36</v>
+      </c>
+      <c r="BD2">
+        <v>70</v>
+      </c>
+      <c r="BE2">
+        <v>180</v>
+      </c>
+      <c r="BF2">
+        <v>48</v>
+      </c>
+      <c r="BG2">
+        <v>85</v>
+      </c>
+      <c r="BH2">
+        <v>2.26</v>
+      </c>
+      <c r="BI2">
+        <v>2.18</v>
+      </c>
+      <c r="BJ2">
+        <v>14</v>
+      </c>
+      <c r="BK2">
+        <v>13</v>
+      </c>
+      <c r="BL2">
+        <v>960</v>
+      </c>
+      <c r="BM2">
+        <v>21</v>
+      </c>
+      <c r="BN2">
+        <v>5.3</v>
+      </c>
+      <c r="BO2">
+        <v>4.7</v>
+      </c>
+      <c r="BP2">
+        <v>38</v>
+      </c>
+      <c r="BQ2">
+        <v>13.5</v>
+      </c>
+      <c r="BR2">
         <v>90</v>
       </c>
-      <c r="BB2">
-        <v>28</v>
-      </c>
-      <c r="BC2">
-        <v>32</v>
-      </c>
-      <c r="BD2">
+      <c r="BS2">
+        <v>55</v>
+      </c>
+      <c r="BT2">
+        <v>6.4</v>
+      </c>
+      <c r="BU2">
+        <v>5.9</v>
+      </c>
+      <c r="BV2">
+        <v>50</v>
+      </c>
+      <c r="BW2">
+        <v>9</v>
+      </c>
+      <c r="BX2">
+        <v>95</v>
+      </c>
+      <c r="BY2">
+        <v>70</v>
+      </c>
+      <c r="BZ2">
+        <v>100</v>
+      </c>
+      <c r="CA2">
         <v>65</v>
-      </c>
-      <c r="BE2">
-        <v>90</v>
-      </c>
-      <c r="BF2">
-        <v>32</v>
-      </c>
-      <c r="BG2">
-        <v>80</v>
-      </c>
-      <c r="BH2">
-        <v>2.64</v>
-      </c>
-      <c r="BI2">
-        <v>2.34</v>
-      </c>
-      <c r="BJ2">
-        <v>12.5</v>
-      </c>
-      <c r="BK2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN2">
-        <v>4.6</v>
-      </c>
-      <c r="BO2">
-        <v>4.3</v>
-      </c>
-      <c r="BP2">
-        <v>20</v>
-      </c>
-      <c r="BQ2">
-        <v>6.4</v>
-      </c>
-      <c r="BR2">
-        <v>75</v>
-      </c>
-      <c r="BS2">
-        <v>7.8</v>
-      </c>
-      <c r="BT2">
-        <v>7.2</v>
-      </c>
-      <c r="BU2">
-        <v>6.4</v>
-      </c>
-      <c r="BV2">
-        <v>60</v>
-      </c>
-      <c r="BW2">
-        <v>7.6</v>
-      </c>
-      <c r="BX2">
-        <v>120</v>
-      </c>
-      <c r="BY2">
-        <v>12.5</v>
-      </c>
-      <c r="BZ2">
-        <v>90</v>
-      </c>
-      <c r="CA2">
-        <v>12</v>
       </c>
       <c r="CB2" t="s">
         <v>123</v>
@@ -1221,28 +1221,28 @@
         <v>111</v>
       </c>
       <c r="F3">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="G3">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I3">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="J3">
         <v>3.35</v>
       </c>
       <c r="K3">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L3">
         <v>1.54</v>
       </c>
       <c r="M3">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N3">
         <v>3</v>
@@ -1251,196 +1251,196 @@
         <v>1.48</v>
       </c>
       <c r="P3">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q3">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S3">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T3">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U3">
         <v>1.86</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W3">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="X3">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Y3">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Z3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AA3">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="AB3">
         <v>7.4</v>
       </c>
       <c r="AC3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD3">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE3">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AF3">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI3">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AK3">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AL3">
         <v>55</v>
       </c>
       <c r="AM3">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN3">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AO3">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="AP3">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ3">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AS3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AT3">
         <v>7</v>
       </c>
       <c r="AU3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV3">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY3">
         <v>9.6</v>
       </c>
       <c r="AZ3">
+        <v>21</v>
+      </c>
+      <c r="BA3">
+        <v>70</v>
+      </c>
+      <c r="BB3">
+        <v>24</v>
+      </c>
+      <c r="BC3">
+        <v>23</v>
+      </c>
+      <c r="BD3">
+        <v>46</v>
+      </c>
+      <c r="BE3">
+        <v>120</v>
+      </c>
+      <c r="BF3">
         <v>20</v>
       </c>
-      <c r="BA3">
+      <c r="BG3">
+        <v>85</v>
+      </c>
+      <c r="BH3">
+        <v>2.88</v>
+      </c>
+      <c r="BI3">
+        <v>2.74</v>
+      </c>
+      <c r="BJ3">
+        <v>11</v>
+      </c>
+      <c r="BK3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BL3">
+        <v>210</v>
+      </c>
+      <c r="BM3">
+        <v>140</v>
+      </c>
+      <c r="BN3">
+        <v>4.5</v>
+      </c>
+      <c r="BO3">
+        <v>4.2</v>
+      </c>
+      <c r="BP3">
+        <v>16</v>
+      </c>
+      <c r="BQ3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR3">
+        <v>42</v>
+      </c>
+      <c r="BS3">
+        <v>13</v>
+      </c>
+      <c r="BT3">
+        <v>7.4</v>
+      </c>
+      <c r="BU3">
+        <v>6.8</v>
+      </c>
+      <c r="BV3">
+        <v>48</v>
+      </c>
+      <c r="BW3">
+        <v>13.5</v>
+      </c>
+      <c r="BX3">
         <v>65</v>
       </c>
-      <c r="BB3">
-        <v>26</v>
-      </c>
-      <c r="BC3">
-        <v>26</v>
-      </c>
-      <c r="BD3">
-        <v>38</v>
-      </c>
-      <c r="BE3">
-        <v>16.5</v>
-      </c>
-      <c r="BF3">
-        <v>24</v>
-      </c>
-      <c r="BG3">
-        <v>70</v>
-      </c>
-      <c r="BH3">
-        <v>2.84</v>
-      </c>
-      <c r="BI3">
-        <v>2.68</v>
-      </c>
-      <c r="BJ3">
-        <v>11.5</v>
-      </c>
-      <c r="BK3">
-        <v>6.4</v>
-      </c>
-      <c r="BL3">
-        <v>220</v>
-      </c>
-      <c r="BM3">
+      <c r="BY3">
+        <v>14</v>
+      </c>
+      <c r="BZ3">
+        <v>44</v>
+      </c>
+      <c r="CA3">
         <v>13</v>
-      </c>
-      <c r="BN3">
-        <v>4.7</v>
-      </c>
-      <c r="BO3">
-        <v>4.3</v>
-      </c>
-      <c r="BP3">
-        <v>21</v>
-      </c>
-      <c r="BQ3">
-        <v>8.4</v>
-      </c>
-      <c r="BR3">
-        <v>46</v>
-      </c>
-      <c r="BS3">
-        <v>10.5</v>
-      </c>
-      <c r="BT3">
-        <v>7</v>
-      </c>
-      <c r="BU3">
-        <v>6.4</v>
-      </c>
-      <c r="BV3">
-        <v>44</v>
-      </c>
-      <c r="BW3">
-        <v>10.5</v>
-      </c>
-      <c r="BX3">
-        <v>60</v>
-      </c>
-      <c r="BY3">
-        <v>11</v>
-      </c>
-      <c r="BZ3">
-        <v>50</v>
-      </c>
-      <c r="CA3">
-        <v>10.5</v>
       </c>
       <c r="CB3" t="s">
         <v>123</v>
@@ -1463,22 +1463,22 @@
         <v>112</v>
       </c>
       <c r="F4">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G4">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="H4">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I4">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K4">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L4">
         <v>1.45</v>
@@ -1487,202 +1487,202 @@
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O4">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P4">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q4">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S4">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T4">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U4">
         <v>1.94</v>
       </c>
       <c r="V4">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W4">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y4">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z4">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AA4">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB4">
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE4">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AF4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL4">
         <v>42</v>
       </c>
       <c r="AM4">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AN4">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO4">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AP4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AS4">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AT4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW4">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AX4">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4">
         <v>18</v>
       </c>
       <c r="BA4">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BB4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD4">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BE4">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BF4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH4">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="BI4">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="BJ4">
         <v>11</v>
       </c>
       <c r="BK4">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>8.6</v>
+        <v>130</v>
       </c>
       <c r="BN4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO4">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP4">
         <v>14.5</v>
       </c>
       <c r="BQ4">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BR4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS4">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="BT4">
         <v>8.199999999999999</v>
       </c>
       <c r="BU4">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BV4">
         <v>44</v>
       </c>
       <c r="BW4">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BZ4">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="CA4">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="s">
         <v>123</v>
@@ -1705,58 +1705,58 @@
         <v>113</v>
       </c>
       <c r="F5">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="G5">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="H5">
+        <v>1.1</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
+      </c>
+      <c r="J5">
+        <v>1.1</v>
+      </c>
+      <c r="K5">
+        <v>3.3</v>
+      </c>
+      <c r="L5">
+        <v>1.03</v>
+      </c>
+      <c r="M5">
+        <v>1.08</v>
+      </c>
+      <c r="N5">
+        <v>1.27</v>
+      </c>
+      <c r="O5">
+        <v>1.04</v>
+      </c>
+      <c r="P5">
+        <v>1.3</v>
+      </c>
+      <c r="Q5">
+        <v>1.01</v>
+      </c>
+      <c r="R5">
+        <v>1.3</v>
+      </c>
+      <c r="S5">
+        <v>3.65</v>
+      </c>
+      <c r="T5">
+        <v>1.05</v>
+      </c>
+      <c r="U5">
         <v>2.24</v>
       </c>
-      <c r="I5">
-        <v>970</v>
-      </c>
-      <c r="J5">
-        <v>1.12</v>
-      </c>
-      <c r="K5">
-        <v>990</v>
-      </c>
-      <c r="L5">
-        <v>1.44</v>
-      </c>
-      <c r="M5">
-        <v>1.07</v>
-      </c>
-      <c r="N5">
-        <v>1.89</v>
-      </c>
-      <c r="O5">
-        <v>1.35</v>
-      </c>
-      <c r="P5">
-        <v>1.89</v>
-      </c>
-      <c r="Q5">
-        <v>1.35</v>
-      </c>
-      <c r="R5">
-        <v>1.31</v>
-      </c>
-      <c r="S5">
-        <v>1.35</v>
-      </c>
-      <c r="T5">
-        <v>1.79</v>
-      </c>
-      <c r="U5">
-        <v>2.08</v>
-      </c>
       <c r="V5">
-        <v>1.6</v>
+        <v>1.03</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
         <v>970</v>
@@ -1774,13 +1774,13 @@
         <v>970</v>
       </c>
       <c r="AC5">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AD5">
         <v>970</v>
       </c>
       <c r="AE5">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
         <v>21</v>
@@ -1804,7 +1804,7 @@
         <v>60</v>
       </c>
       <c r="AM5">
-        <v>95</v>
+        <v>220</v>
       </c>
       <c r="AN5">
         <v>38</v>
@@ -1813,118 +1813,118 @@
         <v>28</v>
       </c>
       <c r="AP5">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AQ5">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AR5">
-        <v>1.97</v>
+        <v>1.6</v>
       </c>
       <c r="AS5">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AT5">
-        <v>9.199999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="AU5">
-        <v>6.4</v>
+        <v>1.33</v>
       </c>
       <c r="AV5">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AW5">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AX5">
-        <v>14</v>
+        <v>1.6</v>
       </c>
       <c r="AY5">
-        <v>10</v>
+        <v>1.6</v>
       </c>
       <c r="AZ5">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BA5">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="BB5">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="BC5">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="BD5">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="BE5">
-        <v>2.18</v>
+        <v>75</v>
       </c>
       <c r="BF5">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="BG5">
-        <v>11.5</v>
+        <v>1.52</v>
       </c>
       <c r="BH5">
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.23</v>
+        <v>90</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="CB5" t="s">
         <v>123</v>
@@ -1947,7 +1947,7 @@
         <v>114</v>
       </c>
       <c r="F6">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="G6">
         <v>7.6</v>
@@ -1956,16 +1956,16 @@
         <v>1.55</v>
       </c>
       <c r="I6">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="J6">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M6">
         <v>1.06</v>
@@ -1995,7 +1995,7 @@
         <v>1.88</v>
       </c>
       <c r="V6">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="W6">
         <v>1.15</v>
@@ -2037,7 +2037,7 @@
         <v>40</v>
       </c>
       <c r="AJ6">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK6">
         <v>400</v>
@@ -2055,40 +2055,40 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AP6">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AQ6">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AR6">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="AS6">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AT6">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="AU6">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV6">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="AW6">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="AX6">
         <v>8.4</v>
       </c>
       <c r="AY6">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="AZ6">
-        <v>7</v>
+        <v>19.5</v>
       </c>
       <c r="BA6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB6">
         <v>9.4</v>
@@ -2100,13 +2100,13 @@
         <v>9</v>
       </c>
       <c r="BE6">
-        <v>9.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BF6">
         <v>9.199999999999999</v>
       </c>
       <c r="BG6">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2189,16 +2189,16 @@
         <v>115</v>
       </c>
       <c r="F7">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="G7">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H7">
         <v>3.3</v>
       </c>
       <c r="I7">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J7">
         <v>2.84</v>
@@ -2213,7 +2213,7 @@
         <v>1.15</v>
       </c>
       <c r="N7">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="O7">
         <v>1.65</v>
@@ -2231,16 +2231,16 @@
         <v>6.4</v>
       </c>
       <c r="T7">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U7">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V7">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W7">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X7">
         <v>7.4</v>
@@ -2264,7 +2264,7 @@
         <v>17</v>
       </c>
       <c r="AE7">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AF7">
         <v>16</v>
@@ -2288,7 +2288,7 @@
         <v>170</v>
       </c>
       <c r="AM7">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AN7">
         <v>60</v>
@@ -2342,7 +2342,7 @@
         <v>10.5</v>
       </c>
       <c r="BE7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF7">
         <v>10</v>
@@ -2449,7 +2449,7 @@
         <v>13</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="M8">
         <v>1.01</v>
@@ -2461,7 +2461,7 @@
         <v>1.09</v>
       </c>
       <c r="P8">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q8">
         <v>1.32</v>
@@ -2470,7 +2470,7 @@
         <v>2.04</v>
       </c>
       <c r="S8">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="T8">
         <v>2.12</v>
@@ -2491,7 +2491,7 @@
         <v>110</v>
       </c>
       <c r="Z8">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AA8">
         <v>1000</v>
@@ -2506,7 +2506,7 @@
         <v>110</v>
       </c>
       <c r="AE8">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="AF8">
         <v>11</v>
@@ -2593,64 +2593,64 @@
         <v>8</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="CB8" t="s">
         <v>123</v>
@@ -2673,76 +2673,76 @@
         <v>117</v>
       </c>
       <c r="F9">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G9">
         <v>1.71</v>
       </c>
       <c r="H9">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I9">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K9">
         <v>3.8</v>
       </c>
       <c r="L9">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M9">
         <v>1.12</v>
       </c>
       <c r="N9">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O9">
         <v>1.54</v>
       </c>
       <c r="P9">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q9">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R9">
         <v>1.2</v>
       </c>
       <c r="S9">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="T9">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U9">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V9">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W9">
         <v>2.4</v>
       </c>
       <c r="X9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y9">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z9">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AA9">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB9">
         <v>5.8</v>
       </c>
       <c r="AC9">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9">
         <v>38</v>
@@ -2757,7 +2757,7 @@
         <v>13</v>
       </c>
       <c r="AH9">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AI9">
         <v>700</v>
@@ -2769,7 +2769,7 @@
         <v>24</v>
       </c>
       <c r="AL9">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AM9">
         <v>700</v>
@@ -2781,16 +2781,16 @@
         <v>420</v>
       </c>
       <c r="AP9">
+        <v>8</v>
+      </c>
+      <c r="AQ9">
+        <v>5.6</v>
+      </c>
+      <c r="AR9">
+        <v>7.4</v>
+      </c>
+      <c r="AS9">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AQ9">
-        <v>4.7</v>
-      </c>
-      <c r="AR9">
-        <v>6</v>
-      </c>
-      <c r="AS9">
-        <v>6.4</v>
       </c>
       <c r="AT9">
         <v>5.1</v>
@@ -2799,10 +2799,10 @@
         <v>7.6</v>
       </c>
       <c r="AV9">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW9">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AX9">
         <v>7.4</v>
@@ -2811,34 +2811,34 @@
         <v>9.6</v>
       </c>
       <c r="AZ9">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA9">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB9">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BC9">
-        <v>17</v>
+        <v>6.2</v>
       </c>
       <c r="BD9">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BE9">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF9">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="BG9">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH9">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BI9">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BJ9">
         <v>13.5</v>
@@ -2859,16 +2859,16 @@
         <v>3.05</v>
       </c>
       <c r="BP9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BT9">
         <v>11</v>
@@ -2889,10 +2889,10 @@
         <v>21</v>
       </c>
       <c r="BZ9">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CA9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CB9" t="s">
         <v>123</v>
@@ -2915,7 +2915,7 @@
         <v>118</v>
       </c>
       <c r="F10">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="G10">
         <v>2.88</v>
@@ -2942,7 +2942,7 @@
         <v>2.72</v>
       </c>
       <c r="O10">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P10">
         <v>1.58</v>
@@ -2951,7 +2951,7 @@
         <v>2.44</v>
       </c>
       <c r="R10">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S10">
         <v>4.8</v>
@@ -2993,7 +2993,7 @@
         <v>55</v>
       </c>
       <c r="AF10">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AG10">
         <v>13.5</v>
@@ -3023,16 +3023,16 @@
         <v>65</v>
       </c>
       <c r="AP10">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ10">
         <v>8.199999999999999</v>
       </c>
       <c r="AR10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS10">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AT10">
         <v>7.2</v>
@@ -3044,7 +3044,7 @@
         <v>12</v>
       </c>
       <c r="AW10">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AX10">
         <v>14</v>
@@ -3053,28 +3053,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ10">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BA10">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB10">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BC10">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BD10">
         <v>5.2</v>
       </c>
       <c r="BE10">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF10">
-        <v>26</v>
+        <v>5.4</v>
       </c>
       <c r="BG10">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3157,16 +3157,16 @@
         <v>119</v>
       </c>
       <c r="F11">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="G11">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="H11">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="I11">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J11">
         <v>3.15</v>
@@ -3190,52 +3190,52 @@
         <v>1.72</v>
       </c>
       <c r="Q11">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R11">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S11">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T11">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="U11">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V11">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X11">
         <v>11.5</v>
       </c>
       <c r="Y11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z11">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AA11">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="AB11">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC11">
         <v>9</v>
       </c>
       <c r="AD11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE11">
         <v>50</v>
       </c>
       <c r="AF11">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="AG11">
         <v>12.5</v>
@@ -3265,58 +3265,58 @@
         <v>55</v>
       </c>
       <c r="AP11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ11">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR11">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS11">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT11">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU11">
         <v>6.6</v>
       </c>
       <c r="AV11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW11">
+        <v>6.6</v>
+      </c>
+      <c r="AX11">
+        <v>5.3</v>
+      </c>
+      <c r="AY11">
+        <v>11</v>
+      </c>
+      <c r="AZ11">
+        <v>5.6</v>
+      </c>
+      <c r="BA11">
+        <v>6.6</v>
+      </c>
+      <c r="BB11">
+        <v>6.4</v>
+      </c>
+      <c r="BC11">
         <v>6</v>
       </c>
-      <c r="AX11">
-        <v>4.8</v>
-      </c>
-      <c r="AY11">
-        <v>10.5</v>
-      </c>
-      <c r="AZ11">
-        <v>5.3</v>
-      </c>
-      <c r="BA11">
-        <v>6</v>
-      </c>
-      <c r="BB11">
-        <v>5.8</v>
-      </c>
-      <c r="BC11">
-        <v>5.6</v>
-      </c>
       <c r="BD11">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE11">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BF11">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG11">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3423,28 +3423,28 @@
         <v>1.12</v>
       </c>
       <c r="N12">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O12">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P12">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q12">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="R12">
         <v>1.21</v>
       </c>
       <c r="S12">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T12">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="U12">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V12">
         <v>1.5</v>
@@ -3468,7 +3468,7 @@
         <v>9.4</v>
       </c>
       <c r="AC12">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD12">
         <v>15.5</v>
@@ -3513,10 +3513,10 @@
         <v>7.6</v>
       </c>
       <c r="AR12">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AS12">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT12">
         <v>7.8</v>
@@ -3528,10 +3528,10 @@
         <v>11</v>
       </c>
       <c r="AW12">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX12">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AY12">
         <v>11.5</v>
@@ -3540,25 +3540,25 @@
         <v>16.5</v>
       </c>
       <c r="BA12">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB12">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BC12">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD12">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE12">
+        <v>6.2</v>
+      </c>
+      <c r="BF12">
         <v>5.9</v>
       </c>
-      <c r="BF12">
-        <v>5.6</v>
-      </c>
       <c r="BG12">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3641,7 +3641,7 @@
         <v>121</v>
       </c>
       <c r="F13">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G13">
         <v>2.04</v>
@@ -3650,52 +3650,52 @@
         <v>4.7</v>
       </c>
       <c r="I13">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J13">
         <v>3.35</v>
       </c>
       <c r="K13">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L13">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="M13">
         <v>1.11</v>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O13">
         <v>1.48</v>
       </c>
       <c r="P13">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q13">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R13">
         <v>1.23</v>
       </c>
       <c r="S13">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T13">
         <v>2.1</v>
       </c>
       <c r="U13">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V13">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W13">
         <v>1.96</v>
       </c>
       <c r="X13">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y13">
         <v>13</v>
@@ -3707,67 +3707,67 @@
         <v>130</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AC13">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AD13">
         <v>20</v>
       </c>
       <c r="AE13">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AF13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG13">
         <v>10.5</v>
       </c>
       <c r="AH13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI13">
         <v>120</v>
       </c>
       <c r="AJ13">
+        <v>26</v>
+      </c>
+      <c r="AK13">
         <v>25</v>
-      </c>
-      <c r="AK13">
-        <v>26</v>
       </c>
       <c r="AL13">
         <v>55</v>
       </c>
       <c r="AM13">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AN13">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO13">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP13">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ13">
         <v>12</v>
       </c>
       <c r="AR13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS13">
-        <v>24</v>
+        <v>16.5</v>
       </c>
       <c r="AT13">
         <v>6.8</v>
       </c>
       <c r="AU13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV13">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW13">
         <v>65</v>
@@ -3776,91 +3776,91 @@
         <v>10</v>
       </c>
       <c r="AY13">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA13">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BB13">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BC13">
         <v>23</v>
       </c>
       <c r="BD13">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="BE13">
         <v>120</v>
       </c>
       <c r="BF13">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BG13">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="BH13">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="BI13">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ13">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BK13">
-        <v>9.800000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="BL13">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="BM13">
         <v>140</v>
       </c>
       <c r="BN13">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BO13">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BP13">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="BQ13">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="BR13">
         <v>44</v>
       </c>
       <c r="BS13">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="BT13">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BU13">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW13">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY13">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="BZ13">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="CA13">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="CB13" t="s">
         <v>123</v>
@@ -3883,16 +3883,16 @@
         <v>122</v>
       </c>
       <c r="F14">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="G14">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="H14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I14">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="J14">
         <v>5.4</v>
@@ -3916,13 +3916,13 @@
         <v>2.36</v>
       </c>
       <c r="Q14">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R14">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S14">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T14">
         <v>2.1</v>
@@ -3931,10 +3931,10 @@
         <v>1.85</v>
       </c>
       <c r="V14">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W14">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="X14">
         <v>21</v>
@@ -3943,10 +3943,10 @@
         <v>42</v>
       </c>
       <c r="Z14">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AA14">
-        <v>450</v>
+        <v>540</v>
       </c>
       <c r="AB14">
         <v>9.199999999999999</v>
@@ -3964,7 +3964,7 @@
         <v>8.4</v>
       </c>
       <c r="AG14">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH14">
         <v>32</v>
@@ -3973,7 +3973,7 @@
         <v>160</v>
       </c>
       <c r="AJ14">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK14">
         <v>15</v>
@@ -3985,22 +3985,22 @@
         <v>180</v>
       </c>
       <c r="AN14">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AO14">
         <v>270</v>
       </c>
       <c r="AP14">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AQ14">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR14">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AS14">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT14">
         <v>8.199999999999999</v>
@@ -4009,10 +4009,10 @@
         <v>11</v>
       </c>
       <c r="AV14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW14">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AX14">
         <v>7.4</v>
@@ -4024,7 +4024,7 @@
         <v>21</v>
       </c>
       <c r="BA14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB14">
         <v>9.4</v>
@@ -4033,22 +4033,22 @@
         <v>13</v>
       </c>
       <c r="BD14">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF14">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BG14">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH14">
         <v>4.1</v>
       </c>
       <c r="BI14">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ14">
         <v>12.5</v>
@@ -4066,7 +4066,7 @@
         <v>3.8</v>
       </c>
       <c r="BO14">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BP14">
         <v>7.8</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -349,7 +349,7 @@
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-09-22 01:49:03</t>
+    <t>2026-09-22 03:59:47</t>
   </si>
 </sst>
 </file>
@@ -943,22 +943,22 @@
         <v>102</v>
       </c>
       <c r="F2">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="G2">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="H2">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="I2">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K2">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="L2">
         <v>1.39</v>
@@ -967,202 +967,202 @@
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O2">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="P2">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q2">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R2">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S2">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="T2">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U2">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="V2">
-        <v>2.28</v>
+        <v>2.68</v>
       </c>
       <c r="W2">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z2">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AA2">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AB2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AC2">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AD2">
         <v>10.5</v>
       </c>
       <c r="AE2">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AF2">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AG2">
+        <v>27</v>
+      </c>
+      <c r="AH2">
+        <v>25</v>
+      </c>
+      <c r="AI2">
+        <v>40</v>
+      </c>
+      <c r="AJ2">
+        <v>700</v>
+      </c>
+      <c r="AK2">
+        <v>110</v>
+      </c>
+      <c r="AL2">
+        <v>110</v>
+      </c>
+      <c r="AM2">
+        <v>160</v>
+      </c>
+      <c r="AN2">
+        <v>130</v>
+      </c>
+      <c r="AO2">
+        <v>8.6</v>
+      </c>
+      <c r="AP2">
+        <v>12.5</v>
+      </c>
+      <c r="AQ2">
+        <v>7</v>
+      </c>
+      <c r="AR2">
+        <v>7.6</v>
+      </c>
+      <c r="AS2">
+        <v>12.5</v>
+      </c>
+      <c r="AT2">
         <v>21</v>
       </c>
-      <c r="AH2">
-        <v>21</v>
-      </c>
-      <c r="AI2">
-        <v>44</v>
-      </c>
-      <c r="AJ2">
-        <v>900</v>
-      </c>
-      <c r="AK2">
-        <v>80</v>
-      </c>
-      <c r="AL2">
-        <v>260</v>
-      </c>
-      <c r="AM2">
-        <v>580</v>
-      </c>
-      <c r="AN2">
-        <v>430</v>
-      </c>
-      <c r="AO2">
-        <v>11.5</v>
-      </c>
-      <c r="AP2">
+      <c r="AU2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW2">
         <v>13.5</v>
       </c>
-      <c r="AQ2">
-        <v>7.6</v>
-      </c>
-      <c r="AR2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS2">
-        <v>16</v>
-      </c>
-      <c r="AT2">
-        <v>16</v>
-      </c>
-      <c r="AU2">
-        <v>8</v>
-      </c>
-      <c r="AV2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW2">
-        <v>16</v>
-      </c>
       <c r="AX2">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AY2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ2">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB2">
+        <v>100</v>
+      </c>
+      <c r="BC2">
         <v>60</v>
       </c>
-      <c r="BC2">
-        <v>46</v>
-      </c>
       <c r="BD2">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BE2">
         <v>55</v>
       </c>
       <c r="BF2">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="BG2">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="BH2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI2">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="BJ2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12.5</v>
+        <v>7.4</v>
       </c>
       <c r="BN2">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BO2">
-        <v>6.6</v>
+        <v>3.85</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="BT2">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BU2">
+        <v>3.65</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>4.7</v>
+      </c>
+      <c r="BX2">
+        <v>26</v>
+      </c>
+      <c r="BY2">
         <v>3.85</v>
       </c>
-      <c r="BV2">
-        <v>12</v>
-      </c>
-      <c r="BW2">
-        <v>6.4</v>
-      </c>
-      <c r="BX2">
-        <v>27</v>
-      </c>
-      <c r="BY2">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BZ2">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>8.4</v>
+        <v>4.7</v>
       </c>
       <c r="CB2" t="s">
         <v>111</v>
@@ -1185,178 +1185,178 @@
         <v>103</v>
       </c>
       <c r="F3">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G3">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="H3">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I3">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="J3">
+        <v>2.7</v>
+      </c>
+      <c r="K3">
         <v>2.86</v>
       </c>
-      <c r="K3">
-        <v>3.05</v>
-      </c>
       <c r="L3">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="M3">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="N3">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="O3">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="P3">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="Q3">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="R3">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="S3">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="T3">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="U3">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="V3">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W3">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X3">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="Y3">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA3">
-        <v>230</v>
+        <v>160</v>
       </c>
       <c r="AB3">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AC3">
         <v>7</v>
       </c>
       <c r="AD3">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AE3">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AF3">
         <v>16</v>
       </c>
       <c r="AG3">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AH3">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AI3">
         <v>460</v>
       </c>
       <c r="AJ3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK3">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AL3">
-        <v>170</v>
+        <v>460</v>
       </c>
       <c r="AM3">
         <v>500</v>
       </c>
       <c r="AN3">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AO3">
         <v>600</v>
       </c>
       <c r="AP3">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AQ3">
+        <v>7</v>
+      </c>
+      <c r="AR3">
+        <v>9.4</v>
+      </c>
+      <c r="AS3">
+        <v>12.5</v>
+      </c>
+      <c r="AT3">
+        <v>5.9</v>
+      </c>
+      <c r="AU3">
+        <v>6.4</v>
+      </c>
+      <c r="AV3">
+        <v>10</v>
+      </c>
+      <c r="AW3">
+        <v>12</v>
+      </c>
+      <c r="AX3">
         <v>7.8</v>
       </c>
-      <c r="AR3">
-        <v>19</v>
-      </c>
-      <c r="AS3">
-        <v>22</v>
-      </c>
-      <c r="AT3">
-        <v>6.2</v>
-      </c>
-      <c r="AU3">
-        <v>6.2</v>
-      </c>
-      <c r="AV3">
-        <v>14</v>
-      </c>
-      <c r="AW3">
-        <v>38</v>
-      </c>
-      <c r="AX3">
-        <v>14</v>
-      </c>
       <c r="AY3">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA3">
         <v>13</v>
       </c>
       <c r="BB3">
-        <v>30</v>
+        <v>11.5</v>
       </c>
       <c r="BC3">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="BD3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BE3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BF3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BG3">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BH3">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="BI3">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="BJ3">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK3">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1368,43 +1368,43 @@
         <v>5.5</v>
       </c>
       <c r="BO3">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BQ3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BR3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BT3">
         <v>6.4</v>
       </c>
       <c r="BU3">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BW3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="CB3" t="s">
         <v>111</v>
@@ -1430,223 +1430,223 @@
         <v>1.12</v>
       </c>
       <c r="G4">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="H4">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="I4">
         <v>34</v>
       </c>
       <c r="J4">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="K4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="L4">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="M4">
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.02</v>
+        <v>7.2</v>
       </c>
       <c r="O4">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P4">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q4">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="R4">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S4">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="T4">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U4">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V4">
         <v>1.03</v>
       </c>
       <c r="W4">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="X4">
         <v>65</v>
       </c>
       <c r="Y4">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="Z4">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="AA4">
         <v>1000</v>
       </c>
       <c r="AB4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AD4">
         <v>110</v>
       </c>
       <c r="AE4">
-        <v>490</v>
+        <v>530</v>
       </c>
       <c r="AF4">
         <v>11</v>
       </c>
       <c r="AG4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AI4">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="AJ4">
         <v>9.6</v>
       </c>
       <c r="AK4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM4">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AN4">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AO4">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="AQ4">
         <v>7.4</v>
       </c>
       <c r="AR4">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AS4">
         <v>4.2</v>
       </c>
       <c r="AT4">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU4">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV4">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="AW4">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX4">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AY4">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AZ4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BA4">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BC4">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BD4">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE4">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="BF4">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="BG4">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH4">
         <v>6.8</v>
       </c>
       <c r="BI4">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BJ4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BK4">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BN4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO4">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BP4">
         <v>6</v>
       </c>
       <c r="BQ4">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BR4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BS4">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BT4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BU4">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BZ4">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="CA4">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="CB4" t="s">
         <v>111</v>
@@ -1684,7 +1684,7 @@
         <v>3.5</v>
       </c>
       <c r="K5">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L5">
         <v>1.53</v>
@@ -1702,7 +1702,7 @@
         <v>1.56</v>
       </c>
       <c r="Q5">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="R5">
         <v>1.2</v>
@@ -1714,7 +1714,7 @@
         <v>2.44</v>
       </c>
       <c r="U5">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V5">
         <v>1.15</v>
@@ -1729,7 +1729,7 @@
         <v>16.5</v>
       </c>
       <c r="Z5">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AA5">
         <v>900</v>
@@ -1777,7 +1777,7 @@
         <v>440</v>
       </c>
       <c r="AP5">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AQ5">
         <v>7.2</v>
@@ -1798,7 +1798,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AX5">
         <v>5</v>
@@ -1810,7 +1810,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BB5">
         <v>7.4</v>
@@ -1828,10 +1828,10 @@
         <v>7.4</v>
       </c>
       <c r="BG5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH5">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BI5">
         <v>2.26</v>
@@ -1858,7 +1858,7 @@
         <v>12.5</v>
       </c>
       <c r="BQ5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BR5">
         <v>1000</v>
@@ -1870,7 +1870,7 @@
         <v>11</v>
       </c>
       <c r="BU5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BV5">
         <v>1000</v>
@@ -1911,7 +1911,7 @@
         <v>106</v>
       </c>
       <c r="F6">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G6">
         <v>2.78</v>
@@ -1926,7 +1926,7 @@
         <v>3.15</v>
       </c>
       <c r="K6">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L6">
         <v>1.55</v>
@@ -1941,7 +1941,7 @@
         <v>1.51</v>
       </c>
       <c r="P6">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q6">
         <v>2.56</v>
@@ -1959,7 +1959,7 @@
         <v>1.83</v>
       </c>
       <c r="V6">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W6">
         <v>1.56</v>
@@ -2028,7 +2028,7 @@
         <v>16</v>
       </c>
       <c r="AS6">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="AT6">
         <v>7.2</v>
@@ -2040,7 +2040,7 @@
         <v>12</v>
       </c>
       <c r="AW6">
-        <v>30</v>
+        <v>4.9</v>
       </c>
       <c r="AX6">
         <v>14</v>
@@ -2052,37 +2052,37 @@
         <v>15.5</v>
       </c>
       <c r="BA6">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BB6">
-        <v>28</v>
+        <v>4.9</v>
       </c>
       <c r="BC6">
-        <v>24</v>
+        <v>4.8</v>
       </c>
       <c r="BD6">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="BE6">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF6">
-        <v>26</v>
+        <v>4.8</v>
       </c>
       <c r="BG6">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2091,43 +2091,43 @@
         <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ6">
         <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS6">
         <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW6">
         <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY6">
         <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA6">
         <v>1.01</v>
@@ -2153,25 +2153,25 @@
         <v>107</v>
       </c>
       <c r="F7">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="G7">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H7">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I7">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="J7">
         <v>3.25</v>
       </c>
       <c r="K7">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L7">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M7">
         <v>1.09</v>
@@ -2183,28 +2183,28 @@
         <v>1.42</v>
       </c>
       <c r="P7">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q7">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R7">
         <v>1.27</v>
       </c>
       <c r="S7">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T7">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U7">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V7">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X7">
         <v>11.5</v>
@@ -2231,13 +2231,13 @@
         <v>140</v>
       </c>
       <c r="AF7">
-        <v>15.5</v>
+        <v>36</v>
       </c>
       <c r="AG7">
         <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AI7">
         <v>370</v>
@@ -2249,79 +2249,79 @@
         <v>90</v>
       </c>
       <c r="AL7">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AM7">
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AO7">
         <v>500</v>
       </c>
       <c r="AP7">
+        <v>5.8</v>
+      </c>
+      <c r="AQ7">
         <v>9.6</v>
       </c>
-      <c r="AQ7">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AR7">
-        <v>18</v>
+        <v>7.6</v>
       </c>
       <c r="AS7">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT7">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AU7">
         <v>6.6</v>
       </c>
       <c r="AV7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW7">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX7">
-        <v>13.5</v>
+        <v>6.6</v>
       </c>
       <c r="AY7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC7">
         <v>8.6</v>
       </c>
-      <c r="BB7">
+      <c r="BD7">
+        <v>9.4</v>
+      </c>
+      <c r="BE7">
+        <v>10.5</v>
+      </c>
+      <c r="BF7">
         <v>8.4</v>
       </c>
-      <c r="BC7">
-        <v>8</v>
-      </c>
-      <c r="BD7">
-        <v>8.6</v>
-      </c>
-      <c r="BE7">
+      <c r="BG7">
         <v>9.4</v>
       </c>
-      <c r="BF7">
-        <v>7.6</v>
-      </c>
-      <c r="BG7">
-        <v>8.4</v>
-      </c>
       <c r="BH7">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI7">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="BJ7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK7">
         <v>6</v>
@@ -2330,7 +2330,7 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BN7">
         <v>5.3</v>
@@ -2342,13 +2342,13 @@
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT7">
         <v>6.4</v>
@@ -2360,19 +2360,19 @@
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB7" t="s">
         <v>111</v>
@@ -2395,13 +2395,13 @@
         <v>108</v>
       </c>
       <c r="F8">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G8">
         <v>3.05</v>
       </c>
       <c r="H8">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I8">
         <v>2.96</v>
@@ -2419,10 +2419,10 @@
         <v>1.12</v>
       </c>
       <c r="N8">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="O8">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P8">
         <v>1.57</v>
@@ -2437,7 +2437,7 @@
         <v>5.2</v>
       </c>
       <c r="T8">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="U8">
         <v>1.83</v>
@@ -2503,43 +2503,43 @@
         <v>55</v>
       </c>
       <c r="AP8">
-        <v>8</v>
+        <v>3.85</v>
       </c>
       <c r="AQ8">
-        <v>7.4</v>
+        <v>3.85</v>
       </c>
       <c r="AR8">
-        <v>15</v>
+        <v>4.5</v>
       </c>
       <c r="AS8">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT8">
-        <v>7.8</v>
+        <v>3.85</v>
       </c>
       <c r="AU8">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV8">
         <v>4.2</v>
       </c>
       <c r="AW8">
-        <v>32</v>
+        <v>5.1</v>
       </c>
       <c r="AX8">
-        <v>15.5</v>
+        <v>4.5</v>
       </c>
       <c r="AY8">
-        <v>11.5</v>
+        <v>4.2</v>
       </c>
       <c r="AZ8">
-        <v>16.5</v>
+        <v>4.7</v>
       </c>
       <c r="BA8">
         <v>5.3</v>
       </c>
       <c r="BB8">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BC8">
         <v>5.1</v>
@@ -2557,13 +2557,13 @@
         <v>5.2</v>
       </c>
       <c r="BH8">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="BI8">
         <v>2.32</v>
       </c>
       <c r="BJ8">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK8">
         <v>8.6</v>
@@ -2572,49 +2572,49 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BN8">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BO8">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP8">
         <v>28</v>
       </c>
       <c r="BQ8">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BR8">
         <v>50</v>
       </c>
       <c r="BS8">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT8">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BU8">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BV8">
         <v>28</v>
       </c>
       <c r="BW8">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BX8">
         <v>50</v>
       </c>
       <c r="BY8">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ8">
         <v>50</v>
       </c>
       <c r="CA8">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB8" t="s">
         <v>111</v>
@@ -2637,19 +2637,19 @@
         <v>109</v>
       </c>
       <c r="F9">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G9">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H9">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I9">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J9">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K9">
         <v>3.45</v>
@@ -2670,7 +2670,7 @@
         <v>1.66</v>
       </c>
       <c r="Q9">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R9">
         <v>1.23</v>
@@ -2679,43 +2679,43 @@
         <v>5.1</v>
       </c>
       <c r="T9">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U9">
         <v>1.84</v>
       </c>
       <c r="V9">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W9">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="X9">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA9">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AB9">
         <v>7.4</v>
       </c>
       <c r="AC9">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD9">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE9">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AF9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG9">
         <v>10.5</v>
@@ -2727,7 +2727,7 @@
         <v>95</v>
       </c>
       <c r="AJ9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK9">
         <v>26</v>
@@ -2736,7 +2736,7 @@
         <v>55</v>
       </c>
       <c r="AM9">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN9">
         <v>21</v>
@@ -2748,37 +2748,37 @@
         <v>9</v>
       </c>
       <c r="AQ9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS9">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AT9">
         <v>6.6</v>
       </c>
       <c r="AU9">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV9">
         <v>17.5</v>
       </c>
       <c r="AW9">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AX9">
         <v>9.800000000000001</v>
       </c>
       <c r="AY9">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9">
         <v>21</v>
       </c>
       <c r="BA9">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="BB9">
         <v>21</v>
@@ -2793,13 +2793,13 @@
         <v>120</v>
       </c>
       <c r="BF9">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BG9">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="BH9">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BI9">
         <v>2.66</v>
@@ -2808,16 +2808,16 @@
         <v>11.5</v>
       </c>
       <c r="BK9">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BM9">
         <v>140</v>
       </c>
       <c r="BN9">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO9">
         <v>4</v>
@@ -2826,37 +2826,37 @@
         <v>19</v>
       </c>
       <c r="BQ9">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BR9">
+        <v>36</v>
+      </c>
+      <c r="BS9">
+        <v>6</v>
+      </c>
+      <c r="BT9">
+        <v>7.6</v>
+      </c>
+      <c r="BU9">
+        <v>3.65</v>
+      </c>
+      <c r="BV9">
         <v>44</v>
       </c>
-      <c r="BS9">
-        <v>5</v>
-      </c>
-      <c r="BT9">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BU9">
-        <v>3.6</v>
-      </c>
-      <c r="BV9">
+      <c r="BW9">
+        <v>6</v>
+      </c>
+      <c r="BX9">
         <v>60</v>
       </c>
-      <c r="BW9">
-        <v>5.1</v>
-      </c>
-      <c r="BX9">
-        <v>1000</v>
-      </c>
       <c r="BY9">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ9">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="CA9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CB9" t="s">
         <v>111</v>
@@ -2879,7 +2879,7 @@
         <v>110</v>
       </c>
       <c r="F10">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="G10">
         <v>1.36</v>
@@ -2888,46 +2888,46 @@
         <v>11.5</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="J10">
         <v>5.5</v>
       </c>
       <c r="K10">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>1.31</v>
       </c>
       <c r="M10">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P10">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q10">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R10">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S10">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T10">
         <v>2.1</v>
       </c>
       <c r="U10">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V10">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W10">
         <v>3.75</v>
@@ -2942,7 +2942,7 @@
         <v>130</v>
       </c>
       <c r="AA10">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="AB10">
         <v>9.199999999999999</v>
@@ -2957,7 +2957,7 @@
         <v>200</v>
       </c>
       <c r="AF10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG10">
         <v>10.5</v>
@@ -2972,40 +2972,40 @@
         <v>10.5</v>
       </c>
       <c r="AK10">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AL10">
         <v>42</v>
       </c>
       <c r="AM10">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN10">
         <v>5.2</v>
       </c>
       <c r="AO10">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="AP10">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AQ10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS10">
         <v>13.5</v>
       </c>
       <c r="AT10">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU10">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AV10">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="AW10">
         <v>13</v>
@@ -3014,22 +3014,22 @@
         <v>7.4</v>
       </c>
       <c r="AY10">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10">
         <v>21</v>
       </c>
       <c r="BA10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BB10">
         <v>9.199999999999999</v>
       </c>
       <c r="BC10">
-        <v>7.4</v>
+        <v>12.5</v>
       </c>
       <c r="BD10">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="BE10">
         <v>13</v>
@@ -3038,7 +3038,7 @@
         <v>4.7</v>
       </c>
       <c r="BG10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH10">
         <v>4.2</v>
@@ -3062,7 +3062,7 @@
         <v>3.8</v>
       </c>
       <c r="BO10">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BP10">
         <v>7.6</v>
@@ -3080,7 +3080,7 @@
         <v>14</v>
       </c>
       <c r="BU10">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BV10">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -349,7 +349,7 @@
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-09-22 03:59:47</t>
+    <t>2026-09-22 06:10:38</t>
   </si>
 </sst>
 </file>
@@ -943,58 +943,58 @@
         <v>102</v>
       </c>
       <c r="F2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="G2">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="H2">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="I2">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="J2">
+        <v>4.2</v>
+      </c>
+      <c r="K2">
         <v>4.5</v>
       </c>
-      <c r="K2">
-        <v>4.8</v>
-      </c>
       <c r="L2">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M2">
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O2">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P2">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q2">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R2">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S2">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T2">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="U2">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="V2">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="W2">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X2">
         <v>16.5</v>
@@ -1003,13 +1003,13 @@
         <v>8.4</v>
       </c>
       <c r="Z2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AA2">
         <v>15.5</v>
       </c>
       <c r="AB2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC2">
         <v>10.5</v>
@@ -1018,16 +1018,16 @@
         <v>10.5</v>
       </c>
       <c r="AE2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AG2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI2">
         <v>40</v>
@@ -1036,133 +1036,133 @@
         <v>700</v>
       </c>
       <c r="AK2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AL2">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AM2">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN2">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AO2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AP2">
+        <v>14</v>
+      </c>
+      <c r="AQ2">
+        <v>7.6</v>
+      </c>
+      <c r="AR2">
+        <v>8.4</v>
+      </c>
+      <c r="AS2">
+        <v>14</v>
+      </c>
+      <c r="AT2">
+        <v>18.5</v>
+      </c>
+      <c r="AU2">
         <v>8.6</v>
-      </c>
-      <c r="AP2">
-        <v>12.5</v>
-      </c>
-      <c r="AQ2">
-        <v>7</v>
-      </c>
-      <c r="AR2">
-        <v>7.6</v>
-      </c>
-      <c r="AS2">
-        <v>12.5</v>
-      </c>
-      <c r="AT2">
-        <v>21</v>
-      </c>
-      <c r="AU2">
-        <v>8.800000000000001</v>
       </c>
       <c r="AV2">
         <v>9.199999999999999</v>
       </c>
       <c r="AW2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX2">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AY2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AZ2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BB2">
         <v>100</v>
       </c>
       <c r="BC2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BD2">
         <v>55</v>
       </c>
       <c r="BE2">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="BF2">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BG2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BH2">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="s">
         <v>111</v>
@@ -1185,226 +1185,226 @@
         <v>103</v>
       </c>
       <c r="F3">
-        <v>2.66</v>
+        <v>2.2</v>
       </c>
       <c r="G3">
-        <v>2.84</v>
+        <v>2.28</v>
       </c>
       <c r="H3">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="I3">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="J3">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="K3">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="L3">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="M3">
         <v>1.2</v>
       </c>
       <c r="N3">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="O3">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="P3">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Q3">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="R3">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="S3">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="T3">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="U3">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="W3">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="X3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="Y3">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="Z3">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AA3">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AB3">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="AC3">
+        <v>7.8</v>
+      </c>
+      <c r="AD3">
+        <v>26</v>
+      </c>
+      <c r="AE3">
+        <v>140</v>
+      </c>
+      <c r="AF3">
+        <v>11.5</v>
+      </c>
+      <c r="AG3">
+        <v>14</v>
+      </c>
+      <c r="AH3">
+        <v>46</v>
+      </c>
+      <c r="AI3">
+        <v>210</v>
+      </c>
+      <c r="AJ3">
+        <v>34</v>
+      </c>
+      <c r="AK3">
+        <v>44</v>
+      </c>
+      <c r="AL3">
+        <v>120</v>
+      </c>
+      <c r="AM3">
+        <v>550</v>
+      </c>
+      <c r="AN3">
+        <v>55</v>
+      </c>
+      <c r="AO3">
+        <v>310</v>
+      </c>
+      <c r="AP3">
+        <v>5.3</v>
+      </c>
+      <c r="AQ3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR3">
+        <v>17</v>
+      </c>
+      <c r="AS3">
+        <v>15</v>
+      </c>
+      <c r="AT3">
+        <v>5.1</v>
+      </c>
+      <c r="AU3">
         <v>7</v>
       </c>
-      <c r="AD3">
-        <v>19</v>
-      </c>
-      <c r="AE3">
-        <v>130</v>
-      </c>
-      <c r="AF3">
+      <c r="AV3">
+        <v>21</v>
+      </c>
+      <c r="AW3">
+        <v>15</v>
+      </c>
+      <c r="AX3">
+        <v>10</v>
+      </c>
+      <c r="AY3">
+        <v>12.5</v>
+      </c>
+      <c r="AZ3">
+        <v>32</v>
+      </c>
+      <c r="BA3">
+        <v>15.5</v>
+      </c>
+      <c r="BB3">
+        <v>14</v>
+      </c>
+      <c r="BC3">
+        <v>38</v>
+      </c>
+      <c r="BD3">
+        <v>14.5</v>
+      </c>
+      <c r="BE3">
         <v>16</v>
       </c>
-      <c r="AG3">
-        <v>15.5</v>
-      </c>
-      <c r="AH3">
-        <v>42</v>
-      </c>
-      <c r="AI3">
-        <v>460</v>
-      </c>
-      <c r="AJ3">
-        <v>55</v>
-      </c>
-      <c r="AK3">
-        <v>70</v>
-      </c>
-      <c r="AL3">
-        <v>460</v>
-      </c>
-      <c r="AM3">
-        <v>500</v>
-      </c>
-      <c r="AN3">
-        <v>150</v>
-      </c>
-      <c r="AO3">
-        <v>600</v>
-      </c>
-      <c r="AP3">
-        <v>5.5</v>
-      </c>
-      <c r="AQ3">
-        <v>7</v>
-      </c>
-      <c r="AR3">
-        <v>9.4</v>
-      </c>
-      <c r="AS3">
-        <v>12.5</v>
-      </c>
-      <c r="AT3">
-        <v>5.9</v>
-      </c>
-      <c r="AU3">
-        <v>6.4</v>
-      </c>
-      <c r="AV3">
-        <v>10</v>
-      </c>
-      <c r="AW3">
-        <v>12</v>
-      </c>
-      <c r="AX3">
-        <v>7.8</v>
-      </c>
-      <c r="AY3">
-        <v>9.4</v>
-      </c>
-      <c r="AZ3">
-        <v>10.5</v>
-      </c>
-      <c r="BA3">
-        <v>13</v>
-      </c>
-      <c r="BB3">
-        <v>11.5</v>
-      </c>
-      <c r="BC3">
-        <v>11.5</v>
-      </c>
-      <c r="BD3">
-        <v>12.5</v>
-      </c>
-      <c r="BE3">
-        <v>15</v>
-      </c>
       <c r="BF3">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BG3">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH3">
-        <v>2.32</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.14</v>
+        <v>1.24</v>
       </c>
       <c r="BJ3">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>10.5</v>
+        <v>1.02</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>21</v>
+        <v>1.02</v>
       </c>
       <c r="BN3">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>4.9</v>
+        <v>1.77</v>
       </c>
       <c r="BP3">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>22</v>
+        <v>1.02</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>50</v>
+        <v>1.02</v>
       </c>
       <c r="BT3">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>5.7</v>
+        <v>1.02</v>
       </c>
       <c r="BV3">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>30</v>
+        <v>1.73</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>21</v>
+        <v>1.02</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>21</v>
+        <v>1.02</v>
       </c>
       <c r="CB3" t="s">
         <v>111</v>
@@ -1430,7 +1430,7 @@
         <v>1.12</v>
       </c>
       <c r="G4">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="H4">
         <v>11.5</v>
@@ -1439,7 +1439,7 @@
         <v>34</v>
       </c>
       <c r="J4">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>13.5</v>
@@ -1451,25 +1451,25 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>7.2</v>
+        <v>3.45</v>
       </c>
       <c r="O4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P4">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="Q4">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="R4">
         <v>2.06</v>
       </c>
       <c r="S4">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="T4">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U4">
         <v>1.65</v>
@@ -1478,7 +1478,7 @@
         <v>1.03</v>
       </c>
       <c r="W4">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="X4">
         <v>65</v>
@@ -1487,7 +1487,7 @@
         <v>120</v>
       </c>
       <c r="Z4">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AA4">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
         <v>110</v>
       </c>
       <c r="AE4">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="AF4">
         <v>11</v>
@@ -1520,7 +1520,7 @@
         <v>9.6</v>
       </c>
       <c r="AK4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL4">
         <v>55</v>
@@ -1529,52 +1529,52 @@
         <v>270</v>
       </c>
       <c r="AN4">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AO4">
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>2.14</v>
+        <v>7</v>
       </c>
       <c r="AQ4">
         <v>7.4</v>
       </c>
       <c r="AR4">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS4">
         <v>4.2</v>
       </c>
       <c r="AT4">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AU4">
         <v>6.2</v>
       </c>
       <c r="AV4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX4">
         <v>4.6</v>
       </c>
       <c r="AY4">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AZ4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BA4">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB4">
         <v>4.3</v>
       </c>
       <c r="BC4">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BD4">
         <v>6.8</v>
@@ -1595,7 +1595,7 @@
         <v>3.6</v>
       </c>
       <c r="BJ4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BK4">
         <v>5.2</v>
@@ -1604,13 +1604,13 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BN4">
         <v>4.4</v>
       </c>
       <c r="BO4">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BP4">
         <v>6</v>
@@ -1622,7 +1622,7 @@
         <v>23</v>
       </c>
       <c r="BS4">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BT4">
         <v>26</v>
@@ -1634,7 +1634,7 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX4">
         <v>1000</v>
@@ -1646,7 +1646,7 @@
         <v>5.9</v>
       </c>
       <c r="CA4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="CB4" t="s">
         <v>111</v>
@@ -1669,64 +1669,64 @@
         <v>105</v>
       </c>
       <c r="F5">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="G5">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L5">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="M5">
         <v>1.12</v>
       </c>
       <c r="N5">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O5">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P5">
         <v>1.56</v>
       </c>
       <c r="Q5">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="R5">
         <v>1.2</v>
       </c>
       <c r="S5">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="T5">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="U5">
         <v>1.6</v>
       </c>
       <c r="V5">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W5">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="X5">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Y5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z5">
         <v>500</v>
@@ -1747,7 +1747,7 @@
         <v>700</v>
       </c>
       <c r="AF5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG5">
         <v>11.5</v>
@@ -1759,10 +1759,10 @@
         <v>700</v>
       </c>
       <c r="AJ5">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL5">
         <v>160</v>
@@ -1771,70 +1771,70 @@
         <v>700</v>
       </c>
       <c r="AN5">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO5">
-        <v>440</v>
+        <v>980</v>
       </c>
       <c r="AP5">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="AQ5">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="AR5">
-        <v>10.5</v>
+        <v>26</v>
       </c>
       <c r="AS5">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AT5">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AU5">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="AW5">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="AX5">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AY5">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ5">
-        <v>9.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="BB5">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="BC5">
-        <v>8.4</v>
+        <v>15.5</v>
       </c>
       <c r="BD5">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="BE5">
+        <v>13.5</v>
+      </c>
+      <c r="BF5">
         <v>12</v>
       </c>
-      <c r="BF5">
-        <v>7.4</v>
-      </c>
       <c r="BG5">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BH5">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BI5">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="BJ5">
         <v>13.5</v>
@@ -1849,16 +1849,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN5">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BO5">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="BP5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR5">
         <v>1000</v>
@@ -1867,10 +1867,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BT5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV5">
         <v>1000</v>
@@ -1885,7 +1885,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BZ5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA5">
         <v>8.800000000000001</v>
@@ -1914,7 +1914,7 @@
         <v>2.64</v>
       </c>
       <c r="G6">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -1926,7 +1926,7 @@
         <v>3.15</v>
       </c>
       <c r="K6">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L6">
         <v>1.55</v>
@@ -1935,19 +1935,19 @@
         <v>1.11</v>
       </c>
       <c r="N6">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O6">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P6">
         <v>1.6</v>
       </c>
       <c r="Q6">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R6">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S6">
         <v>5.1</v>
@@ -1956,28 +1956,28 @@
         <v>2</v>
       </c>
       <c r="U6">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V6">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W6">
         <v>1.56</v>
       </c>
       <c r="X6">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z6">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AA6">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB6">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC6">
         <v>7.6</v>
@@ -1995,7 +1995,7 @@
         <v>15.5</v>
       </c>
       <c r="AH6">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AI6">
         <v>100</v>
@@ -2019,19 +2019,19 @@
         <v>75</v>
       </c>
       <c r="AP6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ6">
         <v>8.199999999999999</v>
       </c>
       <c r="AR6">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS6">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="AT6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU6">
         <v>6.2</v>
@@ -2040,7 +2040,7 @@
         <v>12</v>
       </c>
       <c r="AW6">
-        <v>4.9</v>
+        <v>29</v>
       </c>
       <c r="AX6">
         <v>14</v>
@@ -2049,40 +2049,40 @@
         <v>11</v>
       </c>
       <c r="AZ6">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BA6">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="BB6">
-        <v>4.9</v>
+        <v>29</v>
       </c>
       <c r="BC6">
-        <v>4.8</v>
+        <v>26</v>
       </c>
       <c r="BD6">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="BE6">
-        <v>5.2</v>
+        <v>65</v>
       </c>
       <c r="BF6">
-        <v>4.8</v>
+        <v>30</v>
       </c>
       <c r="BG6">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="BH6">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2091,43 +2091,43 @@
         <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
         <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
         <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
         <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
         <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
         <v>1.01</v>
@@ -2153,16 +2153,16 @@
         <v>107</v>
       </c>
       <c r="F7">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="G7">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="H7">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="I7">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="J7">
         <v>3.25</v>
@@ -2180,7 +2180,7 @@
         <v>3.15</v>
       </c>
       <c r="O7">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P7">
         <v>1.72</v>
@@ -2198,181 +2198,181 @@
         <v>1.9</v>
       </c>
       <c r="U7">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W7">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="X7">
         <v>11.5</v>
       </c>
       <c r="Y7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z7">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="AA7">
         <v>220</v>
       </c>
       <c r="AB7">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC7">
         <v>7.6</v>
       </c>
       <c r="AD7">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE7">
         <v>140</v>
       </c>
       <c r="AF7">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="AG7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH7">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AI7">
         <v>370</v>
       </c>
       <c r="AJ7">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AK7">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="AL7">
-        <v>500</v>
+        <v>370</v>
       </c>
       <c r="AM7">
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AO7">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AP7">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AQ7">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR7">
-        <v>7.6</v>
+        <v>17</v>
       </c>
       <c r="AS7">
-        <v>9.800000000000001</v>
+        <v>46</v>
       </c>
       <c r="AT7">
+        <v>7.8</v>
+      </c>
+      <c r="AU7">
         <v>6.8</v>
       </c>
-      <c r="AU7">
-        <v>6.6</v>
-      </c>
       <c r="AV7">
+        <v>13</v>
+      </c>
+      <c r="AW7">
+        <v>29</v>
+      </c>
+      <c r="AX7">
         <v>12.5</v>
       </c>
-      <c r="AW7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX7">
-        <v>6.6</v>
-      </c>
       <c r="AY7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ7">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA7">
-        <v>9.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="BB7">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BC7">
-        <v>8.6</v>
+        <v>22</v>
       </c>
       <c r="BD7">
-        <v>9.4</v>
+        <v>34</v>
       </c>
       <c r="BE7">
-        <v>10.5</v>
+        <v>90</v>
       </c>
       <c r="BF7">
-        <v>8.4</v>
+        <v>19</v>
       </c>
       <c r="BG7">
-        <v>9.4</v>
+        <v>32</v>
       </c>
       <c r="BH7">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
         <v>111</v>
@@ -2395,13 +2395,13 @@
         <v>108</v>
       </c>
       <c r="F8">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G8">
         <v>3.05</v>
       </c>
       <c r="H8">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I8">
         <v>2.96</v>
@@ -2425,7 +2425,7 @@
         <v>1.52</v>
       </c>
       <c r="P8">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q8">
         <v>2.6</v>
@@ -2437,10 +2437,10 @@
         <v>5.2</v>
       </c>
       <c r="T8">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U8">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V8">
         <v>1.51</v>
@@ -2449,19 +2449,19 @@
         <v>1.48</v>
       </c>
       <c r="X8">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y8">
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA8">
         <v>60</v>
       </c>
       <c r="AB8">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC8">
         <v>7.6</v>
@@ -2473,13 +2473,13 @@
         <v>48</v>
       </c>
       <c r="AF8">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG8">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AH8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI8">
         <v>75</v>
@@ -2503,64 +2503,64 @@
         <v>55</v>
       </c>
       <c r="AP8">
-        <v>3.85</v>
+        <v>7.4</v>
       </c>
       <c r="AQ8">
-        <v>3.85</v>
+        <v>7.6</v>
       </c>
       <c r="AR8">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="AS8">
-        <v>5.2</v>
+        <v>34</v>
       </c>
       <c r="AT8">
-        <v>3.85</v>
+        <v>7.6</v>
       </c>
       <c r="AU8">
         <v>6.2</v>
       </c>
       <c r="AV8">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AW8">
-        <v>5.1</v>
+        <v>27</v>
       </c>
       <c r="AX8">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="AY8">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8">
-        <v>4.7</v>
+        <v>17</v>
       </c>
       <c r="BA8">
-        <v>5.3</v>
+        <v>28</v>
       </c>
       <c r="BB8">
-        <v>5.2</v>
+        <v>36</v>
       </c>
       <c r="BC8">
-        <v>5.1</v>
+        <v>29</v>
       </c>
       <c r="BD8">
-        <v>5.3</v>
+        <v>44</v>
       </c>
       <c r="BE8">
-        <v>5.6</v>
+        <v>28</v>
       </c>
       <c r="BF8">
-        <v>5.2</v>
+        <v>38</v>
       </c>
       <c r="BG8">
-        <v>5.2</v>
+        <v>20</v>
       </c>
       <c r="BH8">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI8">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ8">
         <v>11.5</v>
@@ -2572,13 +2572,13 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN8">
         <v>6</v>
       </c>
       <c r="BO8">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BP8">
         <v>28</v>
@@ -2590,7 +2590,7 @@
         <v>50</v>
       </c>
       <c r="BS8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT8">
         <v>5.9</v>
@@ -2599,22 +2599,22 @@
         <v>4.9</v>
       </c>
       <c r="BV8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BW8">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX8">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ8">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="CA8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB8" t="s">
         <v>111</v>
@@ -2637,37 +2637,37 @@
         <v>109</v>
       </c>
       <c r="F9">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G9">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H9">
         <v>4.6</v>
       </c>
       <c r="I9">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J9">
+        <v>3.3</v>
+      </c>
+      <c r="K9">
         <v>3.35</v>
       </c>
-      <c r="K9">
-        <v>3.45</v>
-      </c>
       <c r="L9">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M9">
         <v>1.11</v>
       </c>
       <c r="N9">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="O9">
         <v>1.49</v>
       </c>
       <c r="P9">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="Q9">
         <v>2.5</v>
@@ -2676,58 +2676,58 @@
         <v>1.23</v>
       </c>
       <c r="S9">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T9">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U9">
         <v>1.84</v>
       </c>
       <c r="V9">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W9">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X9">
         <v>10.5</v>
       </c>
       <c r="Y9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z9">
         <v>32</v>
       </c>
       <c r="AA9">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB9">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC9">
         <v>7.4</v>
       </c>
       <c r="AD9">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AE9">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF9">
+        <v>10.5</v>
+      </c>
+      <c r="AG9">
         <v>11</v>
-      </c>
-      <c r="AG9">
-        <v>10.5</v>
       </c>
       <c r="AH9">
         <v>24</v>
       </c>
       <c r="AI9">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK9">
         <v>26</v>
@@ -2736,13 +2736,13 @@
         <v>55</v>
       </c>
       <c r="AM9">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN9">
         <v>21</v>
       </c>
       <c r="AO9">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP9">
         <v>9</v>
@@ -2754,7 +2754,7 @@
         <v>29</v>
       </c>
       <c r="AS9">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AT9">
         <v>6.6</v>
@@ -2766,7 +2766,7 @@
         <v>17.5</v>
       </c>
       <c r="AW9">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AX9">
         <v>9.800000000000001</v>
@@ -2778,7 +2778,7 @@
         <v>21</v>
       </c>
       <c r="BA9">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BB9">
         <v>21</v>
@@ -2787,7 +2787,7 @@
         <v>23</v>
       </c>
       <c r="BD9">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="BE9">
         <v>120</v>
@@ -2796,67 +2796,67 @@
         <v>19</v>
       </c>
       <c r="BG9">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BH9">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
         <v>2.66</v>
       </c>
       <c r="BJ9">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="BL9">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
         <v>140</v>
       </c>
       <c r="BN9">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BP9">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BR9">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>6</v>
+        <v>1.02</v>
       </c>
       <c r="BT9">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="BV9">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
         <v>111</v>
@@ -2879,22 +2879,22 @@
         <v>110</v>
       </c>
       <c r="F10">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="G10">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="H10">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="I10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="J10">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L10">
         <v>1.31</v>
@@ -2918,22 +2918,22 @@
         <v>1.54</v>
       </c>
       <c r="S10">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T10">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U10">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="V10">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W10">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="X10">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Y10">
         <v>42</v>
@@ -2942,34 +2942,34 @@
         <v>130</v>
       </c>
       <c r="AA10">
-        <v>540</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD10">
         <v>48</v>
       </c>
       <c r="AE10">
+        <v>240</v>
+      </c>
+      <c r="AF10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG10">
+        <v>11</v>
+      </c>
+      <c r="AH10">
+        <v>36</v>
+      </c>
+      <c r="AI10">
         <v>200</v>
       </c>
-      <c r="AF10">
-        <v>8.6</v>
-      </c>
-      <c r="AG10">
-        <v>10.5</v>
-      </c>
-      <c r="AH10">
-        <v>32</v>
-      </c>
-      <c r="AI10">
-        <v>160</v>
-      </c>
       <c r="AJ10">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK10">
         <v>15</v>
@@ -2981,49 +2981,49 @@
         <v>190</v>
       </c>
       <c r="AN10">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AO10">
-        <v>320</v>
+        <v>390</v>
       </c>
       <c r="AP10">
-        <v>16.5</v>
+        <v>7.6</v>
       </c>
       <c r="AQ10">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR10">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="AS10">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AT10">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AW10">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX10">
         <v>7.4</v>
       </c>
       <c r="AY10">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10">
         <v>21</v>
       </c>
       <c r="BA10">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB10">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BC10">
         <v>12.5</v>
@@ -3032,19 +3032,19 @@
         <v>32</v>
       </c>
       <c r="BE10">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF10">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BG10">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BH10">
         <v>4.2</v>
       </c>
       <c r="BI10">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ10">
         <v>12.5</v>
@@ -3056,28 +3056,28 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BN10">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BO10">
         <v>3.45</v>
       </c>
       <c r="BP10">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BQ10">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BR10">
         <v>24</v>
       </c>
       <c r="BS10">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BU10">
         <v>10.5</v>
@@ -3086,16 +3086,16 @@
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BZ10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA10">
         <v>9.199999999999999</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -349,7 +349,7 @@
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-09-22 06:10:38</t>
+    <t>2026-09-22 08:21:15</t>
   </si>
 </sst>
 </file>
@@ -943,25 +943,25 @@
         <v>102</v>
       </c>
       <c r="F2">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="H2">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="I2">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="J2">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K2">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L2">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M2">
         <v>1.06</v>
@@ -973,28 +973,28 @@
         <v>1.3</v>
       </c>
       <c r="P2">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q2">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R2">
         <v>1.4</v>
       </c>
       <c r="S2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T2">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="U2">
         <v>1.9</v>
       </c>
       <c r="V2">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="W2">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X2">
         <v>16.5</v>
@@ -1003,10 +1003,10 @@
         <v>8.4</v>
       </c>
       <c r="Z2">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AB2">
         <v>22</v>
@@ -1018,37 +1018,37 @@
         <v>10.5</v>
       </c>
       <c r="AE2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AF2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AG2">
+        <v>27</v>
+      </c>
+      <c r="AH2">
         <v>26</v>
-      </c>
-      <c r="AH2">
-        <v>24</v>
       </c>
       <c r="AI2">
         <v>40</v>
       </c>
       <c r="AJ2">
-        <v>700</v>
+        <v>280</v>
       </c>
       <c r="AK2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AL2">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AM2">
         <v>580</v>
       </c>
       <c r="AN2">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AO2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AP2">
         <v>14</v>
@@ -1057,16 +1057,16 @@
         <v>7.6</v>
       </c>
       <c r="AR2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT2">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AU2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV2">
         <v>9.199999999999999</v>
@@ -1075,94 +1075,94 @@
         <v>14.5</v>
       </c>
       <c r="AX2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AY2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AZ2">
         <v>21</v>
       </c>
       <c r="BA2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BC2">
+        <v>75</v>
+      </c>
+      <c r="BD2">
         <v>70</v>
       </c>
-      <c r="BD2">
-        <v>55</v>
-      </c>
       <c r="BE2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BF2">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BG2">
         <v>8</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB2" t="s">
         <v>111</v>
@@ -1185,226 +1185,226 @@
         <v>103</v>
       </c>
       <c r="F3">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="G3">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="H3">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I3">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J3">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K3">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="L3">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="M3">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="N3">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="O3">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="P3">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Q3">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="R3">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="S3">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="T3">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="U3">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="V3">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W3">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="X3">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="Y3">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z3">
         <v>34</v>
       </c>
       <c r="AA3">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB3">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AC3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD3">
+        <v>27</v>
+      </c>
+      <c r="AE3">
+        <v>160</v>
+      </c>
+      <c r="AF3">
+        <v>12</v>
+      </c>
+      <c r="AG3">
+        <v>15.5</v>
+      </c>
+      <c r="AH3">
+        <v>48</v>
+      </c>
+      <c r="AI3">
+        <v>250</v>
+      </c>
+      <c r="AJ3">
+        <v>36</v>
+      </c>
+      <c r="AK3">
+        <v>55</v>
+      </c>
+      <c r="AL3">
+        <v>150</v>
+      </c>
+      <c r="AM3">
+        <v>800</v>
+      </c>
+      <c r="AN3">
+        <v>65</v>
+      </c>
+      <c r="AO3">
+        <v>370</v>
+      </c>
+      <c r="AP3">
+        <v>4.9</v>
+      </c>
+      <c r="AQ3">
+        <v>8.4</v>
+      </c>
+      <c r="AR3">
         <v>26</v>
       </c>
-      <c r="AE3">
-        <v>140</v>
-      </c>
-      <c r="AF3">
-        <v>11.5</v>
-      </c>
-      <c r="AG3">
-        <v>14</v>
-      </c>
-      <c r="AH3">
-        <v>46</v>
-      </c>
-      <c r="AI3">
-        <v>210</v>
-      </c>
-      <c r="AJ3">
-        <v>34</v>
-      </c>
-      <c r="AK3">
-        <v>44</v>
-      </c>
-      <c r="AL3">
-        <v>120</v>
-      </c>
-      <c r="AM3">
-        <v>550</v>
-      </c>
-      <c r="AN3">
-        <v>55</v>
-      </c>
-      <c r="AO3">
-        <v>310</v>
-      </c>
-      <c r="AP3">
-        <v>5.3</v>
-      </c>
-      <c r="AQ3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR3">
-        <v>17</v>
-      </c>
       <c r="AS3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AT3">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AU3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AX3">
         <v>10</v>
       </c>
       <c r="AY3">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BA3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BB3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BD3">
         <v>14.5</v>
       </c>
       <c r="BE3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BF3">
-        <v>13.5</v>
+        <v>42</v>
       </c>
       <c r="BG3">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.14</v>
       </c>
       <c r="BI3">
-        <v>1.24</v>
+        <v>1.97</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BK3">
-        <v>1.02</v>
+        <v>2.74</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.02</v>
+        <v>3.25</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO3">
-        <v>1.77</v>
+        <v>4.2</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.02</v>
+        <v>3.3</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.02</v>
+        <v>3.15</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU3">
-        <v>1.02</v>
+        <v>4</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BW3">
-        <v>1.73</v>
+        <v>3.15</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.02</v>
+        <v>3.2</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.02</v>
+        <v>3.2</v>
       </c>
       <c r="CB3" t="s">
         <v>111</v>
@@ -1427,67 +1427,67 @@
         <v>104</v>
       </c>
       <c r="F4">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="G4">
         <v>1.17</v>
       </c>
       <c r="H4">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="I4">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J4">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="K4">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="L4">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M4">
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>3.45</v>
+        <v>8.6</v>
       </c>
       <c r="O4">
         <v>1.09</v>
       </c>
       <c r="P4">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="Q4">
         <v>1.32</v>
       </c>
       <c r="R4">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="S4">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="T4">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U4">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="V4">
         <v>1.03</v>
       </c>
       <c r="W4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="X4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="Y4">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="Z4">
-        <v>350</v>
+        <v>310</v>
       </c>
       <c r="AA4">
         <v>1000</v>
@@ -1496,13 +1496,13 @@
         <v>17</v>
       </c>
       <c r="AC4">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AD4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AE4">
-        <v>520</v>
+        <v>450</v>
       </c>
       <c r="AF4">
         <v>11</v>
@@ -1511,142 +1511,142 @@
         <v>17</v>
       </c>
       <c r="AH4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI4">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="AJ4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK4">
         <v>16.5</v>
       </c>
       <c r="AL4">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM4">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AN4">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>510</v>
       </c>
       <c r="AP4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ4">
+        <v>7.6</v>
+      </c>
+      <c r="AR4">
+        <v>8</v>
+      </c>
+      <c r="AS4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT4">
+        <v>12.5</v>
+      </c>
+      <c r="AU4">
+        <v>20</v>
+      </c>
+      <c r="AV4">
+        <v>7.6</v>
+      </c>
+      <c r="AW4">
+        <v>8.4</v>
+      </c>
+      <c r="AX4">
+        <v>8.4</v>
+      </c>
+      <c r="AY4">
+        <v>12</v>
+      </c>
+      <c r="AZ4">
+        <v>7.2</v>
+      </c>
+      <c r="BA4">
+        <v>7.8</v>
+      </c>
+      <c r="BB4">
         <v>7.4</v>
       </c>
-      <c r="AR4">
-        <v>7.6</v>
-      </c>
-      <c r="AS4">
-        <v>4.2</v>
-      </c>
-      <c r="AT4">
-        <v>5.3</v>
-      </c>
-      <c r="AU4">
-        <v>6.2</v>
-      </c>
-      <c r="AV4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW4">
-        <v>7.6</v>
-      </c>
-      <c r="AX4">
-        <v>4.6</v>
-      </c>
-      <c r="AY4">
-        <v>5.3</v>
-      </c>
-      <c r="AZ4">
-        <v>6.8</v>
-      </c>
-      <c r="BA4">
-        <v>7.6</v>
-      </c>
-      <c r="BB4">
-        <v>4.3</v>
-      </c>
       <c r="BC4">
-        <v>5.3</v>
+        <v>12</v>
       </c>
       <c r="BD4">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE4">
-        <v>2.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF4">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="BG4">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="BH4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BI4">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BJ4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BK4">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BN4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO4">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BP4">
+        <v>6.2</v>
+      </c>
+      <c r="BQ4">
+        <v>4.5</v>
+      </c>
+      <c r="BR4">
+        <v>22</v>
+      </c>
+      <c r="BS4">
         <v>6</v>
       </c>
-      <c r="BQ4">
-        <v>3.35</v>
-      </c>
-      <c r="BR4">
-        <v>23</v>
-      </c>
-      <c r="BS4">
-        <v>5.8</v>
-      </c>
       <c r="BT4">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BU4">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BZ4">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CA4">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="CB4" t="s">
         <v>111</v>
@@ -1669,25 +1669,25 @@
         <v>105</v>
       </c>
       <c r="F5">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G5">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="H5">
         <v>7</v>
       </c>
       <c r="I5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K5">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L5">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M5">
         <v>1.12</v>
@@ -1696,7 +1696,7 @@
         <v>2.72</v>
       </c>
       <c r="O5">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P5">
         <v>1.56</v>
@@ -1708,19 +1708,19 @@
         <v>1.2</v>
       </c>
       <c r="S5">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T5">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="U5">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V5">
         <v>1.14</v>
       </c>
       <c r="W5">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="X5">
         <v>9.6</v>
@@ -1729,7 +1729,7 @@
         <v>17</v>
       </c>
       <c r="Z5">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AA5">
         <v>900</v>
@@ -1765,7 +1765,7 @@
         <v>24</v>
       </c>
       <c r="AL5">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AM5">
         <v>700</v>
@@ -1774,58 +1774,58 @@
         <v>16.5</v>
       </c>
       <c r="AO5">
-        <v>980</v>
+        <v>970</v>
       </c>
       <c r="AP5">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ5">
         <v>12.5</v>
       </c>
       <c r="AR5">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AS5">
         <v>13</v>
       </c>
       <c r="AT5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AU5">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AV5">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="AW5">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AX5">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AY5">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5">
-        <v>15.5</v>
+        <v>24</v>
       </c>
       <c r="BA5">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="BB5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BC5">
         <v>15.5</v>
       </c>
       <c r="BD5">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BE5">
         <v>13.5</v>
       </c>
       <c r="BF5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BG5">
         <v>13</v>
@@ -1849,13 +1849,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN5">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BO5">
         <v>3.4</v>
       </c>
       <c r="BP5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BQ5">
         <v>8.800000000000001</v>
@@ -1867,10 +1867,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BT5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BV5">
         <v>1000</v>
@@ -1911,100 +1911,100 @@
         <v>106</v>
       </c>
       <c r="F6">
-        <v>2.64</v>
+        <v>2.94</v>
       </c>
       <c r="G6">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="I6">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="J6">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K6">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L6">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M6">
         <v>1.11</v>
       </c>
       <c r="N6">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O6">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P6">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q6">
         <v>2.54</v>
       </c>
       <c r="R6">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S6">
         <v>5.1</v>
       </c>
       <c r="T6">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U6">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="V6">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="W6">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="X6">
         <v>10.5</v>
       </c>
       <c r="Y6">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z6">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AA6">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB6">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AC6">
         <v>7.6</v>
       </c>
       <c r="AD6">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE6">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AG6">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AH6">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI6">
         <v>100</v>
       </c>
       <c r="AJ6">
+        <v>65</v>
+      </c>
+      <c r="AK6">
         <v>55</v>
-      </c>
-      <c r="AK6">
-        <v>46</v>
       </c>
       <c r="AL6">
         <v>85</v>
@@ -2013,124 +2013,124 @@
         <v>580</v>
       </c>
       <c r="AN6">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO6">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AP6">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AQ6">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AR6">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AS6">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AT6">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU6">
         <v>6.2</v>
       </c>
       <c r="AV6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW6">
+        <v>27</v>
+      </c>
+      <c r="AX6">
+        <v>16</v>
+      </c>
+      <c r="AY6">
+        <v>11.5</v>
+      </c>
+      <c r="AZ6">
+        <v>18.5</v>
+      </c>
+      <c r="BA6">
+        <v>44</v>
+      </c>
+      <c r="BB6">
+        <v>36</v>
+      </c>
+      <c r="BC6">
+        <v>30</v>
+      </c>
+      <c r="BD6">
+        <v>46</v>
+      </c>
+      <c r="BE6">
+        <v>85</v>
+      </c>
+      <c r="BF6">
+        <v>38</v>
+      </c>
+      <c r="BG6">
         <v>29</v>
       </c>
-      <c r="AX6">
-        <v>14</v>
-      </c>
-      <c r="AY6">
-        <v>11</v>
-      </c>
-      <c r="AZ6">
-        <v>18</v>
-      </c>
-      <c r="BA6">
-        <v>46</v>
-      </c>
-      <c r="BB6">
-        <v>29</v>
-      </c>
-      <c r="BC6">
-        <v>26</v>
-      </c>
-      <c r="BD6">
-        <v>42</v>
-      </c>
-      <c r="BE6">
-        <v>65</v>
-      </c>
-      <c r="BF6">
-        <v>30</v>
-      </c>
-      <c r="BG6">
-        <v>34</v>
-      </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="CB6" t="s">
         <v>111</v>
@@ -2153,19 +2153,19 @@
         <v>107</v>
       </c>
       <c r="F7">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G7">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H7">
         <v>3.35</v>
       </c>
       <c r="I7">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K7">
         <v>3.45</v>
@@ -2177,58 +2177,58 @@
         <v>1.09</v>
       </c>
       <c r="N7">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O7">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P7">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q7">
         <v>2.26</v>
       </c>
       <c r="R7">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S7">
         <v>4.3</v>
       </c>
       <c r="T7">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U7">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V7">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W7">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X7">
         <v>11.5</v>
       </c>
       <c r="Y7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA7">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AB7">
         <v>9</v>
       </c>
       <c r="AC7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD7">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE7">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AF7">
         <v>15</v>
@@ -2237,7 +2237,7 @@
         <v>12</v>
       </c>
       <c r="AH7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI7">
         <v>370</v>
@@ -2255,7 +2255,7 @@
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AO7">
         <v>150</v>
@@ -2267,13 +2267,13 @@
         <v>10</v>
       </c>
       <c r="AR7">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS7">
         <v>46</v>
       </c>
       <c r="AT7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU7">
         <v>6.8</v>
@@ -2282,7 +2282,7 @@
         <v>13</v>
       </c>
       <c r="AW7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX7">
         <v>12.5</v>
@@ -2291,13 +2291,13 @@
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC7">
         <v>22</v>
@@ -2315,64 +2315,64 @@
         <v>32</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB7" t="s">
         <v>111</v>
@@ -2395,13 +2395,13 @@
         <v>108</v>
       </c>
       <c r="F8">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G8">
         <v>3.05</v>
       </c>
       <c r="H8">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="I8">
         <v>2.96</v>
@@ -2413,16 +2413,16 @@
         <v>3.3</v>
       </c>
       <c r="L8">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M8">
         <v>1.12</v>
       </c>
       <c r="N8">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="O8">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P8">
         <v>1.58</v>
@@ -2437,7 +2437,7 @@
         <v>5.2</v>
       </c>
       <c r="T8">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U8">
         <v>1.84</v>
@@ -2452,10 +2452,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA8">
         <v>60</v>
@@ -2464,10 +2464,10 @@
         <v>9.4</v>
       </c>
       <c r="AC8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD8">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE8">
         <v>48</v>
@@ -2503,58 +2503,58 @@
         <v>55</v>
       </c>
       <c r="AP8">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ8">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR8">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AS8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT8">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY8">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AZ8">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BA8">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BB8">
         <v>36</v>
       </c>
       <c r="BC8">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BD8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE8">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="BF8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BG8">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BH8">
         <v>3.1</v>
@@ -2578,7 +2578,7 @@
         <v>6</v>
       </c>
       <c r="BO8">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP8">
         <v>28</v>
@@ -2637,16 +2637,16 @@
         <v>109</v>
       </c>
       <c r="F9">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G9">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H9">
+        <v>4.5</v>
+      </c>
+      <c r="I9">
         <v>4.6</v>
-      </c>
-      <c r="I9">
-        <v>4.8</v>
       </c>
       <c r="J9">
         <v>3.3</v>
@@ -2655,43 +2655,43 @@
         <v>3.35</v>
       </c>
       <c r="L9">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M9">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N9">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O9">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P9">
         <v>1.63</v>
       </c>
       <c r="Q9">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="R9">
         <v>1.23</v>
       </c>
       <c r="S9">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T9">
         <v>2.1</v>
       </c>
       <c r="U9">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V9">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W9">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X9">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y9">
         <v>13</v>
@@ -2700,13 +2700,13 @@
         <v>32</v>
       </c>
       <c r="AA9">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB9">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC9">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD9">
         <v>19.5</v>
@@ -2715,7 +2715,7 @@
         <v>80</v>
       </c>
       <c r="AF9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG9">
         <v>11</v>
@@ -2727,16 +2727,16 @@
         <v>100</v>
       </c>
       <c r="AJ9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL9">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM9">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN9">
         <v>21</v>
@@ -2745,13 +2745,13 @@
         <v>120</v>
       </c>
       <c r="AP9">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AQ9">
         <v>11.5</v>
       </c>
       <c r="AR9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS9">
         <v>20</v>
@@ -2763,100 +2763,100 @@
         <v>6.8</v>
       </c>
       <c r="AV9">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW9">
         <v>65</v>
       </c>
       <c r="AX9">
+        <v>10</v>
+      </c>
+      <c r="AY9">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AY9">
-        <v>9.6</v>
       </c>
       <c r="AZ9">
         <v>21</v>
       </c>
       <c r="BA9">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BB9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC9">
         <v>23</v>
       </c>
       <c r="BD9">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="BE9">
         <v>120</v>
       </c>
       <c r="BF9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BG9">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI9">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK9">
-        <v>3.25</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="BM9">
         <v>140</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO9">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ9">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS9">
-        <v>1.02</v>
+        <v>5.8</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU9">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="CB9" t="s">
         <v>111</v>
@@ -2879,25 +2879,25 @@
         <v>110</v>
       </c>
       <c r="F10">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="G10">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="H10">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="I10">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J10">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="K10">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="L10">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M10">
         <v>1.04</v>
@@ -2906,199 +2906,199 @@
         <v>5</v>
       </c>
       <c r="O10">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P10">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q10">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R10">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S10">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="T10">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="U10">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="V10">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W10">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="X10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y10">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Z10">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AB10">
         <v>9</v>
       </c>
       <c r="AC10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD10">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AE10">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="AF10">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AG10">
+        <v>10.5</v>
+      </c>
+      <c r="AH10">
+        <v>38</v>
+      </c>
+      <c r="AI10">
+        <v>160</v>
+      </c>
+      <c r="AJ10">
         <v>11</v>
-      </c>
-      <c r="AH10">
-        <v>36</v>
-      </c>
-      <c r="AI10">
-        <v>200</v>
-      </c>
-      <c r="AJ10">
-        <v>9.800000000000001</v>
       </c>
       <c r="AK10">
         <v>15</v>
       </c>
       <c r="AL10">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM10">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN10">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AO10">
-        <v>390</v>
+        <v>280</v>
       </c>
       <c r="AP10">
+        <v>9</v>
+      </c>
+      <c r="AQ10">
+        <v>11.5</v>
+      </c>
+      <c r="AR10">
+        <v>11</v>
+      </c>
+      <c r="AS10">
+        <v>12</v>
+      </c>
+      <c r="AT10">
+        <v>8</v>
+      </c>
+      <c r="AU10">
+        <v>11</v>
+      </c>
+      <c r="AV10">
+        <v>12</v>
+      </c>
+      <c r="AW10">
+        <v>11.5</v>
+      </c>
+      <c r="AX10">
         <v>7.6</v>
       </c>
-      <c r="AQ10">
+      <c r="AY10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ10">
         <v>9.800000000000001</v>
       </c>
-      <c r="AR10">
-        <v>9.4</v>
-      </c>
-      <c r="AS10">
-        <v>10</v>
-      </c>
-      <c r="AT10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU10">
+      <c r="BA10">
+        <v>11.5</v>
+      </c>
+      <c r="BB10">
+        <v>9.6</v>
+      </c>
+      <c r="BC10">
+        <v>13</v>
+      </c>
+      <c r="BD10">
+        <v>11.5</v>
+      </c>
+      <c r="BE10">
+        <v>11.5</v>
+      </c>
+      <c r="BF10">
+        <v>5</v>
+      </c>
+      <c r="BG10">
         <v>12</v>
       </c>
-      <c r="AV10">
-        <v>34</v>
-      </c>
-      <c r="AW10">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX10">
-        <v>7.4</v>
-      </c>
-      <c r="AY10">
-        <v>9.6</v>
-      </c>
-      <c r="AZ10">
-        <v>21</v>
-      </c>
-      <c r="BA10">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB10">
-        <v>8.6</v>
-      </c>
-      <c r="BC10">
-        <v>12.5</v>
-      </c>
-      <c r="BD10">
-        <v>32</v>
-      </c>
-      <c r="BE10">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF10">
-        <v>4.5</v>
-      </c>
-      <c r="BG10">
-        <v>10</v>
-      </c>
       <c r="BH10">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI10">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BJ10">
         <v>12.5</v>
       </c>
       <c r="BK10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BN10">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BO10">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP10">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BQ10">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR10">
         <v>24</v>
       </c>
       <c r="BS10">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BT10">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BU10">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BZ10">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA10">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CB10" t="s">
         <v>111</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -349,7 +349,7 @@
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-09-22 08:21:15</t>
+    <t>2026-09-22 10:55:09</t>
   </si>
 </sst>
 </file>
@@ -943,22 +943,22 @@
         <v>102</v>
       </c>
       <c r="F2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="H2">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="I2">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="J2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L2">
         <v>1.4</v>
@@ -967,16 +967,16 @@
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O2">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P2">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q2">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R2">
         <v>1.4</v>
@@ -988,7 +988,7 @@
         <v>2</v>
       </c>
       <c r="U2">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="V2">
         <v>2.68</v>
@@ -997,19 +997,19 @@
         <v>1.16</v>
       </c>
       <c r="X2">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AB2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AC2">
         <v>10.5</v>
@@ -1021,10 +1021,10 @@
         <v>16.5</v>
       </c>
       <c r="AF2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AG2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH2">
         <v>26</v>
@@ -1036,37 +1036,37 @@
         <v>280</v>
       </c>
       <c r="AK2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AL2">
         <v>110</v>
       </c>
       <c r="AM2">
-        <v>580</v>
+        <v>170</v>
       </c>
       <c r="AN2">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AO2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AP2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AS2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AT2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AU2">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV2">
         <v>9.199999999999999</v>
@@ -1075,46 +1075,46 @@
         <v>14.5</v>
       </c>
       <c r="AX2">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AY2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ2">
         <v>21</v>
       </c>
       <c r="BA2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BB2">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="BC2">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BD2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BE2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF2">
         <v>75</v>
       </c>
       <c r="BG2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BH2">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BI2">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1126,43 +1126,43 @@
         <v>10.5</v>
       </c>
       <c r="BO2">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BP2">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BT2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BU2">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BV2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BW2">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="BX2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BY2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="CA2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="CB2" t="s">
         <v>111</v>
@@ -1185,34 +1185,34 @@
         <v>103</v>
       </c>
       <c r="F3">
-        <v>2.26</v>
+        <v>2.52</v>
       </c>
       <c r="G3">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="H3">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I3">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="J3">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="K3">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="L3">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M3">
         <v>1.23</v>
       </c>
       <c r="N3">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>1.29</v>
@@ -1224,61 +1224,61 @@
         <v>1.09</v>
       </c>
       <c r="S3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="T3">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="U3">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="V3">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="W3">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="X3">
         <v>5.4</v>
       </c>
       <c r="Y3">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z3">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AA3">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="AB3">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AC3">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE3">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AF3">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AG3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AI3">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AJ3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AK3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL3">
         <v>150</v>
@@ -1287,124 +1287,124 @@
         <v>800</v>
       </c>
       <c r="AN3">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AO3">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AP3">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AQ3">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AR3">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AS3">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="AT3">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AU3">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AW3">
+        <v>14</v>
+      </c>
+      <c r="AX3">
+        <v>11.5</v>
+      </c>
+      <c r="AY3">
         <v>14.5</v>
       </c>
-      <c r="AX3">
-        <v>10</v>
-      </c>
-      <c r="AY3">
-        <v>13.5</v>
-      </c>
       <c r="AZ3">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BA3">
         <v>15</v>
       </c>
       <c r="BB3">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="BC3">
         <v>40</v>
       </c>
       <c r="BD3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BE3">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="BF3">
         <v>42</v>
       </c>
       <c r="BG3">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH3">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BI3">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="BJ3">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BK3">
-        <v>2.74</v>
+        <v>7.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="BN3">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BO3">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ3">
-        <v>3.3</v>
+        <v>9.6</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>3.15</v>
+        <v>12</v>
       </c>
       <c r="BT3">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BU3">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="BV3">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>3.15</v>
+        <v>14</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>3.2</v>
+        <v>12.5</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>3.2</v>
+        <v>12.5</v>
       </c>
       <c r="CB3" t="s">
         <v>111</v>
@@ -1427,199 +1427,199 @@
         <v>104</v>
       </c>
       <c r="F4">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="G4">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="H4">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="I4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J4">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="K4">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="L4">
         <v>1.2</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N4">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="O4">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="P4">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="Q4">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="R4">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="S4">
+        <v>1.92</v>
+      </c>
+      <c r="T4">
+        <v>2.2</v>
+      </c>
+      <c r="U4">
         <v>1.75</v>
       </c>
-      <c r="T4">
-        <v>2.08</v>
-      </c>
-      <c r="U4">
-        <v>1.7</v>
-      </c>
       <c r="V4">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W4">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="X4">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="Y4">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="Z4">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="AA4">
         <v>1000</v>
       </c>
       <c r="AB4">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="AC4">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AD4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AE4">
         <v>450</v>
       </c>
       <c r="AF4">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG4">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AH4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AI4">
         <v>280</v>
       </c>
       <c r="AJ4">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AK4">
         <v>16.5</v>
       </c>
       <c r="AL4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM4">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AN4">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AO4">
-        <v>510</v>
+        <v>610</v>
       </c>
       <c r="AP4">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AR4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AS4">
         <v>8.199999999999999</v>
       </c>
       <c r="AT4">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AU4">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AV4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AW4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AX4">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AY4">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AZ4">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BA4">
         <v>7.8</v>
       </c>
       <c r="BB4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC4">
         <v>12</v>
       </c>
       <c r="BD4">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE4">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4">
-        <v>2.26</v>
+        <v>2.58</v>
       </c>
       <c r="BG4">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BH4">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BI4">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="BJ4">
         <v>16</v>
       </c>
       <c r="BK4">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BN4">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO4">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="BP4">
         <v>6.2</v>
       </c>
       <c r="BQ4">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BR4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BS4">
         <v>6</v>
@@ -1628,25 +1628,25 @@
         <v>24</v>
       </c>
       <c r="BU4">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ4">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="CA4">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="CB4" t="s">
         <v>111</v>
@@ -1675,7 +1675,7 @@
         <v>1.68</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
         <v>8</v>
@@ -1684,16 +1684,16 @@
         <v>3.65</v>
       </c>
       <c r="K5">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L5">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M5">
         <v>1.12</v>
       </c>
       <c r="N5">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="O5">
         <v>1.52</v>
@@ -1702,16 +1702,16 @@
         <v>1.56</v>
       </c>
       <c r="Q5">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R5">
         <v>1.2</v>
       </c>
       <c r="S5">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T5">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="U5">
         <v>1.61</v>
@@ -1777,10 +1777,10 @@
         <v>970</v>
       </c>
       <c r="AP5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR5">
         <v>40</v>
@@ -1798,7 +1798,7 @@
         <v>23</v>
       </c>
       <c r="AW5">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AX5">
         <v>7.2</v>
@@ -1807,19 +1807,19 @@
         <v>9.6</v>
       </c>
       <c r="AZ5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA5">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="BB5">
         <v>14</v>
       </c>
       <c r="BC5">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="BD5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BE5">
         <v>13.5</v>
@@ -1911,16 +1911,16 @@
         <v>106</v>
       </c>
       <c r="F6">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="G6">
         <v>3.1</v>
       </c>
       <c r="H6">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I6">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="J6">
         <v>3.1</v>
@@ -1941,13 +1941,13 @@
         <v>1.51</v>
       </c>
       <c r="P6">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q6">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R6">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S6">
         <v>5.1</v>
@@ -1956,10 +1956,10 @@
         <v>2.02</v>
       </c>
       <c r="U6">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V6">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W6">
         <v>1.47</v>
@@ -1971,10 +1971,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB6">
         <v>10</v>
@@ -1995,10 +1995,10 @@
         <v>17</v>
       </c>
       <c r="AH6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI6">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AJ6">
         <v>65</v>
@@ -2016,7 +2016,7 @@
         <v>55</v>
       </c>
       <c r="AO6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP6">
         <v>8</v>
@@ -2028,7 +2028,7 @@
         <v>14</v>
       </c>
       <c r="AS6">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AT6">
         <v>7.8</v>
@@ -2055,13 +2055,13 @@
         <v>44</v>
       </c>
       <c r="BB6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE6">
         <v>85</v>
@@ -2082,55 +2082,55 @@
         <v>13</v>
       </c>
       <c r="BK6">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BN6">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BO6">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BP6">
         <v>34</v>
       </c>
       <c r="BQ6">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="BR6">
         <v>60</v>
       </c>
       <c r="BS6">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="BT6">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU6">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BV6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW6">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="BX6">
         <v>55</v>
       </c>
       <c r="BY6">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="BZ6">
         <v>60</v>
       </c>
       <c r="CA6">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="CB6" t="s">
         <v>111</v>
@@ -2183,7 +2183,7 @@
         <v>1.42</v>
       </c>
       <c r="P7">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q7">
         <v>2.26</v>
@@ -2207,7 +2207,7 @@
         <v>1.68</v>
       </c>
       <c r="X7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y7">
         <v>13</v>
@@ -2219,7 +2219,7 @@
         <v>500</v>
       </c>
       <c r="AB7">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC7">
         <v>7.8</v>
@@ -2228,7 +2228,7 @@
         <v>15.5</v>
       </c>
       <c r="AE7">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AF7">
         <v>15</v>
@@ -2255,10 +2255,10 @@
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO7">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="AP7">
         <v>10</v>
@@ -2267,7 +2267,7 @@
         <v>10</v>
       </c>
       <c r="AR7">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS7">
         <v>46</v>
@@ -2303,7 +2303,7 @@
         <v>22</v>
       </c>
       <c r="BD7">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE7">
         <v>90</v>
@@ -2398,7 +2398,7 @@
         <v>2.9</v>
       </c>
       <c r="G8">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H8">
         <v>2.82</v>
@@ -2410,7 +2410,7 @@
         <v>3.05</v>
       </c>
       <c r="K8">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L8">
         <v>1.58</v>
@@ -2419,7 +2419,7 @@
         <v>1.12</v>
       </c>
       <c r="N8">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="O8">
         <v>1.53</v>
@@ -2434,13 +2434,13 @@
         <v>1.21</v>
       </c>
       <c r="S8">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T8">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U8">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V8">
         <v>1.51</v>
@@ -2449,10 +2449,10 @@
         <v>1.48</v>
       </c>
       <c r="X8">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y8">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z8">
         <v>18.5</v>
@@ -2461,7 +2461,7 @@
         <v>60</v>
       </c>
       <c r="AB8">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC8">
         <v>7.4</v>
@@ -2473,7 +2473,7 @@
         <v>48</v>
       </c>
       <c r="AF8">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG8">
         <v>14.5</v>
@@ -2488,7 +2488,7 @@
         <v>60</v>
       </c>
       <c r="AK8">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AL8">
         <v>75</v>
@@ -2503,7 +2503,7 @@
         <v>55</v>
       </c>
       <c r="AP8">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ8">
         <v>7.8</v>
@@ -2557,10 +2557,10 @@
         <v>34</v>
       </c>
       <c r="BH8">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI8">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BJ8">
         <v>11.5</v>
@@ -2572,7 +2572,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN8">
         <v>6</v>
@@ -2581,7 +2581,7 @@
         <v>5</v>
       </c>
       <c r="BP8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BQ8">
         <v>6.6</v>
@@ -2590,7 +2590,7 @@
         <v>50</v>
       </c>
       <c r="BS8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT8">
         <v>5.9</v>
@@ -2602,19 +2602,19 @@
         <v>27</v>
       </c>
       <c r="BW8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX8">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ8">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="CA8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB8" t="s">
         <v>111</v>
@@ -2637,13 +2637,13 @@
         <v>109</v>
       </c>
       <c r="F9">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G9">
         <v>2.1</v>
       </c>
       <c r="H9">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I9">
         <v>4.6</v>
@@ -2655,31 +2655,31 @@
         <v>3.35</v>
       </c>
       <c r="L9">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M9">
         <v>1.12</v>
       </c>
       <c r="N9">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="O9">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P9">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q9">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R9">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S9">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T9">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U9">
         <v>1.85</v>
@@ -2694,25 +2694,25 @@
         <v>9.4</v>
       </c>
       <c r="Y9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z9">
         <v>32</v>
       </c>
       <c r="AA9">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AB9">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC9">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AD9">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE9">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF9">
         <v>11</v>
@@ -2724,10 +2724,10 @@
         <v>24</v>
       </c>
       <c r="AI9">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK9">
         <v>27</v>
@@ -2736,16 +2736,16 @@
         <v>60</v>
       </c>
       <c r="AM9">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AN9">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AO9">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP9">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ9">
         <v>11.5</v>
@@ -2754,34 +2754,34 @@
         <v>28</v>
       </c>
       <c r="AS9">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT9">
         <v>6.6</v>
       </c>
       <c r="AU9">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW9">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AX9">
         <v>10</v>
       </c>
       <c r="AY9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA9">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="BB9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC9">
         <v>23</v>
@@ -2793,70 +2793,70 @@
         <v>120</v>
       </c>
       <c r="BF9">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BG9">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BH9">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="BI9">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BJ9">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BK9">
-        <v>9.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="BL9">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="BM9">
         <v>140</v>
       </c>
       <c r="BN9">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO9">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP9">
         <v>20</v>
       </c>
       <c r="BQ9">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BR9">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BS9">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BT9">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU9">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="BV9">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BW9">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY9">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ9">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="CA9">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CB9" t="s">
         <v>111</v>
@@ -2879,61 +2879,61 @@
         <v>110</v>
       </c>
       <c r="F10">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G10">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="H10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J10">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="K10">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M10">
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O10">
         <v>1.23</v>
       </c>
       <c r="P10">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q10">
         <v>1.69</v>
       </c>
       <c r="R10">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S10">
         <v>2.78</v>
       </c>
       <c r="T10">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U10">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="V10">
         <v>1.09</v>
       </c>
       <c r="W10">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="X10">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y10">
         <v>40</v>
@@ -2942,19 +2942,19 @@
         <v>120</v>
       </c>
       <c r="AA10">
-        <v>490</v>
+        <v>530</v>
       </c>
       <c r="AB10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC10">
         <v>13</v>
       </c>
       <c r="AD10">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AE10">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AF10">
         <v>8.4</v>
@@ -2963,100 +2963,100 @@
         <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AI10">
         <v>160</v>
       </c>
       <c r="AJ10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL10">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM10">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN10">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AO10">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AP10">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AQ10">
+        <v>32</v>
+      </c>
+      <c r="AR10">
+        <v>17</v>
+      </c>
+      <c r="AS10">
+        <v>16</v>
+      </c>
+      <c r="AT10">
+        <v>8.4</v>
+      </c>
+      <c r="AU10">
         <v>11.5</v>
       </c>
-      <c r="AR10">
-        <v>11</v>
-      </c>
-      <c r="AS10">
-        <v>12</v>
-      </c>
-      <c r="AT10">
-        <v>8</v>
-      </c>
-      <c r="AU10">
-        <v>11</v>
-      </c>
       <c r="AV10">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="AW10">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AX10">
         <v>7.6</v>
       </c>
       <c r="AY10">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10">
-        <v>9.800000000000001</v>
+        <v>26</v>
       </c>
       <c r="BA10">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BB10">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC10">
         <v>13</v>
       </c>
       <c r="BD10">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="BE10">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF10">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BG10">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BH10">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI10">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ10">
         <v>12.5</v>
       </c>
       <c r="BK10">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN10">
         <v>3.8</v>
@@ -3065,40 +3065,40 @@
         <v>3.4</v>
       </c>
       <c r="BP10">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BQ10">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="BR10">
         <v>24</v>
       </c>
       <c r="BS10">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT10">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BU10">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CA10">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="CB10" t="s">
         <v>111</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -349,7 +349,7 @@
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-09-22 10:55:09</t>
+    <t>2026-09-22 13:07:11</t>
   </si>
 </sst>
 </file>
@@ -943,226 +943,226 @@
         <v>102</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>210</v>
       </c>
       <c r="G2">
+        <v>1000</v>
+      </c>
+      <c r="H2">
+        <v>1.01</v>
+      </c>
+      <c r="I2">
+        <v>1.02</v>
+      </c>
+      <c r="J2">
+        <v>36</v>
+      </c>
+      <c r="K2">
+        <v>120</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>1.8</v>
+      </c>
+      <c r="Q2">
+        <v>2.22</v>
+      </c>
+      <c r="R2">
+        <v>1.11</v>
+      </c>
+      <c r="S2">
+        <v>9.4</v>
+      </c>
+      <c r="T2">
+        <v>4.5</v>
+      </c>
+      <c r="U2">
+        <v>1.25</v>
+      </c>
+      <c r="V2">
+        <v>34</v>
+      </c>
+      <c r="W2">
+        <v>1.01</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1.86</v>
+      </c>
+      <c r="AA2">
+        <v>4.8</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>24</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>850</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>24</v>
+      </c>
+      <c r="AP2">
+        <v>38</v>
+      </c>
+      <c r="AQ2">
+        <v>38</v>
+      </c>
+      <c r="AR2">
+        <v>1.83</v>
+      </c>
+      <c r="AS2">
+        <v>4.5</v>
+      </c>
+      <c r="AT2">
+        <v>38</v>
+      </c>
+      <c r="AU2">
+        <v>38</v>
+      </c>
+      <c r="AV2">
         <v>7.2</v>
       </c>
-      <c r="H2">
-        <v>1.56</v>
-      </c>
-      <c r="I2">
-        <v>1.58</v>
-      </c>
-      <c r="J2">
-        <v>4.3</v>
-      </c>
-      <c r="K2">
-        <v>4.6</v>
-      </c>
-      <c r="L2">
-        <v>1.4</v>
-      </c>
-      <c r="M2">
-        <v>1.06</v>
-      </c>
-      <c r="N2">
-        <v>4.2</v>
-      </c>
-      <c r="O2">
-        <v>1.28</v>
-      </c>
-      <c r="P2">
-        <v>2.06</v>
-      </c>
-      <c r="Q2">
-        <v>1.89</v>
-      </c>
-      <c r="R2">
-        <v>1.4</v>
-      </c>
-      <c r="S2">
-        <v>3.3</v>
-      </c>
-      <c r="T2">
-        <v>2</v>
-      </c>
-      <c r="U2">
-        <v>1.87</v>
-      </c>
-      <c r="V2">
-        <v>2.68</v>
-      </c>
-      <c r="W2">
-        <v>1.16</v>
-      </c>
-      <c r="X2">
-        <v>17</v>
-      </c>
-      <c r="Y2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z2">
-        <v>9</v>
-      </c>
-      <c r="AA2">
-        <v>14.5</v>
-      </c>
-      <c r="AB2">
-        <v>24</v>
-      </c>
-      <c r="AC2">
-        <v>10.5</v>
-      </c>
-      <c r="AD2">
-        <v>10.5</v>
-      </c>
-      <c r="AE2">
-        <v>16.5</v>
-      </c>
-      <c r="AF2">
-        <v>65</v>
-      </c>
-      <c r="AG2">
-        <v>28</v>
-      </c>
-      <c r="AH2">
-        <v>26</v>
-      </c>
-      <c r="AI2">
-        <v>40</v>
-      </c>
-      <c r="AJ2">
-        <v>280</v>
-      </c>
-      <c r="AK2">
-        <v>120</v>
-      </c>
-      <c r="AL2">
-        <v>110</v>
-      </c>
-      <c r="AM2">
-        <v>170</v>
-      </c>
-      <c r="AN2">
-        <v>170</v>
-      </c>
-      <c r="AO2">
-        <v>8.4</v>
-      </c>
-      <c r="AP2">
-        <v>14.5</v>
-      </c>
-      <c r="AQ2">
-        <v>7.4</v>
-      </c>
-      <c r="AR2">
-        <v>8</v>
-      </c>
-      <c r="AS2">
-        <v>12.5</v>
-      </c>
-      <c r="AT2">
+      <c r="AW2">
         <v>20</v>
       </c>
-      <c r="AU2">
-        <v>9.4</v>
-      </c>
-      <c r="AV2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW2">
-        <v>14.5</v>
-      </c>
       <c r="AX2">
+        <v>38</v>
+      </c>
+      <c r="AY2">
+        <v>38</v>
+      </c>
+      <c r="AZ2">
         <v>50</v>
       </c>
-      <c r="AY2">
-        <v>24</v>
-      </c>
-      <c r="AZ2">
-        <v>21</v>
-      </c>
       <c r="BA2">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="BB2">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="BC2">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="BD2">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="BE2">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="BF2">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="BG2">
-        <v>7.6</v>
+        <v>19.5</v>
       </c>
       <c r="BH2">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>111</v>
@@ -1185,7 +1185,7 @@
         <v>103</v>
       </c>
       <c r="F3">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="G3">
         <v>2.6</v>
@@ -1194,115 +1194,115 @@
         <v>3.9</v>
       </c>
       <c r="I3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J3">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="K3">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P3">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Q3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="R3">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="S3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="T3">
         <v>2.68</v>
       </c>
       <c r="U3">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="V3">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
         <v>1.62</v>
       </c>
       <c r="X3">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Y3">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z3">
+        <v>28</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>6</v>
+      </c>
+      <c r="AC3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD3">
+        <v>990</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
         <v>27</v>
       </c>
-      <c r="AA3">
-        <v>140</v>
-      </c>
-      <c r="AB3">
-        <v>5.8</v>
-      </c>
-      <c r="AC3">
-        <v>7.6</v>
-      </c>
-      <c r="AD3">
-        <v>23</v>
-      </c>
-      <c r="AE3">
-        <v>120</v>
-      </c>
-      <c r="AF3">
-        <v>13.5</v>
-      </c>
       <c r="AG3">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="AH3">
-        <v>46</v>
+        <v>990</v>
       </c>
       <c r="AI3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AQ3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AR3">
-        <v>22</v>
+        <v>3.75</v>
       </c>
       <c r="AS3">
-        <v>70</v>
+        <v>4.1</v>
       </c>
       <c r="AT3">
         <v>5.2</v>
@@ -1311,100 +1311,100 @@
         <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="AX3">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AY3">
-        <v>14.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>36</v>
+        <v>9.6</v>
       </c>
       <c r="BA3">
+        <v>4.4</v>
+      </c>
+      <c r="BB3">
+        <v>4</v>
+      </c>
+      <c r="BC3">
+        <v>4.5</v>
+      </c>
+      <c r="BD3">
+        <v>4.4</v>
+      </c>
+      <c r="BE3">
+        <v>3.25</v>
+      </c>
+      <c r="BF3">
+        <v>4.5</v>
+      </c>
+      <c r="BG3">
+        <v>4.5</v>
+      </c>
+      <c r="BH3">
+        <v>2.14</v>
+      </c>
+      <c r="BI3">
+        <v>1.98</v>
+      </c>
+      <c r="BJ3">
+        <v>970</v>
+      </c>
+      <c r="BK3">
         <v>15</v>
       </c>
-      <c r="BB3">
-        <v>34</v>
-      </c>
-      <c r="BC3">
-        <v>40</v>
-      </c>
-      <c r="BD3">
-        <v>14</v>
-      </c>
-      <c r="BE3">
-        <v>28</v>
-      </c>
-      <c r="BF3">
-        <v>42</v>
-      </c>
-      <c r="BG3">
-        <v>13.5</v>
-      </c>
-      <c r="BH3">
-        <v>2.12</v>
-      </c>
-      <c r="BI3">
-        <v>1.99</v>
-      </c>
-      <c r="BJ3">
-        <v>15.5</v>
-      </c>
-      <c r="BK3">
-        <v>7.4</v>
-      </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="BM3">
-        <v>1.85</v>
+        <v>4.8</v>
       </c>
       <c r="BN3">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BO3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP3">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>9.6</v>
+        <v>4.9</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="BS3">
-        <v>12</v>
+        <v>4.8</v>
       </c>
       <c r="BT3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU3">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>14</v>
+        <v>4.9</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BY3">
-        <v>12.5</v>
+        <v>4.8</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="CA3">
-        <v>12.5</v>
+        <v>4.8</v>
       </c>
       <c r="CB3" t="s">
         <v>111</v>
@@ -1427,226 +1427,226 @@
         <v>104</v>
       </c>
       <c r="F4">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="G4">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="H4">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="I4">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K4">
         <v>11.5</v>
       </c>
       <c r="L4">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N4">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O4">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="P4">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="Q4">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="R4">
-        <v>1.86</v>
+        <v>2.24</v>
       </c>
       <c r="S4">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="T4">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="U4">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="V4">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W4">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="X4">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="Y4">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="Z4">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="AA4">
         <v>1000</v>
       </c>
       <c r="AB4">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="AC4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AD4">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AE4">
-        <v>450</v>
+        <v>260</v>
       </c>
       <c r="AF4">
+        <v>12.5</v>
+      </c>
+      <c r="AG4">
+        <v>14.5</v>
+      </c>
+      <c r="AH4">
+        <v>40</v>
+      </c>
+      <c r="AI4">
+        <v>200</v>
+      </c>
+      <c r="AJ4">
+        <v>10.5</v>
+      </c>
+      <c r="AK4">
+        <v>14.5</v>
+      </c>
+      <c r="AL4">
+        <v>38</v>
+      </c>
+      <c r="AM4">
+        <v>180</v>
+      </c>
+      <c r="AN4">
+        <v>2.7</v>
+      </c>
+      <c r="AO4">
+        <v>260</v>
+      </c>
+      <c r="AP4">
+        <v>18.5</v>
+      </c>
+      <c r="AQ4">
         <v>9.800000000000001</v>
       </c>
-      <c r="AG4">
-        <v>15.5</v>
-      </c>
-      <c r="AH4">
-        <v>50</v>
-      </c>
-      <c r="AI4">
-        <v>280</v>
-      </c>
-      <c r="AJ4">
-        <v>9.4</v>
-      </c>
-      <c r="AK4">
-        <v>16.5</v>
-      </c>
-      <c r="AL4">
-        <v>50</v>
-      </c>
-      <c r="AM4">
-        <v>260</v>
-      </c>
-      <c r="AN4">
-        <v>3</v>
-      </c>
-      <c r="AO4">
-        <v>610</v>
-      </c>
-      <c r="AP4">
-        <v>7.6</v>
-      </c>
-      <c r="AQ4">
-        <v>8</v>
-      </c>
       <c r="AR4">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS4">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT4">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AU4">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AV4">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW4">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX4">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY4">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AZ4">
-        <v>7.8</v>
+        <v>18.5</v>
       </c>
       <c r="BA4">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB4">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BC4">
         <v>12</v>
       </c>
       <c r="BD4">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="BE4">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF4">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="BG4">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BH4">
+        <v>6.6</v>
+      </c>
+      <c r="BI4">
+        <v>5.3</v>
+      </c>
+      <c r="BJ4">
+        <v>14</v>
+      </c>
+      <c r="BK4">
+        <v>5.7</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>8.6</v>
+      </c>
+      <c r="BN4">
+        <v>4.4</v>
+      </c>
+      <c r="BO4">
+        <v>3.65</v>
+      </c>
+      <c r="BP4">
+        <v>6.4</v>
+      </c>
+      <c r="BQ4">
+        <v>5.1</v>
+      </c>
+      <c r="BR4">
+        <v>19.5</v>
+      </c>
+      <c r="BS4">
         <v>6.2</v>
       </c>
-      <c r="BI4">
-        <v>4.8</v>
-      </c>
-      <c r="BJ4">
-        <v>16</v>
-      </c>
-      <c r="BK4">
-        <v>5.4</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>7.8</v>
-      </c>
-      <c r="BN4">
-        <v>4.2</v>
-      </c>
-      <c r="BO4">
-        <v>3.35</v>
-      </c>
-      <c r="BP4">
+      <c r="BT4">
+        <v>21</v>
+      </c>
+      <c r="BU4">
+        <v>6.4</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>8.6</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>8.4</v>
+      </c>
+      <c r="BZ4">
         <v>6.2</v>
       </c>
-      <c r="BQ4">
-        <v>4.8</v>
-      </c>
-      <c r="BR4">
-        <v>23</v>
-      </c>
-      <c r="BS4">
-        <v>6</v>
-      </c>
-      <c r="BT4">
-        <v>24</v>
-      </c>
-      <c r="BU4">
-        <v>6</v>
-      </c>
-      <c r="BV4">
-        <v>1000</v>
-      </c>
-      <c r="BW4">
-        <v>7.8</v>
-      </c>
-      <c r="BX4">
-        <v>1000</v>
-      </c>
-      <c r="BY4">
-        <v>7.6</v>
-      </c>
-      <c r="BZ4">
-        <v>6.6</v>
-      </c>
       <c r="CA4">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="CB4" t="s">
         <v>111</v>
@@ -1678,19 +1678,19 @@
         <v>6.8</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
         <v>3.65</v>
       </c>
       <c r="K5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L5">
         <v>1.55</v>
       </c>
       <c r="M5">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N5">
         <v>2.68</v>
@@ -1699,16 +1699,16 @@
         <v>1.52</v>
       </c>
       <c r="P5">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q5">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R5">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T5">
         <v>2.42</v>
@@ -1720,7 +1720,7 @@
         <v>1.14</v>
       </c>
       <c r="W5">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="X5">
         <v>9.6</v>
@@ -1765,7 +1765,7 @@
         <v>24</v>
       </c>
       <c r="AL5">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AM5">
         <v>700</v>
@@ -1774,7 +1774,7 @@
         <v>16.5</v>
       </c>
       <c r="AO5">
-        <v>970</v>
+        <v>750</v>
       </c>
       <c r="AP5">
         <v>8.4</v>
@@ -1786,7 +1786,7 @@
         <v>40</v>
       </c>
       <c r="AS5">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="AT5">
         <v>5.2</v>
@@ -1798,7 +1798,7 @@
         <v>23</v>
       </c>
       <c r="AW5">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AX5">
         <v>7.2</v>
@@ -1810,7 +1810,7 @@
         <v>23</v>
       </c>
       <c r="BA5">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BB5">
         <v>14</v>
@@ -1819,10 +1819,10 @@
         <v>20</v>
       </c>
       <c r="BD5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE5">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="BF5">
         <v>14</v>
@@ -1834,7 +1834,7 @@
         <v>2.82</v>
       </c>
       <c r="BI5">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ5">
         <v>13.5</v>
@@ -1852,13 +1852,13 @@
         <v>3.85</v>
       </c>
       <c r="BO5">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP5">
         <v>12.5</v>
       </c>
       <c r="BQ5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR5">
         <v>1000</v>
@@ -1911,16 +1911,16 @@
         <v>106</v>
       </c>
       <c r="F6">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="G6">
         <v>3.1</v>
       </c>
       <c r="H6">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I6">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J6">
         <v>3.1</v>
@@ -1929,13 +1929,13 @@
         <v>3.3</v>
       </c>
       <c r="L6">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="M6">
         <v>1.11</v>
       </c>
       <c r="N6">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O6">
         <v>1.51</v>
@@ -1944,7 +1944,7 @@
         <v>1.6</v>
       </c>
       <c r="Q6">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R6">
         <v>1.22</v>
@@ -1953,13 +1953,13 @@
         <v>5.1</v>
       </c>
       <c r="T6">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U6">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V6">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W6">
         <v>1.47</v>
@@ -1968,16 +1968,16 @@
         <v>10.5</v>
       </c>
       <c r="Y6">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Z6">
         <v>17.5</v>
       </c>
       <c r="AA6">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC6">
         <v>7.6</v>
@@ -1992,10 +1992,10 @@
         <v>22</v>
       </c>
       <c r="AG6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI6">
         <v>80</v>
@@ -2004,10 +2004,10 @@
         <v>65</v>
       </c>
       <c r="AK6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL6">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM6">
         <v>580</v>
@@ -2016,10 +2016,10 @@
         <v>55</v>
       </c>
       <c r="AO6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ6">
         <v>7.8</v>
@@ -2028,13 +2028,13 @@
         <v>14</v>
       </c>
       <c r="AS6">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AT6">
         <v>7.8</v>
       </c>
       <c r="AU6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV6">
         <v>11.5</v>
@@ -2055,7 +2055,7 @@
         <v>44</v>
       </c>
       <c r="BB6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BC6">
         <v>29</v>
@@ -2067,7 +2067,7 @@
         <v>85</v>
       </c>
       <c r="BF6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BG6">
         <v>29</v>
@@ -2076,61 +2076,61 @@
         <v>3.2</v>
       </c>
       <c r="BI6">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BJ6">
         <v>13</v>
       </c>
       <c r="BK6">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BN6">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BO6">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BP6">
         <v>34</v>
       </c>
       <c r="BQ6">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BR6">
         <v>60</v>
       </c>
       <c r="BS6">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BT6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU6">
         <v>4.3</v>
       </c>
       <c r="BV6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW6">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BX6">
         <v>55</v>
       </c>
       <c r="BY6">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BZ6">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="CB6" t="s">
         <v>111</v>
@@ -2153,25 +2153,25 @@
         <v>107</v>
       </c>
       <c r="F7">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="G7">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="H7">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I7">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J7">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K7">
         <v>3.45</v>
       </c>
       <c r="L7">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M7">
         <v>1.09</v>
@@ -2201,22 +2201,22 @@
         <v>2</v>
       </c>
       <c r="V7">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="X7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y7">
         <v>13</v>
       </c>
       <c r="Z7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA7">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AB7">
         <v>9.199999999999999</v>
@@ -2225,13 +2225,13 @@
         <v>7.8</v>
       </c>
       <c r="AD7">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE7">
         <v>140</v>
       </c>
       <c r="AF7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG7">
         <v>12</v>
@@ -2255,7 +2255,7 @@
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AO7">
         <v>600</v>
@@ -2264,13 +2264,13 @@
         <v>10</v>
       </c>
       <c r="AQ7">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR7">
         <v>17</v>
       </c>
       <c r="AS7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AT7">
         <v>8</v>
@@ -2279,7 +2279,7 @@
         <v>6.8</v>
       </c>
       <c r="AV7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW7">
         <v>30</v>
@@ -2288,7 +2288,7 @@
         <v>12.5</v>
       </c>
       <c r="AY7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7">
         <v>17</v>
@@ -2297,10 +2297,10 @@
         <v>42</v>
       </c>
       <c r="BB7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD7">
         <v>38</v>
@@ -2309,13 +2309,13 @@
         <v>90</v>
       </c>
       <c r="BF7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BG7">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BH7">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI7">
         <v>2.54</v>
@@ -2324,55 +2324,55 @@
         <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN7">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO7">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ7">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
+        <v>10.5</v>
+      </c>
+      <c r="BT7">
+        <v>6.4</v>
+      </c>
+      <c r="BU7">
+        <v>4.8</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
         <v>10</v>
       </c>
-      <c r="BT7">
-        <v>6.6</v>
-      </c>
-      <c r="BU7">
-        <v>4.9</v>
-      </c>
-      <c r="BV7">
-        <v>1000</v>
-      </c>
-      <c r="BW7">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB7" t="s">
         <v>111</v>
@@ -2395,16 +2395,16 @@
         <v>108</v>
       </c>
       <c r="F8">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G8">
         <v>3.1</v>
       </c>
       <c r="H8">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="I8">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J8">
         <v>3.05</v>
@@ -2413,7 +2413,7 @@
         <v>3.25</v>
       </c>
       <c r="L8">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M8">
         <v>1.12</v>
@@ -2506,13 +2506,13 @@
         <v>8</v>
       </c>
       <c r="AQ8">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR8">
         <v>15.5</v>
       </c>
       <c r="AS8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT8">
         <v>7.8</v>
@@ -2524,7 +2524,7 @@
         <v>11.5</v>
       </c>
       <c r="AW8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX8">
         <v>16</v>
@@ -2536,7 +2536,7 @@
         <v>18.5</v>
       </c>
       <c r="BA8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB8">
         <v>36</v>
@@ -2548,13 +2548,13 @@
         <v>46</v>
       </c>
       <c r="BE8">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BF8">
         <v>40</v>
       </c>
       <c r="BG8">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BH8">
         <v>3.05</v>
@@ -2572,10 +2572,10 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN8">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO8">
         <v>5</v>
@@ -2590,31 +2590,31 @@
         <v>50</v>
       </c>
       <c r="BS8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT8">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU8">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV8">
         <v>27</v>
       </c>
       <c r="BW8">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX8">
         <v>50</v>
       </c>
       <c r="BY8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ8">
         <v>50</v>
       </c>
       <c r="CA8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB8" t="s">
         <v>111</v>
@@ -2655,34 +2655,34 @@
         <v>3.35</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M9">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N9">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O9">
         <v>1.51</v>
       </c>
       <c r="P9">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q9">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="R9">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S9">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="T9">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U9">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V9">
         <v>1.27</v>
@@ -2691,7 +2691,7 @@
         <v>1.9</v>
       </c>
       <c r="X9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Y9">
         <v>12.5</v>
@@ -2703,16 +2703,16 @@
         <v>110</v>
       </c>
       <c r="AB9">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC9">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD9">
         <v>18.5</v>
       </c>
       <c r="AE9">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF9">
         <v>11</v>
@@ -2727,25 +2727,25 @@
         <v>110</v>
       </c>
       <c r="AJ9">
+        <v>24</v>
+      </c>
+      <c r="AK9">
         <v>26</v>
       </c>
-      <c r="AK9">
+      <c r="AL9">
+        <v>55</v>
+      </c>
+      <c r="AM9">
+        <v>210</v>
+      </c>
+      <c r="AN9">
         <v>27</v>
-      </c>
-      <c r="AL9">
-        <v>60</v>
-      </c>
-      <c r="AM9">
-        <v>500</v>
-      </c>
-      <c r="AN9">
-        <v>26</v>
       </c>
       <c r="AO9">
         <v>110</v>
       </c>
       <c r="AP9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ9">
         <v>11.5</v>
@@ -2754,7 +2754,7 @@
         <v>28</v>
       </c>
       <c r="AS9">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="AT9">
         <v>6.6</v>
@@ -2763,7 +2763,7 @@
         <v>7</v>
       </c>
       <c r="AV9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW9">
         <v>55</v>
@@ -2778,85 +2778,85 @@
         <v>22</v>
       </c>
       <c r="BA9">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="BB9">
         <v>23</v>
       </c>
       <c r="BC9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BE9">
         <v>120</v>
       </c>
       <c r="BF9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BG9">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BH9">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="BI9">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="BJ9">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BK9">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL9">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="BM9">
         <v>140</v>
       </c>
       <c r="BN9">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BO9">
         <v>4.1</v>
       </c>
       <c r="BP9">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BQ9">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="BR9">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="BS9">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BT9">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BU9">
         <v>6.4</v>
       </c>
       <c r="BV9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BW9">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BX9">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BY9">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="BZ9">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="CA9">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="CB9" t="s">
         <v>111</v>
@@ -2879,82 +2879,82 @@
         <v>110</v>
       </c>
       <c r="F10">
+        <v>1.32</v>
+      </c>
+      <c r="G10">
         <v>1.34</v>
       </c>
-      <c r="G10">
-        <v>1.36</v>
-      </c>
       <c r="H10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J10">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L10">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M10">
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O10">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P10">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q10">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="R10">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="S10">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="T10">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U10">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V10">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W10">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="X10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y10">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z10">
         <v>120</v>
       </c>
       <c r="AA10">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="AB10">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD10">
         <v>42</v>
       </c>
       <c r="AE10">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AF10">
         <v>8.4</v>
@@ -2963,31 +2963,31 @@
         <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI10">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ10">
         <v>10.5</v>
       </c>
       <c r="AK10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL10">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM10">
         <v>170</v>
       </c>
       <c r="AN10">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AO10">
         <v>300</v>
       </c>
       <c r="AP10">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ10">
         <v>32</v>
@@ -2996,19 +2996,19 @@
         <v>17</v>
       </c>
       <c r="AS10">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AT10">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV10">
         <v>32</v>
       </c>
       <c r="AW10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AX10">
         <v>7.6</v>
@@ -3020,43 +3020,43 @@
         <v>26</v>
       </c>
       <c r="BA10">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BB10">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE10">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BF10">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BG10">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI10">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BJ10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK10">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="BN10">
         <v>3.8</v>
@@ -3065,40 +3065,40 @@
         <v>3.4</v>
       </c>
       <c r="BP10">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BQ10">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BR10">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BS10">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BT10">
         <v>14.5</v>
       </c>
       <c r="BU10">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BX10">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BY10">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="BZ10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CA10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CB10" t="s">
         <v>111</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="106">
   <si>
     <t>League</t>
   </si>
@@ -274,12 +274,6 @@
     <t>2026-09-22</t>
   </si>
   <si>
-    <t>14:30:00</t>
-  </si>
-  <si>
-    <t>16:00:00</t>
-  </si>
-  <si>
     <t>17:00:00</t>
   </si>
   <si>
@@ -295,12 +289,6 @@
     <t>23:00:00</t>
   </si>
   <si>
-    <t>ACS Dumbravita</t>
-  </si>
-  <si>
-    <t>US Biskra</t>
-  </si>
-  <si>
     <t>ASA Targu Mures</t>
   </si>
   <si>
@@ -322,12 +310,6 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>CSM Scolar Resita</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
     <t>CS FC Dinamo Bucuresti</t>
   </si>
   <si>
@@ -349,7 +331,7 @@
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-09-22 13:07:11</t>
+    <t>2026-09-22 15:17:44</t>
   </si>
 </sst>
 </file>
@@ -681,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -937,28 +919,28 @@
         <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F2">
-        <v>210</v>
+        <v>2.1</v>
       </c>
       <c r="G2">
-        <v>1000</v>
+        <v>2.2</v>
       </c>
       <c r="H2">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="I2">
-        <v>1.02</v>
+        <v>4.3</v>
       </c>
       <c r="J2">
-        <v>36</v>
+        <v>3.25</v>
       </c>
       <c r="K2">
-        <v>120</v>
+        <v>3.5</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -973,136 +955,136 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>1.11</v>
+        <v>7.2</v>
       </c>
       <c r="S2">
+        <v>1.15</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>1.33</v>
+      </c>
+      <c r="W2">
+        <v>1.79</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>8</v>
+      </c>
+      <c r="AE2">
+        <v>42</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>4</v>
+      </c>
+      <c r="AI2">
+        <v>20</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>4</v>
+      </c>
+      <c r="AM2">
+        <v>26</v>
+      </c>
+      <c r="AN2">
+        <v>6.8</v>
+      </c>
+      <c r="AO2">
+        <v>65</v>
+      </c>
+      <c r="AP2">
+        <v>110</v>
+      </c>
+      <c r="AQ2">
         <v>9.4</v>
       </c>
-      <c r="T2">
-        <v>4.5</v>
-      </c>
-      <c r="U2">
-        <v>1.25</v>
-      </c>
-      <c r="V2">
-        <v>34</v>
-      </c>
-      <c r="W2">
-        <v>1.01</v>
-      </c>
-      <c r="X2">
-        <v>1000</v>
-      </c>
-      <c r="Y2">
-        <v>1000</v>
-      </c>
-      <c r="Z2">
-        <v>1.86</v>
-      </c>
-      <c r="AA2">
-        <v>4.8</v>
-      </c>
-      <c r="AB2">
-        <v>1000</v>
-      </c>
-      <c r="AC2">
-        <v>1000</v>
-      </c>
-      <c r="AD2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AE2">
-        <v>24</v>
-      </c>
-      <c r="AF2">
-        <v>1000</v>
-      </c>
-      <c r="AG2">
-        <v>1000</v>
-      </c>
-      <c r="AH2">
-        <v>850</v>
-      </c>
-      <c r="AI2">
-        <v>1000</v>
-      </c>
-      <c r="AJ2">
-        <v>1000</v>
-      </c>
-      <c r="AK2">
-        <v>1000</v>
-      </c>
-      <c r="AL2">
-        <v>1000</v>
-      </c>
-      <c r="AM2">
-        <v>1000</v>
-      </c>
-      <c r="AN2">
-        <v>1000</v>
-      </c>
-      <c r="AO2">
-        <v>24</v>
-      </c>
-      <c r="AP2">
-        <v>38</v>
-      </c>
-      <c r="AQ2">
-        <v>38</v>
-      </c>
       <c r="AR2">
-        <v>1.83</v>
+        <v>9</v>
       </c>
       <c r="AS2">
-        <v>4.5</v>
+        <v>55</v>
       </c>
       <c r="AT2">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AU2">
-        <v>38</v>
+        <v>9.4</v>
       </c>
       <c r="AV2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AW2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AX2">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AY2">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="AZ2">
-        <v>50</v>
+        <v>3.5</v>
       </c>
       <c r="BA2">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="BB2">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BC2">
-        <v>38</v>
+        <v>9.4</v>
       </c>
       <c r="BD2">
-        <v>38</v>
+        <v>3.4</v>
       </c>
       <c r="BE2">
-        <v>46</v>
+        <v>16.5</v>
       </c>
       <c r="BF2">
-        <v>46</v>
+        <v>4.1</v>
       </c>
       <c r="BG2">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH2">
         <v>0</v>
@@ -1165,7 +1147,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1179,240 +1161,240 @@
         <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F3">
-        <v>2.48</v>
+        <v>1.63</v>
       </c>
       <c r="G3">
-        <v>2.6</v>
+        <v>1.69</v>
       </c>
       <c r="H3">
+        <v>7.2</v>
+      </c>
+      <c r="I3">
+        <v>7.8</v>
+      </c>
+      <c r="J3">
+        <v>3.65</v>
+      </c>
+      <c r="K3">
         <v>3.9</v>
       </c>
-      <c r="I3">
-        <v>4.1</v>
-      </c>
-      <c r="J3">
+      <c r="L3">
+        <v>1.55</v>
+      </c>
+      <c r="M3">
+        <v>1.11</v>
+      </c>
+      <c r="N3">
         <v>2.76</v>
       </c>
-      <c r="K3">
-        <v>2.86</v>
-      </c>
-      <c r="L3">
-        <v>1.88</v>
-      </c>
-      <c r="M3">
-        <v>1.22</v>
-      </c>
-      <c r="N3">
-        <v>2.02</v>
-      </c>
       <c r="O3">
-        <v>1.93</v>
+        <v>1.51</v>
       </c>
       <c r="P3">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="Q3">
-        <v>4</v>
+        <v>2.54</v>
       </c>
       <c r="R3">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="S3">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="T3">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="U3">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="W3">
-        <v>1.62</v>
+        <v>2.44</v>
       </c>
       <c r="X3">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="Y3">
-        <v>8.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="Z3">
-        <v>28</v>
+        <v>160</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB3">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AC3">
         <v>8.800000000000001</v>
       </c>
       <c r="AD3">
-        <v>990</v>
+        <v>30</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF3">
-        <v>27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG3">
-        <v>990</v>
+        <v>11</v>
       </c>
       <c r="AH3">
-        <v>990</v>
+        <v>34</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ3">
-        <v>44</v>
+        <v>16.5</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AP3">
+        <v>8.6</v>
+      </c>
+      <c r="AQ3">
+        <v>16</v>
+      </c>
+      <c r="AR3">
+        <v>12</v>
+      </c>
+      <c r="AS3">
+        <v>70</v>
+      </c>
+      <c r="AT3">
         <v>5.3</v>
       </c>
-      <c r="AQ3">
-        <v>7</v>
-      </c>
-      <c r="AR3">
-        <v>3.75</v>
-      </c>
-      <c r="AS3">
-        <v>4.1</v>
-      </c>
-      <c r="AT3">
-        <v>5.2</v>
-      </c>
       <c r="AU3">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AV3">
+        <v>23</v>
+      </c>
+      <c r="AW3">
+        <v>70</v>
+      </c>
+      <c r="AX3">
+        <v>7.2</v>
+      </c>
+      <c r="AY3">
+        <v>9.6</v>
+      </c>
+      <c r="AZ3">
+        <v>10</v>
+      </c>
+      <c r="BA3">
+        <v>65</v>
+      </c>
+      <c r="BB3">
+        <v>14</v>
+      </c>
+      <c r="BC3">
+        <v>20</v>
+      </c>
+      <c r="BD3">
+        <v>12</v>
+      </c>
+      <c r="BE3">
+        <v>13.5</v>
+      </c>
+      <c r="BF3">
+        <v>14</v>
+      </c>
+      <c r="BG3">
+        <v>14.5</v>
+      </c>
+      <c r="BH3">
+        <v>2.86</v>
+      </c>
+      <c r="BI3">
+        <v>2.64</v>
+      </c>
+      <c r="BJ3">
+        <v>13.5</v>
+      </c>
+      <c r="BK3">
+        <v>11.5</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN3">
+        <v>3.85</v>
+      </c>
+      <c r="BO3">
+        <v>3.5</v>
+      </c>
+      <c r="BP3">
         <v>12.5</v>
       </c>
-      <c r="AW3">
-        <v>4.5</v>
-      </c>
-      <c r="AX3">
-        <v>8.4</v>
-      </c>
-      <c r="AY3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ3">
-        <v>9.6</v>
-      </c>
-      <c r="BA3">
-        <v>4.4</v>
-      </c>
-      <c r="BB3">
-        <v>4</v>
-      </c>
-      <c r="BC3">
-        <v>4.5</v>
-      </c>
-      <c r="BD3">
-        <v>4.4</v>
-      </c>
-      <c r="BE3">
-        <v>3.25</v>
-      </c>
-      <c r="BF3">
-        <v>4.5</v>
-      </c>
-      <c r="BG3">
-        <v>4.5</v>
-      </c>
-      <c r="BH3">
-        <v>2.14</v>
-      </c>
-      <c r="BI3">
-        <v>1.98</v>
-      </c>
-      <c r="BJ3">
-        <v>970</v>
-      </c>
-      <c r="BK3">
-        <v>15</v>
-      </c>
-      <c r="BL3">
-        <v>960</v>
-      </c>
-      <c r="BM3">
-        <v>4.8</v>
-      </c>
-      <c r="BN3">
-        <v>5.4</v>
-      </c>
-      <c r="BO3">
-        <v>4.6</v>
-      </c>
-      <c r="BP3">
-        <v>1000</v>
-      </c>
       <c r="BQ3">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="BR3">
-        <v>910</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BU3">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX3">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ3">
-        <v>960</v>
+        <v>34</v>
       </c>
       <c r="CA3">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
         <v>85</v>
@@ -1421,477 +1403,477 @@
         <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F4">
-        <v>1.17</v>
+        <v>2.88</v>
       </c>
       <c r="G4">
-        <v>1.21</v>
+        <v>3.05</v>
       </c>
       <c r="H4">
-        <v>16</v>
+        <v>2.76</v>
       </c>
       <c r="I4">
-        <v>21</v>
+        <v>2.94</v>
       </c>
       <c r="J4">
-        <v>8.800000000000001</v>
+        <v>3.15</v>
       </c>
       <c r="K4">
-        <v>11.5</v>
+        <v>3.25</v>
       </c>
       <c r="L4">
-        <v>1.19</v>
+        <v>1.56</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N4">
-        <v>9.199999999999999</v>
+        <v>2.84</v>
       </c>
       <c r="O4">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="P4">
-        <v>3.95</v>
+        <v>1.61</v>
       </c>
       <c r="Q4">
-        <v>1.3</v>
+        <v>2.46</v>
       </c>
       <c r="R4">
-        <v>2.24</v>
+        <v>1.22</v>
       </c>
       <c r="S4">
-        <v>1.75</v>
+        <v>5.1</v>
       </c>
       <c r="T4">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="U4">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="V4">
-        <v>1.05</v>
+        <v>1.52</v>
       </c>
       <c r="W4">
-        <v>5.7</v>
+        <v>1.48</v>
       </c>
       <c r="X4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y4">
+        <v>9.4</v>
+      </c>
+      <c r="Z4">
+        <v>17.5</v>
+      </c>
+      <c r="AA4">
         <v>60</v>
       </c>
-      <c r="Y4">
-        <v>110</v>
-      </c>
-      <c r="Z4">
-        <v>230</v>
-      </c>
-      <c r="AA4">
-        <v>1000</v>
-      </c>
       <c r="AB4">
-        <v>18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4">
-        <v>26</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="AE4">
-        <v>260</v>
+        <v>48</v>
       </c>
       <c r="AF4">
-        <v>12.5</v>
+        <v>22</v>
       </c>
       <c r="AG4">
         <v>14.5</v>
       </c>
       <c r="AH4">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="AI4">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AJ4">
-        <v>10.5</v>
+        <v>65</v>
       </c>
       <c r="AK4">
-        <v>14.5</v>
+        <v>50</v>
       </c>
       <c r="AL4">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AM4">
-        <v>180</v>
+        <v>580</v>
       </c>
       <c r="AN4">
-        <v>2.7</v>
+        <v>55</v>
       </c>
       <c r="AO4">
-        <v>260</v>
+        <v>55</v>
       </c>
       <c r="AP4">
-        <v>18.5</v>
+        <v>8.4</v>
       </c>
       <c r="AQ4">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AR4">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="AS4">
-        <v>9.6</v>
+        <v>32</v>
       </c>
       <c r="AT4">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AU4">
-        <v>19.5</v>
+        <v>6.4</v>
       </c>
       <c r="AV4">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="AW4">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="AX4">
-        <v>9.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="AY4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ4">
         <v>18.5</v>
       </c>
       <c r="BA4">
-        <v>9.199999999999999</v>
+        <v>44</v>
       </c>
       <c r="BB4">
-        <v>8.4</v>
+        <v>34</v>
       </c>
       <c r="BC4">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="BD4">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="BE4">
-        <v>10.5</v>
+        <v>85</v>
       </c>
       <c r="BF4">
-        <v>2.5</v>
+        <v>36</v>
       </c>
       <c r="BG4">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="BH4">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BP4">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
         <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F5">
-        <v>1.63</v>
+        <v>2.38</v>
       </c>
       <c r="G5">
+        <v>2.46</v>
+      </c>
+      <c r="H5">
+        <v>3.35</v>
+      </c>
+      <c r="I5">
+        <v>3.55</v>
+      </c>
+      <c r="J5">
+        <v>3.25</v>
+      </c>
+      <c r="K5">
+        <v>3.45</v>
+      </c>
+      <c r="L5">
+        <v>1.49</v>
+      </c>
+      <c r="M5">
+        <v>1.09</v>
+      </c>
+      <c r="N5">
+        <v>3.2</v>
+      </c>
+      <c r="O5">
+        <v>1.42</v>
+      </c>
+      <c r="P5">
+        <v>1.75</v>
+      </c>
+      <c r="Q5">
+        <v>2.26</v>
+      </c>
+      <c r="R5">
+        <v>1.27</v>
+      </c>
+      <c r="S5">
+        <v>4.3</v>
+      </c>
+      <c r="T5">
+        <v>1.92</v>
+      </c>
+      <c r="U5">
+        <v>1.98</v>
+      </c>
+      <c r="V5">
+        <v>1.39</v>
+      </c>
+      <c r="W5">
         <v>1.68</v>
       </c>
-      <c r="H5">
+      <c r="X5">
+        <v>11.5</v>
+      </c>
+      <c r="Y5">
+        <v>13</v>
+      </c>
+      <c r="Z5">
+        <v>24</v>
+      </c>
+      <c r="AA5">
+        <v>220</v>
+      </c>
+      <c r="AB5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC5">
+        <v>7.8</v>
+      </c>
+      <c r="AD5">
+        <v>15</v>
+      </c>
+      <c r="AE5">
+        <v>120</v>
+      </c>
+      <c r="AF5">
+        <v>15</v>
+      </c>
+      <c r="AG5">
+        <v>12</v>
+      </c>
+      <c r="AH5">
+        <v>21</v>
+      </c>
+      <c r="AI5">
+        <v>370</v>
+      </c>
+      <c r="AJ5">
+        <v>95</v>
+      </c>
+      <c r="AK5">
+        <v>40</v>
+      </c>
+      <c r="AL5">
+        <v>120</v>
+      </c>
+      <c r="AM5">
+        <v>500</v>
+      </c>
+      <c r="AN5">
+        <v>34</v>
+      </c>
+      <c r="AO5">
+        <v>500</v>
+      </c>
+      <c r="AP5">
+        <v>10</v>
+      </c>
+      <c r="AQ5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR5">
+        <v>17</v>
+      </c>
+      <c r="AS5">
+        <v>46</v>
+      </c>
+      <c r="AT5">
+        <v>7.8</v>
+      </c>
+      <c r="AU5">
         <v>6.8</v>
       </c>
-      <c r="I5">
-        <v>7.8</v>
-      </c>
-      <c r="J5">
-        <v>3.65</v>
-      </c>
-      <c r="K5">
-        <v>3.9</v>
-      </c>
-      <c r="L5">
-        <v>1.55</v>
-      </c>
-      <c r="M5">
-        <v>1.11</v>
-      </c>
-      <c r="N5">
-        <v>2.68</v>
-      </c>
-      <c r="O5">
-        <v>1.52</v>
-      </c>
-      <c r="P5">
-        <v>1.58</v>
-      </c>
-      <c r="Q5">
-        <v>2.56</v>
-      </c>
-      <c r="R5">
-        <v>1.21</v>
-      </c>
-      <c r="S5">
-        <v>5.3</v>
-      </c>
-      <c r="T5">
-        <v>2.42</v>
-      </c>
-      <c r="U5">
-        <v>1.61</v>
-      </c>
-      <c r="V5">
-        <v>1.14</v>
-      </c>
-      <c r="W5">
-        <v>2.4</v>
-      </c>
-      <c r="X5">
-        <v>9.6</v>
-      </c>
-      <c r="Y5">
+      <c r="AV5">
+        <v>13</v>
+      </c>
+      <c r="AW5">
+        <v>30</v>
+      </c>
+      <c r="AX5">
+        <v>12.5</v>
+      </c>
+      <c r="AY5">
+        <v>10.5</v>
+      </c>
+      <c r="AZ5">
         <v>17</v>
       </c>
-      <c r="Z5">
-        <v>160</v>
-      </c>
-      <c r="AA5">
-        <v>900</v>
-      </c>
-      <c r="AB5">
-        <v>5.8</v>
-      </c>
-      <c r="AC5">
-        <v>9</v>
-      </c>
-      <c r="AD5">
-        <v>32</v>
-      </c>
-      <c r="AE5">
-        <v>700</v>
-      </c>
-      <c r="AF5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AG5">
-        <v>11.5</v>
-      </c>
-      <c r="AH5">
-        <v>34</v>
-      </c>
-      <c r="AI5">
-        <v>700</v>
-      </c>
-      <c r="AJ5">
-        <v>16.5</v>
-      </c>
-      <c r="AK5">
-        <v>24</v>
-      </c>
-      <c r="AL5">
-        <v>160</v>
-      </c>
-      <c r="AM5">
-        <v>700</v>
-      </c>
-      <c r="AN5">
-        <v>16.5</v>
-      </c>
-      <c r="AO5">
-        <v>750</v>
-      </c>
-      <c r="AP5">
-        <v>8.4</v>
-      </c>
-      <c r="AQ5">
-        <v>13</v>
-      </c>
-      <c r="AR5">
-        <v>40</v>
-      </c>
-      <c r="AS5">
-        <v>150</v>
-      </c>
-      <c r="AT5">
-        <v>5.2</v>
-      </c>
-      <c r="AU5">
-        <v>8</v>
-      </c>
-      <c r="AV5">
+      <c r="BA5">
+        <v>42</v>
+      </c>
+      <c r="BB5">
         <v>23</v>
       </c>
-      <c r="AW5">
-        <v>75</v>
-      </c>
-      <c r="AX5">
-        <v>7.2</v>
-      </c>
-      <c r="AY5">
-        <v>9.6</v>
-      </c>
-      <c r="AZ5">
-        <v>23</v>
-      </c>
-      <c r="BA5">
-        <v>70</v>
-      </c>
-      <c r="BB5">
-        <v>14</v>
-      </c>
       <c r="BC5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BD5">
         <v>32</v>
       </c>
       <c r="BE5">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="BF5">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="BG5">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="BH5">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="BI5">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="BJ5">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BN5">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="BO5">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="BP5">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="BQ5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT5">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="BU5">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ5">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1902,136 +1884,136 @@
         <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F6">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="G6">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H6">
         <v>2.76</v>
       </c>
       <c r="I6">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="J6">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L6">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="M6">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N6">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="O6">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P6">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q6">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="R6">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S6">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="T6">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="U6">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="V6">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W6">
         <v>1.47</v>
       </c>
       <c r="X6">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y6">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA6">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="AB6">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD6">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AE6">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF6">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AG6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH6">
         <v>23</v>
       </c>
       <c r="AI6">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK6">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL6">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM6">
-        <v>580</v>
+        <v>190</v>
       </c>
       <c r="AN6">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AO6">
         <v>55</v>
       </c>
       <c r="AP6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR6">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AS6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU6">
         <v>6.4</v>
@@ -2046,7 +2028,7 @@
         <v>16</v>
       </c>
       <c r="AY6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ6">
         <v>18.5</v>
@@ -2058,243 +2040,243 @@
         <v>36</v>
       </c>
       <c r="BC6">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BD6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE6">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="BF6">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BG6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH6">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BI6">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BJ6">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BK6">
-        <v>4</v>
+        <v>8.6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN6">
         <v>6.2</v>
       </c>
       <c r="BO6">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BP6">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BQ6">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BR6">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BS6">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BT6">
+        <v>5.8</v>
+      </c>
+      <c r="BU6">
+        <v>4.8</v>
+      </c>
+      <c r="BV6">
+        <v>27</v>
+      </c>
+      <c r="BW6">
         <v>6.4</v>
       </c>
-      <c r="BU6">
-        <v>4.3</v>
-      </c>
-      <c r="BV6">
-        <v>30</v>
-      </c>
-      <c r="BW6">
-        <v>4.9</v>
-      </c>
       <c r="BX6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY6">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA6">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="CB6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
         <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F7">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="G7">
-        <v>2.52</v>
+        <v>2.16</v>
       </c>
       <c r="H7">
+        <v>4.2</v>
+      </c>
+      <c r="I7">
+        <v>4.3</v>
+      </c>
+      <c r="J7">
         <v>3.3</v>
       </c>
-      <c r="I7">
-        <v>3.45</v>
-      </c>
-      <c r="J7">
-        <v>3.25</v>
-      </c>
       <c r="K7">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L7">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="M7">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N7">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="O7">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="P7">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="Q7">
-        <v>2.26</v>
+        <v>2.54</v>
       </c>
       <c r="R7">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="S7">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="T7">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="U7">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W7">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="X7">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z7">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AA7">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="AB7">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AC7">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD7">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AE7">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="AF7">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AG7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH7">
         <v>24</v>
       </c>
       <c r="AI7">
-        <v>370</v>
+        <v>100</v>
       </c>
       <c r="AJ7">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="AK7">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="AL7">
-        <v>370</v>
+        <v>55</v>
       </c>
       <c r="AM7">
-        <v>580</v>
+        <v>190</v>
       </c>
       <c r="AN7">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AO7">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="AP7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ7">
+        <v>11</v>
+      </c>
+      <c r="AR7">
+        <v>27</v>
+      </c>
+      <c r="AS7">
+        <v>26</v>
+      </c>
+      <c r="AT7">
+        <v>6.6</v>
+      </c>
+      <c r="AU7">
+        <v>7.2</v>
+      </c>
+      <c r="AV7">
+        <v>17</v>
+      </c>
+      <c r="AW7">
+        <v>55</v>
+      </c>
+      <c r="AX7">
         <v>10</v>
       </c>
-      <c r="AQ7">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR7">
-        <v>17</v>
-      </c>
-      <c r="AS7">
-        <v>44</v>
-      </c>
-      <c r="AT7">
-        <v>8</v>
-      </c>
-      <c r="AU7">
-        <v>6.8</v>
-      </c>
-      <c r="AV7">
-        <v>12.5</v>
-      </c>
-      <c r="AW7">
-        <v>30</v>
-      </c>
-      <c r="AX7">
-        <v>12.5</v>
-      </c>
       <c r="AY7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ7">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BA7">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="BB7">
         <v>25</v>
@@ -2303,84 +2285,84 @@
         <v>23</v>
       </c>
       <c r="BD7">
+        <v>48</v>
+      </c>
+      <c r="BE7">
+        <v>120</v>
+      </c>
+      <c r="BF7">
+        <v>24</v>
+      </c>
+      <c r="BG7">
+        <v>75</v>
+      </c>
+      <c r="BH7">
+        <v>2.94</v>
+      </c>
+      <c r="BI7">
+        <v>2.74</v>
+      </c>
+      <c r="BJ7">
+        <v>13.5</v>
+      </c>
+      <c r="BK7">
+        <v>6.6</v>
+      </c>
+      <c r="BL7">
+        <v>210</v>
+      </c>
+      <c r="BM7">
+        <v>140</v>
+      </c>
+      <c r="BN7">
+        <v>4.7</v>
+      </c>
+      <c r="BO7">
+        <v>4.2</v>
+      </c>
+      <c r="BP7">
+        <v>17</v>
+      </c>
+      <c r="BQ7">
+        <v>7</v>
+      </c>
+      <c r="BR7">
+        <v>44</v>
+      </c>
+      <c r="BS7">
+        <v>9.4</v>
+      </c>
+      <c r="BT7">
+        <v>7.2</v>
+      </c>
+      <c r="BU7">
+        <v>6.4</v>
+      </c>
+      <c r="BV7">
+        <v>48</v>
+      </c>
+      <c r="BW7">
+        <v>9.6</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ7">
         <v>38</v>
       </c>
-      <c r="BE7">
-        <v>90</v>
-      </c>
-      <c r="BF7">
-        <v>20</v>
-      </c>
-      <c r="BG7">
-        <v>38</v>
-      </c>
-      <c r="BH7">
-        <v>3.05</v>
-      </c>
-      <c r="BI7">
-        <v>2.54</v>
-      </c>
-      <c r="BJ7">
-        <v>10.5</v>
-      </c>
-      <c r="BK7">
-        <v>6.2</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>13.5</v>
-      </c>
-      <c r="BN7">
-        <v>5.3</v>
-      </c>
-      <c r="BO7">
-        <v>4</v>
-      </c>
-      <c r="BP7">
-        <v>20</v>
-      </c>
-      <c r="BQ7">
-        <v>8.6</v>
-      </c>
-      <c r="BR7">
-        <v>1000</v>
-      </c>
-      <c r="BS7">
-        <v>10.5</v>
-      </c>
-      <c r="BT7">
-        <v>6.4</v>
-      </c>
-      <c r="BU7">
-        <v>4.8</v>
-      </c>
-      <c r="BV7">
-        <v>1000</v>
-      </c>
-      <c r="BW7">
-        <v>10</v>
-      </c>
-      <c r="BX7">
-        <v>1000</v>
-      </c>
-      <c r="BY7">
-        <v>11.5</v>
-      </c>
-      <c r="BZ7">
-        <v>1000</v>
-      </c>
       <c r="CA7">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="CB7" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
         <v>85</v>
@@ -2389,719 +2371,235 @@
         <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F8">
-        <v>2.92</v>
+        <v>1.36</v>
       </c>
       <c r="G8">
-        <v>3.1</v>
+        <v>1.37</v>
       </c>
       <c r="H8">
-        <v>2.76</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>2.94</v>
+        <v>11</v>
       </c>
       <c r="J8">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="K8">
-        <v>3.25</v>
+        <v>5.8</v>
       </c>
       <c r="L8">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="M8">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="N8">
-        <v>2.76</v>
+        <v>5.4</v>
       </c>
       <c r="O8">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="P8">
+        <v>2.48</v>
+      </c>
+      <c r="Q8">
+        <v>1.65</v>
+      </c>
+      <c r="R8">
         <v>1.58</v>
       </c>
-      <c r="Q8">
-        <v>2.6</v>
-      </c>
-      <c r="R8">
-        <v>1.21</v>
-      </c>
       <c r="S8">
-        <v>5.3</v>
+        <v>2.64</v>
       </c>
       <c r="T8">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U8">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="V8">
-        <v>1.51</v>
+        <v>1.1</v>
       </c>
       <c r="W8">
-        <v>1.48</v>
+        <v>3.6</v>
       </c>
       <c r="X8">
+        <v>24</v>
+      </c>
+      <c r="Y8">
+        <v>36</v>
+      </c>
+      <c r="Z8">
+        <v>150</v>
+      </c>
+      <c r="AA8">
+        <v>410</v>
+      </c>
+      <c r="AB8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC8">
+        <v>13</v>
+      </c>
+      <c r="AD8">
+        <v>36</v>
+      </c>
+      <c r="AE8">
+        <v>160</v>
+      </c>
+      <c r="AF8">
+        <v>8.4</v>
+      </c>
+      <c r="AG8">
+        <v>10.5</v>
+      </c>
+      <c r="AH8">
+        <v>29</v>
+      </c>
+      <c r="AI8">
+        <v>180</v>
+      </c>
+      <c r="AJ8">
+        <v>11</v>
+      </c>
+      <c r="AK8">
+        <v>14</v>
+      </c>
+      <c r="AL8">
+        <v>36</v>
+      </c>
+      <c r="AM8">
+        <v>150</v>
+      </c>
+      <c r="AN8">
+        <v>5.4</v>
+      </c>
+      <c r="AO8">
+        <v>210</v>
+      </c>
+      <c r="AP8">
+        <v>20</v>
+      </c>
+      <c r="AQ8">
+        <v>27</v>
+      </c>
+      <c r="AR8">
+        <v>14.5</v>
+      </c>
+      <c r="AS8">
+        <v>16.5</v>
+      </c>
+      <c r="AT8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU8">
+        <v>11.5</v>
+      </c>
+      <c r="AV8">
+        <v>30</v>
+      </c>
+      <c r="AW8">
+        <v>14.5</v>
+      </c>
+      <c r="AX8">
+        <v>7.6</v>
+      </c>
+      <c r="AY8">
         <v>9.4</v>
       </c>
-      <c r="Y8">
-        <v>9</v>
-      </c>
-      <c r="Z8">
-        <v>18.5</v>
-      </c>
-      <c r="AA8">
-        <v>60</v>
-      </c>
-      <c r="AB8">
-        <v>9</v>
-      </c>
-      <c r="AC8">
-        <v>7.4</v>
-      </c>
-      <c r="AD8">
-        <v>14</v>
-      </c>
-      <c r="AE8">
-        <v>48</v>
-      </c>
-      <c r="AF8">
-        <v>19</v>
-      </c>
-      <c r="AG8">
+      <c r="AZ8">
+        <v>23</v>
+      </c>
+      <c r="BA8">
+        <v>15</v>
+      </c>
+      <c r="BB8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC8">
+        <v>12.5</v>
+      </c>
+      <c r="BD8">
+        <v>30</v>
+      </c>
+      <c r="BE8">
         <v>14.5</v>
       </c>
-      <c r="AH8">
-        <v>23</v>
-      </c>
-      <c r="AI8">
-        <v>75</v>
-      </c>
-      <c r="AJ8">
-        <v>60</v>
-      </c>
-      <c r="AK8">
-        <v>55</v>
-      </c>
-      <c r="AL8">
-        <v>75</v>
-      </c>
-      <c r="AM8">
-        <v>580</v>
-      </c>
-      <c r="AN8">
-        <v>55</v>
-      </c>
-      <c r="AO8">
-        <v>55</v>
-      </c>
-      <c r="AP8">
-        <v>8</v>
-      </c>
-      <c r="AQ8">
-        <v>7.6</v>
-      </c>
-      <c r="AR8">
-        <v>15.5</v>
-      </c>
-      <c r="AS8">
-        <v>34</v>
-      </c>
-      <c r="AT8">
-        <v>7.8</v>
-      </c>
-      <c r="AU8">
-        <v>6.4</v>
-      </c>
-      <c r="AV8">
-        <v>11.5</v>
-      </c>
-      <c r="AW8">
-        <v>27</v>
-      </c>
-      <c r="AX8">
-        <v>16</v>
-      </c>
-      <c r="AY8">
-        <v>12</v>
-      </c>
-      <c r="AZ8">
-        <v>18.5</v>
-      </c>
-      <c r="BA8">
-        <v>44</v>
-      </c>
-      <c r="BB8">
-        <v>36</v>
-      </c>
-      <c r="BC8">
-        <v>32</v>
-      </c>
-      <c r="BD8">
-        <v>46</v>
-      </c>
-      <c r="BE8">
-        <v>75</v>
-      </c>
       <c r="BF8">
-        <v>40</v>
+        <v>4.9</v>
       </c>
       <c r="BG8">
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="BH8">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="BI8">
-        <v>2.32</v>
+        <v>3.5</v>
       </c>
       <c r="BJ8">
         <v>11.5</v>
       </c>
       <c r="BK8">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>8.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BN8">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="BO8">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="BP8">
-        <v>29</v>
+        <v>7.8</v>
       </c>
       <c r="BQ8">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BR8">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="BS8">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BT8">
-        <v>5.8</v>
+        <v>13.5</v>
       </c>
       <c r="BU8">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="BV8">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="BW8">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="BX8">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>7.2</v>
+        <v>13.5</v>
       </c>
       <c r="BZ8">
-        <v>50</v>
+        <v>11.5</v>
       </c>
       <c r="CA8">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:80">
-      <c r="A9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E9" t="s">
-        <v>109</v>
-      </c>
-      <c r="F9">
-        <v>2.08</v>
-      </c>
-      <c r="G9">
-        <v>2.1</v>
-      </c>
-      <c r="H9">
-        <v>4.4</v>
-      </c>
-      <c r="I9">
-        <v>4.6</v>
-      </c>
-      <c r="J9">
-        <v>3.3</v>
-      </c>
-      <c r="K9">
-        <v>3.35</v>
-      </c>
-      <c r="L9">
-        <v>1.54</v>
-      </c>
-      <c r="M9">
-        <v>1.11</v>
-      </c>
-      <c r="N9">
-        <v>2.92</v>
-      </c>
-      <c r="O9">
-        <v>1.51</v>
-      </c>
-      <c r="P9">
-        <v>1.63</v>
-      </c>
-      <c r="Q9">
-        <v>2.54</v>
-      </c>
-      <c r="R9">
-        <v>1.22</v>
-      </c>
-      <c r="S9">
-        <v>5.1</v>
-      </c>
-      <c r="T9">
-        <v>2.16</v>
-      </c>
-      <c r="U9">
-        <v>1.84</v>
-      </c>
-      <c r="V9">
-        <v>1.27</v>
-      </c>
-      <c r="W9">
-        <v>1.9</v>
-      </c>
-      <c r="X9">
-        <v>9.6</v>
-      </c>
-      <c r="Y9">
-        <v>12.5</v>
-      </c>
-      <c r="Z9">
-        <v>32</v>
-      </c>
-      <c r="AA9">
-        <v>110</v>
-      </c>
-      <c r="AB9">
-        <v>7</v>
-      </c>
-      <c r="AC9">
-        <v>7.2</v>
-      </c>
-      <c r="AD9">
-        <v>18.5</v>
-      </c>
-      <c r="AE9">
-        <v>70</v>
-      </c>
-      <c r="AF9">
-        <v>11</v>
-      </c>
-      <c r="AG9">
-        <v>11</v>
-      </c>
-      <c r="AH9">
-        <v>24</v>
-      </c>
-      <c r="AI9">
-        <v>110</v>
-      </c>
-      <c r="AJ9">
-        <v>24</v>
-      </c>
-      <c r="AK9">
-        <v>26</v>
-      </c>
-      <c r="AL9">
-        <v>55</v>
-      </c>
-      <c r="AM9">
-        <v>210</v>
-      </c>
-      <c r="AN9">
-        <v>27</v>
-      </c>
-      <c r="AO9">
-        <v>110</v>
-      </c>
-      <c r="AP9">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ9">
-        <v>11.5</v>
-      </c>
-      <c r="AR9">
-        <v>28</v>
-      </c>
-      <c r="AS9">
-        <v>85</v>
-      </c>
-      <c r="AT9">
-        <v>6.6</v>
-      </c>
-      <c r="AU9">
-        <v>7</v>
-      </c>
-      <c r="AV9">
-        <v>17</v>
-      </c>
-      <c r="AW9">
-        <v>55</v>
-      </c>
-      <c r="AX9">
-        <v>10</v>
-      </c>
-      <c r="AY9">
-        <v>10</v>
-      </c>
-      <c r="AZ9">
-        <v>22</v>
-      </c>
-      <c r="BA9">
-        <v>50</v>
-      </c>
-      <c r="BB9">
-        <v>23</v>
-      </c>
-      <c r="BC9">
-        <v>24</v>
-      </c>
-      <c r="BD9">
-        <v>48</v>
-      </c>
-      <c r="BE9">
-        <v>120</v>
-      </c>
-      <c r="BF9">
-        <v>23</v>
-      </c>
-      <c r="BG9">
-        <v>21</v>
-      </c>
-      <c r="BH9">
-        <v>2.94</v>
-      </c>
-      <c r="BI9">
-        <v>2.72</v>
-      </c>
-      <c r="BJ9">
-        <v>11.5</v>
-      </c>
-      <c r="BK9">
-        <v>6.8</v>
-      </c>
-      <c r="BL9">
-        <v>220</v>
-      </c>
-      <c r="BM9">
-        <v>140</v>
-      </c>
-      <c r="BN9">
-        <v>4.6</v>
-      </c>
-      <c r="BO9">
-        <v>4.1</v>
-      </c>
-      <c r="BP9">
-        <v>16.5</v>
-      </c>
-      <c r="BQ9">
-        <v>8.4</v>
-      </c>
-      <c r="BR9">
-        <v>36</v>
-      </c>
-      <c r="BS9">
-        <v>10.5</v>
-      </c>
-      <c r="BT9">
-        <v>7.4</v>
-      </c>
-      <c r="BU9">
-        <v>6.4</v>
-      </c>
-      <c r="BV9">
-        <v>48</v>
-      </c>
-      <c r="BW9">
-        <v>11.5</v>
-      </c>
-      <c r="BX9">
-        <v>60</v>
-      </c>
-      <c r="BY9">
-        <v>12</v>
-      </c>
-      <c r="BZ9">
-        <v>38</v>
-      </c>
-      <c r="CA9">
-        <v>11</v>
-      </c>
-      <c r="CB9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:80">
-      <c r="A10" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" t="s">
-        <v>101</v>
-      </c>
-      <c r="E10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F10">
-        <v>1.32</v>
-      </c>
-      <c r="G10">
-        <v>1.34</v>
-      </c>
-      <c r="H10">
-        <v>11.5</v>
-      </c>
-      <c r="I10">
-        <v>13</v>
-      </c>
-      <c r="J10">
-        <v>5.8</v>
-      </c>
-      <c r="K10">
-        <v>6.2</v>
-      </c>
-      <c r="L10">
-        <v>1.3</v>
-      </c>
-      <c r="M10">
-        <v>1.04</v>
-      </c>
-      <c r="N10">
-        <v>5.4</v>
-      </c>
-      <c r="O10">
-        <v>1.21</v>
-      </c>
-      <c r="P10">
-        <v>2.5</v>
-      </c>
-      <c r="Q10">
-        <v>1.63</v>
-      </c>
-      <c r="R10">
-        <v>1.59</v>
-      </c>
-      <c r="S10">
-        <v>2.62</v>
-      </c>
-      <c r="T10">
-        <v>2.08</v>
-      </c>
-      <c r="U10">
-        <v>1.89</v>
-      </c>
-      <c r="V10">
-        <v>1.08</v>
-      </c>
-      <c r="W10">
-        <v>3.9</v>
-      </c>
-      <c r="X10">
-        <v>24</v>
-      </c>
-      <c r="Y10">
-        <v>38</v>
-      </c>
-      <c r="Z10">
-        <v>120</v>
-      </c>
-      <c r="AA10">
-        <v>550</v>
-      </c>
-      <c r="AB10">
-        <v>9.6</v>
-      </c>
-      <c r="AC10">
-        <v>13.5</v>
-      </c>
-      <c r="AD10">
-        <v>42</v>
-      </c>
-      <c r="AE10">
-        <v>190</v>
-      </c>
-      <c r="AF10">
-        <v>8.4</v>
-      </c>
-      <c r="AG10">
-        <v>10.5</v>
-      </c>
-      <c r="AH10">
-        <v>29</v>
-      </c>
-      <c r="AI10">
-        <v>150</v>
-      </c>
-      <c r="AJ10">
-        <v>10.5</v>
-      </c>
-      <c r="AK10">
-        <v>14</v>
-      </c>
-      <c r="AL10">
-        <v>38</v>
-      </c>
-      <c r="AM10">
-        <v>170</v>
-      </c>
-      <c r="AN10">
-        <v>4.9</v>
-      </c>
-      <c r="AO10">
-        <v>300</v>
-      </c>
-      <c r="AP10">
-        <v>21</v>
-      </c>
-      <c r="AQ10">
-        <v>32</v>
-      </c>
-      <c r="AR10">
-        <v>17</v>
-      </c>
-      <c r="AS10">
-        <v>19.5</v>
-      </c>
-      <c r="AT10">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU10">
-        <v>12</v>
-      </c>
-      <c r="AV10">
-        <v>32</v>
-      </c>
-      <c r="AW10">
-        <v>18</v>
-      </c>
-      <c r="AX10">
-        <v>7.6</v>
-      </c>
-      <c r="AY10">
-        <v>9.6</v>
-      </c>
-      <c r="AZ10">
-        <v>26</v>
-      </c>
-      <c r="BA10">
-        <v>17.5</v>
-      </c>
-      <c r="BB10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC10">
-        <v>12.5</v>
-      </c>
-      <c r="BD10">
-        <v>30</v>
-      </c>
-      <c r="BE10">
-        <v>18</v>
-      </c>
-      <c r="BF10">
-        <v>4.6</v>
-      </c>
-      <c r="BG10">
-        <v>18.5</v>
-      </c>
-      <c r="BH10">
-        <v>4.3</v>
-      </c>
-      <c r="BI10">
-        <v>3.55</v>
-      </c>
-      <c r="BJ10">
-        <v>12</v>
-      </c>
-      <c r="BK10">
-        <v>7.4</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>18</v>
-      </c>
-      <c r="BN10">
-        <v>3.8</v>
-      </c>
-      <c r="BO10">
-        <v>3.4</v>
-      </c>
-      <c r="BP10">
-        <v>7.2</v>
-      </c>
-      <c r="BQ10">
-        <v>6</v>
-      </c>
-      <c r="BR10">
-        <v>22</v>
-      </c>
-      <c r="BS10">
-        <v>10.5</v>
-      </c>
-      <c r="BT10">
-        <v>14.5</v>
-      </c>
-      <c r="BU10">
-        <v>8.4</v>
-      </c>
-      <c r="BV10">
-        <v>1000</v>
-      </c>
-      <c r="BW10">
-        <v>17</v>
-      </c>
-      <c r="BX10">
-        <v>100</v>
-      </c>
-      <c r="BY10">
-        <v>16.5</v>
-      </c>
-      <c r="BZ10">
-        <v>11</v>
-      </c>
-      <c r="CA10">
-        <v>7</v>
-      </c>
-      <c r="CB10" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="102">
   <si>
     <t>League</t>
   </si>
@@ -256,9 +256,6 @@
     <t>SnapshotTS</t>
   </si>
   <si>
-    <t>Romanian Liga II</t>
-  </si>
-  <si>
     <t>Algerian Ligue 1</t>
   </si>
   <si>
@@ -274,9 +271,6 @@
     <t>2026-09-22</t>
   </si>
   <si>
-    <t>17:00:00</t>
-  </si>
-  <si>
     <t>19:00:00</t>
   </si>
   <si>
@@ -289,9 +283,6 @@
     <t>23:00:00</t>
   </si>
   <si>
-    <t>ASA Targu Mures</t>
-  </si>
-  <si>
     <t>MC Alger</t>
   </si>
   <si>
@@ -310,9 +301,6 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>CS FC Dinamo Bucuresti</t>
-  </si>
-  <si>
     <t>MC Oran</t>
   </si>
   <si>
@@ -331,7 +319,7 @@
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-09-22 15:17:44</t>
+    <t>2026-09-22 17:29:27</t>
   </si>
 </sst>
 </file>
@@ -663,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -913,241 +901,241 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" t="s">
         <v>85</v>
       </c>
-      <c r="C2" t="s">
-        <v>86</v>
-      </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F2">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="G2">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="H2">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="I2">
+        <v>960</v>
+      </c>
+      <c r="J2">
+        <v>3.4</v>
+      </c>
+      <c r="K2">
         <v>4.3</v>
       </c>
-      <c r="J2">
-        <v>3.25</v>
-      </c>
-      <c r="K2">
-        <v>3.5</v>
-      </c>
       <c r="L2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="R2">
-        <v>7.2</v>
+        <v>1.12</v>
       </c>
       <c r="S2">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
+        <v>980</v>
+      </c>
+      <c r="AC2">
+        <v>24</v>
+      </c>
+      <c r="AD2">
+        <v>34</v>
+      </c>
+      <c r="AE2">
         <v>1000</v>
       </c>
-      <c r="AC2">
+      <c r="AF2">
+        <v>8</v>
+      </c>
+      <c r="AG2">
+        <v>65</v>
+      </c>
+      <c r="AH2">
+        <v>36</v>
+      </c>
+      <c r="AI2">
         <v>1000</v>
       </c>
-      <c r="AD2">
-        <v>8</v>
-      </c>
-      <c r="AE2">
-        <v>42</v>
-      </c>
-      <c r="AF2">
+      <c r="AJ2">
+        <v>16.5</v>
+      </c>
+      <c r="AK2">
+        <v>22</v>
+      </c>
+      <c r="AL2">
+        <v>90</v>
+      </c>
+      <c r="AM2">
         <v>1000</v>
       </c>
-      <c r="AG2">
+      <c r="AN2">
+        <v>23</v>
+      </c>
+      <c r="AO2">
+        <v>420</v>
+      </c>
+      <c r="AP2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ2">
+        <v>6.4</v>
+      </c>
+      <c r="AR2">
+        <v>3.35</v>
+      </c>
+      <c r="AS2">
+        <v>75</v>
+      </c>
+      <c r="AT2">
+        <v>4.9</v>
+      </c>
+      <c r="AU2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV2">
+        <v>3.35</v>
+      </c>
+      <c r="AW2">
+        <v>70</v>
+      </c>
+      <c r="AX2">
+        <v>6.2</v>
+      </c>
+      <c r="AY2">
+        <v>9.6</v>
+      </c>
+      <c r="AZ2">
+        <v>7.6</v>
+      </c>
+      <c r="BA2">
+        <v>65</v>
+      </c>
+      <c r="BB2">
+        <v>11.5</v>
+      </c>
+      <c r="BC2">
+        <v>6.6</v>
+      </c>
+      <c r="BD2">
+        <v>3.3</v>
+      </c>
+      <c r="BE2">
+        <v>3.25</v>
+      </c>
+      <c r="BF2">
+        <v>5.7</v>
+      </c>
+      <c r="BG2">
+        <v>3.5</v>
+      </c>
+      <c r="BH2">
         <v>1000</v>
       </c>
-      <c r="AH2">
-        <v>4</v>
-      </c>
-      <c r="AI2">
-        <v>20</v>
-      </c>
-      <c r="AJ2">
+      <c r="BI2">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2">
         <v>1000</v>
       </c>
-      <c r="AK2">
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
         <v>1000</v>
       </c>
-      <c r="AL2">
-        <v>4</v>
-      </c>
-      <c r="AM2">
-        <v>26</v>
-      </c>
-      <c r="AN2">
-        <v>6.8</v>
-      </c>
-      <c r="AO2">
-        <v>65</v>
-      </c>
-      <c r="AP2">
-        <v>110</v>
-      </c>
-      <c r="AQ2">
-        <v>9.4</v>
-      </c>
-      <c r="AR2">
-        <v>9</v>
-      </c>
-      <c r="AS2">
-        <v>55</v>
-      </c>
-      <c r="AT2">
-        <v>28</v>
-      </c>
-      <c r="AU2">
-        <v>9.4</v>
-      </c>
-      <c r="AV2">
-        <v>7</v>
-      </c>
-      <c r="AW2">
-        <v>10</v>
-      </c>
-      <c r="AX2">
-        <v>28</v>
-      </c>
-      <c r="AY2">
-        <v>9</v>
-      </c>
-      <c r="AZ2">
-        <v>3.5</v>
-      </c>
-      <c r="BA2">
-        <v>14</v>
-      </c>
-      <c r="BB2">
-        <v>28</v>
-      </c>
-      <c r="BC2">
-        <v>9.4</v>
-      </c>
-      <c r="BD2">
-        <v>3.4</v>
-      </c>
-      <c r="BE2">
-        <v>16.5</v>
-      </c>
-      <c r="BF2">
-        <v>4.1</v>
-      </c>
-      <c r="BG2">
-        <v>10.5</v>
-      </c>
-      <c r="BH2">
-        <v>0</v>
-      </c>
-      <c r="BI2">
-        <v>0</v>
-      </c>
-      <c r="BJ2">
-        <v>0</v>
-      </c>
-      <c r="BK2">
-        <v>0</v>
-      </c>
-      <c r="BL2">
-        <v>0</v>
-      </c>
       <c r="BM2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1155,43 +1143,43 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F3">
-        <v>1.63</v>
+        <v>2.84</v>
       </c>
       <c r="G3">
-        <v>1.69</v>
+        <v>2.94</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>2.8</v>
       </c>
       <c r="I3">
-        <v>7.8</v>
+        <v>2.94</v>
       </c>
       <c r="J3">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="K3">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="L3">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M3">
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="O3">
         <v>1.51</v>
@@ -1203,677 +1191,677 @@
         <v>2.54</v>
       </c>
       <c r="R3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S3">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T3">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="U3">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="V3">
-        <v>1.14</v>
+        <v>1.51</v>
       </c>
       <c r="W3">
-        <v>2.44</v>
+        <v>1.51</v>
       </c>
       <c r="X3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y3">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="Z3">
-        <v>160</v>
+        <v>17.5</v>
       </c>
       <c r="AA3">
-        <v>900</v>
+        <v>60</v>
       </c>
       <c r="AB3">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>30</v>
+        <v>14.5</v>
       </c>
       <c r="AE3">
-        <v>700</v>
+        <v>50</v>
       </c>
       <c r="AF3">
-        <v>8.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="AG3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AH3">
+        <v>24</v>
+      </c>
+      <c r="AI3">
+        <v>80</v>
+      </c>
+      <c r="AJ3">
+        <v>60</v>
+      </c>
+      <c r="AK3">
+        <v>55</v>
+      </c>
+      <c r="AL3">
+        <v>75</v>
+      </c>
+      <c r="AM3">
+        <v>770</v>
+      </c>
+      <c r="AN3">
+        <v>55</v>
+      </c>
+      <c r="AO3">
+        <v>55</v>
+      </c>
+      <c r="AP3">
+        <v>8.4</v>
+      </c>
+      <c r="AQ3">
+        <v>8</v>
+      </c>
+      <c r="AR3">
+        <v>14.5</v>
+      </c>
+      <c r="AS3">
+        <v>38</v>
+      </c>
+      <c r="AT3">
+        <v>8</v>
+      </c>
+      <c r="AU3">
+        <v>6.4</v>
+      </c>
+      <c r="AV3">
+        <v>11.5</v>
+      </c>
+      <c r="AW3">
+        <v>32</v>
+      </c>
+      <c r="AX3">
+        <v>16</v>
+      </c>
+      <c r="AY3">
+        <v>12</v>
+      </c>
+      <c r="AZ3">
+        <v>19</v>
+      </c>
+      <c r="BA3">
+        <v>46</v>
+      </c>
+      <c r="BB3">
         <v>34</v>
       </c>
-      <c r="AI3">
-        <v>700</v>
-      </c>
-      <c r="AJ3">
-        <v>16.5</v>
-      </c>
-      <c r="AK3">
-        <v>24</v>
-      </c>
-      <c r="AL3">
-        <v>160</v>
-      </c>
-      <c r="AM3">
-        <v>700</v>
-      </c>
-      <c r="AN3">
-        <v>16.5</v>
-      </c>
-      <c r="AO3">
-        <v>410</v>
-      </c>
-      <c r="AP3">
-        <v>8.6</v>
-      </c>
-      <c r="AQ3">
-        <v>16</v>
-      </c>
-      <c r="AR3">
-        <v>12</v>
-      </c>
-      <c r="AS3">
-        <v>70</v>
-      </c>
-      <c r="AT3">
-        <v>5.3</v>
-      </c>
-      <c r="AU3">
-        <v>8</v>
-      </c>
-      <c r="AV3">
-        <v>23</v>
-      </c>
-      <c r="AW3">
-        <v>70</v>
-      </c>
-      <c r="AX3">
-        <v>7.2</v>
-      </c>
-      <c r="AY3">
-        <v>9.6</v>
-      </c>
-      <c r="AZ3">
-        <v>10</v>
-      </c>
-      <c r="BA3">
-        <v>65</v>
-      </c>
-      <c r="BB3">
-        <v>14</v>
-      </c>
       <c r="BC3">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="BD3">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="BE3">
-        <v>13.5</v>
+        <v>130</v>
       </c>
       <c r="BF3">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="BG3">
-        <v>14.5</v>
+        <v>32</v>
       </c>
       <c r="BH3">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="BI3">
-        <v>2.64</v>
+        <v>2.36</v>
       </c>
       <c r="BJ3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK3">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>8.800000000000001</v>
+        <v>150</v>
       </c>
       <c r="BN3">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="BO3">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="BP3">
-        <v>12.5</v>
+        <v>30</v>
       </c>
       <c r="BQ3">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS3">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BT3">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
       <c r="BU3">
-        <v>8.6</v>
+        <v>5</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW3">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY3">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BZ3">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="CA3">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="CB3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F4">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="G4">
-        <v>3.05</v>
+        <v>2.42</v>
       </c>
       <c r="H4">
-        <v>2.76</v>
+        <v>3.45</v>
       </c>
       <c r="I4">
-        <v>2.94</v>
+        <v>3.65</v>
       </c>
       <c r="J4">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K4">
+        <v>3.45</v>
+      </c>
+      <c r="L4">
+        <v>1.49</v>
+      </c>
+      <c r="M4">
+        <v>1.09</v>
+      </c>
+      <c r="N4">
         <v>3.25</v>
       </c>
-      <c r="L4">
-        <v>1.56</v>
-      </c>
-      <c r="M4">
-        <v>1.11</v>
-      </c>
-      <c r="N4">
-        <v>2.84</v>
-      </c>
       <c r="O4">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="P4">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="Q4">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="R4">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S4">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="T4">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="U4">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="V4">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="W4">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="X4">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="Y4">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="Z4">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="AA4">
+        <v>160</v>
+      </c>
+      <c r="AB4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC4">
+        <v>7.6</v>
+      </c>
+      <c r="AD4">
+        <v>15.5</v>
+      </c>
+      <c r="AE4">
         <v>60</v>
       </c>
-      <c r="AB4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC4">
-        <v>7.4</v>
-      </c>
-      <c r="AD4">
-        <v>14</v>
-      </c>
-      <c r="AE4">
-        <v>48</v>
-      </c>
       <c r="AF4">
+        <v>14.5</v>
+      </c>
+      <c r="AG4">
+        <v>11.5</v>
+      </c>
+      <c r="AH4">
         <v>22</v>
       </c>
-      <c r="AG4">
-        <v>14.5</v>
-      </c>
-      <c r="AH4">
-        <v>23</v>
-      </c>
       <c r="AI4">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AJ4">
+        <v>38</v>
+      </c>
+      <c r="AK4">
+        <v>32</v>
+      </c>
+      <c r="AL4">
         <v>65</v>
-      </c>
-      <c r="AK4">
-        <v>50</v>
-      </c>
-      <c r="AL4">
-        <v>85</v>
       </c>
       <c r="AM4">
         <v>580</v>
       </c>
       <c r="AN4">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="AO4">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AP4">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR4">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AS4">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AT4">
         <v>8</v>
       </c>
       <c r="AU4">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW4">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AX4">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AY4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ4">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA4">
         <v>44</v>
       </c>
       <c r="BB4">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BC4">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BD4">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BE4">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="BF4">
+        <v>21</v>
+      </c>
+      <c r="BG4">
         <v>36</v>
       </c>
-      <c r="BG4">
-        <v>29</v>
-      </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>130</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="CB4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F5">
-        <v>2.38</v>
+        <v>2.96</v>
       </c>
       <c r="G5">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="H5">
-        <v>3.35</v>
+        <v>2.78</v>
       </c>
       <c r="I5">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="J5">
+        <v>3.05</v>
+      </c>
+      <c r="K5">
         <v>3.25</v>
       </c>
-      <c r="K5">
-        <v>3.45</v>
-      </c>
       <c r="L5">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N5">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="O5">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="P5">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="Q5">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="R5">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="S5">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="T5">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="U5">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="V5">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="W5">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="X5">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y5">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z5">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AA5">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="AB5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC5">
+        <v>7.2</v>
+      </c>
+      <c r="AD5">
+        <v>14</v>
+      </c>
+      <c r="AE5">
+        <v>50</v>
+      </c>
+      <c r="AF5">
+        <v>19</v>
+      </c>
+      <c r="AG5">
+        <v>14.5</v>
+      </c>
+      <c r="AH5">
+        <v>23</v>
+      </c>
+      <c r="AI5">
+        <v>75</v>
+      </c>
+      <c r="AJ5">
+        <v>60</v>
+      </c>
+      <c r="AK5">
+        <v>55</v>
+      </c>
+      <c r="AL5">
+        <v>70</v>
+      </c>
+      <c r="AM5">
+        <v>200</v>
+      </c>
+      <c r="AN5">
+        <v>65</v>
+      </c>
+      <c r="AO5">
+        <v>55</v>
+      </c>
+      <c r="AP5">
+        <v>8.4</v>
+      </c>
+      <c r="AQ5">
         <v>7.8</v>
       </c>
-      <c r="AD5">
-        <v>15</v>
-      </c>
-      <c r="AE5">
-        <v>120</v>
-      </c>
-      <c r="AF5">
-        <v>15</v>
-      </c>
-      <c r="AG5">
+      <c r="AR5">
+        <v>15.5</v>
+      </c>
+      <c r="AS5">
+        <v>36</v>
+      </c>
+      <c r="AT5">
+        <v>8</v>
+      </c>
+      <c r="AU5">
+        <v>6.4</v>
+      </c>
+      <c r="AV5">
         <v>12</v>
-      </c>
-      <c r="AH5">
-        <v>21</v>
-      </c>
-      <c r="AI5">
-        <v>370</v>
-      </c>
-      <c r="AJ5">
-        <v>95</v>
-      </c>
-      <c r="AK5">
-        <v>40</v>
-      </c>
-      <c r="AL5">
-        <v>120</v>
-      </c>
-      <c r="AM5">
-        <v>500</v>
-      </c>
-      <c r="AN5">
-        <v>34</v>
-      </c>
-      <c r="AO5">
-        <v>500</v>
-      </c>
-      <c r="AP5">
-        <v>10</v>
-      </c>
-      <c r="AQ5">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR5">
-        <v>17</v>
-      </c>
-      <c r="AS5">
-        <v>46</v>
-      </c>
-      <c r="AT5">
-        <v>7.8</v>
-      </c>
-      <c r="AU5">
-        <v>6.8</v>
-      </c>
-      <c r="AV5">
-        <v>13</v>
       </c>
       <c r="AW5">
         <v>30</v>
       </c>
       <c r="AX5">
+        <v>16</v>
+      </c>
+      <c r="AY5">
         <v>12.5</v>
       </c>
-      <c r="AY5">
-        <v>10.5</v>
-      </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BA5">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BB5">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="BC5">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="BD5">
+        <v>46</v>
+      </c>
+      <c r="BE5">
+        <v>130</v>
+      </c>
+      <c r="BF5">
+        <v>40</v>
+      </c>
+      <c r="BG5">
         <v>32</v>
       </c>
-      <c r="BE5">
-        <v>90</v>
-      </c>
-      <c r="BF5">
-        <v>19</v>
-      </c>
-      <c r="BG5">
-        <v>38</v>
-      </c>
       <c r="BH5">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="BI5">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="BJ5">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK5">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>12.5</v>
+        <v>170</v>
       </c>
       <c r="BN5">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BO5">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="BP5">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="BQ5">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT5">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BU5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW5">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY5">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1881,241 +1869,241 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F6">
-        <v>2.94</v>
+        <v>2.2</v>
       </c>
       <c r="G6">
-        <v>3.15</v>
+        <v>2.22</v>
       </c>
       <c r="H6">
-        <v>2.76</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="K6">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="L6">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="M6">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N6">
-        <v>2.74</v>
+        <v>2.98</v>
       </c>
       <c r="O6">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="P6">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="Q6">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="R6">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S6">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>2.08</v>
       </c>
       <c r="U6">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="V6">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="W6">
-        <v>1.47</v>
+        <v>1.81</v>
       </c>
       <c r="X6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Y6">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="Z6">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AA6">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="AB6">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AC6">
         <v>7.4</v>
       </c>
       <c r="AD6">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AE6">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AF6">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AG6">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AH6">
         <v>23</v>
       </c>
       <c r="AI6">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AJ6">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AK6">
+        <v>28</v>
+      </c>
+      <c r="AL6">
         <v>55</v>
-      </c>
-      <c r="AL6">
-        <v>75</v>
       </c>
       <c r="AM6">
         <v>190</v>
       </c>
       <c r="AN6">
-        <v>600</v>
+        <v>29</v>
       </c>
       <c r="AO6">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="AP6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ6">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AR6">
+        <v>24</v>
+      </c>
+      <c r="AS6">
+        <v>70</v>
+      </c>
+      <c r="AT6">
+        <v>7.2</v>
+      </c>
+      <c r="AU6">
+        <v>7</v>
+      </c>
+      <c r="AV6">
         <v>15.5</v>
       </c>
-      <c r="AS6">
-        <v>34</v>
-      </c>
-      <c r="AT6">
-        <v>8</v>
-      </c>
-      <c r="AU6">
-        <v>6.4</v>
-      </c>
-      <c r="AV6">
-        <v>11.5</v>
-      </c>
       <c r="AW6">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="AX6">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AY6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ6">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BA6">
         <v>44</v>
       </c>
       <c r="BB6">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BC6">
+        <v>25</v>
+      </c>
+      <c r="BD6">
         <v>32</v>
       </c>
-      <c r="BD6">
-        <v>46</v>
-      </c>
       <c r="BE6">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="BF6">
+        <v>24</v>
+      </c>
+      <c r="BG6">
+        <v>65</v>
+      </c>
+      <c r="BH6">
+        <v>2.88</v>
+      </c>
+      <c r="BI6">
+        <v>2.7</v>
+      </c>
+      <c r="BJ6">
+        <v>11</v>
+      </c>
+      <c r="BK6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BL6">
+        <v>210</v>
+      </c>
+      <c r="BM6">
+        <v>140</v>
+      </c>
+      <c r="BN6">
+        <v>4.7</v>
+      </c>
+      <c r="BO6">
+        <v>4.2</v>
+      </c>
+      <c r="BP6">
+        <v>17.5</v>
+      </c>
+      <c r="BQ6">
+        <v>9</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>12</v>
+      </c>
+      <c r="BT6">
+        <v>7</v>
+      </c>
+      <c r="BU6">
+        <v>6.2</v>
+      </c>
+      <c r="BV6">
         <v>40</v>
       </c>
-      <c r="BG6">
-        <v>30</v>
-      </c>
-      <c r="BH6">
-        <v>3.05</v>
-      </c>
-      <c r="BI6">
-        <v>2.32</v>
-      </c>
-      <c r="BJ6">
-        <v>11.5</v>
-      </c>
-      <c r="BK6">
-        <v>8.6</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BN6">
-        <v>6.2</v>
-      </c>
-      <c r="BO6">
-        <v>5</v>
-      </c>
-      <c r="BP6">
-        <v>29</v>
-      </c>
-      <c r="BQ6">
-        <v>6.6</v>
-      </c>
-      <c r="BR6">
-        <v>50</v>
-      </c>
-      <c r="BS6">
-        <v>7.2</v>
-      </c>
-      <c r="BT6">
-        <v>5.8</v>
-      </c>
-      <c r="BU6">
-        <v>4.8</v>
-      </c>
-      <c r="BV6">
-        <v>27</v>
-      </c>
       <c r="BW6">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="BX6">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BY6">
-        <v>7.2</v>
+        <v>13.5</v>
       </c>
       <c r="BZ6">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="CA6">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="CB6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2123,483 +2111,241 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F7">
-        <v>2.12</v>
+        <v>1.36</v>
       </c>
       <c r="G7">
-        <v>2.16</v>
+        <v>1.37</v>
       </c>
       <c r="H7">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="I7">
+        <v>11.5</v>
+      </c>
+      <c r="J7">
+        <v>5.7</v>
+      </c>
+      <c r="K7">
+        <v>5.9</v>
+      </c>
+      <c r="L7">
+        <v>1.31</v>
+      </c>
+      <c r="M7">
+        <v>1.04</v>
+      </c>
+      <c r="N7">
+        <v>5.4</v>
+      </c>
+      <c r="O7">
+        <v>1.21</v>
+      </c>
+      <c r="P7">
+        <v>2.48</v>
+      </c>
+      <c r="Q7">
+        <v>1.64</v>
+      </c>
+      <c r="R7">
+        <v>1.6</v>
+      </c>
+      <c r="S7">
+        <v>2.62</v>
+      </c>
+      <c r="T7">
+        <v>2.02</v>
+      </c>
+      <c r="U7">
+        <v>1.93</v>
+      </c>
+      <c r="V7">
+        <v>1.09</v>
+      </c>
+      <c r="W7">
+        <v>3.7</v>
+      </c>
+      <c r="X7">
+        <v>24</v>
+      </c>
+      <c r="Y7">
+        <v>36</v>
+      </c>
+      <c r="Z7">
+        <v>120</v>
+      </c>
+      <c r="AA7">
+        <v>410</v>
+      </c>
+      <c r="AB7">
+        <v>9.6</v>
+      </c>
+      <c r="AC7">
+        <v>13</v>
+      </c>
+      <c r="AD7">
+        <v>38</v>
+      </c>
+      <c r="AE7">
+        <v>160</v>
+      </c>
+      <c r="AF7">
+        <v>8.6</v>
+      </c>
+      <c r="AG7">
+        <v>10.5</v>
+      </c>
+      <c r="AH7">
+        <v>29</v>
+      </c>
+      <c r="AI7">
+        <v>130</v>
+      </c>
+      <c r="AJ7">
+        <v>11</v>
+      </c>
+      <c r="AK7">
+        <v>14</v>
+      </c>
+      <c r="AL7">
+        <v>36</v>
+      </c>
+      <c r="AM7">
+        <v>150</v>
+      </c>
+      <c r="AN7">
+        <v>5.2</v>
+      </c>
+      <c r="AO7">
+        <v>200</v>
+      </c>
+      <c r="AP7">
+        <v>21</v>
+      </c>
+      <c r="AQ7">
+        <v>34</v>
+      </c>
+      <c r="AR7">
+        <v>16</v>
+      </c>
+      <c r="AS7">
+        <v>20</v>
+      </c>
+      <c r="AT7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU7">
+        <v>11.5</v>
+      </c>
+      <c r="AV7">
+        <v>32</v>
+      </c>
+      <c r="AW7">
+        <v>17.5</v>
+      </c>
+      <c r="AX7">
+        <v>7.8</v>
+      </c>
+      <c r="AY7">
+        <v>9.4</v>
+      </c>
+      <c r="AZ7">
+        <v>24</v>
+      </c>
+      <c r="BA7">
+        <v>17</v>
+      </c>
+      <c r="BB7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC7">
+        <v>12.5</v>
+      </c>
+      <c r="BD7">
+        <v>30</v>
+      </c>
+      <c r="BE7">
+        <v>17</v>
+      </c>
+      <c r="BF7">
+        <v>4.8</v>
+      </c>
+      <c r="BG7">
+        <v>17.5</v>
+      </c>
+      <c r="BH7">
         <v>4.3</v>
       </c>
-      <c r="J7">
-        <v>3.3</v>
-      </c>
-      <c r="K7">
-        <v>3.35</v>
-      </c>
-      <c r="L7">
-        <v>1.54</v>
-      </c>
-      <c r="M7">
-        <v>1.11</v>
-      </c>
-      <c r="N7">
-        <v>2.94</v>
-      </c>
-      <c r="O7">
-        <v>1.5</v>
-      </c>
-      <c r="P7">
-        <v>1.64</v>
-      </c>
-      <c r="Q7">
-        <v>2.54</v>
-      </c>
-      <c r="R7">
-        <v>1.23</v>
-      </c>
-      <c r="S7">
-        <v>5</v>
-      </c>
-      <c r="T7">
-        <v>2.1</v>
-      </c>
-      <c r="U7">
-        <v>1.82</v>
-      </c>
-      <c r="V7">
-        <v>1.3</v>
-      </c>
-      <c r="W7">
-        <v>1.86</v>
-      </c>
-      <c r="X7">
-        <v>9.6</v>
-      </c>
-      <c r="Y7">
-        <v>12</v>
-      </c>
-      <c r="Z7">
-        <v>30</v>
-      </c>
-      <c r="AA7">
-        <v>110</v>
-      </c>
-      <c r="AB7">
-        <v>7</v>
-      </c>
-      <c r="AC7">
-        <v>7.4</v>
-      </c>
-      <c r="AD7">
-        <v>18</v>
-      </c>
-      <c r="AE7">
-        <v>70</v>
-      </c>
-      <c r="AF7">
-        <v>11</v>
-      </c>
-      <c r="AG7">
-        <v>11</v>
-      </c>
-      <c r="AH7">
-        <v>24</v>
-      </c>
-      <c r="AI7">
-        <v>100</v>
-      </c>
-      <c r="AJ7">
-        <v>29</v>
-      </c>
-      <c r="AK7">
-        <v>27</v>
-      </c>
-      <c r="AL7">
-        <v>55</v>
-      </c>
-      <c r="AM7">
-        <v>190</v>
-      </c>
-      <c r="AN7">
-        <v>34</v>
-      </c>
-      <c r="AO7">
-        <v>110</v>
-      </c>
-      <c r="AP7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ7">
-        <v>11</v>
-      </c>
-      <c r="AR7">
-        <v>27</v>
-      </c>
-      <c r="AS7">
-        <v>26</v>
-      </c>
-      <c r="AT7">
-        <v>6.6</v>
-      </c>
-      <c r="AU7">
-        <v>7.2</v>
-      </c>
-      <c r="AV7">
-        <v>17</v>
-      </c>
-      <c r="AW7">
-        <v>55</v>
-      </c>
-      <c r="AX7">
-        <v>10</v>
-      </c>
-      <c r="AY7">
-        <v>10</v>
-      </c>
-      <c r="AZ7">
-        <v>21</v>
-      </c>
-      <c r="BA7">
-        <v>70</v>
-      </c>
-      <c r="BB7">
-        <v>25</v>
-      </c>
-      <c r="BC7">
-        <v>23</v>
-      </c>
-      <c r="BD7">
-        <v>48</v>
-      </c>
-      <c r="BE7">
-        <v>120</v>
-      </c>
-      <c r="BF7">
-        <v>24</v>
-      </c>
-      <c r="BG7">
-        <v>75</v>
-      </c>
-      <c r="BH7">
-        <v>2.94</v>
-      </c>
       <c r="BI7">
-        <v>2.74</v>
+        <v>3.85</v>
       </c>
       <c r="BJ7">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL7">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="BM7">
-        <v>140</v>
+        <v>15.5</v>
       </c>
       <c r="BN7">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="BO7">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="BP7">
-        <v>17</v>
+        <v>7.8</v>
       </c>
       <c r="BQ7">
         <v>7</v>
       </c>
       <c r="BR7">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="BS7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT7">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="BU7">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BV7">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="BW7">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY7">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BZ7">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="CA7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CB7" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:80">
-      <c r="A8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" t="s">
-        <v>97</v>
-      </c>
-      <c r="E8" t="s">
-        <v>104</v>
-      </c>
-      <c r="F8">
-        <v>1.36</v>
-      </c>
-      <c r="G8">
-        <v>1.37</v>
-      </c>
-      <c r="H8">
-        <v>10</v>
-      </c>
-      <c r="I8">
-        <v>11</v>
-      </c>
-      <c r="J8">
-        <v>5.5</v>
-      </c>
-      <c r="K8">
-        <v>5.8</v>
-      </c>
-      <c r="L8">
-        <v>1.3</v>
-      </c>
-      <c r="M8">
-        <v>1.04</v>
-      </c>
-      <c r="N8">
-        <v>5.4</v>
-      </c>
-      <c r="O8">
-        <v>1.22</v>
-      </c>
-      <c r="P8">
-        <v>2.48</v>
-      </c>
-      <c r="Q8">
-        <v>1.65</v>
-      </c>
-      <c r="R8">
-        <v>1.58</v>
-      </c>
-      <c r="S8">
-        <v>2.64</v>
-      </c>
-      <c r="T8">
-        <v>2.04</v>
-      </c>
-      <c r="U8">
-        <v>1.92</v>
-      </c>
-      <c r="V8">
-        <v>1.1</v>
-      </c>
-      <c r="W8">
-        <v>3.6</v>
-      </c>
-      <c r="X8">
-        <v>24</v>
-      </c>
-      <c r="Y8">
-        <v>36</v>
-      </c>
-      <c r="Z8">
-        <v>150</v>
-      </c>
-      <c r="AA8">
-        <v>410</v>
-      </c>
-      <c r="AB8">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC8">
-        <v>13</v>
-      </c>
-      <c r="AD8">
-        <v>36</v>
-      </c>
-      <c r="AE8">
-        <v>160</v>
-      </c>
-      <c r="AF8">
-        <v>8.4</v>
-      </c>
-      <c r="AG8">
-        <v>10.5</v>
-      </c>
-      <c r="AH8">
-        <v>29</v>
-      </c>
-      <c r="AI8">
-        <v>180</v>
-      </c>
-      <c r="AJ8">
-        <v>11</v>
-      </c>
-      <c r="AK8">
-        <v>14</v>
-      </c>
-      <c r="AL8">
-        <v>36</v>
-      </c>
-      <c r="AM8">
-        <v>150</v>
-      </c>
-      <c r="AN8">
-        <v>5.4</v>
-      </c>
-      <c r="AO8">
-        <v>210</v>
-      </c>
-      <c r="AP8">
-        <v>20</v>
-      </c>
-      <c r="AQ8">
-        <v>27</v>
-      </c>
-      <c r="AR8">
-        <v>14.5</v>
-      </c>
-      <c r="AS8">
-        <v>16.5</v>
-      </c>
-      <c r="AT8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU8">
-        <v>11.5</v>
-      </c>
-      <c r="AV8">
-        <v>30</v>
-      </c>
-      <c r="AW8">
-        <v>14.5</v>
-      </c>
-      <c r="AX8">
-        <v>7.6</v>
-      </c>
-      <c r="AY8">
-        <v>9.4</v>
-      </c>
-      <c r="AZ8">
-        <v>23</v>
-      </c>
-      <c r="BA8">
-        <v>15</v>
-      </c>
-      <c r="BB8">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC8">
-        <v>12.5</v>
-      </c>
-      <c r="BD8">
-        <v>30</v>
-      </c>
-      <c r="BE8">
-        <v>14.5</v>
-      </c>
-      <c r="BF8">
-        <v>4.9</v>
-      </c>
-      <c r="BG8">
-        <v>13.5</v>
-      </c>
-      <c r="BH8">
-        <v>4.3</v>
-      </c>
-      <c r="BI8">
-        <v>3.5</v>
-      </c>
-      <c r="BJ8">
-        <v>11.5</v>
-      </c>
-      <c r="BK8">
-        <v>9</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>15</v>
-      </c>
-      <c r="BN8">
-        <v>3.9</v>
-      </c>
-      <c r="BO8">
-        <v>3.2</v>
-      </c>
-      <c r="BP8">
-        <v>7.8</v>
-      </c>
-      <c r="BQ8">
-        <v>6</v>
-      </c>
-      <c r="BR8">
-        <v>23</v>
-      </c>
-      <c r="BS8">
-        <v>9.6</v>
-      </c>
-      <c r="BT8">
-        <v>13.5</v>
-      </c>
-      <c r="BU8">
-        <v>10</v>
-      </c>
-      <c r="BV8">
-        <v>85</v>
-      </c>
-      <c r="BW8">
-        <v>14</v>
-      </c>
-      <c r="BX8">
-        <v>1000</v>
-      </c>
-      <c r="BY8">
-        <v>13.5</v>
-      </c>
-      <c r="BZ8">
-        <v>11.5</v>
-      </c>
-      <c r="CA8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="CB8" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-22.xlsx
@@ -319,7 +319,7 @@
     <t>Jaguares de Cordoba</t>
   </si>
   <si>
-    <t>2026-09-22 17:29:27</t>
+    <t>2026-09-22 19:40:27</t>
   </si>
 </sst>
 </file>
@@ -1009,7 +1009,7 @@
         <v>22</v>
       </c>
       <c r="AL2">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AM2">
         <v>1000</v>
@@ -1155,226 +1155,226 @@
         <v>96</v>
       </c>
       <c r="F3">
-        <v>2.84</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>2.94</v>
+        <v>140</v>
       </c>
       <c r="H3">
-        <v>2.8</v>
+        <v>1.16</v>
       </c>
       <c r="I3">
-        <v>2.94</v>
+        <v>1.19</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>6.6</v>
       </c>
       <c r="K3">
-        <v>3.35</v>
+        <v>7.4</v>
       </c>
       <c r="L3">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>1.5</v>
+      </c>
+      <c r="O3">
+        <v>2.92</v>
+      </c>
+      <c r="P3">
+        <v>1.05</v>
+      </c>
+      <c r="Q3">
+        <v>18</v>
+      </c>
+      <c r="R3">
+        <v>1.01</v>
+      </c>
+      <c r="S3">
+        <v>100</v>
+      </c>
+      <c r="T3">
+        <v>3.5</v>
+      </c>
+      <c r="U3">
         <v>1.11</v>
       </c>
-      <c r="N3">
-        <v>2.84</v>
-      </c>
-      <c r="O3">
-        <v>1.51</v>
-      </c>
-      <c r="P3">
-        <v>1.61</v>
-      </c>
-      <c r="Q3">
-        <v>2.54</v>
-      </c>
-      <c r="R3">
-        <v>1.22</v>
-      </c>
-      <c r="S3">
-        <v>5.2</v>
-      </c>
-      <c r="T3">
-        <v>2.06</v>
-      </c>
-      <c r="U3">
-        <v>1.85</v>
-      </c>
       <c r="V3">
-        <v>1.51</v>
+        <v>5.6</v>
       </c>
       <c r="W3">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>9</v>
+        <v>1.53</v>
       </c>
       <c r="Z3">
-        <v>17.5</v>
+        <v>9.6</v>
       </c>
       <c r="AA3">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="AB3">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AD3">
-        <v>14.5</v>
+        <v>48</v>
       </c>
       <c r="AE3">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="AH3">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>770</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ3">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="AR3">
-        <v>14.5</v>
+        <v>6.8</v>
       </c>
       <c r="AS3">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="AT3">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AU3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
+        <v>23</v>
+      </c>
+      <c r="AW3">
+        <v>10.5</v>
+      </c>
+      <c r="AX3">
+        <v>10.5</v>
+      </c>
+      <c r="AY3">
+        <v>44</v>
+      </c>
+      <c r="AZ3">
         <v>11.5</v>
       </c>
-      <c r="AW3">
-        <v>32</v>
-      </c>
-      <c r="AX3">
-        <v>16</v>
-      </c>
-      <c r="AY3">
-        <v>12</v>
-      </c>
-      <c r="AZ3">
-        <v>19</v>
-      </c>
       <c r="BA3">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="BB3">
-        <v>34</v>
+        <v>10.5</v>
       </c>
       <c r="BC3">
-        <v>29</v>
+        <v>10.5</v>
       </c>
       <c r="BD3">
-        <v>48</v>
+        <v>10.5</v>
       </c>
       <c r="BE3">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="BF3">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="BG3">
-        <v>32</v>
+        <v>10.5</v>
       </c>
       <c r="BH3">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
         <v>101</v>
@@ -1397,226 +1397,226 @@
         <v>97</v>
       </c>
       <c r="F4">
-        <v>2.32</v>
+        <v>6.6</v>
       </c>
       <c r="G4">
-        <v>2.42</v>
+        <v>7.2</v>
       </c>
       <c r="H4">
-        <v>3.45</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
-        <v>3.65</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
-        <v>3.3</v>
+        <v>1.39</v>
       </c>
       <c r="K4">
-        <v>3.45</v>
+        <v>1.42</v>
       </c>
       <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>2.64</v>
+      </c>
+      <c r="N4">
+        <v>1.05</v>
+      </c>
+      <c r="O4">
+        <v>18.5</v>
+      </c>
+      <c r="P4">
+        <v>1.01</v>
+      </c>
+      <c r="Q4">
+        <v>130</v>
+      </c>
+      <c r="R4">
+        <v>1.01</v>
+      </c>
+      <c r="S4">
+        <v>480</v>
+      </c>
+      <c r="T4">
+        <v>24</v>
+      </c>
+      <c r="U4">
+        <v>1.02</v>
+      </c>
+      <c r="V4">
+        <v>1.17</v>
+      </c>
+      <c r="W4">
+        <v>1.17</v>
+      </c>
+      <c r="X4">
+        <v>1.53</v>
+      </c>
+      <c r="Y4">
+        <v>850</v>
+      </c>
+      <c r="Z4">
+        <v>970</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>7.8</v>
+      </c>
+      <c r="AC4">
+        <v>990</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>970</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
         <v>1.49</v>
       </c>
-      <c r="M4">
-        <v>1.09</v>
-      </c>
-      <c r="N4">
-        <v>3.25</v>
-      </c>
-      <c r="O4">
-        <v>1.42</v>
-      </c>
-      <c r="P4">
-        <v>1.75</v>
-      </c>
-      <c r="Q4">
-        <v>2.26</v>
-      </c>
-      <c r="R4">
-        <v>1.28</v>
-      </c>
-      <c r="S4">
+      <c r="AQ4">
+        <v>6.2</v>
+      </c>
+      <c r="AR4">
+        <v>50</v>
+      </c>
+      <c r="AS4">
+        <v>70</v>
+      </c>
+      <c r="AT4">
+        <v>6.4</v>
+      </c>
+      <c r="AU4">
+        <v>27</v>
+      </c>
+      <c r="AV4">
+        <v>150</v>
+      </c>
+      <c r="AW4">
         <v>4.4</v>
       </c>
-      <c r="T4">
-        <v>1.94</v>
-      </c>
-      <c r="U4">
-        <v>1.98</v>
-      </c>
-      <c r="V4">
-        <v>1.37</v>
-      </c>
-      <c r="W4">
-        <v>1.7</v>
-      </c>
-      <c r="X4">
-        <v>11.5</v>
-      </c>
-      <c r="Y4">
-        <v>11.5</v>
-      </c>
-      <c r="Z4">
-        <v>24</v>
-      </c>
-      <c r="AA4">
-        <v>160</v>
-      </c>
-      <c r="AB4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC4">
-        <v>7.6</v>
-      </c>
-      <c r="AD4">
-        <v>15.5</v>
-      </c>
-      <c r="AE4">
-        <v>60</v>
-      </c>
-      <c r="AF4">
-        <v>14.5</v>
-      </c>
-      <c r="AG4">
-        <v>11.5</v>
-      </c>
-      <c r="AH4">
-        <v>22</v>
-      </c>
-      <c r="AI4">
-        <v>130</v>
-      </c>
-      <c r="AJ4">
-        <v>38</v>
-      </c>
-      <c r="AK4">
-        <v>32</v>
-      </c>
-      <c r="AL4">
-        <v>65</v>
-      </c>
-      <c r="AM4">
-        <v>580</v>
-      </c>
-      <c r="AN4">
-        <v>27</v>
-      </c>
-      <c r="AO4">
-        <v>75</v>
-      </c>
-      <c r="AP4">
-        <v>10</v>
-      </c>
-      <c r="AQ4">
-        <v>10</v>
-      </c>
-      <c r="AR4">
-        <v>19</v>
-      </c>
-      <c r="AS4">
-        <v>46</v>
-      </c>
-      <c r="AT4">
-        <v>8</v>
-      </c>
-      <c r="AU4">
-        <v>6.8</v>
-      </c>
-      <c r="AV4">
-        <v>13.5</v>
-      </c>
-      <c r="AW4">
+      <c r="AX4">
+        <v>50</v>
+      </c>
+      <c r="AY4">
+        <v>100</v>
+      </c>
+      <c r="AZ4">
+        <v>4.4</v>
+      </c>
+      <c r="BA4">
+        <v>4.4</v>
+      </c>
+      <c r="BB4">
         <v>34</v>
       </c>
-      <c r="AX4">
-        <v>12.5</v>
-      </c>
-      <c r="AY4">
-        <v>11</v>
-      </c>
-      <c r="AZ4">
-        <v>17.5</v>
-      </c>
-      <c r="BA4">
-        <v>44</v>
-      </c>
-      <c r="BB4">
-        <v>24</v>
-      </c>
       <c r="BC4">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="BD4">
-        <v>36</v>
+        <v>4.4</v>
       </c>
       <c r="BE4">
-        <v>100</v>
+        <v>4.4</v>
       </c>
       <c r="BF4">
-        <v>21</v>
+        <v>4.4</v>
       </c>
       <c r="BG4">
-        <v>36</v>
+        <v>4.4</v>
       </c>
       <c r="BH4">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BI4">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK4">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BO4">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BP4">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BQ4">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BT4">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BU4">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BV4">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BW4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BX4">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BY4">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BZ4">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
         <v>101</v>
@@ -1639,226 +1639,226 @@
         <v>98</v>
       </c>
       <c r="F5">
-        <v>2.96</v>
+        <v>160</v>
       </c>
       <c r="G5">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="H5">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="I5">
-        <v>2.9</v>
+        <v>1.02</v>
       </c>
       <c r="J5">
-        <v>3.05</v>
+        <v>38</v>
       </c>
       <c r="K5">
-        <v>3.25</v>
+        <v>80</v>
       </c>
       <c r="L5">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q5">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="R5">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="S5">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="T5">
-        <v>2.08</v>
+        <v>4.4</v>
       </c>
       <c r="U5">
-        <v>1.86</v>
+        <v>1.26</v>
       </c>
       <c r="V5">
-        <v>1.52</v>
+        <v>36</v>
       </c>
       <c r="W5">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>18</v>
+        <v>1.68</v>
       </c>
       <c r="AA5">
-        <v>55</v>
+        <v>6.2</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
+        <v>1000</v>
+      </c>
+      <c r="AD5">
         <v>7.2</v>
       </c>
-      <c r="AD5">
-        <v>14</v>
-      </c>
       <c r="AE5">
+        <v>34</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
+        <v>1000</v>
+      </c>
+      <c r="AH5">
+        <v>65</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>1000</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>1000</v>
+      </c>
+      <c r="AO5">
+        <v>48</v>
+      </c>
+      <c r="AP5">
+        <v>30</v>
+      </c>
+      <c r="AQ5">
+        <v>30</v>
+      </c>
+      <c r="AR5">
+        <v>1.61</v>
+      </c>
+      <c r="AS5">
+        <v>5.4</v>
+      </c>
+      <c r="AT5">
+        <v>30</v>
+      </c>
+      <c r="AU5">
         <v>50</v>
       </c>
-      <c r="AF5">
-        <v>19</v>
-      </c>
-      <c r="AG5">
-        <v>14.5</v>
-      </c>
-      <c r="AH5">
-        <v>23</v>
-      </c>
-      <c r="AI5">
-        <v>75</v>
-      </c>
-      <c r="AJ5">
+      <c r="AV5">
+        <v>6.4</v>
+      </c>
+      <c r="AW5">
+        <v>25</v>
+      </c>
+      <c r="AX5">
+        <v>30</v>
+      </c>
+      <c r="AY5">
+        <v>50</v>
+      </c>
+      <c r="AZ5">
+        <v>46</v>
+      </c>
+      <c r="BA5">
+        <v>170</v>
+      </c>
+      <c r="BB5">
+        <v>30</v>
+      </c>
+      <c r="BC5">
         <v>60</v>
       </c>
-      <c r="AK5">
-        <v>55</v>
-      </c>
-      <c r="AL5">
-        <v>70</v>
-      </c>
-      <c r="AM5">
-        <v>200</v>
-      </c>
-      <c r="AN5">
-        <v>65</v>
-      </c>
-      <c r="AO5">
-        <v>55</v>
-      </c>
-      <c r="AP5">
-        <v>8.4</v>
-      </c>
-      <c r="AQ5">
-        <v>7.8</v>
-      </c>
-      <c r="AR5">
-        <v>15.5</v>
-      </c>
-      <c r="AS5">
-        <v>36</v>
-      </c>
-      <c r="AT5">
-        <v>8</v>
-      </c>
-      <c r="AU5">
-        <v>6.4</v>
-      </c>
-      <c r="AV5">
-        <v>12</v>
-      </c>
-      <c r="AW5">
-        <v>30</v>
-      </c>
-      <c r="AX5">
-        <v>16</v>
-      </c>
-      <c r="AY5">
-        <v>12.5</v>
-      </c>
-      <c r="AZ5">
-        <v>19.5</v>
-      </c>
-      <c r="BA5">
-        <v>46</v>
-      </c>
-      <c r="BB5">
-        <v>38</v>
-      </c>
-      <c r="BC5">
-        <v>34</v>
-      </c>
       <c r="BD5">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="BE5">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="BF5">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BG5">
         <v>32</v>
       </c>
       <c r="BH5">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="BI5">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BJ5">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BK5">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="BN5">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BO5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BP5">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BQ5">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BR5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BS5">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BT5">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BU5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BV5">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BW5">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BX5">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BY5">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BZ5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="CA5">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="s">
         <v>101</v>
@@ -1881,226 +1881,226 @@
         <v>99</v>
       </c>
       <c r="F6">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="G6">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I6">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="J6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K6">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L6">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M6">
         <v>1.11</v>
       </c>
       <c r="N6">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O6">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="P6">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q6">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R6">
         <v>1.23</v>
       </c>
       <c r="S6">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T6">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U6">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V6">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="W6">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="X6">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z6">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AA6">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="AB6">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC6">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AD6">
         <v>17.5</v>
       </c>
       <c r="AE6">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AF6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI6">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AJ6">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AK6">
         <v>28</v>
       </c>
       <c r="AL6">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM6">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="AN6">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AO6">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AP6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR6">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AS6">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AT6">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU6">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AV6">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW6">
         <v>50</v>
       </c>
       <c r="AX6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6">
         <v>21</v>
       </c>
       <c r="BA6">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="BB6">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BC6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD6">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BE6">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BF6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BG6">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BH6">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="BI6">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="BJ6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK6">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BL6">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="BM6">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="BN6">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BO6">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ6">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV6">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="BW6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX6">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BY6">
-        <v>13.5</v>
+        <v>55</v>
       </c>
       <c r="BZ6">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="CA6">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="CB6" t="s">
         <v>101</v>
@@ -2123,97 +2123,97 @@
         <v>100</v>
       </c>
       <c r="F7">
+        <v>1.35</v>
+      </c>
+      <c r="G7">
         <v>1.36</v>
       </c>
-      <c r="G7">
-        <v>1.37</v>
-      </c>
       <c r="H7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I7">
         <v>11.5</v>
       </c>
       <c r="J7">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K7">
         <v>5.9</v>
       </c>
       <c r="L7">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M7">
         <v>1.04</v>
       </c>
       <c r="N7">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O7">
         <v>1.21</v>
       </c>
       <c r="P7">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="Q7">
         <v>1.64</v>
       </c>
       <c r="R7">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S7">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T7">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U7">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="V7">
         <v>1.09</v>
       </c>
       <c r="W7">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="X7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y7">
         <v>36</v>
       </c>
       <c r="Z7">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AA7">
-        <v>410</v>
+        <v>450</v>
       </c>
       <c r="AB7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AE7">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AF7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH7">
         <v>29</v>
       </c>
       <c r="AI7">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK7">
         <v>14</v>
@@ -2222,13 +2222,13 @@
         <v>36</v>
       </c>
       <c r="AM7">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN7">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AO7">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AP7">
         <v>21</v>
@@ -2237,112 +2237,112 @@
         <v>34</v>
       </c>
       <c r="AR7">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="AS7">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AT7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV7">
         <v>32</v>
       </c>
       <c r="AW7">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="AX7">
         <v>7.8</v>
       </c>
       <c r="AY7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA7">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="BB7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE7">
-        <v>17</v>
+        <v>110</v>
       </c>
       <c r="BF7">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG7">
-        <v>17.5</v>
+        <v>95</v>
       </c>
       <c r="BH7">
         <v>4.3</v>
       </c>
       <c r="BI7">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BJ7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK7">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BL7">
         <v>140</v>
       </c>
       <c r="BM7">
-        <v>15.5</v>
+        <v>130</v>
       </c>
       <c r="BN7">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BO7">
         <v>3.55</v>
       </c>
       <c r="BP7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BQ7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR7">
         <v>22</v>
       </c>
       <c r="BS7">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BU7">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BV7">
+        <v>90</v>
+      </c>
+      <c r="BW7">
+        <v>15</v>
+      </c>
+      <c r="BX7">
         <v>80</v>
       </c>
-      <c r="BW7">
-        <v>14</v>
-      </c>
-      <c r="BX7">
-        <v>75</v>
-      </c>
       <c r="BY7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BZ7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="CB7" t="s">
         <v>101</v>
